--- a/AI_CFT_Labeling.xlsx
+++ b/AI_CFT_Labeling.xlsx
@@ -942,10 +942,10 @@
   </sheetData>
   <mergeCells count="17">
     <mergeCell ref="B26:E26"/>
+    <mergeCell ref="B17:E17"/>
     <mergeCell ref="B27:E27"/>
+    <mergeCell ref="B23:E23"/>
     <mergeCell ref="B18:E18"/>
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="B17:E17"/>
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="B21:E21"/>
     <mergeCell ref="B16:E16"/>
@@ -3364,67 +3364,67 @@
       <c r="C3" s="24" t="inlineStr">
         <is>
           <t>Blank 1
-Label name</t>
+Target Label</t>
         </is>
       </c>
       <c r="D3" s="24" t="inlineStr">
         <is>
           <t>Blank 2
-Object name</t>
+Data Object</t>
         </is>
       </c>
       <c r="E3" s="24" t="inlineStr">
         <is>
           <t>Blank 3
-Feature name</t>
+Feature Name</t>
         </is>
       </c>
       <c r="F3" s="24" t="inlineStr">
         <is>
           <t>Blank 4
-Feature value</t>
+Feature Value</t>
         </is>
       </c>
       <c r="G3" s="24" t="inlineStr">
         <is>
           <t>Blank 5
-Object definition</t>
+Data Instance</t>
         </is>
       </c>
       <c r="H3" s="24" t="inlineStr">
         <is>
           <t>Blank 6
-Object example</t>
+Specific Object</t>
         </is>
       </c>
       <c r="I3" s="24" t="inlineStr">
         <is>
           <t>Blank 7
-Feature term</t>
+Feature Variable</t>
         </is>
       </c>
       <c r="J3" s="24" t="inlineStr">
         <is>
           <t>Blank 8
-Feature count</t>
+Feature Count</t>
         </is>
       </c>
       <c r="K3" s="24" t="inlineStr">
         <is>
           <t>Blank 9
-Feature list</t>
+Feature List</t>
         </is>
       </c>
       <c r="L3" s="24" t="inlineStr">
         <is>
           <t>Blank 10
-Object example 2</t>
+Instance Name</t>
         </is>
       </c>
       <c r="M3" s="24" t="inlineStr">
         <is>
           <t>Blank 11
-Label term</t>
+Assigned Label</t>
         </is>
       </c>
       <c r="N3" s="24" t="inlineStr">

--- a/AI_CFT_Labeling.xlsx
+++ b/AI_CFT_Labeling.xlsx
@@ -226,7 +226,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -360,6 +360,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1376,42 +1382,38 @@
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="26" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B5" s="27" t="inlineStr">
-        <is>
-          <t>Ozzy</t>
-        </is>
-      </c>
-      <c r="C5" s="28" t="inlineStr"/>
-      <c r="D5" s="28" t="inlineStr"/>
-      <c r="E5" s="28" t="inlineStr"/>
-      <c r="F5" s="28" t="inlineStr"/>
-      <c r="G5" s="28" t="inlineStr"/>
-      <c r="H5" s="28" t="inlineStr"/>
-      <c r="I5" s="28" t="inlineStr"/>
-      <c r="J5" s="28" t="inlineStr"/>
-      <c r="K5" s="28" t="inlineStr"/>
-      <c r="L5" s="28" t="inlineStr"/>
-      <c r="M5" s="28" t="inlineStr"/>
-      <c r="N5" s="28" t="inlineStr"/>
-      <c r="O5" s="28" t="inlineStr"/>
-      <c r="P5" s="28" t="inlineStr"/>
-      <c r="Q5" s="28" t="inlineStr"/>
-      <c r="R5" s="28" t="inlineStr"/>
-      <c r="S5" s="28" t="inlineStr"/>
-      <c r="T5" s="28" t="inlineStr"/>
-      <c r="U5" s="28" t="inlineStr"/>
-      <c r="V5" s="28" t="inlineStr"/>
-      <c r="W5" s="28" t="inlineStr"/>
-      <c r="X5" s="28" t="inlineStr"/>
-      <c r="Y5" s="28" t="inlineStr"/>
-      <c r="Z5" s="28" t="inlineStr"/>
-      <c r="AA5" s="29" t="inlineStr"/>
-      <c r="AB5" s="30" t="inlineStr"/>
+      <c r="A5" s="49" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B5" s="47" t="n"/>
+      <c r="C5" s="47" t="n"/>
+      <c r="D5" s="47" t="n"/>
+      <c r="E5" s="47" t="n"/>
+      <c r="F5" s="47" t="n"/>
+      <c r="G5" s="47" t="n"/>
+      <c r="H5" s="47" t="n"/>
+      <c r="I5" s="47" t="n"/>
+      <c r="J5" s="47" t="n"/>
+      <c r="K5" s="47" t="n"/>
+      <c r="L5" s="47" t="n"/>
+      <c r="M5" s="47" t="n"/>
+      <c r="N5" s="47" t="n"/>
+      <c r="O5" s="47" t="n"/>
+      <c r="P5" s="47" t="n"/>
+      <c r="Q5" s="47" t="n"/>
+      <c r="R5" s="47" t="n"/>
+      <c r="S5" s="47" t="n"/>
+      <c r="T5" s="47" t="n"/>
+      <c r="U5" s="47" t="n"/>
+      <c r="V5" s="47" t="n"/>
+      <c r="W5" s="47" t="n"/>
+      <c r="X5" s="47" t="n"/>
+      <c r="Y5" s="47" t="n"/>
+      <c r="Z5" s="47" t="n"/>
+      <c r="AA5" s="47" t="n"/>
+      <c r="AB5" s="48" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="31" t="inlineStr">
@@ -2519,42 +2521,38 @@
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="26" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="B36" s="27" t="inlineStr">
-        <is>
-          <t>Sheila</t>
-        </is>
-      </c>
-      <c r="C36" s="28" t="inlineStr"/>
-      <c r="D36" s="28" t="inlineStr"/>
-      <c r="E36" s="28" t="inlineStr"/>
-      <c r="F36" s="28" t="inlineStr"/>
-      <c r="G36" s="28" t="inlineStr"/>
-      <c r="H36" s="28" t="inlineStr"/>
-      <c r="I36" s="28" t="inlineStr"/>
-      <c r="J36" s="28" t="inlineStr"/>
-      <c r="K36" s="28" t="inlineStr"/>
-      <c r="L36" s="28" t="inlineStr"/>
-      <c r="M36" s="28" t="inlineStr"/>
-      <c r="N36" s="28" t="inlineStr"/>
-      <c r="O36" s="28" t="inlineStr"/>
-      <c r="P36" s="28" t="inlineStr"/>
-      <c r="Q36" s="28" t="inlineStr"/>
-      <c r="R36" s="28" t="inlineStr"/>
-      <c r="S36" s="28" t="inlineStr"/>
-      <c r="T36" s="28" t="inlineStr"/>
-      <c r="U36" s="28" t="inlineStr"/>
-      <c r="V36" s="28" t="inlineStr"/>
-      <c r="W36" s="28" t="inlineStr"/>
-      <c r="X36" s="28" t="inlineStr"/>
-      <c r="Y36" s="28" t="inlineStr"/>
-      <c r="Z36" s="28" t="inlineStr"/>
-      <c r="AA36" s="29" t="inlineStr"/>
-      <c r="AB36" s="30" t="inlineStr"/>
+      <c r="A36" s="49" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B36" s="47" t="n"/>
+      <c r="C36" s="47" t="n"/>
+      <c r="D36" s="47" t="n"/>
+      <c r="E36" s="47" t="n"/>
+      <c r="F36" s="47" t="n"/>
+      <c r="G36" s="47" t="n"/>
+      <c r="H36" s="47" t="n"/>
+      <c r="I36" s="47" t="n"/>
+      <c r="J36" s="47" t="n"/>
+      <c r="K36" s="47" t="n"/>
+      <c r="L36" s="47" t="n"/>
+      <c r="M36" s="47" t="n"/>
+      <c r="N36" s="47" t="n"/>
+      <c r="O36" s="47" t="n"/>
+      <c r="P36" s="47" t="n"/>
+      <c r="Q36" s="47" t="n"/>
+      <c r="R36" s="47" t="n"/>
+      <c r="S36" s="47" t="n"/>
+      <c r="T36" s="47" t="n"/>
+      <c r="U36" s="47" t="n"/>
+      <c r="V36" s="47" t="n"/>
+      <c r="W36" s="47" t="n"/>
+      <c r="X36" s="47" t="n"/>
+      <c r="Y36" s="47" t="n"/>
+      <c r="Z36" s="47" t="n"/>
+      <c r="AA36" s="47" t="n"/>
+      <c r="AB36" s="48" t="n"/>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="31" t="inlineStr">
@@ -3126,7 +3124,6 @@
       <c r="AA51" s="29" t="inlineStr"/>
       <c r="AB51" s="30" t="inlineStr"/>
     </row>
-    <row r="52"/>
     <row r="53">
       <c r="A53" s="34" t="inlineStr">
         <is>
@@ -3414,78 +3411,67 @@
       <c r="C3" s="24" t="inlineStr">
         <is>
           <t>Blank 1
-Target Label
-Determining the final classification result (e.g., 'not recommendable')</t>
+Target Label</t>
         </is>
       </c>
       <c r="D3" s="24" t="inlineStr">
         <is>
           <t>Blank 2
-Data Object
-Recognizing the fundamental data entity or item (e.g., 'Hazelnut Wafer')</t>
+Data Object</t>
         </is>
       </c>
       <c r="E3" s="24" t="inlineStr">
         <is>
           <t>Blank 3
-Feature Name
-Identifying the name of the independent variable (e.g., 'Fat')</t>
+Feature Name</t>
         </is>
       </c>
       <c r="F3" s="24" t="inlineStr">
         <is>
           <t>Blank 4
-Feature Value
-Extracting the specific quantitative measurement for an attribute (e.g., '31.9 g')</t>
+Feature Value</t>
         </is>
       </c>
       <c r="G3" s="24" t="inlineStr">
         <is>
           <t>Blank 5
-Data Instance
-Comprehending that an item acts as a single row or data point in a dataset (e.g., 'Individual foods are called objects...')</t>
+Data Instance</t>
         </is>
       </c>
       <c r="H3" s="24" t="inlineStr">
         <is>
           <t>Blank 6
-Specific Object
-Mapping a concrete, real-world example to the concept of a data object (e.g., 'A hazelnut wafer is an object')</t>
+Specific Object</t>
         </is>
       </c>
       <c r="I3" s="24" t="inlineStr">
         <is>
           <t>Blank 7
-Feature Variable
-Understanding the structural attributes (columns) that describe the data (e.g., 'features are located in the left column')</t>
+Feature Variable</t>
         </is>
       </c>
       <c r="J3" s="24" t="inlineStr">
         <is>
           <t>Blank 8
-Feature Count
-Calculating the dimensionality or total number of variables in the dataset (e.g., 'there are 7 features')</t>
+Feature Count</t>
         </is>
       </c>
       <c r="K3" s="24" t="inlineStr">
         <is>
           <t>Blank 9
-Feature List
-Enumerating all the independent variables that can be extracted (e.g., 'Energy, Fat, Saturated Fat...')</t>
+Feature List</t>
         </is>
       </c>
       <c r="L3" s="24" t="inlineStr">
         <is>
           <t>Blank 10
-Instance Name
-Associating a specific data value (like 31.9 g) back to the specific object it belongs to (e.g., 'Hazelnut Wafer contains 31.9 g of fat')</t>
+Instance Name</t>
         </is>
       </c>
       <c r="M3" s="24" t="inlineStr">
         <is>
           <t>Blank 11
-Assigned Label
-Grasping that the target variable serves as the final decision or output for that specific item (e.g., 'given the note not recommendable as a label...')</t>
+Assigned Label</t>
         </is>
       </c>
       <c r="N3" s="24" t="inlineStr">
@@ -3507,29 +3493,25 @@
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="26" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B5" s="27" t="inlineStr">
-        <is>
-          <t>Ozzy</t>
-        </is>
-      </c>
-      <c r="C5" s="28" t="inlineStr"/>
-      <c r="D5" s="28" t="inlineStr"/>
-      <c r="E5" s="28" t="inlineStr"/>
-      <c r="F5" s="28" t="inlineStr"/>
-      <c r="G5" s="28" t="inlineStr"/>
-      <c r="H5" s="28" t="inlineStr"/>
-      <c r="I5" s="28" t="inlineStr"/>
-      <c r="J5" s="28" t="inlineStr"/>
-      <c r="K5" s="28" t="inlineStr"/>
-      <c r="L5" s="28" t="inlineStr"/>
-      <c r="M5" s="28" t="inlineStr"/>
-      <c r="N5" s="29" t="inlineStr"/>
-      <c r="O5" s="30" t="inlineStr"/>
+      <c r="A5" s="49" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B5" s="47" t="n"/>
+      <c r="C5" s="47" t="n"/>
+      <c r="D5" s="47" t="n"/>
+      <c r="E5" s="47" t="n"/>
+      <c r="F5" s="47" t="n"/>
+      <c r="G5" s="47" t="n"/>
+      <c r="H5" s="47" t="n"/>
+      <c r="I5" s="47" t="n"/>
+      <c r="J5" s="47" t="n"/>
+      <c r="K5" s="47" t="n"/>
+      <c r="L5" s="47" t="n"/>
+      <c r="M5" s="47" t="n"/>
+      <c r="N5" s="47" t="n"/>
+      <c r="O5" s="48" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="31" t="inlineStr">
@@ -4260,29 +4242,25 @@
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="26" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="B36" s="27" t="inlineStr">
-        <is>
-          <t>Sheila</t>
-        </is>
-      </c>
-      <c r="C36" s="28" t="inlineStr"/>
-      <c r="D36" s="28" t="inlineStr"/>
-      <c r="E36" s="28" t="inlineStr"/>
-      <c r="F36" s="28" t="inlineStr"/>
-      <c r="G36" s="28" t="inlineStr"/>
-      <c r="H36" s="28" t="inlineStr"/>
-      <c r="I36" s="28" t="inlineStr"/>
-      <c r="J36" s="28" t="inlineStr"/>
-      <c r="K36" s="28" t="inlineStr"/>
-      <c r="L36" s="28" t="inlineStr"/>
-      <c r="M36" s="28" t="inlineStr"/>
-      <c r="N36" s="29" t="inlineStr"/>
-      <c r="O36" s="30" t="inlineStr"/>
+      <c r="A36" s="49" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B36" s="47" t="n"/>
+      <c r="C36" s="47" t="n"/>
+      <c r="D36" s="47" t="n"/>
+      <c r="E36" s="47" t="n"/>
+      <c r="F36" s="47" t="n"/>
+      <c r="G36" s="47" t="n"/>
+      <c r="H36" s="47" t="n"/>
+      <c r="I36" s="47" t="n"/>
+      <c r="J36" s="47" t="n"/>
+      <c r="K36" s="47" t="n"/>
+      <c r="L36" s="47" t="n"/>
+      <c r="M36" s="47" t="n"/>
+      <c r="N36" s="47" t="n"/>
+      <c r="O36" s="48" t="n"/>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="31" t="inlineStr">
@@ -4659,7 +4637,6 @@
       <c r="N51" s="29" t="inlineStr"/>
       <c r="O51" s="30" t="inlineStr"/>
     </row>
-    <row r="52"/>
     <row r="53">
       <c r="A53" s="34" t="inlineStr">
         <is>
@@ -4764,7 +4741,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H54"/>
+  <dimension ref="A1:J54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4880,22 +4857,18 @@
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="26" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B5" s="27" t="inlineStr">
-        <is>
-          <t>Ozzy</t>
-        </is>
-      </c>
-      <c r="C5" s="28" t="inlineStr"/>
-      <c r="D5" s="28" t="inlineStr"/>
-      <c r="E5" s="28" t="inlineStr"/>
-      <c r="F5" s="28" t="inlineStr"/>
-      <c r="G5" s="29" t="inlineStr"/>
-      <c r="H5" s="30" t="inlineStr"/>
+      <c r="A5" s="49" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B5" s="47" t="n"/>
+      <c r="C5" s="47" t="n"/>
+      <c r="D5" s="47" t="n"/>
+      <c r="E5" s="47" t="n"/>
+      <c r="F5" s="47" t="n"/>
+      <c r="G5" s="47" t="n"/>
+      <c r="H5" s="48" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="31" t="inlineStr">
@@ -5423,22 +5396,18 @@
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="26" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="B36" s="27" t="inlineStr">
-        <is>
-          <t>Sheila</t>
-        </is>
-      </c>
-      <c r="C36" s="28" t="inlineStr"/>
-      <c r="D36" s="28" t="inlineStr"/>
-      <c r="E36" s="28" t="inlineStr"/>
-      <c r="F36" s="28" t="inlineStr"/>
-      <c r="G36" s="29" t="inlineStr"/>
-      <c r="H36" s="30" t="inlineStr"/>
+      <c r="A36" s="49" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B36" s="47" t="n"/>
+      <c r="C36" s="47" t="n"/>
+      <c r="D36" s="47" t="n"/>
+      <c r="E36" s="47" t="n"/>
+      <c r="F36" s="47" t="n"/>
+      <c r="G36" s="47" t="n"/>
+      <c r="H36" s="48" t="n"/>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="31" t="inlineStr">
@@ -5710,7 +5679,6 @@
       <c r="G51" s="29" t="inlineStr"/>
       <c r="H51" s="30" t="inlineStr"/>
     </row>
-    <row r="52"/>
     <row r="53">
       <c r="A53" s="34" t="inlineStr">
         <is>
@@ -5725,34 +5693,44 @@
         </is>
       </c>
       <c r="B54" s="35" t="inlineStr"/>
-      <c r="C54" s="36" t="inlineStr">
-        <is>
-          <t>Classifies popcorn as recommended (fat &lt;= 8g) AND gives correct justification</t>
-        </is>
-      </c>
-      <c r="D54" s="36" t="inlineStr">
-        <is>
-          <t>Classifies apple as recommended AND gives correct justification referencing fat value</t>
-        </is>
-      </c>
-      <c r="E54" s="36" t="inlineStr">
-        <is>
-          <t>Classifies french fries as not recommended (fat &gt; 8g) AND gives correct justification</t>
-        </is>
-      </c>
-      <c r="F54" s="36" t="inlineStr">
-        <is>
-          <t>Writes own threshold for the Energy variable with correct &lt;= / &gt; notation in the diagram</t>
-        </is>
-      </c>
-      <c r="G54" s="36" t="inlineStr">
-        <is>
-          <t>Overall AI-CFT level for WS3 as a whole</t>
-        </is>
-      </c>
-      <c r="H54" s="36" t="inlineStr">
-        <is>
-          <t>Free notes</t>
+      <c r="C54" s="50" t="inlineStr">
+        <is>
+          <t>Instance Classification (Popcorn): Applying the established decision rule to predict and assign a target class label to a specific data object (e.g., "tavsiye edilemez").</t>
+        </is>
+      </c>
+      <c r="D54" s="50" t="inlineStr">
+        <is>
+          <t>Rule Verification (Popcorn): Justifying the classification outcome by mathematically comparing the object's feature value to the threshold (e.g., "23.0 &gt; 8.0").</t>
+        </is>
+      </c>
+      <c r="E54" s="50" t="inlineStr">
+        <is>
+          <t>Instance Classification (Apple): Applying the established decision rule to predict and assign a target class label to a specific data object (e.g., "tavsiye edilebilir").</t>
+        </is>
+      </c>
+      <c r="F54" s="50" t="inlineStr">
+        <is>
+          <t>Rule Verification (Apple): Justifying the classification outcome by mathematically comparing the object's feature value to the threshold (e.g., "8.0 &gt; 0.2").</t>
+        </is>
+      </c>
+      <c r="G54" s="50" t="inlineStr">
+        <is>
+          <t>Instance Classification (French Fries): Applying the established decision rule to predict and assign a target class label to a specific data object (e.g., "tavsiye edilemez").</t>
+        </is>
+      </c>
+      <c r="H54" s="50" t="inlineStr">
+        <is>
+          <t>Rule Verification (French Fries): Justifying the classification outcome by mathematically comparing the object's feature value to the threshold (e.g., "14.0 &gt; 8.0").</t>
+        </is>
+      </c>
+      <c r="I54" s="45" t="inlineStr">
+        <is>
+          <t>Left Branching Condition: Establishing the mathematical boundary expression (≤) for a split node based on the data distribution of the feature (e.g., ≤ 71 kcal).</t>
+        </is>
+      </c>
+      <c r="J54" s="45" t="inlineStr">
+        <is>
+          <t>Right Branching Condition: Establishing the corresponding inverse mathematical expression (&gt;) for a split node to partition the remaining instances in the dataset (e.g., &gt; 71 kcal).</t>
         </is>
       </c>
     </row>
@@ -5896,22 +5874,18 @@
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="26" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B5" s="27" t="inlineStr">
-        <is>
-          <t>Ozzy</t>
-        </is>
-      </c>
-      <c r="C5" s="28" t="inlineStr"/>
-      <c r="D5" s="28" t="inlineStr"/>
-      <c r="E5" s="28" t="inlineStr"/>
-      <c r="F5" s="28" t="inlineStr"/>
-      <c r="G5" s="29" t="inlineStr"/>
-      <c r="H5" s="30" t="inlineStr"/>
+      <c r="A5" s="49" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B5" s="47" t="n"/>
+      <c r="C5" s="47" t="n"/>
+      <c r="D5" s="47" t="n"/>
+      <c r="E5" s="47" t="n"/>
+      <c r="F5" s="47" t="n"/>
+      <c r="G5" s="47" t="n"/>
+      <c r="H5" s="48" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="31" t="inlineStr">
@@ -6439,22 +6413,18 @@
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="26" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="B36" s="27" t="inlineStr">
-        <is>
-          <t>Sheila</t>
-        </is>
-      </c>
-      <c r="C36" s="28" t="inlineStr"/>
-      <c r="D36" s="28" t="inlineStr"/>
-      <c r="E36" s="28" t="inlineStr"/>
-      <c r="F36" s="28" t="inlineStr"/>
-      <c r="G36" s="29" t="inlineStr"/>
-      <c r="H36" s="30" t="inlineStr"/>
+      <c r="A36" s="49" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B36" s="47" t="n"/>
+      <c r="C36" s="47" t="n"/>
+      <c r="D36" s="47" t="n"/>
+      <c r="E36" s="47" t="n"/>
+      <c r="F36" s="47" t="n"/>
+      <c r="G36" s="47" t="n"/>
+      <c r="H36" s="48" t="n"/>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="31" t="inlineStr">
@@ -6726,7 +6696,6 @@
       <c r="G51" s="29" t="inlineStr"/>
       <c r="H51" s="30" t="inlineStr"/>
     </row>
-    <row r="52"/>
     <row r="53">
       <c r="A53" s="34" t="inlineStr">
         <is>
@@ -6948,25 +6917,21 @@
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="26" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B5" s="27" t="inlineStr">
-        <is>
-          <t>Ozzy</t>
-        </is>
-      </c>
-      <c r="C5" s="28" t="inlineStr"/>
-      <c r="D5" s="28" t="inlineStr"/>
-      <c r="E5" s="28" t="inlineStr"/>
-      <c r="F5" s="28" t="inlineStr"/>
-      <c r="G5" s="28" t="inlineStr"/>
-      <c r="H5" s="28" t="inlineStr"/>
-      <c r="I5" s="28" t="inlineStr"/>
-      <c r="J5" s="29" t="inlineStr"/>
-      <c r="K5" s="30" t="inlineStr"/>
+      <c r="A5" s="49" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B5" s="47" t="n"/>
+      <c r="C5" s="47" t="n"/>
+      <c r="D5" s="47" t="n"/>
+      <c r="E5" s="47" t="n"/>
+      <c r="F5" s="47" t="n"/>
+      <c r="G5" s="47" t="n"/>
+      <c r="H5" s="47" t="n"/>
+      <c r="I5" s="47" t="n"/>
+      <c r="J5" s="47" t="n"/>
+      <c r="K5" s="48" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="31" t="inlineStr">
@@ -7581,25 +7546,21 @@
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="26" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="B36" s="27" t="inlineStr">
-        <is>
-          <t>Sheila</t>
-        </is>
-      </c>
-      <c r="C36" s="28" t="inlineStr"/>
-      <c r="D36" s="28" t="inlineStr"/>
-      <c r="E36" s="28" t="inlineStr"/>
-      <c r="F36" s="28" t="inlineStr"/>
-      <c r="G36" s="28" t="inlineStr"/>
-      <c r="H36" s="28" t="inlineStr"/>
-      <c r="I36" s="28" t="inlineStr"/>
-      <c r="J36" s="29" t="inlineStr"/>
-      <c r="K36" s="30" t="inlineStr"/>
+      <c r="A36" s="49" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B36" s="47" t="n"/>
+      <c r="C36" s="47" t="n"/>
+      <c r="D36" s="47" t="n"/>
+      <c r="E36" s="47" t="n"/>
+      <c r="F36" s="47" t="n"/>
+      <c r="G36" s="47" t="n"/>
+      <c r="H36" s="47" t="n"/>
+      <c r="I36" s="47" t="n"/>
+      <c r="J36" s="47" t="n"/>
+      <c r="K36" s="48" t="n"/>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="31" t="inlineStr">
@@ -7916,7 +7877,6 @@
       <c r="J51" s="29" t="inlineStr"/>
       <c r="K51" s="30" t="inlineStr"/>
     </row>
-    <row r="52"/>
     <row r="53">
       <c r="A53" s="34" t="inlineStr">
         <is>
@@ -8153,25 +8113,21 @@
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="26" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B5" s="27" t="inlineStr">
-        <is>
-          <t>Ozzy</t>
-        </is>
-      </c>
-      <c r="C5" s="28" t="inlineStr"/>
-      <c r="D5" s="28" t="inlineStr"/>
-      <c r="E5" s="28" t="inlineStr"/>
-      <c r="F5" s="28" t="inlineStr"/>
-      <c r="G5" s="28" t="inlineStr"/>
-      <c r="H5" s="28" t="inlineStr"/>
-      <c r="I5" s="28" t="inlineStr"/>
-      <c r="J5" s="29" t="inlineStr"/>
-      <c r="K5" s="30" t="inlineStr"/>
+      <c r="A5" s="49" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B5" s="47" t="n"/>
+      <c r="C5" s="47" t="n"/>
+      <c r="D5" s="47" t="n"/>
+      <c r="E5" s="47" t="n"/>
+      <c r="F5" s="47" t="n"/>
+      <c r="G5" s="47" t="n"/>
+      <c r="H5" s="47" t="n"/>
+      <c r="I5" s="47" t="n"/>
+      <c r="J5" s="47" t="n"/>
+      <c r="K5" s="48" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="31" t="inlineStr">
@@ -8786,25 +8742,21 @@
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="26" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="B36" s="27" t="inlineStr">
-        <is>
-          <t>Sheila</t>
-        </is>
-      </c>
-      <c r="C36" s="28" t="inlineStr"/>
-      <c r="D36" s="28" t="inlineStr"/>
-      <c r="E36" s="28" t="inlineStr"/>
-      <c r="F36" s="28" t="inlineStr"/>
-      <c r="G36" s="28" t="inlineStr"/>
-      <c r="H36" s="28" t="inlineStr"/>
-      <c r="I36" s="28" t="inlineStr"/>
-      <c r="J36" s="29" t="inlineStr"/>
-      <c r="K36" s="30" t="inlineStr"/>
+      <c r="A36" s="49" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B36" s="47" t="n"/>
+      <c r="C36" s="47" t="n"/>
+      <c r="D36" s="47" t="n"/>
+      <c r="E36" s="47" t="n"/>
+      <c r="F36" s="47" t="n"/>
+      <c r="G36" s="47" t="n"/>
+      <c r="H36" s="47" t="n"/>
+      <c r="I36" s="47" t="n"/>
+      <c r="J36" s="47" t="n"/>
+      <c r="K36" s="48" t="n"/>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="31" t="inlineStr">
@@ -9121,7 +9073,6 @@
       <c r="J51" s="29" t="inlineStr"/>
       <c r="K51" s="30" t="inlineStr"/>
     </row>
-    <row r="52"/>
     <row r="53">
       <c r="A53" s="34" t="inlineStr">
         <is>
@@ -9358,25 +9309,21 @@
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="26" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B5" s="27" t="inlineStr">
-        <is>
-          <t>Ozzy</t>
-        </is>
-      </c>
-      <c r="C5" s="28" t="inlineStr"/>
-      <c r="D5" s="28" t="inlineStr"/>
-      <c r="E5" s="28" t="inlineStr"/>
-      <c r="F5" s="28" t="inlineStr"/>
-      <c r="G5" s="28" t="inlineStr"/>
-      <c r="H5" s="28" t="inlineStr"/>
-      <c r="I5" s="28" t="inlineStr"/>
-      <c r="J5" s="29" t="inlineStr"/>
-      <c r="K5" s="30" t="inlineStr"/>
+      <c r="A5" s="49" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B5" s="47" t="n"/>
+      <c r="C5" s="47" t="n"/>
+      <c r="D5" s="47" t="n"/>
+      <c r="E5" s="47" t="n"/>
+      <c r="F5" s="47" t="n"/>
+      <c r="G5" s="47" t="n"/>
+      <c r="H5" s="47" t="n"/>
+      <c r="I5" s="47" t="n"/>
+      <c r="J5" s="47" t="n"/>
+      <c r="K5" s="48" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="31" t="inlineStr">
@@ -9991,25 +9938,21 @@
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="26" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="B36" s="27" t="inlineStr">
-        <is>
-          <t>Sheila</t>
-        </is>
-      </c>
-      <c r="C36" s="28" t="inlineStr"/>
-      <c r="D36" s="28" t="inlineStr"/>
-      <c r="E36" s="28" t="inlineStr"/>
-      <c r="F36" s="28" t="inlineStr"/>
-      <c r="G36" s="28" t="inlineStr"/>
-      <c r="H36" s="28" t="inlineStr"/>
-      <c r="I36" s="28" t="inlineStr"/>
-      <c r="J36" s="29" t="inlineStr"/>
-      <c r="K36" s="30" t="inlineStr"/>
+      <c r="A36" s="49" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B36" s="47" t="n"/>
+      <c r="C36" s="47" t="n"/>
+      <c r="D36" s="47" t="n"/>
+      <c r="E36" s="47" t="n"/>
+      <c r="F36" s="47" t="n"/>
+      <c r="G36" s="47" t="n"/>
+      <c r="H36" s="47" t="n"/>
+      <c r="I36" s="47" t="n"/>
+      <c r="J36" s="47" t="n"/>
+      <c r="K36" s="48" t="n"/>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="31" t="inlineStr">
@@ -10326,7 +10269,6 @@
       <c r="J51" s="29" t="inlineStr"/>
       <c r="K51" s="30" t="inlineStr"/>
     </row>
-    <row r="52"/>
     <row r="53">
       <c r="A53" s="34" t="inlineStr">
         <is>
@@ -10515,21 +10457,17 @@
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="26" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B5" s="27" t="inlineStr">
-        <is>
-          <t>Ozzy</t>
-        </is>
-      </c>
-      <c r="C5" s="28" t="inlineStr"/>
-      <c r="D5" s="28" t="inlineStr"/>
-      <c r="E5" s="28" t="inlineStr"/>
-      <c r="F5" s="29" t="inlineStr"/>
-      <c r="G5" s="30" t="inlineStr"/>
+      <c r="A5" s="49" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B5" s="47" t="n"/>
+      <c r="C5" s="47" t="n"/>
+      <c r="D5" s="47" t="n"/>
+      <c r="E5" s="47" t="n"/>
+      <c r="F5" s="47" t="n"/>
+      <c r="G5" s="48" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="31" t="inlineStr">
@@ -11028,21 +10966,17 @@
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="26" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="B36" s="27" t="inlineStr">
-        <is>
-          <t>Sheila</t>
-        </is>
-      </c>
-      <c r="C36" s="28" t="inlineStr"/>
-      <c r="D36" s="28" t="inlineStr"/>
-      <c r="E36" s="28" t="inlineStr"/>
-      <c r="F36" s="29" t="inlineStr"/>
-      <c r="G36" s="30" t="inlineStr"/>
+      <c r="A36" s="49" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B36" s="47" t="n"/>
+      <c r="C36" s="47" t="n"/>
+      <c r="D36" s="47" t="n"/>
+      <c r="E36" s="47" t="n"/>
+      <c r="F36" s="47" t="n"/>
+      <c r="G36" s="48" t="n"/>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="31" t="inlineStr">
@@ -11299,7 +11233,6 @@
       <c r="F51" s="29" t="inlineStr"/>
       <c r="G51" s="30" t="inlineStr"/>
     </row>
-    <row r="52"/>
     <row r="53">
       <c r="A53" s="34" t="inlineStr">
         <is>
@@ -11516,25 +11449,21 @@
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="26" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B5" s="27" t="inlineStr">
-        <is>
-          <t>Ozzy</t>
-        </is>
-      </c>
-      <c r="C5" s="28" t="inlineStr"/>
-      <c r="D5" s="28" t="inlineStr"/>
-      <c r="E5" s="28" t="inlineStr"/>
-      <c r="F5" s="28" t="inlineStr"/>
-      <c r="G5" s="28" t="inlineStr"/>
-      <c r="H5" s="28" t="inlineStr"/>
-      <c r="I5" s="28" t="inlineStr"/>
-      <c r="J5" s="29" t="inlineStr"/>
-      <c r="K5" s="30" t="inlineStr"/>
+      <c r="A5" s="49" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B5" s="47" t="n"/>
+      <c r="C5" s="47" t="n"/>
+      <c r="D5" s="47" t="n"/>
+      <c r="E5" s="47" t="n"/>
+      <c r="F5" s="47" t="n"/>
+      <c r="G5" s="47" t="n"/>
+      <c r="H5" s="47" t="n"/>
+      <c r="I5" s="47" t="n"/>
+      <c r="J5" s="47" t="n"/>
+      <c r="K5" s="48" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="31" t="inlineStr">
@@ -12149,25 +12078,21 @@
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="26" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="B36" s="27" t="inlineStr">
-        <is>
-          <t>Sheila</t>
-        </is>
-      </c>
-      <c r="C36" s="28" t="inlineStr"/>
-      <c r="D36" s="28" t="inlineStr"/>
-      <c r="E36" s="28" t="inlineStr"/>
-      <c r="F36" s="28" t="inlineStr"/>
-      <c r="G36" s="28" t="inlineStr"/>
-      <c r="H36" s="28" t="inlineStr"/>
-      <c r="I36" s="28" t="inlineStr"/>
-      <c r="J36" s="29" t="inlineStr"/>
-      <c r="K36" s="30" t="inlineStr"/>
+      <c r="A36" s="49" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B36" s="47" t="n"/>
+      <c r="C36" s="47" t="n"/>
+      <c r="D36" s="47" t="n"/>
+      <c r="E36" s="47" t="n"/>
+      <c r="F36" s="47" t="n"/>
+      <c r="G36" s="47" t="n"/>
+      <c r="H36" s="47" t="n"/>
+      <c r="I36" s="47" t="n"/>
+      <c r="J36" s="47" t="n"/>
+      <c r="K36" s="48" t="n"/>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="31" t="inlineStr">
@@ -12484,7 +12409,6 @@
       <c r="J51" s="29" t="inlineStr"/>
       <c r="K51" s="30" t="inlineStr"/>
     </row>
-    <row r="52"/>
     <row r="53">
       <c r="A53" s="34" t="inlineStr">
         <is>

--- a/AI_CFT_Labeling.xlsx
+++ b/AI_CFT_Labeling.xlsx
@@ -25,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="14">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -113,6 +113,16 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
       <sz val="9"/>
     </font>
   </fonts>
@@ -225,7 +235,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -364,6 +374,18 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4789,38 +4811,44 @@
           <t>Student Name</t>
         </is>
       </c>
-      <c r="C3" s="16" t="inlineStr">
-        <is>
-          <t>Task 1
-Popcorn</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>Task 2
-Apple</t>
-        </is>
-      </c>
-      <c r="E3" s="16" t="inlineStr">
-        <is>
-          <t>Task 3
-Fries</t>
-        </is>
-      </c>
-      <c r="F3" s="16" t="inlineStr">
-        <is>
-          <t>Task 4
-Own energy threshold</t>
-        </is>
-      </c>
-      <c r="G3" s="16" t="inlineStr">
-        <is>
-          <t>Overall WS3</t>
-        </is>
-      </c>
-      <c r="H3" s="16" t="inlineStr">
-        <is>
-          <t>Notes WS3</t>
+      <c r="C3" s="52" t="inlineStr">
+        <is>
+          <t>Instance Classification (Popcorn)</t>
+        </is>
+      </c>
+      <c r="D3" s="52" t="inlineStr">
+        <is>
+          <t>Rule Verification (Popcorn)</t>
+        </is>
+      </c>
+      <c r="E3" s="52" t="inlineStr">
+        <is>
+          <t>Instance Classification (Apple)</t>
+        </is>
+      </c>
+      <c r="F3" s="52" t="inlineStr">
+        <is>
+          <t>Rule Verification (Apple)</t>
+        </is>
+      </c>
+      <c r="G3" s="52" t="inlineStr">
+        <is>
+          <t>Instance Classification (French Fries)</t>
+        </is>
+      </c>
+      <c r="H3" s="52" t="inlineStr">
+        <is>
+          <t>Rule Verification (French Fries)</t>
+        </is>
+      </c>
+      <c r="I3" s="53" t="inlineStr">
+        <is>
+          <t>Left Branching Condition</t>
+        </is>
+      </c>
+      <c r="J3" s="53" t="inlineStr">
+        <is>
+          <t>Right Branching Condition</t>
         </is>
       </c>
     </row>
@@ -5668,52 +5696,44 @@
         </is>
       </c>
       <c r="B54" s="25" t="n"/>
-      <c r="C54" s="50" t="inlineStr">
-        <is>
-          <t>Instance Classification (Popcorn)
-Applying the established decision rule to predict and assign a target class label to a specific data object (e.g., "tavsiye edilemez").</t>
-        </is>
-      </c>
-      <c r="D54" s="50" t="inlineStr">
-        <is>
-          <t>Rule Verification (Popcorn)
-Justifying the classification outcome by mathematically comparing the object's feature value to the threshold (e.g., "23.0 &gt; 8.0").</t>
-        </is>
-      </c>
-      <c r="E54" s="50" t="inlineStr">
-        <is>
-          <t>Instance Classification (Apple)
-Applying the established decision rule to predict and assign a target class label to a specific data object (e.g., "tavsiye edilebilir").</t>
-        </is>
-      </c>
-      <c r="F54" s="50" t="inlineStr">
-        <is>
-          <t>Rule Verification (Apple)
-Justifying the classification outcome by mathematically comparing the object's feature value to the threshold (e.g., "8.0 &gt; 0.2").</t>
-        </is>
-      </c>
-      <c r="G54" s="50" t="inlineStr">
-        <is>
-          <t>Instance Classification (French Fries)
-Applying the established decision rule to predict and assign a target class label to a specific data object (e.g., "tavsiye edilemez").</t>
-        </is>
-      </c>
-      <c r="H54" s="50" t="inlineStr">
-        <is>
-          <t>Rule Verification (French Fries)
-Justifying the classification outcome by mathematically comparing the object's feature value to the threshold (e.g., "14.0 &gt; 8.0").</t>
-        </is>
-      </c>
-      <c r="I54" s="51" t="inlineStr">
-        <is>
-          <t>Left Branching Condition
-Establishing the mathematical boundary expression (≤) for a split node based on the data distribution of the feature (e.g., ≤ 71 kcal).</t>
-        </is>
-      </c>
-      <c r="J54" s="51" t="inlineStr">
-        <is>
-          <t>Right Branching Condition
-Establishing the corresponding inverse mathematical expression (&gt;) for a split node to partition the remaining instances in the dataset (e.g., &gt; 71 kcal).</t>
+      <c r="C54" s="54" t="inlineStr">
+        <is>
+          <t>Applying the established decision rule to predict and assign a target class label to a specific data object (e.g., "tavsiye edilemez").</t>
+        </is>
+      </c>
+      <c r="D54" s="54" t="inlineStr">
+        <is>
+          <t>Justifying the classification outcome by mathematically comparing the object's feature value to the threshold (e.g., "23.0 &gt; 8.0").</t>
+        </is>
+      </c>
+      <c r="E54" s="54" t="inlineStr">
+        <is>
+          <t>Applying the established decision rule to predict and assign a target class label to a specific data object (e.g., "tavsiye edilebilir").</t>
+        </is>
+      </c>
+      <c r="F54" s="54" t="inlineStr">
+        <is>
+          <t>Justifying the classification outcome by mathematically comparing the object's feature value to the threshold (e.g., "8.0 &gt; 0.2").</t>
+        </is>
+      </c>
+      <c r="G54" s="54" t="inlineStr">
+        <is>
+          <t>Applying the established decision rule to predict and assign a target class label to a specific data object (e.g., "tavsiye edilemez").</t>
+        </is>
+      </c>
+      <c r="H54" s="54" t="inlineStr">
+        <is>
+          <t>Justifying the classification outcome by mathematically comparing the object's feature value to the threshold (e.g., "14.0 &gt; 8.0").</t>
+        </is>
+      </c>
+      <c r="I54" s="55" t="inlineStr">
+        <is>
+          <t>Establishing the mathematical boundary expression (≤) for a split node based on the data distribution of the feature (e.g., ≤ 71 kcal).</t>
+        </is>
+      </c>
+      <c r="J54" s="55" t="inlineStr">
+        <is>
+          <t>Establishing the corresponding inverse mathematical expression (&gt;) for a split node to partition the remaining instances in the dataset (e.g., &gt; 71 kcal).</t>
         </is>
       </c>
     </row>

--- a/AI_CFT_Labeling.xlsx
+++ b/AI_CFT_Labeling.xlsx
@@ -25,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -124,6 +124,12 @@
       <name val="Calibri"/>
       <i val="1"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="11">
@@ -235,7 +241,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -386,6 +392,12 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4811,44 +4823,52 @@
           <t>Student Name</t>
         </is>
       </c>
-      <c r="C3" s="52" t="inlineStr">
-        <is>
-          <t>Instance Classification (Popcorn)</t>
-        </is>
-      </c>
-      <c r="D3" s="52" t="inlineStr">
-        <is>
-          <t>Rule Verification (Popcorn)</t>
-        </is>
-      </c>
-      <c r="E3" s="52" t="inlineStr">
-        <is>
-          <t>Instance Classification (Apple)</t>
-        </is>
-      </c>
-      <c r="F3" s="52" t="inlineStr">
-        <is>
-          <t>Rule Verification (Apple)</t>
-        </is>
-      </c>
-      <c r="G3" s="52" t="inlineStr">
-        <is>
-          <t>Instance Classification (French Fries)</t>
-        </is>
-      </c>
-      <c r="H3" s="52" t="inlineStr">
-        <is>
-          <t>Rule Verification (French Fries)</t>
-        </is>
-      </c>
-      <c r="I3" s="53" t="inlineStr">
-        <is>
-          <t>Left Branching Condition</t>
-        </is>
-      </c>
-      <c r="J3" s="53" t="inlineStr">
-        <is>
-          <t>Right Branching Condition</t>
+      <c r="C3" s="56" t="inlineStr">
+        <is>
+          <t>Blank 1
+Instance Classification (Popcorn)</t>
+        </is>
+      </c>
+      <c r="D3" s="56" t="inlineStr">
+        <is>
+          <t>Blank 2
+Rule Verification (Popcorn)</t>
+        </is>
+      </c>
+      <c r="E3" s="56" t="inlineStr">
+        <is>
+          <t>Blank 3
+Instance Classification (Apple)</t>
+        </is>
+      </c>
+      <c r="F3" s="56" t="inlineStr">
+        <is>
+          <t>Blank 4
+Rule Verification (Apple)</t>
+        </is>
+      </c>
+      <c r="G3" s="56" t="inlineStr">
+        <is>
+          <t>Blank 5
+Instance Classification (French Fries)</t>
+        </is>
+      </c>
+      <c r="H3" s="56" t="inlineStr">
+        <is>
+          <t>Blank 6
+Rule Verification (French Fries)</t>
+        </is>
+      </c>
+      <c r="I3" s="57" t="inlineStr">
+        <is>
+          <t>Blank 7
+Left Branching Condition</t>
+        </is>
+      </c>
+      <c r="J3" s="57" t="inlineStr">
+        <is>
+          <t>Blank 8
+Right Branching Condition</t>
         </is>
       </c>
     </row>

--- a/AI_CFT_Labeling.xlsx
+++ b/AI_CFT_Labeling.xlsx
@@ -241,7 +241,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -398,6 +398,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4753,7 +4756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J54"/>
+  <dimension ref="A1:L54"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" style="36" min="1" max="1"/>
@@ -4801,12 +4804,32 @@
           <t>Deepen</t>
         </is>
       </c>
-      <c r="G2" s="29" t="inlineStr">
+      <c r="G2" s="28" t="inlineStr">
+        <is>
+          <t>Acquire</t>
+        </is>
+      </c>
+      <c r="H2" s="28" t="inlineStr">
+        <is>
+          <t>Acquire</t>
+        </is>
+      </c>
+      <c r="I2" s="28" t="inlineStr">
+        <is>
+          <t>Acquire</t>
+        </is>
+      </c>
+      <c r="J2" s="28" t="inlineStr">
+        <is>
+          <t>Acquire</t>
+        </is>
+      </c>
+      <c r="K2" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H2" s="29" t="inlineStr">
+      <c r="L2" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4869,6 +4892,16 @@
         <is>
           <t>Blank 8
 Right Branching Condition</t>
+        </is>
+      </c>
+      <c r="K3" s="58" t="inlineStr">
+        <is>
+          <t>Overall WS3</t>
+        </is>
+      </c>
+      <c r="L3" s="58" t="inlineStr">
+        <is>
+          <t>Notes WS3</t>
         </is>
       </c>
     </row>
@@ -5702,6 +5735,7 @@
       <c r="G51" s="45" t="n"/>
       <c r="H51" s="46" t="n"/>
     </row>
+    <row r="52"/>
     <row r="53">
       <c r="A53" s="48" t="inlineStr">
         <is>
@@ -5759,12 +5793,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A4:H4"/>
     <mergeCell ref="A53:H53"/>
-    <mergeCell ref="A35:H35"/>
+    <mergeCell ref="A1:L1"/>
     <mergeCell ref="A36:H36"/>
     <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A35:L35"/>
+    <mergeCell ref="A4:L4"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 C17 C18 C19 C20 C21 C22 C23 C24 C25 C26 C27 C28 C29 C30 C31 C32 C33 C34 C36 C37 C38 C39 C40 C41 C42 C43 C44 C45 C46 C47 C48 C49 C50 C51 D5 D6 D7 D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19 D20 D21 D22 D23 D24 D25 D26 D27 D28 D29 D30 D31 D32 D33 D34 D36 D37 D38 D39 D40 D41 D42 D43 D44 D45 D46 D47 D48 D49 D50 D51 E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E24 E25 E26 E27 E28 E29 E30 E31 E32 E33 E34 E36 E37 E38 E39 E40 E41 E42 E43 E44 E45 E46 E47 E48 E49 E50 E51 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34 F36 F37 F38 F39 F40 F41 F42 F43 F44 F45 F46 F47 F48 F49 F50 F51 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 G31 G32 G33 G34 G36 G37 G38 G39 G40 G41 G42 G43 G44 G45 G46 G47 G48 G49 G50 G51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Choose: Acquire, Deepen, Create, or ?" promptTitle="Select level" prompt="AI-CFT level" type="list">

--- a/AI_CFT_Labeling.xlsx
+++ b/AI_CFT_Labeling.xlsx
@@ -4799,29 +4799,29 @@
           <t>Acquire</t>
         </is>
       </c>
-      <c r="F2" s="30" t="inlineStr">
+      <c r="F2" s="28" t="inlineStr">
+        <is>
+          <t>Acquire</t>
+        </is>
+      </c>
+      <c r="G2" s="28" t="inlineStr">
+        <is>
+          <t>Acquire</t>
+        </is>
+      </c>
+      <c r="H2" s="28" t="inlineStr">
+        <is>
+          <t>Acquire</t>
+        </is>
+      </c>
+      <c r="I2" s="30" t="inlineStr">
         <is>
           <t>Deepen</t>
         </is>
       </c>
-      <c r="G2" s="28" t="inlineStr">
-        <is>
-          <t>Acquire</t>
-        </is>
-      </c>
-      <c r="H2" s="28" t="inlineStr">
-        <is>
-          <t>Acquire</t>
-        </is>
-      </c>
-      <c r="I2" s="28" t="inlineStr">
-        <is>
-          <t>Acquire</t>
-        </is>
-      </c>
-      <c r="J2" s="28" t="inlineStr">
-        <is>
-          <t>Acquire</t>
+      <c r="J2" s="30" t="inlineStr">
+        <is>
+          <t>Deepen</t>
         </is>
       </c>
       <c r="K2" s="29" t="inlineStr">
@@ -5735,7 +5735,6 @@
       <c r="G51" s="45" t="n"/>
       <c r="H51" s="46" t="n"/>
     </row>
-    <row r="52"/>
     <row r="53">
       <c r="A53" s="48" t="inlineStr">
         <is>

--- a/AI_CFT_Labeling.xlsx
+++ b/AI_CFT_Labeling.xlsx
@@ -4760,10 +4760,17 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" style="36" min="1" max="1"/>
-    <col width="18" customWidth="1" style="36" min="2" max="2"/>
-    <col width="13" customWidth="1" style="36" min="3" max="6"/>
-    <col width="14" customWidth="1" style="36" min="7" max="7"/>
-    <col width="40" customWidth="1" style="36" min="8" max="8"/>
+    <col width="16" customWidth="1" style="36" min="2" max="2"/>
+    <col width="22" customWidth="1" style="36" min="3" max="6"/>
+    <col width="22" customWidth="1" style="36" min="4" max="4"/>
+    <col width="22" customWidth="1" style="36" min="5" max="5"/>
+    <col width="22" customWidth="1" style="36" min="6" max="6"/>
+    <col width="22" customWidth="1" style="36" min="7" max="7"/>
+    <col width="22" customWidth="1" style="36" min="8" max="8"/>
+    <col width="22" customWidth="1" style="36" min="9" max="9"/>
+    <col width="22" customWidth="1" style="36" min="10" max="10"/>
+    <col width="14" customWidth="1" style="36" min="11" max="11"/>
+    <col width="20" customWidth="1" style="36" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" s="36">
@@ -4835,7 +4842,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="36" customHeight="1" s="36">
+    <row r="3" ht="50" customHeight="1" s="36">
       <c r="A3" s="15" t="inlineStr">
         <is>
           <t>Cohort</t>

--- a/AI_CFT_Labeling.xlsx
+++ b/AI_CFT_Labeling.xlsx
@@ -25,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="17">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -131,8 +131,28 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="001F3864"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00595959"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="17">
     <fill>
       <patternFill/>
     </fill>
@@ -182,6 +202,36 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E75B6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAF4FB"/>
       </patternFill>
     </fill>
   </fills>
@@ -241,7 +291,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -402,6 +452,60 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4761,986 +4865,1170 @@
   <cols>
     <col width="10" customWidth="1" style="36" min="1" max="1"/>
     <col width="16" customWidth="1" style="36" min="2" max="2"/>
-    <col width="22" customWidth="1" style="36" min="3" max="6"/>
-    <col width="22" customWidth="1" style="36" min="4" max="4"/>
-    <col width="22" customWidth="1" style="36" min="5" max="5"/>
-    <col width="22" customWidth="1" style="36" min="6" max="6"/>
-    <col width="22" customWidth="1" style="36" min="7" max="7"/>
-    <col width="22" customWidth="1" style="36" min="8" max="8"/>
-    <col width="22" customWidth="1" style="36" min="9" max="9"/>
-    <col width="22" customWidth="1" style="36" min="10" max="10"/>
+    <col width="20" customWidth="1" style="36" min="3" max="6"/>
+    <col width="20" customWidth="1" style="36" min="4" max="4"/>
+    <col width="20" customWidth="1" style="36" min="5" max="5"/>
+    <col width="20" customWidth="1" style="36" min="6" max="6"/>
+    <col width="20" customWidth="1" style="36" min="7" max="7"/>
+    <col width="20" customWidth="1" style="36" min="8" max="8"/>
+    <col width="20" customWidth="1" style="36" min="9" max="9"/>
+    <col width="20" customWidth="1" style="36" min="10" max="10"/>
     <col width="14" customWidth="1" style="36" min="11" max="11"/>
-    <col width="20" customWidth="1" style="36" min="12" max="12"/>
+    <col width="22" customWidth="1" style="36" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" s="36">
-      <c r="A1" s="47" t="inlineStr">
+      <c r="A1" s="59" t="inlineStr">
         <is>
           <t>AI-CFT Labeling — WS3 - Threshold Apply</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1" s="36">
-      <c r="A2" s="27" t="inlineStr">
+      <c r="A2" s="60" t="inlineStr">
         <is>
           <t>Cohort</t>
         </is>
       </c>
-      <c r="B2" s="27" t="inlineStr">
+      <c r="B2" s="60" t="inlineStr">
         <is>
           <t>Student</t>
         </is>
       </c>
-      <c r="C2" s="28" t="inlineStr">
+      <c r="C2" s="61" t="inlineStr">
         <is>
           <t>Acquire</t>
         </is>
       </c>
-      <c r="D2" s="28" t="inlineStr">
+      <c r="D2" s="61" t="inlineStr">
         <is>
           <t>Acquire</t>
         </is>
       </c>
-      <c r="E2" s="28" t="inlineStr">
+      <c r="E2" s="61" t="inlineStr">
         <is>
           <t>Acquire</t>
         </is>
       </c>
-      <c r="F2" s="28" t="inlineStr">
+      <c r="F2" s="61" t="inlineStr">
         <is>
           <t>Acquire</t>
         </is>
       </c>
-      <c r="G2" s="28" t="inlineStr">
+      <c r="G2" s="61" t="inlineStr">
         <is>
           <t>Acquire</t>
         </is>
       </c>
-      <c r="H2" s="28" t="inlineStr">
+      <c r="H2" s="61" t="inlineStr">
         <is>
           <t>Acquire</t>
         </is>
       </c>
-      <c r="I2" s="30" t="inlineStr">
+      <c r="I2" s="62" t="inlineStr">
         <is>
           <t>Deepen</t>
         </is>
       </c>
-      <c r="J2" s="30" t="inlineStr">
+      <c r="J2" s="62" t="inlineStr">
         <is>
           <t>Deepen</t>
         </is>
       </c>
-      <c r="K2" s="29" t="inlineStr">
+      <c r="K2" s="63" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L2" s="29" t="inlineStr">
+      <c r="L2" s="63" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="50" customHeight="1" s="36">
-      <c r="A3" s="15" t="inlineStr">
+    <row r="3" ht="48" customHeight="1" s="36">
+      <c r="A3" s="64" t="inlineStr">
         <is>
           <t>Cohort</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="64" t="inlineStr">
         <is>
           <t>Student Name</t>
         </is>
       </c>
-      <c r="C3" s="56" t="inlineStr">
+      <c r="C3" s="65" t="inlineStr">
         <is>
           <t>Blank 1
 Instance Classification (Popcorn)</t>
         </is>
       </c>
-      <c r="D3" s="56" t="inlineStr">
+      <c r="D3" s="65" t="inlineStr">
         <is>
           <t>Blank 2
 Rule Verification (Popcorn)</t>
         </is>
       </c>
-      <c r="E3" s="56" t="inlineStr">
+      <c r="E3" s="65" t="inlineStr">
         <is>
           <t>Blank 3
 Instance Classification (Apple)</t>
         </is>
       </c>
-      <c r="F3" s="56" t="inlineStr">
+      <c r="F3" s="65" t="inlineStr">
         <is>
           <t>Blank 4
 Rule Verification (Apple)</t>
         </is>
       </c>
-      <c r="G3" s="56" t="inlineStr">
+      <c r="G3" s="65" t="inlineStr">
         <is>
           <t>Blank 5
 Instance Classification (French Fries)</t>
         </is>
       </c>
-      <c r="H3" s="56" t="inlineStr">
+      <c r="H3" s="65" t="inlineStr">
         <is>
           <t>Blank 6
 Rule Verification (French Fries)</t>
         </is>
       </c>
-      <c r="I3" s="57" t="inlineStr">
+      <c r="I3" s="66" t="inlineStr">
         <is>
           <t>Blank 7
 Left Branching Condition</t>
         </is>
       </c>
-      <c r="J3" s="57" t="inlineStr">
+      <c r="J3" s="66" t="inlineStr">
         <is>
           <t>Blank 8
 Right Branching Condition</t>
         </is>
       </c>
-      <c r="K3" s="58" t="inlineStr">
+      <c r="K3" s="66" t="inlineStr">
         <is>
           <t>Overall WS3</t>
         </is>
       </c>
-      <c r="L3" s="58" t="inlineStr">
+      <c r="L3" s="66" t="inlineStr">
         <is>
           <t>Notes WS3</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="45" customHeight="1" s="36">
-      <c r="A4" s="41" t="inlineStr">
+    <row r="4" ht="20" customHeight="1" s="36">
+      <c r="A4" s="67" t="inlineStr">
         <is>
           <t>▶  Cohort 2025</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" s="36">
-      <c r="A5" s="49" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B5" s="33" t="n"/>
-      <c r="C5" s="33" t="n"/>
-      <c r="D5" s="33" t="n"/>
-      <c r="E5" s="33" t="n"/>
-      <c r="F5" s="33" t="n"/>
-      <c r="G5" s="33" t="n"/>
-      <c r="H5" s="34" t="n"/>
+      <c r="A5" s="68" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B5" s="69" t="n"/>
+      <c r="C5" s="69" t="n"/>
+      <c r="D5" s="69" t="n"/>
+      <c r="E5" s="69" t="n"/>
+      <c r="F5" s="69" t="n"/>
+      <c r="G5" s="69" t="n"/>
+      <c r="H5" s="68" t="n"/>
+      <c r="I5" s="70" t="n"/>
+      <c r="J5" s="70" t="n"/>
+      <c r="K5" s="71" t="n"/>
+      <c r="L5" s="71" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1" s="36">
-      <c r="A6" s="22" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="A6" s="72" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B6" s="72" t="inlineStr">
         <is>
           <t>Ally</t>
         </is>
       </c>
-      <c r="C6" s="24" t="n"/>
-      <c r="D6" s="24" t="n"/>
-      <c r="E6" s="24" t="n"/>
-      <c r="F6" s="24" t="n"/>
-      <c r="G6" s="45" t="n"/>
-      <c r="H6" s="46" t="n"/>
+      <c r="C6" s="73" t="n"/>
+      <c r="D6" s="73" t="n"/>
+      <c r="E6" s="73" t="n"/>
+      <c r="F6" s="73" t="n"/>
+      <c r="G6" s="73" t="n"/>
+      <c r="H6" s="73" t="n"/>
+      <c r="I6" s="72" t="n"/>
+      <c r="J6" s="72" t="n"/>
+      <c r="K6" s="71" t="n"/>
+      <c r="L6" s="71" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1" s="36">
-      <c r="A7" s="42" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B7" s="43" t="inlineStr">
+      <c r="A7" s="70" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B7" s="70" t="inlineStr">
         <is>
           <t>Bella</t>
         </is>
       </c>
-      <c r="C7" s="44" t="n"/>
-      <c r="D7" s="44" t="n"/>
-      <c r="E7" s="44" t="n"/>
-      <c r="F7" s="44" t="n"/>
-      <c r="G7" s="45" t="n"/>
-      <c r="H7" s="46" t="n"/>
+      <c r="C7" s="74" t="n"/>
+      <c r="D7" s="74" t="n"/>
+      <c r="E7" s="74" t="n"/>
+      <c r="F7" s="74" t="n"/>
+      <c r="G7" s="74" t="n"/>
+      <c r="H7" s="74" t="n"/>
+      <c r="I7" s="70" t="n"/>
+      <c r="J7" s="70" t="n"/>
+      <c r="K7" s="71" t="n"/>
+      <c r="L7" s="71" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1" s="36">
-      <c r="A8" s="22" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B8" s="23" t="inlineStr">
+      <c r="A8" s="72" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B8" s="72" t="inlineStr">
         <is>
           <t>Bob</t>
         </is>
       </c>
-      <c r="C8" s="24" t="n"/>
-      <c r="D8" s="24" t="n"/>
-      <c r="E8" s="24" t="n"/>
-      <c r="F8" s="24" t="n"/>
-      <c r="G8" s="45" t="n"/>
-      <c r="H8" s="46" t="n"/>
+      <c r="C8" s="73" t="n"/>
+      <c r="D8" s="73" t="n"/>
+      <c r="E8" s="73" t="n"/>
+      <c r="F8" s="73" t="n"/>
+      <c r="G8" s="73" t="n"/>
+      <c r="H8" s="73" t="n"/>
+      <c r="I8" s="72" t="n"/>
+      <c r="J8" s="72" t="n"/>
+      <c r="K8" s="71" t="n"/>
+      <c r="L8" s="71" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1" s="36">
-      <c r="A9" s="42" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B9" s="43" t="inlineStr">
+      <c r="A9" s="70" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B9" s="70" t="inlineStr">
         <is>
           <t>Daisy</t>
         </is>
       </c>
-      <c r="C9" s="44" t="n"/>
-      <c r="D9" s="44" t="n"/>
-      <c r="E9" s="44" t="n"/>
-      <c r="F9" s="44" t="n"/>
-      <c r="G9" s="45" t="n"/>
-      <c r="H9" s="46" t="n"/>
+      <c r="C9" s="74" t="n"/>
+      <c r="D9" s="74" t="n"/>
+      <c r="E9" s="74" t="n"/>
+      <c r="F9" s="74" t="n"/>
+      <c r="G9" s="74" t="n"/>
+      <c r="H9" s="74" t="n"/>
+      <c r="I9" s="70" t="n"/>
+      <c r="J9" s="70" t="n"/>
+      <c r="K9" s="71" t="n"/>
+      <c r="L9" s="71" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1" s="36">
-      <c r="A10" s="22" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B10" s="23" t="inlineStr">
+      <c r="A10" s="72" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B10" s="72" t="inlineStr">
         <is>
           <t>Daniella</t>
         </is>
       </c>
-      <c r="C10" s="24" t="n"/>
-      <c r="D10" s="24" t="n"/>
-      <c r="E10" s="24" t="n"/>
-      <c r="F10" s="24" t="n"/>
-      <c r="G10" s="45" t="n"/>
-      <c r="H10" s="46" t="n"/>
+      <c r="C10" s="73" t="n"/>
+      <c r="D10" s="73" t="n"/>
+      <c r="E10" s="73" t="n"/>
+      <c r="F10" s="73" t="n"/>
+      <c r="G10" s="73" t="n"/>
+      <c r="H10" s="73" t="n"/>
+      <c r="I10" s="72" t="n"/>
+      <c r="J10" s="72" t="n"/>
+      <c r="K10" s="71" t="n"/>
+      <c r="L10" s="71" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1" s="36">
-      <c r="A11" s="42" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B11" s="43" t="inlineStr">
+      <c r="A11" s="70" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B11" s="70" t="inlineStr">
         <is>
           <t>David</t>
         </is>
       </c>
-      <c r="C11" s="44" t="n"/>
-      <c r="D11" s="44" t="n"/>
-      <c r="E11" s="44" t="n"/>
-      <c r="F11" s="44" t="n"/>
-      <c r="G11" s="45" t="n"/>
-      <c r="H11" s="46" t="n"/>
+      <c r="C11" s="74" t="n"/>
+      <c r="D11" s="74" t="n"/>
+      <c r="E11" s="74" t="n"/>
+      <c r="F11" s="74" t="n"/>
+      <c r="G11" s="74" t="n"/>
+      <c r="H11" s="74" t="n"/>
+      <c r="I11" s="70" t="n"/>
+      <c r="J11" s="70" t="n"/>
+      <c r="K11" s="71" t="n"/>
+      <c r="L11" s="71" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1" s="36">
-      <c r="A12" s="22" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B12" s="23" t="inlineStr">
+      <c r="A12" s="72" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B12" s="72" t="inlineStr">
         <is>
           <t>Eliot</t>
         </is>
       </c>
-      <c r="C12" s="24" t="n"/>
-      <c r="D12" s="24" t="n"/>
-      <c r="E12" s="24" t="n"/>
-      <c r="F12" s="24" t="n"/>
-      <c r="G12" s="45" t="n"/>
-      <c r="H12" s="46" t="n"/>
+      <c r="C12" s="73" t="n"/>
+      <c r="D12" s="73" t="n"/>
+      <c r="E12" s="73" t="n"/>
+      <c r="F12" s="73" t="n"/>
+      <c r="G12" s="73" t="n"/>
+      <c r="H12" s="73" t="n"/>
+      <c r="I12" s="72" t="n"/>
+      <c r="J12" s="72" t="n"/>
+      <c r="K12" s="71" t="n"/>
+      <c r="L12" s="71" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1" s="36">
-      <c r="A13" s="42" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B13" s="43" t="inlineStr">
+      <c r="A13" s="70" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B13" s="70" t="inlineStr">
         <is>
           <t>Henry</t>
         </is>
       </c>
-      <c r="C13" s="44" t="n"/>
-      <c r="D13" s="44" t="n"/>
-      <c r="E13" s="44" t="n"/>
-      <c r="F13" s="44" t="n"/>
-      <c r="G13" s="45" t="n"/>
-      <c r="H13" s="46" t="n"/>
+      <c r="C13" s="74" t="n"/>
+      <c r="D13" s="74" t="n"/>
+      <c r="E13" s="74" t="n"/>
+      <c r="F13" s="74" t="n"/>
+      <c r="G13" s="74" t="n"/>
+      <c r="H13" s="74" t="n"/>
+      <c r="I13" s="70" t="n"/>
+      <c r="J13" s="70" t="n"/>
+      <c r="K13" s="71" t="n"/>
+      <c r="L13" s="71" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1" s="36">
-      <c r="A14" s="22" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B14" s="23" t="inlineStr">
+      <c r="A14" s="72" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B14" s="72" t="inlineStr">
         <is>
           <t>Irene</t>
         </is>
       </c>
-      <c r="C14" s="24" t="n"/>
-      <c r="D14" s="24" t="n"/>
-      <c r="E14" s="24" t="n"/>
-      <c r="F14" s="24" t="n"/>
-      <c r="G14" s="45" t="n"/>
-      <c r="H14" s="46" t="n"/>
+      <c r="C14" s="73" t="n"/>
+      <c r="D14" s="73" t="n"/>
+      <c r="E14" s="73" t="n"/>
+      <c r="F14" s="73" t="n"/>
+      <c r="G14" s="73" t="n"/>
+      <c r="H14" s="73" t="n"/>
+      <c r="I14" s="72" t="n"/>
+      <c r="J14" s="72" t="n"/>
+      <c r="K14" s="71" t="n"/>
+      <c r="L14" s="71" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1" s="36">
-      <c r="A15" s="42" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B15" s="43" t="inlineStr">
+      <c r="A15" s="70" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B15" s="70" t="inlineStr">
         <is>
           <t>Isabel</t>
         </is>
       </c>
-      <c r="C15" s="44" t="n"/>
-      <c r="D15" s="44" t="n"/>
-      <c r="E15" s="44" t="n"/>
-      <c r="F15" s="44" t="n"/>
-      <c r="G15" s="45" t="n"/>
-      <c r="H15" s="46" t="n"/>
+      <c r="C15" s="74" t="n"/>
+      <c r="D15" s="74" t="n"/>
+      <c r="E15" s="74" t="n"/>
+      <c r="F15" s="74" t="n"/>
+      <c r="G15" s="74" t="n"/>
+      <c r="H15" s="74" t="n"/>
+      <c r="I15" s="70" t="n"/>
+      <c r="J15" s="70" t="n"/>
+      <c r="K15" s="71" t="n"/>
+      <c r="L15" s="71" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1" s="36">
-      <c r="A16" s="22" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B16" s="23" t="inlineStr">
+      <c r="A16" s="72" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B16" s="72" t="inlineStr">
         <is>
           <t>Karl</t>
         </is>
       </c>
-      <c r="C16" s="24" t="n"/>
-      <c r="D16" s="24" t="n"/>
-      <c r="E16" s="24" t="n"/>
-      <c r="F16" s="24" t="n"/>
-      <c r="G16" s="45" t="n"/>
-      <c r="H16" s="46" t="n"/>
+      <c r="C16" s="73" t="n"/>
+      <c r="D16" s="73" t="n"/>
+      <c r="E16" s="73" t="n"/>
+      <c r="F16" s="73" t="n"/>
+      <c r="G16" s="73" t="n"/>
+      <c r="H16" s="73" t="n"/>
+      <c r="I16" s="72" t="n"/>
+      <c r="J16" s="72" t="n"/>
+      <c r="K16" s="71" t="n"/>
+      <c r="L16" s="71" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1" s="36">
-      <c r="A17" s="42" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B17" s="43" t="inlineStr">
+      <c r="A17" s="70" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B17" s="70" t="inlineStr">
         <is>
           <t>Michael</t>
         </is>
       </c>
-      <c r="C17" s="44" t="n"/>
-      <c r="D17" s="44" t="n"/>
-      <c r="E17" s="44" t="n"/>
-      <c r="F17" s="44" t="n"/>
-      <c r="G17" s="45" t="n"/>
-      <c r="H17" s="46" t="n"/>
+      <c r="C17" s="74" t="n"/>
+      <c r="D17" s="74" t="n"/>
+      <c r="E17" s="74" t="n"/>
+      <c r="F17" s="74" t="n"/>
+      <c r="G17" s="74" t="n"/>
+      <c r="H17" s="74" t="n"/>
+      <c r="I17" s="70" t="n"/>
+      <c r="J17" s="70" t="n"/>
+      <c r="K17" s="71" t="n"/>
+      <c r="L17" s="71" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1" s="36">
-      <c r="A18" s="22" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="A18" s="72" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B18" s="72" t="inlineStr">
         <is>
           <t>Mike</t>
         </is>
       </c>
-      <c r="C18" s="24" t="n"/>
-      <c r="D18" s="24" t="n"/>
-      <c r="E18" s="24" t="n"/>
-      <c r="F18" s="24" t="n"/>
-      <c r="G18" s="45" t="n"/>
-      <c r="H18" s="46" t="n"/>
+      <c r="C18" s="73" t="n"/>
+      <c r="D18" s="73" t="n"/>
+      <c r="E18" s="73" t="n"/>
+      <c r="F18" s="73" t="n"/>
+      <c r="G18" s="73" t="n"/>
+      <c r="H18" s="73" t="n"/>
+      <c r="I18" s="72" t="n"/>
+      <c r="J18" s="72" t="n"/>
+      <c r="K18" s="71" t="n"/>
+      <c r="L18" s="71" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1" s="36">
-      <c r="A19" s="42" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B19" s="43" t="inlineStr">
+      <c r="A19" s="70" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B19" s="70" t="inlineStr">
         <is>
           <t>Nicolas</t>
         </is>
       </c>
-      <c r="C19" s="44" t="n"/>
-      <c r="D19" s="44" t="n"/>
-      <c r="E19" s="44" t="n"/>
-      <c r="F19" s="44" t="n"/>
-      <c r="G19" s="45" t="n"/>
-      <c r="H19" s="46" t="n"/>
+      <c r="C19" s="74" t="n"/>
+      <c r="D19" s="74" t="n"/>
+      <c r="E19" s="74" t="n"/>
+      <c r="F19" s="74" t="n"/>
+      <c r="G19" s="74" t="n"/>
+      <c r="H19" s="74" t="n"/>
+      <c r="I19" s="70" t="n"/>
+      <c r="J19" s="70" t="n"/>
+      <c r="K19" s="71" t="n"/>
+      <c r="L19" s="71" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1" s="36">
-      <c r="A20" s="22" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B20" s="23" t="inlineStr">
+      <c r="A20" s="72" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B20" s="72" t="inlineStr">
         <is>
           <t>Zabby</t>
         </is>
       </c>
-      <c r="C20" s="24" t="n"/>
-      <c r="D20" s="24" t="n"/>
-      <c r="E20" s="24" t="n"/>
-      <c r="F20" s="24" t="n"/>
-      <c r="G20" s="45" t="n"/>
-      <c r="H20" s="46" t="n"/>
+      <c r="C20" s="73" t="n"/>
+      <c r="D20" s="73" t="n"/>
+      <c r="E20" s="73" t="n"/>
+      <c r="F20" s="73" t="n"/>
+      <c r="G20" s="73" t="n"/>
+      <c r="H20" s="73" t="n"/>
+      <c r="I20" s="72" t="n"/>
+      <c r="J20" s="72" t="n"/>
+      <c r="K20" s="71" t="n"/>
+      <c r="L20" s="71" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1" s="36">
-      <c r="A21" s="42" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B21" s="43" t="inlineStr">
+      <c r="A21" s="70" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B21" s="70" t="inlineStr">
         <is>
           <t>Adam</t>
         </is>
       </c>
-      <c r="C21" s="44" t="n"/>
-      <c r="D21" s="44" t="n"/>
-      <c r="E21" s="44" t="n"/>
-      <c r="F21" s="44" t="n"/>
-      <c r="G21" s="45" t="n"/>
-      <c r="H21" s="46" t="n"/>
+      <c r="C21" s="74" t="n"/>
+      <c r="D21" s="74" t="n"/>
+      <c r="E21" s="74" t="n"/>
+      <c r="F21" s="74" t="n"/>
+      <c r="G21" s="74" t="n"/>
+      <c r="H21" s="74" t="n"/>
+      <c r="I21" s="70" t="n"/>
+      <c r="J21" s="70" t="n"/>
+      <c r="K21" s="71" t="n"/>
+      <c r="L21" s="71" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1" s="36">
-      <c r="A22" s="22" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B22" s="23" t="inlineStr">
+      <c r="A22" s="72" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B22" s="72" t="inlineStr">
         <is>
           <t>Eddy</t>
         </is>
       </c>
-      <c r="C22" s="24" t="n"/>
-      <c r="D22" s="24" t="n"/>
-      <c r="E22" s="24" t="n"/>
-      <c r="F22" s="24" t="n"/>
-      <c r="G22" s="45" t="n"/>
-      <c r="H22" s="46" t="n"/>
+      <c r="C22" s="73" t="n"/>
+      <c r="D22" s="73" t="n"/>
+      <c r="E22" s="73" t="n"/>
+      <c r="F22" s="73" t="n"/>
+      <c r="G22" s="73" t="n"/>
+      <c r="H22" s="73" t="n"/>
+      <c r="I22" s="72" t="n"/>
+      <c r="J22" s="72" t="n"/>
+      <c r="K22" s="71" t="n"/>
+      <c r="L22" s="71" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1" s="36">
-      <c r="A23" s="42" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B23" s="43" t="inlineStr">
+      <c r="A23" s="70" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B23" s="70" t="inlineStr">
         <is>
           <t>Aden</t>
         </is>
       </c>
-      <c r="C23" s="44" t="n"/>
-      <c r="D23" s="44" t="n"/>
-      <c r="E23" s="44" t="n"/>
-      <c r="F23" s="44" t="n"/>
-      <c r="G23" s="45" t="n"/>
-      <c r="H23" s="46" t="n"/>
+      <c r="C23" s="74" t="n"/>
+      <c r="D23" s="74" t="n"/>
+      <c r="E23" s="74" t="n"/>
+      <c r="F23" s="74" t="n"/>
+      <c r="G23" s="74" t="n"/>
+      <c r="H23" s="74" t="n"/>
+      <c r="I23" s="70" t="n"/>
+      <c r="J23" s="70" t="n"/>
+      <c r="K23" s="71" t="n"/>
+      <c r="L23" s="71" t="n"/>
     </row>
     <row r="24" ht="18" customHeight="1" s="36">
-      <c r="A24" s="22" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B24" s="23" t="inlineStr">
+      <c r="A24" s="72" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B24" s="72" t="inlineStr">
         <is>
           <t>Barbara</t>
         </is>
       </c>
-      <c r="C24" s="24" t="n"/>
-      <c r="D24" s="24" t="n"/>
-      <c r="E24" s="24" t="n"/>
-      <c r="F24" s="24" t="n"/>
-      <c r="G24" s="45" t="n"/>
-      <c r="H24" s="46" t="n"/>
+      <c r="C24" s="73" t="n"/>
+      <c r="D24" s="73" t="n"/>
+      <c r="E24" s="73" t="n"/>
+      <c r="F24" s="73" t="n"/>
+      <c r="G24" s="73" t="n"/>
+      <c r="H24" s="73" t="n"/>
+      <c r="I24" s="72" t="n"/>
+      <c r="J24" s="72" t="n"/>
+      <c r="K24" s="71" t="n"/>
+      <c r="L24" s="71" t="n"/>
     </row>
     <row r="25" ht="18" customHeight="1" s="36">
-      <c r="A25" s="42" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B25" s="43" t="inlineStr">
+      <c r="A25" s="70" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B25" s="70" t="inlineStr">
         <is>
           <t>Boris</t>
         </is>
       </c>
-      <c r="C25" s="44" t="n"/>
-      <c r="D25" s="44" t="n"/>
-      <c r="E25" s="44" t="n"/>
-      <c r="F25" s="44" t="n"/>
-      <c r="G25" s="45" t="n"/>
-      <c r="H25" s="46" t="n"/>
+      <c r="C25" s="74" t="n"/>
+      <c r="D25" s="74" t="n"/>
+      <c r="E25" s="74" t="n"/>
+      <c r="F25" s="74" t="n"/>
+      <c r="G25" s="74" t="n"/>
+      <c r="H25" s="74" t="n"/>
+      <c r="I25" s="70" t="n"/>
+      <c r="J25" s="70" t="n"/>
+      <c r="K25" s="71" t="n"/>
+      <c r="L25" s="71" t="n"/>
     </row>
     <row r="26" ht="18" customHeight="1" s="36">
-      <c r="A26" s="22" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B26" s="23" t="inlineStr">
+      <c r="A26" s="72" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B26" s="72" t="inlineStr">
         <is>
           <t>Calvin</t>
         </is>
       </c>
-      <c r="C26" s="24" t="n"/>
-      <c r="D26" s="24" t="n"/>
-      <c r="E26" s="24" t="n"/>
-      <c r="F26" s="24" t="n"/>
-      <c r="G26" s="45" t="n"/>
-      <c r="H26" s="46" t="n"/>
+      <c r="C26" s="73" t="n"/>
+      <c r="D26" s="73" t="n"/>
+      <c r="E26" s="73" t="n"/>
+      <c r="F26" s="73" t="n"/>
+      <c r="G26" s="73" t="n"/>
+      <c r="H26" s="73" t="n"/>
+      <c r="I26" s="72" t="n"/>
+      <c r="J26" s="72" t="n"/>
+      <c r="K26" s="71" t="n"/>
+      <c r="L26" s="71" t="n"/>
     </row>
     <row r="27" ht="18" customHeight="1" s="36">
-      <c r="A27" s="42" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B27" s="43" t="inlineStr">
+      <c r="A27" s="70" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B27" s="70" t="inlineStr">
         <is>
           <t>Darby</t>
         </is>
       </c>
-      <c r="C27" s="44" t="n"/>
-      <c r="D27" s="44" t="n"/>
-      <c r="E27" s="44" t="n"/>
-      <c r="F27" s="44" t="n"/>
-      <c r="G27" s="45" t="n"/>
-      <c r="H27" s="46" t="n"/>
+      <c r="C27" s="74" t="n"/>
+      <c r="D27" s="74" t="n"/>
+      <c r="E27" s="74" t="n"/>
+      <c r="F27" s="74" t="n"/>
+      <c r="G27" s="74" t="n"/>
+      <c r="H27" s="74" t="n"/>
+      <c r="I27" s="70" t="n"/>
+      <c r="J27" s="70" t="n"/>
+      <c r="K27" s="71" t="n"/>
+      <c r="L27" s="71" t="n"/>
     </row>
     <row r="28" ht="18" customHeight="1" s="36">
-      <c r="A28" s="22" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B28" s="23" t="inlineStr">
+      <c r="A28" s="72" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B28" s="72" t="inlineStr">
         <is>
           <t>Demi</t>
         </is>
       </c>
-      <c r="C28" s="24" t="n"/>
-      <c r="D28" s="24" t="n"/>
-      <c r="E28" s="24" t="n"/>
-      <c r="F28" s="24" t="n"/>
-      <c r="G28" s="45" t="n"/>
-      <c r="H28" s="46" t="n"/>
+      <c r="C28" s="73" t="n"/>
+      <c r="D28" s="73" t="n"/>
+      <c r="E28" s="73" t="n"/>
+      <c r="F28" s="73" t="n"/>
+      <c r="G28" s="73" t="n"/>
+      <c r="H28" s="73" t="n"/>
+      <c r="I28" s="72" t="n"/>
+      <c r="J28" s="72" t="n"/>
+      <c r="K28" s="71" t="n"/>
+      <c r="L28" s="71" t="n"/>
     </row>
     <row r="29" ht="18" customHeight="1" s="36">
-      <c r="A29" s="42" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B29" s="43" t="inlineStr">
+      <c r="A29" s="70" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B29" s="70" t="inlineStr">
         <is>
           <t>Daryl</t>
         </is>
       </c>
-      <c r="C29" s="44" t="n"/>
-      <c r="D29" s="44" t="n"/>
-      <c r="E29" s="44" t="n"/>
-      <c r="F29" s="44" t="n"/>
-      <c r="G29" s="45" t="n"/>
-      <c r="H29" s="46" t="n"/>
+      <c r="C29" s="74" t="n"/>
+      <c r="D29" s="74" t="n"/>
+      <c r="E29" s="74" t="n"/>
+      <c r="F29" s="74" t="n"/>
+      <c r="G29" s="74" t="n"/>
+      <c r="H29" s="74" t="n"/>
+      <c r="I29" s="70" t="n"/>
+      <c r="J29" s="70" t="n"/>
+      <c r="K29" s="71" t="n"/>
+      <c r="L29" s="71" t="n"/>
     </row>
     <row r="30" ht="18" customHeight="1" s="36">
-      <c r="A30" s="22" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B30" s="23" t="inlineStr">
+      <c r="A30" s="72" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B30" s="72" t="inlineStr">
         <is>
           <t>Edgar</t>
         </is>
       </c>
-      <c r="C30" s="24" t="n"/>
-      <c r="D30" s="24" t="n"/>
-      <c r="E30" s="24" t="n"/>
-      <c r="F30" s="24" t="n"/>
-      <c r="G30" s="45" t="n"/>
-      <c r="H30" s="46" t="n"/>
+      <c r="C30" s="73" t="n"/>
+      <c r="D30" s="73" t="n"/>
+      <c r="E30" s="73" t="n"/>
+      <c r="F30" s="73" t="n"/>
+      <c r="G30" s="73" t="n"/>
+      <c r="H30" s="73" t="n"/>
+      <c r="I30" s="72" t="n"/>
+      <c r="J30" s="72" t="n"/>
+      <c r="K30" s="71" t="n"/>
+      <c r="L30" s="71" t="n"/>
     </row>
     <row r="31" ht="18" customHeight="1" s="36">
-      <c r="A31" s="42" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B31" s="43" t="inlineStr">
+      <c r="A31" s="70" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B31" s="70" t="inlineStr">
         <is>
           <t>Frank</t>
         </is>
       </c>
-      <c r="C31" s="44" t="n"/>
-      <c r="D31" s="44" t="n"/>
-      <c r="E31" s="44" t="n"/>
-      <c r="F31" s="44" t="n"/>
-      <c r="G31" s="45" t="n"/>
-      <c r="H31" s="46" t="n"/>
+      <c r="C31" s="74" t="n"/>
+      <c r="D31" s="74" t="n"/>
+      <c r="E31" s="74" t="n"/>
+      <c r="F31" s="74" t="n"/>
+      <c r="G31" s="74" t="n"/>
+      <c r="H31" s="74" t="n"/>
+      <c r="I31" s="70" t="n"/>
+      <c r="J31" s="70" t="n"/>
+      <c r="K31" s="71" t="n"/>
+      <c r="L31" s="71" t="n"/>
     </row>
     <row r="32" ht="18" customHeight="1" s="36">
-      <c r="A32" s="22" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B32" s="23" t="inlineStr">
+      <c r="A32" s="72" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B32" s="72" t="inlineStr">
         <is>
           <t>Felicity</t>
         </is>
       </c>
-      <c r="C32" s="24" t="n"/>
-      <c r="D32" s="24" t="n"/>
-      <c r="E32" s="24" t="n"/>
-      <c r="F32" s="24" t="n"/>
-      <c r="G32" s="45" t="n"/>
-      <c r="H32" s="46" t="n"/>
+      <c r="C32" s="73" t="n"/>
+      <c r="D32" s="73" t="n"/>
+      <c r="E32" s="73" t="n"/>
+      <c r="F32" s="73" t="n"/>
+      <c r="G32" s="73" t="n"/>
+      <c r="H32" s="73" t="n"/>
+      <c r="I32" s="72" t="n"/>
+      <c r="J32" s="72" t="n"/>
+      <c r="K32" s="71" t="n"/>
+      <c r="L32" s="71" t="n"/>
     </row>
     <row r="33" ht="18" customHeight="1" s="36">
-      <c r="A33" s="42" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B33" s="43" t="inlineStr">
+      <c r="A33" s="70" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B33" s="70" t="inlineStr">
         <is>
           <t>Kim</t>
         </is>
       </c>
-      <c r="C33" s="44" t="n"/>
-      <c r="D33" s="44" t="n"/>
-      <c r="E33" s="44" t="n"/>
-      <c r="F33" s="44" t="n"/>
-      <c r="G33" s="45" t="n"/>
-      <c r="H33" s="46" t="n"/>
+      <c r="C33" s="74" t="n"/>
+      <c r="D33" s="74" t="n"/>
+      <c r="E33" s="74" t="n"/>
+      <c r="F33" s="74" t="n"/>
+      <c r="G33" s="74" t="n"/>
+      <c r="H33" s="74" t="n"/>
+      <c r="I33" s="70" t="n"/>
+      <c r="J33" s="70" t="n"/>
+      <c r="K33" s="71" t="n"/>
+      <c r="L33" s="71" t="n"/>
     </row>
     <row r="34" ht="18" customHeight="1" s="36">
-      <c r="A34" s="32" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B34" s="33" t="n"/>
-      <c r="C34" s="33" t="n"/>
-      <c r="D34" s="33" t="n"/>
-      <c r="E34" s="33" t="n"/>
-      <c r="F34" s="33" t="n"/>
-      <c r="G34" s="33" t="n"/>
-      <c r="H34" s="34" t="n"/>
-    </row>
-    <row r="35" ht="18" customHeight="1" s="36">
-      <c r="A35" s="41" t="inlineStr">
+      <c r="A34" s="75" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B34" s="76" t="n"/>
+      <c r="C34" s="76" t="n"/>
+      <c r="D34" s="76" t="n"/>
+      <c r="E34" s="76" t="n"/>
+      <c r="F34" s="76" t="n"/>
+      <c r="G34" s="76" t="n"/>
+      <c r="H34" s="75" t="n"/>
+      <c r="I34" s="72" t="n"/>
+      <c r="J34" s="72" t="n"/>
+      <c r="K34" s="71" t="n"/>
+      <c r="L34" s="71" t="n"/>
+    </row>
+    <row r="35" ht="20" customHeight="1" s="36">
+      <c r="A35" s="67" t="inlineStr">
         <is>
           <t>▶  Cohort 2026</t>
         </is>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1" s="36">
-      <c r="A36" s="49" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="B36" s="33" t="n"/>
-      <c r="C36" s="33" t="n"/>
-      <c r="D36" s="33" t="n"/>
-      <c r="E36" s="33" t="n"/>
-      <c r="F36" s="33" t="n"/>
-      <c r="G36" s="33" t="n"/>
-      <c r="H36" s="34" t="n"/>
+      <c r="A36" s="68" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B36" s="69" t="n"/>
+      <c r="C36" s="69" t="n"/>
+      <c r="D36" s="69" t="n"/>
+      <c r="E36" s="69" t="n"/>
+      <c r="F36" s="69" t="n"/>
+      <c r="G36" s="69" t="n"/>
+      <c r="H36" s="68" t="n"/>
+      <c r="I36" s="70" t="n"/>
+      <c r="J36" s="70" t="n"/>
+      <c r="K36" s="71" t="n"/>
+      <c r="L36" s="71" t="n"/>
     </row>
     <row r="37" ht="18" customHeight="1" s="36">
-      <c r="A37" s="22" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="B37" s="23" t="inlineStr">
+      <c r="A37" s="72" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B37" s="72" t="inlineStr">
         <is>
           <t>Marco</t>
         </is>
       </c>
-      <c r="C37" s="24" t="n"/>
-      <c r="D37" s="24" t="n"/>
-      <c r="E37" s="24" t="n"/>
-      <c r="F37" s="24" t="n"/>
-      <c r="G37" s="45" t="n"/>
-      <c r="H37" s="46" t="n"/>
+      <c r="C37" s="73" t="n"/>
+      <c r="D37" s="73" t="n"/>
+      <c r="E37" s="73" t="n"/>
+      <c r="F37" s="73" t="n"/>
+      <c r="G37" s="73" t="n"/>
+      <c r="H37" s="73" t="n"/>
+      <c r="I37" s="72" t="n"/>
+      <c r="J37" s="72" t="n"/>
+      <c r="K37" s="71" t="n"/>
+      <c r="L37" s="71" t="n"/>
     </row>
     <row r="38" ht="18" customHeight="1" s="36">
-      <c r="A38" s="42" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="B38" s="43" t="inlineStr">
+      <c r="A38" s="70" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B38" s="70" t="inlineStr">
         <is>
           <t>Iris</t>
         </is>
       </c>
-      <c r="C38" s="44" t="n"/>
-      <c r="D38" s="44" t="n"/>
-      <c r="E38" s="44" t="n"/>
-      <c r="F38" s="44" t="n"/>
-      <c r="G38" s="45" t="n"/>
-      <c r="H38" s="46" t="n"/>
+      <c r="C38" s="74" t="n"/>
+      <c r="D38" s="74" t="n"/>
+      <c r="E38" s="74" t="n"/>
+      <c r="F38" s="74" t="n"/>
+      <c r="G38" s="74" t="n"/>
+      <c r="H38" s="74" t="n"/>
+      <c r="I38" s="70" t="n"/>
+      <c r="J38" s="70" t="n"/>
+      <c r="K38" s="71" t="n"/>
+      <c r="L38" s="71" t="n"/>
     </row>
     <row r="39" ht="18" customHeight="1" s="36">
-      <c r="A39" s="22" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="B39" s="23" t="inlineStr">
+      <c r="A39" s="72" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B39" s="72" t="inlineStr">
         <is>
           <t>Marcus</t>
         </is>
       </c>
-      <c r="C39" s="24" t="n"/>
-      <c r="D39" s="24" t="n"/>
-      <c r="E39" s="24" t="n"/>
-      <c r="F39" s="24" t="n"/>
-      <c r="G39" s="45" t="n"/>
-      <c r="H39" s="46" t="n"/>
+      <c r="C39" s="73" t="n"/>
+      <c r="D39" s="73" t="n"/>
+      <c r="E39" s="73" t="n"/>
+      <c r="F39" s="73" t="n"/>
+      <c r="G39" s="73" t="n"/>
+      <c r="H39" s="73" t="n"/>
+      <c r="I39" s="72" t="n"/>
+      <c r="J39" s="72" t="n"/>
+      <c r="K39" s="71" t="n"/>
+      <c r="L39" s="71" t="n"/>
     </row>
     <row r="40" ht="18" customHeight="1" s="36">
-      <c r="A40" s="42" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="B40" s="43" t="inlineStr">
+      <c r="A40" s="70" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B40" s="70" t="inlineStr">
         <is>
           <t>Isabel</t>
         </is>
       </c>
-      <c r="C40" s="44" t="n"/>
-      <c r="D40" s="44" t="n"/>
-      <c r="E40" s="44" t="n"/>
-      <c r="F40" s="44" t="n"/>
-      <c r="G40" s="45" t="n"/>
-      <c r="H40" s="46" t="n"/>
+      <c r="C40" s="74" t="n"/>
+      <c r="D40" s="74" t="n"/>
+      <c r="E40" s="74" t="n"/>
+      <c r="F40" s="74" t="n"/>
+      <c r="G40" s="74" t="n"/>
+      <c r="H40" s="74" t="n"/>
+      <c r="I40" s="70" t="n"/>
+      <c r="J40" s="70" t="n"/>
+      <c r="K40" s="71" t="n"/>
+      <c r="L40" s="71" t="n"/>
     </row>
     <row r="41" ht="18" customHeight="1" s="36">
-      <c r="A41" s="22" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="B41" s="23" t="inlineStr">
+      <c r="A41" s="72" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B41" s="72" t="inlineStr">
         <is>
           <t>Amy</t>
         </is>
       </c>
-      <c r="C41" s="24" t="n"/>
-      <c r="D41" s="24" t="n"/>
-      <c r="E41" s="24" t="n"/>
-      <c r="F41" s="24" t="n"/>
-      <c r="G41" s="45" t="n"/>
-      <c r="H41" s="46" t="n"/>
+      <c r="C41" s="73" t="n"/>
+      <c r="D41" s="73" t="n"/>
+      <c r="E41" s="73" t="n"/>
+      <c r="F41" s="73" t="n"/>
+      <c r="G41" s="73" t="n"/>
+      <c r="H41" s="73" t="n"/>
+      <c r="I41" s="72" t="n"/>
+      <c r="J41" s="72" t="n"/>
+      <c r="K41" s="71" t="n"/>
+      <c r="L41" s="71" t="n"/>
     </row>
     <row r="42" ht="18" customHeight="1" s="36">
-      <c r="A42" s="42" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="B42" s="43" t="inlineStr">
+      <c r="A42" s="70" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B42" s="70" t="inlineStr">
         <is>
           <t>Serena</t>
         </is>
       </c>
-      <c r="C42" s="44" t="n"/>
-      <c r="D42" s="44" t="n"/>
-      <c r="E42" s="44" t="n"/>
-      <c r="F42" s="44" t="n"/>
-      <c r="G42" s="45" t="n"/>
-      <c r="H42" s="46" t="n"/>
+      <c r="C42" s="74" t="n"/>
+      <c r="D42" s="74" t="n"/>
+      <c r="E42" s="74" t="n"/>
+      <c r="F42" s="74" t="n"/>
+      <c r="G42" s="74" t="n"/>
+      <c r="H42" s="74" t="n"/>
+      <c r="I42" s="70" t="n"/>
+      <c r="J42" s="70" t="n"/>
+      <c r="K42" s="71" t="n"/>
+      <c r="L42" s="71" t="n"/>
     </row>
     <row r="43" ht="18" customHeight="1" s="36">
-      <c r="A43" s="22" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="B43" s="23" t="inlineStr">
+      <c r="A43" s="72" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B43" s="72" t="inlineStr">
         <is>
           <t>Irma</t>
         </is>
       </c>
-      <c r="C43" s="24" t="n"/>
-      <c r="D43" s="24" t="n"/>
-      <c r="E43" s="24" t="n"/>
-      <c r="F43" s="24" t="n"/>
-      <c r="G43" s="45" t="n"/>
-      <c r="H43" s="46" t="n"/>
+      <c r="C43" s="73" t="n"/>
+      <c r="D43" s="73" t="n"/>
+      <c r="E43" s="73" t="n"/>
+      <c r="F43" s="73" t="n"/>
+      <c r="G43" s="73" t="n"/>
+      <c r="H43" s="73" t="n"/>
+      <c r="I43" s="72" t="n"/>
+      <c r="J43" s="72" t="n"/>
+      <c r="K43" s="71" t="n"/>
+      <c r="L43" s="71" t="n"/>
     </row>
     <row r="44" ht="18" customHeight="1" s="36">
-      <c r="A44" s="42" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="B44" s="43" t="inlineStr">
+      <c r="A44" s="70" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B44" s="70" t="inlineStr">
         <is>
           <t>Kate</t>
         </is>
       </c>
-      <c r="C44" s="44" t="n"/>
-      <c r="D44" s="44" t="n"/>
-      <c r="E44" s="44" t="n"/>
-      <c r="F44" s="44" t="n"/>
-      <c r="G44" s="45" t="n"/>
-      <c r="H44" s="46" t="n"/>
+      <c r="C44" s="74" t="n"/>
+      <c r="D44" s="74" t="n"/>
+      <c r="E44" s="74" t="n"/>
+      <c r="F44" s="74" t="n"/>
+      <c r="G44" s="74" t="n"/>
+      <c r="H44" s="74" t="n"/>
+      <c r="I44" s="70" t="n"/>
+      <c r="J44" s="70" t="n"/>
+      <c r="K44" s="71" t="n"/>
+      <c r="L44" s="71" t="n"/>
     </row>
     <row r="45" ht="18" customHeight="1" s="36">
-      <c r="A45" s="22" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="B45" s="23" t="inlineStr">
+      <c r="A45" s="72" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B45" s="72" t="inlineStr">
         <is>
           <t>Bruno</t>
         </is>
       </c>
-      <c r="C45" s="24" t="n"/>
-      <c r="D45" s="24" t="n"/>
-      <c r="E45" s="24" t="n"/>
-      <c r="F45" s="24" t="n"/>
-      <c r="G45" s="45" t="n"/>
-      <c r="H45" s="46" t="n"/>
+      <c r="C45" s="73" t="n"/>
+      <c r="D45" s="73" t="n"/>
+      <c r="E45" s="73" t="n"/>
+      <c r="F45" s="73" t="n"/>
+      <c r="G45" s="73" t="n"/>
+      <c r="H45" s="73" t="n"/>
+      <c r="I45" s="72" t="n"/>
+      <c r="J45" s="72" t="n"/>
+      <c r="K45" s="71" t="n"/>
+      <c r="L45" s="71" t="n"/>
     </row>
     <row r="46" ht="18" customHeight="1" s="36">
-      <c r="A46" s="42" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="B46" s="43" t="inlineStr">
+      <c r="A46" s="70" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B46" s="70" t="inlineStr">
         <is>
           <t>Zara</t>
         </is>
       </c>
-      <c r="C46" s="44" t="n"/>
-      <c r="D46" s="44" t="n"/>
-      <c r="E46" s="44" t="n"/>
-      <c r="F46" s="44" t="n"/>
-      <c r="G46" s="45" t="n"/>
-      <c r="H46" s="46" t="n"/>
+      <c r="C46" s="74" t="n"/>
+      <c r="D46" s="74" t="n"/>
+      <c r="E46" s="74" t="n"/>
+      <c r="F46" s="74" t="n"/>
+      <c r="G46" s="74" t="n"/>
+      <c r="H46" s="74" t="n"/>
+      <c r="I46" s="70" t="n"/>
+      <c r="J46" s="70" t="n"/>
+      <c r="K46" s="71" t="n"/>
+      <c r="L46" s="71" t="n"/>
     </row>
     <row r="47" ht="18" customHeight="1" s="36">
-      <c r="A47" s="22" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="B47" s="23" t="inlineStr">
+      <c r="A47" s="72" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B47" s="72" t="inlineStr">
         <is>
           <t>Shana</t>
         </is>
       </c>
-      <c r="C47" s="24" t="n"/>
-      <c r="D47" s="24" t="n"/>
-      <c r="E47" s="24" t="n"/>
-      <c r="F47" s="24" t="n"/>
-      <c r="G47" s="45" t="n"/>
-      <c r="H47" s="46" t="n"/>
+      <c r="C47" s="73" t="n"/>
+      <c r="D47" s="73" t="n"/>
+      <c r="E47" s="73" t="n"/>
+      <c r="F47" s="73" t="n"/>
+      <c r="G47" s="73" t="n"/>
+      <c r="H47" s="73" t="n"/>
+      <c r="I47" s="72" t="n"/>
+      <c r="J47" s="72" t="n"/>
+      <c r="K47" s="71" t="n"/>
+      <c r="L47" s="71" t="n"/>
     </row>
     <row r="48" ht="18" customHeight="1" s="36">
-      <c r="A48" s="42" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="B48" s="43" t="inlineStr">
+      <c r="A48" s="70" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B48" s="70" t="inlineStr">
         <is>
           <t>Melinda</t>
         </is>
       </c>
-      <c r="C48" s="44" t="n"/>
-      <c r="D48" s="44" t="n"/>
-      <c r="E48" s="44" t="n"/>
-      <c r="F48" s="44" t="n"/>
-      <c r="G48" s="45" t="n"/>
-      <c r="H48" s="46" t="n"/>
+      <c r="C48" s="74" t="n"/>
+      <c r="D48" s="74" t="n"/>
+      <c r="E48" s="74" t="n"/>
+      <c r="F48" s="74" t="n"/>
+      <c r="G48" s="74" t="n"/>
+      <c r="H48" s="74" t="n"/>
+      <c r="I48" s="70" t="n"/>
+      <c r="J48" s="70" t="n"/>
+      <c r="K48" s="71" t="n"/>
+      <c r="L48" s="71" t="n"/>
     </row>
     <row r="49" ht="18" customHeight="1" s="36">
-      <c r="A49" s="22" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="B49" s="23" t="inlineStr">
+      <c r="A49" s="72" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B49" s="72" t="inlineStr">
         <is>
           <t>Helena</t>
         </is>
       </c>
-      <c r="C49" s="24" t="n"/>
-      <c r="D49" s="24" t="n"/>
-      <c r="E49" s="24" t="n"/>
-      <c r="F49" s="24" t="n"/>
-      <c r="G49" s="45" t="n"/>
-      <c r="H49" s="46" t="n"/>
+      <c r="C49" s="73" t="n"/>
+      <c r="D49" s="73" t="n"/>
+      <c r="E49" s="73" t="n"/>
+      <c r="F49" s="73" t="n"/>
+      <c r="G49" s="73" t="n"/>
+      <c r="H49" s="73" t="n"/>
+      <c r="I49" s="72" t="n"/>
+      <c r="J49" s="72" t="n"/>
+      <c r="K49" s="71" t="n"/>
+      <c r="L49" s="71" t="n"/>
     </row>
     <row r="50" ht="18" customHeight="1" s="36">
-      <c r="A50" s="42" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="B50" s="43" t="inlineStr">
+      <c r="A50" s="70" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B50" s="70" t="inlineStr">
         <is>
           <t>Nadia</t>
         </is>
       </c>
-      <c r="C50" s="44" t="n"/>
-      <c r="D50" s="44" t="n"/>
-      <c r="E50" s="44" t="n"/>
-      <c r="F50" s="44" t="n"/>
-      <c r="G50" s="45" t="n"/>
-      <c r="H50" s="46" t="n"/>
+      <c r="C50" s="74" t="n"/>
+      <c r="D50" s="74" t="n"/>
+      <c r="E50" s="74" t="n"/>
+      <c r="F50" s="74" t="n"/>
+      <c r="G50" s="74" t="n"/>
+      <c r="H50" s="74" t="n"/>
+      <c r="I50" s="70" t="n"/>
+      <c r="J50" s="70" t="n"/>
+      <c r="K50" s="71" t="n"/>
+      <c r="L50" s="71" t="n"/>
     </row>
     <row r="51" ht="18" customHeight="1" s="36">
-      <c r="A51" s="22" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="B51" s="23" t="inlineStr">
+      <c r="A51" s="72" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B51" s="72" t="inlineStr">
         <is>
           <t>Ulysses</t>
         </is>
       </c>
-      <c r="C51" s="24" t="n"/>
-      <c r="D51" s="24" t="n"/>
-      <c r="E51" s="24" t="n"/>
-      <c r="F51" s="24" t="n"/>
-      <c r="G51" s="45" t="n"/>
-      <c r="H51" s="46" t="n"/>
+      <c r="C51" s="73" t="n"/>
+      <c r="D51" s="73" t="n"/>
+      <c r="E51" s="73" t="n"/>
+      <c r="F51" s="73" t="n"/>
+      <c r="G51" s="73" t="n"/>
+      <c r="H51" s="73" t="n"/>
+      <c r="I51" s="72" t="n"/>
+      <c r="J51" s="72" t="n"/>
+      <c r="K51" s="71" t="n"/>
+      <c r="L51" s="71" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="48" t="inlineStr">

--- a/AI_CFT_Labeling.xlsx
+++ b/AI_CFT_Labeling.xlsx
@@ -152,7 +152,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="18">
     <fill>
       <patternFill/>
     </fill>
@@ -234,6 +234,11 @@
         <fgColor rgb="00EAF4FB"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="5">
     <border>
@@ -291,7 +296,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -505,6 +510,33 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4947,70 +4979,70 @@
       </c>
     </row>
     <row r="3" ht="48" customHeight="1" s="36">
-      <c r="A3" s="64" t="inlineStr">
+      <c r="A3" s="77" t="inlineStr">
         <is>
           <t>Cohort</t>
         </is>
       </c>
-      <c r="B3" s="64" t="inlineStr">
+      <c r="B3" s="77" t="inlineStr">
         <is>
           <t>Student Name</t>
         </is>
       </c>
-      <c r="C3" s="65" t="inlineStr">
+      <c r="C3" s="78" t="inlineStr">
         <is>
           <t>Blank 1
 Instance Classification (Popcorn)</t>
         </is>
       </c>
-      <c r="D3" s="65" t="inlineStr">
+      <c r="D3" s="78" t="inlineStr">
         <is>
           <t>Blank 2
 Rule Verification (Popcorn)</t>
         </is>
       </c>
-      <c r="E3" s="65" t="inlineStr">
+      <c r="E3" s="78" t="inlineStr">
         <is>
           <t>Blank 3
 Instance Classification (Apple)</t>
         </is>
       </c>
-      <c r="F3" s="65" t="inlineStr">
+      <c r="F3" s="78" t="inlineStr">
         <is>
           <t>Blank 4
 Rule Verification (Apple)</t>
         </is>
       </c>
-      <c r="G3" s="65" t="inlineStr">
+      <c r="G3" s="78" t="inlineStr">
         <is>
           <t>Blank 5
 Instance Classification (French Fries)</t>
         </is>
       </c>
-      <c r="H3" s="65" t="inlineStr">
+      <c r="H3" s="78" t="inlineStr">
         <is>
           <t>Blank 6
 Rule Verification (French Fries)</t>
         </is>
       </c>
-      <c r="I3" s="66" t="inlineStr">
+      <c r="I3" s="79" t="inlineStr">
         <is>
           <t>Blank 7
 Left Branching Condition</t>
         </is>
       </c>
-      <c r="J3" s="66" t="inlineStr">
+      <c r="J3" s="79" t="inlineStr">
         <is>
           <t>Blank 8
 Right Branching Condition</t>
         </is>
       </c>
-      <c r="K3" s="66" t="inlineStr">
+      <c r="K3" s="79" t="inlineStr">
         <is>
           <t>Overall WS3</t>
         </is>
       </c>
-      <c r="L3" s="66" t="inlineStr">
+      <c r="L3" s="79" t="inlineStr">
         <is>
           <t>Notes WS3</t>
         </is>
@@ -5029,39 +5061,39 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="B5" s="69" t="n"/>
-      <c r="C5" s="69" t="n"/>
-      <c r="D5" s="69" t="n"/>
-      <c r="E5" s="69" t="n"/>
-      <c r="F5" s="69" t="n"/>
-      <c r="G5" s="69" t="n"/>
-      <c r="H5" s="68" t="n"/>
+      <c r="B5" s="80" t="n"/>
+      <c r="C5" s="80" t="n"/>
+      <c r="D5" s="80" t="n"/>
+      <c r="E5" s="80" t="n"/>
+      <c r="F5" s="80" t="n"/>
+      <c r="G5" s="80" t="n"/>
+      <c r="H5" s="81" t="n"/>
       <c r="I5" s="70" t="n"/>
       <c r="J5" s="70" t="n"/>
-      <c r="K5" s="71" t="n"/>
-      <c r="L5" s="71" t="n"/>
+      <c r="K5" s="70" t="n"/>
+      <c r="L5" s="70" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1" s="36">
-      <c r="A6" s="72" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B6" s="72" t="inlineStr">
+      <c r="A6" s="82" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B6" s="82" t="inlineStr">
         <is>
           <t>Ally</t>
         </is>
       </c>
-      <c r="C6" s="73" t="n"/>
-      <c r="D6" s="73" t="n"/>
-      <c r="E6" s="73" t="n"/>
-      <c r="F6" s="73" t="n"/>
-      <c r="G6" s="73" t="n"/>
-      <c r="H6" s="73" t="n"/>
-      <c r="I6" s="72" t="n"/>
-      <c r="J6" s="72" t="n"/>
-      <c r="K6" s="71" t="n"/>
-      <c r="L6" s="71" t="n"/>
+      <c r="C6" s="83" t="n"/>
+      <c r="D6" s="83" t="n"/>
+      <c r="E6" s="83" t="n"/>
+      <c r="F6" s="83" t="n"/>
+      <c r="G6" s="83" t="n"/>
+      <c r="H6" s="83" t="n"/>
+      <c r="I6" s="82" t="n"/>
+      <c r="J6" s="82" t="n"/>
+      <c r="K6" s="82" t="n"/>
+      <c r="L6" s="82" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1" s="36">
       <c r="A7" s="70" t="inlineStr">
@@ -5082,30 +5114,30 @@
       <c r="H7" s="74" t="n"/>
       <c r="I7" s="70" t="n"/>
       <c r="J7" s="70" t="n"/>
-      <c r="K7" s="71" t="n"/>
-      <c r="L7" s="71" t="n"/>
+      <c r="K7" s="70" t="n"/>
+      <c r="L7" s="70" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1" s="36">
-      <c r="A8" s="72" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B8" s="72" t="inlineStr">
+      <c r="A8" s="82" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B8" s="82" t="inlineStr">
         <is>
           <t>Bob</t>
         </is>
       </c>
-      <c r="C8" s="73" t="n"/>
-      <c r="D8" s="73" t="n"/>
-      <c r="E8" s="73" t="n"/>
-      <c r="F8" s="73" t="n"/>
-      <c r="G8" s="73" t="n"/>
-      <c r="H8" s="73" t="n"/>
-      <c r="I8" s="72" t="n"/>
-      <c r="J8" s="72" t="n"/>
-      <c r="K8" s="71" t="n"/>
-      <c r="L8" s="71" t="n"/>
+      <c r="C8" s="83" t="n"/>
+      <c r="D8" s="83" t="n"/>
+      <c r="E8" s="83" t="n"/>
+      <c r="F8" s="83" t="n"/>
+      <c r="G8" s="83" t="n"/>
+      <c r="H8" s="83" t="n"/>
+      <c r="I8" s="82" t="n"/>
+      <c r="J8" s="82" t="n"/>
+      <c r="K8" s="82" t="n"/>
+      <c r="L8" s="82" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1" s="36">
       <c r="A9" s="70" t="inlineStr">
@@ -5126,30 +5158,30 @@
       <c r="H9" s="74" t="n"/>
       <c r="I9" s="70" t="n"/>
       <c r="J9" s="70" t="n"/>
-      <c r="K9" s="71" t="n"/>
-      <c r="L9" s="71" t="n"/>
+      <c r="K9" s="70" t="n"/>
+      <c r="L9" s="70" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1" s="36">
-      <c r="A10" s="72" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B10" s="72" t="inlineStr">
+      <c r="A10" s="82" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B10" s="82" t="inlineStr">
         <is>
           <t>Daniella</t>
         </is>
       </c>
-      <c r="C10" s="73" t="n"/>
-      <c r="D10" s="73" t="n"/>
-      <c r="E10" s="73" t="n"/>
-      <c r="F10" s="73" t="n"/>
-      <c r="G10" s="73" t="n"/>
-      <c r="H10" s="73" t="n"/>
-      <c r="I10" s="72" t="n"/>
-      <c r="J10" s="72" t="n"/>
-      <c r="K10" s="71" t="n"/>
-      <c r="L10" s="71" t="n"/>
+      <c r="C10" s="83" t="n"/>
+      <c r="D10" s="83" t="n"/>
+      <c r="E10" s="83" t="n"/>
+      <c r="F10" s="83" t="n"/>
+      <c r="G10" s="83" t="n"/>
+      <c r="H10" s="83" t="n"/>
+      <c r="I10" s="82" t="n"/>
+      <c r="J10" s="82" t="n"/>
+      <c r="K10" s="82" t="n"/>
+      <c r="L10" s="82" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1" s="36">
       <c r="A11" s="70" t="inlineStr">
@@ -5170,30 +5202,30 @@
       <c r="H11" s="74" t="n"/>
       <c r="I11" s="70" t="n"/>
       <c r="J11" s="70" t="n"/>
-      <c r="K11" s="71" t="n"/>
-      <c r="L11" s="71" t="n"/>
+      <c r="K11" s="70" t="n"/>
+      <c r="L11" s="70" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1" s="36">
-      <c r="A12" s="72" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B12" s="72" t="inlineStr">
+      <c r="A12" s="82" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B12" s="82" t="inlineStr">
         <is>
           <t>Eliot</t>
         </is>
       </c>
-      <c r="C12" s="73" t="n"/>
-      <c r="D12" s="73" t="n"/>
-      <c r="E12" s="73" t="n"/>
-      <c r="F12" s="73" t="n"/>
-      <c r="G12" s="73" t="n"/>
-      <c r="H12" s="73" t="n"/>
-      <c r="I12" s="72" t="n"/>
-      <c r="J12" s="72" t="n"/>
-      <c r="K12" s="71" t="n"/>
-      <c r="L12" s="71" t="n"/>
+      <c r="C12" s="83" t="n"/>
+      <c r="D12" s="83" t="n"/>
+      <c r="E12" s="83" t="n"/>
+      <c r="F12" s="83" t="n"/>
+      <c r="G12" s="83" t="n"/>
+      <c r="H12" s="83" t="n"/>
+      <c r="I12" s="82" t="n"/>
+      <c r="J12" s="82" t="n"/>
+      <c r="K12" s="82" t="n"/>
+      <c r="L12" s="82" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1" s="36">
       <c r="A13" s="70" t="inlineStr">
@@ -5214,30 +5246,30 @@
       <c r="H13" s="74" t="n"/>
       <c r="I13" s="70" t="n"/>
       <c r="J13" s="70" t="n"/>
-      <c r="K13" s="71" t="n"/>
-      <c r="L13" s="71" t="n"/>
+      <c r="K13" s="70" t="n"/>
+      <c r="L13" s="70" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1" s="36">
-      <c r="A14" s="72" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B14" s="72" t="inlineStr">
+      <c r="A14" s="82" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B14" s="82" t="inlineStr">
         <is>
           <t>Irene</t>
         </is>
       </c>
-      <c r="C14" s="73" t="n"/>
-      <c r="D14" s="73" t="n"/>
-      <c r="E14" s="73" t="n"/>
-      <c r="F14" s="73" t="n"/>
-      <c r="G14" s="73" t="n"/>
-      <c r="H14" s="73" t="n"/>
-      <c r="I14" s="72" t="n"/>
-      <c r="J14" s="72" t="n"/>
-      <c r="K14" s="71" t="n"/>
-      <c r="L14" s="71" t="n"/>
+      <c r="C14" s="83" t="n"/>
+      <c r="D14" s="83" t="n"/>
+      <c r="E14" s="83" t="n"/>
+      <c r="F14" s="83" t="n"/>
+      <c r="G14" s="83" t="n"/>
+      <c r="H14" s="83" t="n"/>
+      <c r="I14" s="82" t="n"/>
+      <c r="J14" s="82" t="n"/>
+      <c r="K14" s="82" t="n"/>
+      <c r="L14" s="82" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1" s="36">
       <c r="A15" s="70" t="inlineStr">
@@ -5258,30 +5290,30 @@
       <c r="H15" s="74" t="n"/>
       <c r="I15" s="70" t="n"/>
       <c r="J15" s="70" t="n"/>
-      <c r="K15" s="71" t="n"/>
-      <c r="L15" s="71" t="n"/>
+      <c r="K15" s="70" t="n"/>
+      <c r="L15" s="70" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1" s="36">
-      <c r="A16" s="72" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B16" s="72" t="inlineStr">
+      <c r="A16" s="82" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B16" s="82" t="inlineStr">
         <is>
           <t>Karl</t>
         </is>
       </c>
-      <c r="C16" s="73" t="n"/>
-      <c r="D16" s="73" t="n"/>
-      <c r="E16" s="73" t="n"/>
-      <c r="F16" s="73" t="n"/>
-      <c r="G16" s="73" t="n"/>
-      <c r="H16" s="73" t="n"/>
-      <c r="I16" s="72" t="n"/>
-      <c r="J16" s="72" t="n"/>
-      <c r="K16" s="71" t="n"/>
-      <c r="L16" s="71" t="n"/>
+      <c r="C16" s="83" t="n"/>
+      <c r="D16" s="83" t="n"/>
+      <c r="E16" s="83" t="n"/>
+      <c r="F16" s="83" t="n"/>
+      <c r="G16" s="83" t="n"/>
+      <c r="H16" s="83" t="n"/>
+      <c r="I16" s="82" t="n"/>
+      <c r="J16" s="82" t="n"/>
+      <c r="K16" s="82" t="n"/>
+      <c r="L16" s="82" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1" s="36">
       <c r="A17" s="70" t="inlineStr">
@@ -5302,30 +5334,30 @@
       <c r="H17" s="74" t="n"/>
       <c r="I17" s="70" t="n"/>
       <c r="J17" s="70" t="n"/>
-      <c r="K17" s="71" t="n"/>
-      <c r="L17" s="71" t="n"/>
+      <c r="K17" s="70" t="n"/>
+      <c r="L17" s="70" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1" s="36">
-      <c r="A18" s="72" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B18" s="72" t="inlineStr">
+      <c r="A18" s="82" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B18" s="82" t="inlineStr">
         <is>
           <t>Mike</t>
         </is>
       </c>
-      <c r="C18" s="73" t="n"/>
-      <c r="D18" s="73" t="n"/>
-      <c r="E18" s="73" t="n"/>
-      <c r="F18" s="73" t="n"/>
-      <c r="G18" s="73" t="n"/>
-      <c r="H18" s="73" t="n"/>
-      <c r="I18" s="72" t="n"/>
-      <c r="J18" s="72" t="n"/>
-      <c r="K18" s="71" t="n"/>
-      <c r="L18" s="71" t="n"/>
+      <c r="C18" s="83" t="n"/>
+      <c r="D18" s="83" t="n"/>
+      <c r="E18" s="83" t="n"/>
+      <c r="F18" s="83" t="n"/>
+      <c r="G18" s="83" t="n"/>
+      <c r="H18" s="83" t="n"/>
+      <c r="I18" s="82" t="n"/>
+      <c r="J18" s="82" t="n"/>
+      <c r="K18" s="82" t="n"/>
+      <c r="L18" s="82" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1" s="36">
       <c r="A19" s="70" t="inlineStr">
@@ -5346,30 +5378,30 @@
       <c r="H19" s="74" t="n"/>
       <c r="I19" s="70" t="n"/>
       <c r="J19" s="70" t="n"/>
-      <c r="K19" s="71" t="n"/>
-      <c r="L19" s="71" t="n"/>
+      <c r="K19" s="70" t="n"/>
+      <c r="L19" s="70" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1" s="36">
-      <c r="A20" s="72" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B20" s="72" t="inlineStr">
+      <c r="A20" s="82" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B20" s="82" t="inlineStr">
         <is>
           <t>Zabby</t>
         </is>
       </c>
-      <c r="C20" s="73" t="n"/>
-      <c r="D20" s="73" t="n"/>
-      <c r="E20" s="73" t="n"/>
-      <c r="F20" s="73" t="n"/>
-      <c r="G20" s="73" t="n"/>
-      <c r="H20" s="73" t="n"/>
-      <c r="I20" s="72" t="n"/>
-      <c r="J20" s="72" t="n"/>
-      <c r="K20" s="71" t="n"/>
-      <c r="L20" s="71" t="n"/>
+      <c r="C20" s="83" t="n"/>
+      <c r="D20" s="83" t="n"/>
+      <c r="E20" s="83" t="n"/>
+      <c r="F20" s="83" t="n"/>
+      <c r="G20" s="83" t="n"/>
+      <c r="H20" s="83" t="n"/>
+      <c r="I20" s="82" t="n"/>
+      <c r="J20" s="82" t="n"/>
+      <c r="K20" s="82" t="n"/>
+      <c r="L20" s="82" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1" s="36">
       <c r="A21" s="70" t="inlineStr">
@@ -5390,30 +5422,30 @@
       <c r="H21" s="74" t="n"/>
       <c r="I21" s="70" t="n"/>
       <c r="J21" s="70" t="n"/>
-      <c r="K21" s="71" t="n"/>
-      <c r="L21" s="71" t="n"/>
+      <c r="K21" s="70" t="n"/>
+      <c r="L21" s="70" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1" s="36">
-      <c r="A22" s="72" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B22" s="72" t="inlineStr">
+      <c r="A22" s="82" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B22" s="82" t="inlineStr">
         <is>
           <t>Eddy</t>
         </is>
       </c>
-      <c r="C22" s="73" t="n"/>
-      <c r="D22" s="73" t="n"/>
-      <c r="E22" s="73" t="n"/>
-      <c r="F22" s="73" t="n"/>
-      <c r="G22" s="73" t="n"/>
-      <c r="H22" s="73" t="n"/>
-      <c r="I22" s="72" t="n"/>
-      <c r="J22" s="72" t="n"/>
-      <c r="K22" s="71" t="n"/>
-      <c r="L22" s="71" t="n"/>
+      <c r="C22" s="83" t="n"/>
+      <c r="D22" s="83" t="n"/>
+      <c r="E22" s="83" t="n"/>
+      <c r="F22" s="83" t="n"/>
+      <c r="G22" s="83" t="n"/>
+      <c r="H22" s="83" t="n"/>
+      <c r="I22" s="82" t="n"/>
+      <c r="J22" s="82" t="n"/>
+      <c r="K22" s="82" t="n"/>
+      <c r="L22" s="82" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1" s="36">
       <c r="A23" s="70" t="inlineStr">
@@ -5434,30 +5466,30 @@
       <c r="H23" s="74" t="n"/>
       <c r="I23" s="70" t="n"/>
       <c r="J23" s="70" t="n"/>
-      <c r="K23" s="71" t="n"/>
-      <c r="L23" s="71" t="n"/>
+      <c r="K23" s="70" t="n"/>
+      <c r="L23" s="70" t="n"/>
     </row>
     <row r="24" ht="18" customHeight="1" s="36">
-      <c r="A24" s="72" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B24" s="72" t="inlineStr">
+      <c r="A24" s="82" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B24" s="82" t="inlineStr">
         <is>
           <t>Barbara</t>
         </is>
       </c>
-      <c r="C24" s="73" t="n"/>
-      <c r="D24" s="73" t="n"/>
-      <c r="E24" s="73" t="n"/>
-      <c r="F24" s="73" t="n"/>
-      <c r="G24" s="73" t="n"/>
-      <c r="H24" s="73" t="n"/>
-      <c r="I24" s="72" t="n"/>
-      <c r="J24" s="72" t="n"/>
-      <c r="K24" s="71" t="n"/>
-      <c r="L24" s="71" t="n"/>
+      <c r="C24" s="83" t="n"/>
+      <c r="D24" s="83" t="n"/>
+      <c r="E24" s="83" t="n"/>
+      <c r="F24" s="83" t="n"/>
+      <c r="G24" s="83" t="n"/>
+      <c r="H24" s="83" t="n"/>
+      <c r="I24" s="82" t="n"/>
+      <c r="J24" s="82" t="n"/>
+      <c r="K24" s="82" t="n"/>
+      <c r="L24" s="82" t="n"/>
     </row>
     <row r="25" ht="18" customHeight="1" s="36">
       <c r="A25" s="70" t="inlineStr">
@@ -5478,30 +5510,30 @@
       <c r="H25" s="74" t="n"/>
       <c r="I25" s="70" t="n"/>
       <c r="J25" s="70" t="n"/>
-      <c r="K25" s="71" t="n"/>
-      <c r="L25" s="71" t="n"/>
+      <c r="K25" s="70" t="n"/>
+      <c r="L25" s="70" t="n"/>
     </row>
     <row r="26" ht="18" customHeight="1" s="36">
-      <c r="A26" s="72" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B26" s="72" t="inlineStr">
+      <c r="A26" s="82" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B26" s="82" t="inlineStr">
         <is>
           <t>Calvin</t>
         </is>
       </c>
-      <c r="C26" s="73" t="n"/>
-      <c r="D26" s="73" t="n"/>
-      <c r="E26" s="73" t="n"/>
-      <c r="F26" s="73" t="n"/>
-      <c r="G26" s="73" t="n"/>
-      <c r="H26" s="73" t="n"/>
-      <c r="I26" s="72" t="n"/>
-      <c r="J26" s="72" t="n"/>
-      <c r="K26" s="71" t="n"/>
-      <c r="L26" s="71" t="n"/>
+      <c r="C26" s="83" t="n"/>
+      <c r="D26" s="83" t="n"/>
+      <c r="E26" s="83" t="n"/>
+      <c r="F26" s="83" t="n"/>
+      <c r="G26" s="83" t="n"/>
+      <c r="H26" s="83" t="n"/>
+      <c r="I26" s="82" t="n"/>
+      <c r="J26" s="82" t="n"/>
+      <c r="K26" s="82" t="n"/>
+      <c r="L26" s="82" t="n"/>
     </row>
     <row r="27" ht="18" customHeight="1" s="36">
       <c r="A27" s="70" t="inlineStr">
@@ -5522,30 +5554,30 @@
       <c r="H27" s="74" t="n"/>
       <c r="I27" s="70" t="n"/>
       <c r="J27" s="70" t="n"/>
-      <c r="K27" s="71" t="n"/>
-      <c r="L27" s="71" t="n"/>
+      <c r="K27" s="70" t="n"/>
+      <c r="L27" s="70" t="n"/>
     </row>
     <row r="28" ht="18" customHeight="1" s="36">
-      <c r="A28" s="72" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B28" s="72" t="inlineStr">
+      <c r="A28" s="82" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B28" s="82" t="inlineStr">
         <is>
           <t>Demi</t>
         </is>
       </c>
-      <c r="C28" s="73" t="n"/>
-      <c r="D28" s="73" t="n"/>
-      <c r="E28" s="73" t="n"/>
-      <c r="F28" s="73" t="n"/>
-      <c r="G28" s="73" t="n"/>
-      <c r="H28" s="73" t="n"/>
-      <c r="I28" s="72" t="n"/>
-      <c r="J28" s="72" t="n"/>
-      <c r="K28" s="71" t="n"/>
-      <c r="L28" s="71" t="n"/>
+      <c r="C28" s="83" t="n"/>
+      <c r="D28" s="83" t="n"/>
+      <c r="E28" s="83" t="n"/>
+      <c r="F28" s="83" t="n"/>
+      <c r="G28" s="83" t="n"/>
+      <c r="H28" s="83" t="n"/>
+      <c r="I28" s="82" t="n"/>
+      <c r="J28" s="82" t="n"/>
+      <c r="K28" s="82" t="n"/>
+      <c r="L28" s="82" t="n"/>
     </row>
     <row r="29" ht="18" customHeight="1" s="36">
       <c r="A29" s="70" t="inlineStr">
@@ -5566,30 +5598,30 @@
       <c r="H29" s="74" t="n"/>
       <c r="I29" s="70" t="n"/>
       <c r="J29" s="70" t="n"/>
-      <c r="K29" s="71" t="n"/>
-      <c r="L29" s="71" t="n"/>
+      <c r="K29" s="70" t="n"/>
+      <c r="L29" s="70" t="n"/>
     </row>
     <row r="30" ht="18" customHeight="1" s="36">
-      <c r="A30" s="72" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B30" s="72" t="inlineStr">
+      <c r="A30" s="82" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B30" s="82" t="inlineStr">
         <is>
           <t>Edgar</t>
         </is>
       </c>
-      <c r="C30" s="73" t="n"/>
-      <c r="D30" s="73" t="n"/>
-      <c r="E30" s="73" t="n"/>
-      <c r="F30" s="73" t="n"/>
-      <c r="G30" s="73" t="n"/>
-      <c r="H30" s="73" t="n"/>
-      <c r="I30" s="72" t="n"/>
-      <c r="J30" s="72" t="n"/>
-      <c r="K30" s="71" t="n"/>
-      <c r="L30" s="71" t="n"/>
+      <c r="C30" s="83" t="n"/>
+      <c r="D30" s="83" t="n"/>
+      <c r="E30" s="83" t="n"/>
+      <c r="F30" s="83" t="n"/>
+      <c r="G30" s="83" t="n"/>
+      <c r="H30" s="83" t="n"/>
+      <c r="I30" s="82" t="n"/>
+      <c r="J30" s="82" t="n"/>
+      <c r="K30" s="82" t="n"/>
+      <c r="L30" s="82" t="n"/>
     </row>
     <row r="31" ht="18" customHeight="1" s="36">
       <c r="A31" s="70" t="inlineStr">
@@ -5610,30 +5642,30 @@
       <c r="H31" s="74" t="n"/>
       <c r="I31" s="70" t="n"/>
       <c r="J31" s="70" t="n"/>
-      <c r="K31" s="71" t="n"/>
-      <c r="L31" s="71" t="n"/>
+      <c r="K31" s="70" t="n"/>
+      <c r="L31" s="70" t="n"/>
     </row>
     <row r="32" ht="18" customHeight="1" s="36">
-      <c r="A32" s="72" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B32" s="72" t="inlineStr">
+      <c r="A32" s="82" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B32" s="82" t="inlineStr">
         <is>
           <t>Felicity</t>
         </is>
       </c>
-      <c r="C32" s="73" t="n"/>
-      <c r="D32" s="73" t="n"/>
-      <c r="E32" s="73" t="n"/>
-      <c r="F32" s="73" t="n"/>
-      <c r="G32" s="73" t="n"/>
-      <c r="H32" s="73" t="n"/>
-      <c r="I32" s="72" t="n"/>
-      <c r="J32" s="72" t="n"/>
-      <c r="K32" s="71" t="n"/>
-      <c r="L32" s="71" t="n"/>
+      <c r="C32" s="83" t="n"/>
+      <c r="D32" s="83" t="n"/>
+      <c r="E32" s="83" t="n"/>
+      <c r="F32" s="83" t="n"/>
+      <c r="G32" s="83" t="n"/>
+      <c r="H32" s="83" t="n"/>
+      <c r="I32" s="82" t="n"/>
+      <c r="J32" s="82" t="n"/>
+      <c r="K32" s="82" t="n"/>
+      <c r="L32" s="82" t="n"/>
     </row>
     <row r="33" ht="18" customHeight="1" s="36">
       <c r="A33" s="70" t="inlineStr">
@@ -5654,26 +5686,26 @@
       <c r="H33" s="74" t="n"/>
       <c r="I33" s="70" t="n"/>
       <c r="J33" s="70" t="n"/>
-      <c r="K33" s="71" t="n"/>
-      <c r="L33" s="71" t="n"/>
+      <c r="K33" s="70" t="n"/>
+      <c r="L33" s="70" t="n"/>
     </row>
     <row r="34" ht="18" customHeight="1" s="36">
-      <c r="A34" s="75" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B34" s="76" t="n"/>
-      <c r="C34" s="76" t="n"/>
-      <c r="D34" s="76" t="n"/>
-      <c r="E34" s="76" t="n"/>
-      <c r="F34" s="76" t="n"/>
-      <c r="G34" s="76" t="n"/>
-      <c r="H34" s="75" t="n"/>
-      <c r="I34" s="72" t="n"/>
-      <c r="J34" s="72" t="n"/>
-      <c r="K34" s="71" t="n"/>
-      <c r="L34" s="71" t="n"/>
+      <c r="A34" s="84" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B34" s="85" t="n"/>
+      <c r="C34" s="85" t="n"/>
+      <c r="D34" s="85" t="n"/>
+      <c r="E34" s="85" t="n"/>
+      <c r="F34" s="85" t="n"/>
+      <c r="G34" s="85" t="n"/>
+      <c r="H34" s="84" t="n"/>
+      <c r="I34" s="82" t="n"/>
+      <c r="J34" s="82" t="n"/>
+      <c r="K34" s="82" t="n"/>
+      <c r="L34" s="82" t="n"/>
     </row>
     <row r="35" ht="20" customHeight="1" s="36">
       <c r="A35" s="67" t="inlineStr">
@@ -5688,39 +5720,39 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="B36" s="69" t="n"/>
-      <c r="C36" s="69" t="n"/>
-      <c r="D36" s="69" t="n"/>
-      <c r="E36" s="69" t="n"/>
-      <c r="F36" s="69" t="n"/>
-      <c r="G36" s="69" t="n"/>
-      <c r="H36" s="68" t="n"/>
+      <c r="B36" s="80" t="n"/>
+      <c r="C36" s="80" t="n"/>
+      <c r="D36" s="80" t="n"/>
+      <c r="E36" s="80" t="n"/>
+      <c r="F36" s="80" t="n"/>
+      <c r="G36" s="80" t="n"/>
+      <c r="H36" s="81" t="n"/>
       <c r="I36" s="70" t="n"/>
       <c r="J36" s="70" t="n"/>
-      <c r="K36" s="71" t="n"/>
-      <c r="L36" s="71" t="n"/>
+      <c r="K36" s="70" t="n"/>
+      <c r="L36" s="70" t="n"/>
     </row>
     <row r="37" ht="18" customHeight="1" s="36">
-      <c r="A37" s="72" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="B37" s="72" t="inlineStr">
+      <c r="A37" s="82" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B37" s="82" t="inlineStr">
         <is>
           <t>Marco</t>
         </is>
       </c>
-      <c r="C37" s="73" t="n"/>
-      <c r="D37" s="73" t="n"/>
-      <c r="E37" s="73" t="n"/>
-      <c r="F37" s="73" t="n"/>
-      <c r="G37" s="73" t="n"/>
-      <c r="H37" s="73" t="n"/>
-      <c r="I37" s="72" t="n"/>
-      <c r="J37" s="72" t="n"/>
-      <c r="K37" s="71" t="n"/>
-      <c r="L37" s="71" t="n"/>
+      <c r="C37" s="83" t="n"/>
+      <c r="D37" s="83" t="n"/>
+      <c r="E37" s="83" t="n"/>
+      <c r="F37" s="83" t="n"/>
+      <c r="G37" s="83" t="n"/>
+      <c r="H37" s="83" t="n"/>
+      <c r="I37" s="82" t="n"/>
+      <c r="J37" s="82" t="n"/>
+      <c r="K37" s="82" t="n"/>
+      <c r="L37" s="82" t="n"/>
     </row>
     <row r="38" ht="18" customHeight="1" s="36">
       <c r="A38" s="70" t="inlineStr">
@@ -5741,30 +5773,30 @@
       <c r="H38" s="74" t="n"/>
       <c r="I38" s="70" t="n"/>
       <c r="J38" s="70" t="n"/>
-      <c r="K38" s="71" t="n"/>
-      <c r="L38" s="71" t="n"/>
+      <c r="K38" s="70" t="n"/>
+      <c r="L38" s="70" t="n"/>
     </row>
     <row r="39" ht="18" customHeight="1" s="36">
-      <c r="A39" s="72" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="B39" s="72" t="inlineStr">
+      <c r="A39" s="82" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B39" s="82" t="inlineStr">
         <is>
           <t>Marcus</t>
         </is>
       </c>
-      <c r="C39" s="73" t="n"/>
-      <c r="D39" s="73" t="n"/>
-      <c r="E39" s="73" t="n"/>
-      <c r="F39" s="73" t="n"/>
-      <c r="G39" s="73" t="n"/>
-      <c r="H39" s="73" t="n"/>
-      <c r="I39" s="72" t="n"/>
-      <c r="J39" s="72" t="n"/>
-      <c r="K39" s="71" t="n"/>
-      <c r="L39" s="71" t="n"/>
+      <c r="C39" s="83" t="n"/>
+      <c r="D39" s="83" t="n"/>
+      <c r="E39" s="83" t="n"/>
+      <c r="F39" s="83" t="n"/>
+      <c r="G39" s="83" t="n"/>
+      <c r="H39" s="83" t="n"/>
+      <c r="I39" s="82" t="n"/>
+      <c r="J39" s="82" t="n"/>
+      <c r="K39" s="82" t="n"/>
+      <c r="L39" s="82" t="n"/>
     </row>
     <row r="40" ht="18" customHeight="1" s="36">
       <c r="A40" s="70" t="inlineStr">
@@ -5785,30 +5817,30 @@
       <c r="H40" s="74" t="n"/>
       <c r="I40" s="70" t="n"/>
       <c r="J40" s="70" t="n"/>
-      <c r="K40" s="71" t="n"/>
-      <c r="L40" s="71" t="n"/>
+      <c r="K40" s="70" t="n"/>
+      <c r="L40" s="70" t="n"/>
     </row>
     <row r="41" ht="18" customHeight="1" s="36">
-      <c r="A41" s="72" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="B41" s="72" t="inlineStr">
+      <c r="A41" s="82" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B41" s="82" t="inlineStr">
         <is>
           <t>Amy</t>
         </is>
       </c>
-      <c r="C41" s="73" t="n"/>
-      <c r="D41" s="73" t="n"/>
-      <c r="E41" s="73" t="n"/>
-      <c r="F41" s="73" t="n"/>
-      <c r="G41" s="73" t="n"/>
-      <c r="H41" s="73" t="n"/>
-      <c r="I41" s="72" t="n"/>
-      <c r="J41" s="72" t="n"/>
-      <c r="K41" s="71" t="n"/>
-      <c r="L41" s="71" t="n"/>
+      <c r="C41" s="83" t="n"/>
+      <c r="D41" s="83" t="n"/>
+      <c r="E41" s="83" t="n"/>
+      <c r="F41" s="83" t="n"/>
+      <c r="G41" s="83" t="n"/>
+      <c r="H41" s="83" t="n"/>
+      <c r="I41" s="82" t="n"/>
+      <c r="J41" s="82" t="n"/>
+      <c r="K41" s="82" t="n"/>
+      <c r="L41" s="82" t="n"/>
     </row>
     <row r="42" ht="18" customHeight="1" s="36">
       <c r="A42" s="70" t="inlineStr">
@@ -5829,30 +5861,30 @@
       <c r="H42" s="74" t="n"/>
       <c r="I42" s="70" t="n"/>
       <c r="J42" s="70" t="n"/>
-      <c r="K42" s="71" t="n"/>
-      <c r="L42" s="71" t="n"/>
+      <c r="K42" s="70" t="n"/>
+      <c r="L42" s="70" t="n"/>
     </row>
     <row r="43" ht="18" customHeight="1" s="36">
-      <c r="A43" s="72" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="B43" s="72" t="inlineStr">
+      <c r="A43" s="82" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B43" s="82" t="inlineStr">
         <is>
           <t>Irma</t>
         </is>
       </c>
-      <c r="C43" s="73" t="n"/>
-      <c r="D43" s="73" t="n"/>
-      <c r="E43" s="73" t="n"/>
-      <c r="F43" s="73" t="n"/>
-      <c r="G43" s="73" t="n"/>
-      <c r="H43" s="73" t="n"/>
-      <c r="I43" s="72" t="n"/>
-      <c r="J43" s="72" t="n"/>
-      <c r="K43" s="71" t="n"/>
-      <c r="L43" s="71" t="n"/>
+      <c r="C43" s="83" t="n"/>
+      <c r="D43" s="83" t="n"/>
+      <c r="E43" s="83" t="n"/>
+      <c r="F43" s="83" t="n"/>
+      <c r="G43" s="83" t="n"/>
+      <c r="H43" s="83" t="n"/>
+      <c r="I43" s="82" t="n"/>
+      <c r="J43" s="82" t="n"/>
+      <c r="K43" s="82" t="n"/>
+      <c r="L43" s="82" t="n"/>
     </row>
     <row r="44" ht="18" customHeight="1" s="36">
       <c r="A44" s="70" t="inlineStr">
@@ -5873,30 +5905,30 @@
       <c r="H44" s="74" t="n"/>
       <c r="I44" s="70" t="n"/>
       <c r="J44" s="70" t="n"/>
-      <c r="K44" s="71" t="n"/>
-      <c r="L44" s="71" t="n"/>
+      <c r="K44" s="70" t="n"/>
+      <c r="L44" s="70" t="n"/>
     </row>
     <row r="45" ht="18" customHeight="1" s="36">
-      <c r="A45" s="72" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="B45" s="72" t="inlineStr">
+      <c r="A45" s="82" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B45" s="82" t="inlineStr">
         <is>
           <t>Bruno</t>
         </is>
       </c>
-      <c r="C45" s="73" t="n"/>
-      <c r="D45" s="73" t="n"/>
-      <c r="E45" s="73" t="n"/>
-      <c r="F45" s="73" t="n"/>
-      <c r="G45" s="73" t="n"/>
-      <c r="H45" s="73" t="n"/>
-      <c r="I45" s="72" t="n"/>
-      <c r="J45" s="72" t="n"/>
-      <c r="K45" s="71" t="n"/>
-      <c r="L45" s="71" t="n"/>
+      <c r="C45" s="83" t="n"/>
+      <c r="D45" s="83" t="n"/>
+      <c r="E45" s="83" t="n"/>
+      <c r="F45" s="83" t="n"/>
+      <c r="G45" s="83" t="n"/>
+      <c r="H45" s="83" t="n"/>
+      <c r="I45" s="82" t="n"/>
+      <c r="J45" s="82" t="n"/>
+      <c r="K45" s="82" t="n"/>
+      <c r="L45" s="82" t="n"/>
     </row>
     <row r="46" ht="18" customHeight="1" s="36">
       <c r="A46" s="70" t="inlineStr">
@@ -5917,30 +5949,30 @@
       <c r="H46" s="74" t="n"/>
       <c r="I46" s="70" t="n"/>
       <c r="J46" s="70" t="n"/>
-      <c r="K46" s="71" t="n"/>
-      <c r="L46" s="71" t="n"/>
+      <c r="K46" s="70" t="n"/>
+      <c r="L46" s="70" t="n"/>
     </row>
     <row r="47" ht="18" customHeight="1" s="36">
-      <c r="A47" s="72" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="B47" s="72" t="inlineStr">
+      <c r="A47" s="82" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B47" s="82" t="inlineStr">
         <is>
           <t>Shana</t>
         </is>
       </c>
-      <c r="C47" s="73" t="n"/>
-      <c r="D47" s="73" t="n"/>
-      <c r="E47" s="73" t="n"/>
-      <c r="F47" s="73" t="n"/>
-      <c r="G47" s="73" t="n"/>
-      <c r="H47" s="73" t="n"/>
-      <c r="I47" s="72" t="n"/>
-      <c r="J47" s="72" t="n"/>
-      <c r="K47" s="71" t="n"/>
-      <c r="L47" s="71" t="n"/>
+      <c r="C47" s="83" t="n"/>
+      <c r="D47" s="83" t="n"/>
+      <c r="E47" s="83" t="n"/>
+      <c r="F47" s="83" t="n"/>
+      <c r="G47" s="83" t="n"/>
+      <c r="H47" s="83" t="n"/>
+      <c r="I47" s="82" t="n"/>
+      <c r="J47" s="82" t="n"/>
+      <c r="K47" s="82" t="n"/>
+      <c r="L47" s="82" t="n"/>
     </row>
     <row r="48" ht="18" customHeight="1" s="36">
       <c r="A48" s="70" t="inlineStr">
@@ -5961,30 +5993,30 @@
       <c r="H48" s="74" t="n"/>
       <c r="I48" s="70" t="n"/>
       <c r="J48" s="70" t="n"/>
-      <c r="K48" s="71" t="n"/>
-      <c r="L48" s="71" t="n"/>
+      <c r="K48" s="70" t="n"/>
+      <c r="L48" s="70" t="n"/>
     </row>
     <row r="49" ht="18" customHeight="1" s="36">
-      <c r="A49" s="72" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="B49" s="72" t="inlineStr">
+      <c r="A49" s="82" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B49" s="82" t="inlineStr">
         <is>
           <t>Helena</t>
         </is>
       </c>
-      <c r="C49" s="73" t="n"/>
-      <c r="D49" s="73" t="n"/>
-      <c r="E49" s="73" t="n"/>
-      <c r="F49" s="73" t="n"/>
-      <c r="G49" s="73" t="n"/>
-      <c r="H49" s="73" t="n"/>
-      <c r="I49" s="72" t="n"/>
-      <c r="J49" s="72" t="n"/>
-      <c r="K49" s="71" t="n"/>
-      <c r="L49" s="71" t="n"/>
+      <c r="C49" s="83" t="n"/>
+      <c r="D49" s="83" t="n"/>
+      <c r="E49" s="83" t="n"/>
+      <c r="F49" s="83" t="n"/>
+      <c r="G49" s="83" t="n"/>
+      <c r="H49" s="83" t="n"/>
+      <c r="I49" s="82" t="n"/>
+      <c r="J49" s="82" t="n"/>
+      <c r="K49" s="82" t="n"/>
+      <c r="L49" s="82" t="n"/>
     </row>
     <row r="50" ht="18" customHeight="1" s="36">
       <c r="A50" s="70" t="inlineStr">
@@ -6005,30 +6037,30 @@
       <c r="H50" s="74" t="n"/>
       <c r="I50" s="70" t="n"/>
       <c r="J50" s="70" t="n"/>
-      <c r="K50" s="71" t="n"/>
-      <c r="L50" s="71" t="n"/>
+      <c r="K50" s="70" t="n"/>
+      <c r="L50" s="70" t="n"/>
     </row>
     <row r="51" ht="18" customHeight="1" s="36">
-      <c r="A51" s="72" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="B51" s="72" t="inlineStr">
+      <c r="A51" s="82" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B51" s="82" t="inlineStr">
         <is>
           <t>Ulysses</t>
         </is>
       </c>
-      <c r="C51" s="73" t="n"/>
-      <c r="D51" s="73" t="n"/>
-      <c r="E51" s="73" t="n"/>
-      <c r="F51" s="73" t="n"/>
-      <c r="G51" s="73" t="n"/>
-      <c r="H51" s="73" t="n"/>
-      <c r="I51" s="72" t="n"/>
-      <c r="J51" s="72" t="n"/>
-      <c r="K51" s="71" t="n"/>
-      <c r="L51" s="71" t="n"/>
+      <c r="C51" s="83" t="n"/>
+      <c r="D51" s="83" t="n"/>
+      <c r="E51" s="83" t="n"/>
+      <c r="F51" s="83" t="n"/>
+      <c r="G51" s="83" t="n"/>
+      <c r="H51" s="83" t="n"/>
+      <c r="I51" s="82" t="n"/>
+      <c r="J51" s="82" t="n"/>
+      <c r="K51" s="82" t="n"/>
+      <c r="L51" s="82" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="48" t="inlineStr">

--- a/AI_CFT_Labeling.xlsx
+++ b/AI_CFT_Labeling.xlsx
@@ -25,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -173,6 +173,11 @@
     <font>
       <name val="Calibri"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="26">
@@ -417,7 +422,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -661,6 +666,9 @@
     </xf>
     <xf numFmtId="0" fontId="21" fillId="25" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1517,145 +1525,145 @@
       </c>
       <c r="C3" s="82" t="inlineStr">
         <is>
-          <t>A1
+          <t>Blank 1
 Prior belief</t>
         </is>
       </c>
       <c r="D3" s="82" t="inlineStr">
         <is>
-          <t>A2
+          <t>Blank 2
 Data-based exploration</t>
         </is>
       </c>
       <c r="E3" s="82" t="inlineStr">
         <is>
-          <t>A3
+          <t>Blank 3
 Meaningful difference found</t>
         </is>
       </c>
       <c r="F3" s="82" t="inlineStr">
         <is>
-          <t>A4
+          <t>Blank 4
 First variable justification</t>
         </is>
       </c>
       <c r="G3" s="82" t="inlineStr">
         <is>
-          <t>B1
+          <t>Blank 5
 Tree 1 — build + EMIT</t>
         </is>
       </c>
       <c r="H3" s="82" t="inlineStr">
         <is>
-          <t>B2
+          <t>Blank 6
 Tree 2 — build + EMIT</t>
         </is>
       </c>
       <c r="I3" s="82" t="inlineStr">
         <is>
-          <t>B3
+          <t>Blank 7
 Tree 3 — build + EMIT</t>
         </is>
       </c>
       <c r="J3" s="82" t="inlineStr">
         <is>
-          <t>B4
+          <t>Blank 8
 Best tree + criteria</t>
         </is>
       </c>
       <c r="K3" s="82" t="inlineStr">
         <is>
-          <t>C1
+          <t>Blank 9
 Threshold optimization</t>
         </is>
       </c>
       <c r="L3" s="82" t="inlineStr">
         <is>
-          <t>C2
+          <t>Blank 10
 Threshold effect</t>
         </is>
       </c>
       <c r="M3" s="82" t="inlineStr">
         <is>
-          <t>C3
+          <t>Blank 11
 Best threshold + reasoning</t>
         </is>
       </c>
       <c r="N3" s="82" t="inlineStr">
         <is>
-          <t>D1
+          <t>Blank 12
 Two-level tree — build + EMIT</t>
         </is>
       </c>
       <c r="O3" s="82" t="inlineStr">
         <is>
-          <t>D2
+          <t>Blank 13
 Second level effect</t>
         </is>
       </c>
       <c r="P3" s="82" t="inlineStr">
         <is>
-          <t>D3
+          <t>Blank 14
 Best variable combination</t>
         </is>
       </c>
       <c r="Q3" s="82" t="inlineStr">
         <is>
-          <t>D4
+          <t>Blank 15
 Stopping criterion</t>
         </is>
       </c>
       <c r="R3" s="82" t="inlineStr">
         <is>
-          <t>E
+          <t>Blank 16
 Metrics</t>
         </is>
       </c>
       <c r="S3" s="82" t="inlineStr">
         <is>
-          <t>E1
+          <t>Blank 17
 Metric interpretation</t>
         </is>
       </c>
       <c r="T3" s="82" t="inlineStr">
         <is>
-          <t>E2
+          <t>Blank 18
 Error type analysis</t>
         </is>
       </c>
       <c r="U3" s="82" t="inlineStr">
         <is>
-          <t>E3
+          <t>Blank 19
 Good-enough criterion</t>
         </is>
       </c>
       <c r="V3" s="82" t="inlineStr">
         <is>
-          <t>E4
+          <t>Blank 20
 Perfect classification</t>
         </is>
       </c>
       <c r="W3" s="82" t="inlineStr">
         <is>
-          <t>F1
+          <t>Blank 21
 Test set application</t>
         </is>
       </c>
       <c r="X3" s="82" t="inlineStr">
         <is>
-          <t>F2
+          <t>Blank 22
 Train vs test comparison</t>
         </is>
       </c>
       <c r="Y3" s="82" t="inlineStr">
         <is>
-          <t>G1
+          <t>Blank 23
 What the model learned</t>
         </is>
       </c>
       <c r="Z3" s="82" t="inlineStr">
         <is>
-          <t>G2
+          <t>Blank 24
 Personal reflection</t>
         </is>
       </c>
@@ -1683,33 +1691,33 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="B5" s="84" t="n"/>
-      <c r="C5" s="84" t="n"/>
-      <c r="D5" s="84" t="n"/>
-      <c r="E5" s="84" t="n"/>
-      <c r="F5" s="84" t="n"/>
-      <c r="G5" s="84" t="n"/>
-      <c r="H5" s="84" t="n"/>
-      <c r="I5" s="84" t="n"/>
-      <c r="J5" s="84" t="n"/>
-      <c r="K5" s="84" t="n"/>
-      <c r="L5" s="84" t="n"/>
-      <c r="M5" s="84" t="n"/>
-      <c r="N5" s="84" t="n"/>
-      <c r="O5" s="84" t="n"/>
-      <c r="P5" s="84" t="n"/>
-      <c r="Q5" s="84" t="n"/>
-      <c r="R5" s="84" t="n"/>
-      <c r="S5" s="84" t="n"/>
-      <c r="T5" s="84" t="n"/>
-      <c r="U5" s="84" t="n"/>
-      <c r="V5" s="84" t="n"/>
-      <c r="W5" s="84" t="n"/>
-      <c r="X5" s="84" t="n"/>
-      <c r="Y5" s="84" t="n"/>
-      <c r="Z5" s="84" t="n"/>
-      <c r="AA5" s="84" t="n"/>
-      <c r="AB5" s="84" t="n"/>
+      <c r="B5" s="86" t="n"/>
+      <c r="C5" s="86" t="n"/>
+      <c r="D5" s="86" t="n"/>
+      <c r="E5" s="86" t="n"/>
+      <c r="F5" s="86" t="n"/>
+      <c r="G5" s="86" t="n"/>
+      <c r="H5" s="86" t="n"/>
+      <c r="I5" s="86" t="n"/>
+      <c r="J5" s="86" t="n"/>
+      <c r="K5" s="86" t="n"/>
+      <c r="L5" s="86" t="n"/>
+      <c r="M5" s="86" t="n"/>
+      <c r="N5" s="86" t="n"/>
+      <c r="O5" s="86" t="n"/>
+      <c r="P5" s="86" t="n"/>
+      <c r="Q5" s="86" t="n"/>
+      <c r="R5" s="86" t="n"/>
+      <c r="S5" s="86" t="n"/>
+      <c r="T5" s="86" t="n"/>
+      <c r="U5" s="86" t="n"/>
+      <c r="V5" s="86" t="n"/>
+      <c r="W5" s="86" t="n"/>
+      <c r="X5" s="86" t="n"/>
+      <c r="Y5" s="86" t="n"/>
+      <c r="Z5" s="86" t="n"/>
+      <c r="AA5" s="86" t="n"/>
+      <c r="AB5" s="87" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1" s="51">
       <c r="A6" s="85" t="inlineStr">
@@ -2822,33 +2830,33 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="B36" s="84" t="n"/>
-      <c r="C36" s="84" t="n"/>
-      <c r="D36" s="84" t="n"/>
-      <c r="E36" s="84" t="n"/>
-      <c r="F36" s="84" t="n"/>
-      <c r="G36" s="84" t="n"/>
-      <c r="H36" s="84" t="n"/>
-      <c r="I36" s="84" t="n"/>
-      <c r="J36" s="84" t="n"/>
-      <c r="K36" s="84" t="n"/>
-      <c r="L36" s="84" t="n"/>
-      <c r="M36" s="84" t="n"/>
-      <c r="N36" s="84" t="n"/>
-      <c r="O36" s="84" t="n"/>
-      <c r="P36" s="84" t="n"/>
-      <c r="Q36" s="84" t="n"/>
-      <c r="R36" s="84" t="n"/>
-      <c r="S36" s="84" t="n"/>
-      <c r="T36" s="84" t="n"/>
-      <c r="U36" s="84" t="n"/>
-      <c r="V36" s="84" t="n"/>
-      <c r="W36" s="84" t="n"/>
-      <c r="X36" s="84" t="n"/>
-      <c r="Y36" s="84" t="n"/>
-      <c r="Z36" s="84" t="n"/>
-      <c r="AA36" s="84" t="n"/>
-      <c r="AB36" s="84" t="n"/>
+      <c r="B36" s="86" t="n"/>
+      <c r="C36" s="86" t="n"/>
+      <c r="D36" s="86" t="n"/>
+      <c r="E36" s="86" t="n"/>
+      <c r="F36" s="86" t="n"/>
+      <c r="G36" s="86" t="n"/>
+      <c r="H36" s="86" t="n"/>
+      <c r="I36" s="86" t="n"/>
+      <c r="J36" s="86" t="n"/>
+      <c r="K36" s="86" t="n"/>
+      <c r="L36" s="86" t="n"/>
+      <c r="M36" s="86" t="n"/>
+      <c r="N36" s="86" t="n"/>
+      <c r="O36" s="86" t="n"/>
+      <c r="P36" s="86" t="n"/>
+      <c r="Q36" s="86" t="n"/>
+      <c r="R36" s="86" t="n"/>
+      <c r="S36" s="86" t="n"/>
+      <c r="T36" s="86" t="n"/>
+      <c r="U36" s="86" t="n"/>
+      <c r="V36" s="86" t="n"/>
+      <c r="W36" s="86" t="n"/>
+      <c r="X36" s="86" t="n"/>
+      <c r="Y36" s="86" t="n"/>
+      <c r="Z36" s="86" t="n"/>
+      <c r="AA36" s="86" t="n"/>
+      <c r="AB36" s="87" t="n"/>
     </row>
     <row r="37" ht="18" customHeight="1" s="51">
       <c r="A37" s="85" t="inlineStr">
@@ -3420,40 +3428,39 @@
       <c r="AA51" s="85" t="n"/>
       <c r="AB51" s="85" t="n"/>
     </row>
-    <row r="52"/>
     <row r="53">
       <c r="A53" s="84" t="inlineStr">
         <is>
           <t>Dropdown values: Acquire | Deepen | Create | ? (unscorable/blank)</t>
         </is>
       </c>
-      <c r="B53" s="84" t="n"/>
-      <c r="C53" s="84" t="n"/>
-      <c r="D53" s="84" t="n"/>
-      <c r="E53" s="84" t="n"/>
-      <c r="F53" s="84" t="n"/>
-      <c r="G53" s="84" t="n"/>
-      <c r="H53" s="84" t="n"/>
-      <c r="I53" s="84" t="n"/>
-      <c r="J53" s="84" t="n"/>
-      <c r="K53" s="84" t="n"/>
-      <c r="L53" s="84" t="n"/>
-      <c r="M53" s="84" t="n"/>
-      <c r="N53" s="84" t="n"/>
-      <c r="O53" s="84" t="n"/>
-      <c r="P53" s="84" t="n"/>
-      <c r="Q53" s="84" t="n"/>
-      <c r="R53" s="84" t="n"/>
-      <c r="S53" s="84" t="n"/>
-      <c r="T53" s="84" t="n"/>
-      <c r="U53" s="84" t="n"/>
-      <c r="V53" s="84" t="n"/>
-      <c r="W53" s="84" t="n"/>
-      <c r="X53" s="84" t="n"/>
-      <c r="Y53" s="84" t="n"/>
-      <c r="Z53" s="84" t="n"/>
-      <c r="AA53" s="84" t="n"/>
-      <c r="AB53" s="84" t="n"/>
+      <c r="B53" s="86" t="n"/>
+      <c r="C53" s="86" t="n"/>
+      <c r="D53" s="86" t="n"/>
+      <c r="E53" s="86" t="n"/>
+      <c r="F53" s="86" t="n"/>
+      <c r="G53" s="86" t="n"/>
+      <c r="H53" s="86" t="n"/>
+      <c r="I53" s="86" t="n"/>
+      <c r="J53" s="86" t="n"/>
+      <c r="K53" s="86" t="n"/>
+      <c r="L53" s="86" t="n"/>
+      <c r="M53" s="86" t="n"/>
+      <c r="N53" s="86" t="n"/>
+      <c r="O53" s="86" t="n"/>
+      <c r="P53" s="86" t="n"/>
+      <c r="Q53" s="86" t="n"/>
+      <c r="R53" s="86" t="n"/>
+      <c r="S53" s="86" t="n"/>
+      <c r="T53" s="86" t="n"/>
+      <c r="U53" s="86" t="n"/>
+      <c r="V53" s="86" t="n"/>
+      <c r="W53" s="86" t="n"/>
+      <c r="X53" s="86" t="n"/>
+      <c r="Y53" s="86" t="n"/>
+      <c r="Z53" s="86" t="n"/>
+      <c r="AA53" s="86" t="n"/>
+      <c r="AB53" s="87" t="n"/>
     </row>
     <row r="54" ht="40" customHeight="1" s="51">
       <c r="A54" s="85" t="inlineStr">
@@ -3462,124 +3469,148 @@
         </is>
       </c>
       <c r="B54" s="85" t="n"/>
-      <c r="C54" s="85" t="inlineStr">
-        <is>
-          <t>A1: Names variable(s) predicted to determine recommendability — based on intuition, any answer ok</t>
-        </is>
-      </c>
-      <c r="D54" s="85" t="inlineStr">
-        <is>
-          <t>A2: Names variable(s) based on data WITH graph/visualization evidence (not just intuition)</t>
-        </is>
-      </c>
-      <c r="E54" s="85" t="inlineStr">
-        <is>
-          <t>A3: Yes/No response AND references actual data to support the answer</t>
-        </is>
-      </c>
-      <c r="F54" s="85" t="inlineStr">
-        <is>
-          <t>A4: Justifies first-variable choice using data evidence (not general knowledge such as 'fat is unhealthy')</t>
-        </is>
-      </c>
-      <c r="G54" s="85" t="inlineStr">
-        <is>
-          <t>B1: Builds single-level tree with one variable, records EMIT accuracy result</t>
-        </is>
-      </c>
-      <c r="H54" s="85" t="inlineStr">
-        <is>
-          <t>B2: Builds second single-level tree with a different variable, records EMIT</t>
-        </is>
-      </c>
-      <c r="I54" s="85" t="inlineStr">
-        <is>
-          <t>B3: Builds third single-level tree with yet another variable, records EMIT</t>
-        </is>
-      </c>
-      <c r="J54" s="85" t="inlineStr">
-        <is>
-          <t>B4: Identifies best tree among B1-B3 AND lists criteria used for comparison</t>
-        </is>
-      </c>
-      <c r="K54" s="85" t="inlineStr">
-        <is>
-          <t>C1: Tries different threshold values for best variable from B; saves best with EMIT</t>
-        </is>
-      </c>
-      <c r="L54" s="85" t="inlineStr">
-        <is>
-          <t>C2: Explains how changing the threshold value affects decision tree performance</t>
-        </is>
-      </c>
-      <c r="M54" s="85" t="inlineStr">
-        <is>
-          <t>C3: Identifies best threshold and explains how that conclusion was reached</t>
-        </is>
-      </c>
-      <c r="N54" s="85" t="inlineStr">
-        <is>
-          <t>D1: Adds a second variable to create a two-level tree; saves with EMIT</t>
-        </is>
-      </c>
-      <c r="O54" s="85" t="inlineStr">
-        <is>
-          <t>D2: Explains whether and how the second variable improved classification</t>
-        </is>
-      </c>
-      <c r="P54" s="85" t="inlineStr">
-        <is>
-          <t>D3: States which variable combination produced the best result</t>
-        </is>
-      </c>
-      <c r="Q54" s="85" t="inlineStr">
-        <is>
-          <t>D4: Explains how they decided they had reached their best decision tree</t>
-        </is>
-      </c>
-      <c r="R54" s="85" t="inlineStr">
-        <is>
-          <t>E (intro): Records Sensitivity and MCR values from EMIT for the best tree</t>
-        </is>
-      </c>
-      <c r="S54" s="85" t="inlineStr">
-        <is>
-          <t>E1: Explains which metric matters more for this model's purpose and why</t>
-        </is>
-      </c>
-      <c r="T54" s="85" t="inlineStr">
-        <is>
-          <t>E2: Identifies whether the model made more false positives or false negatives</t>
-        </is>
-      </c>
-      <c r="U54" s="85" t="inlineStr">
-        <is>
-          <t>E3: Reflects on how software / they would decide when a tree is good enough</t>
-        </is>
-      </c>
-      <c r="V54" s="85" t="inlineStr">
-        <is>
-          <t>E4: Reflects on whether DTs can achieve zero error; gives a reasoned answer</t>
-        </is>
-      </c>
-      <c r="W54" s="85" t="inlineStr">
-        <is>
-          <t>F1: Applies best tree to test dataset, evaluates with EMIT, records result</t>
-        </is>
-      </c>
-      <c r="X54" s="85" t="inlineStr">
-        <is>
-          <t>F2: Compares test vs. training performance and explains any difference</t>
-        </is>
-      </c>
-      <c r="Y54" s="85" t="inlineStr">
-        <is>
-          <t>G1: Explains what the decision tree model 'learned' from the training data</t>
-        </is>
-      </c>
-      <c r="Z54" s="85" t="inlineStr">
-        <is>
-          <t>G2: Reflects on personal learning during the tree-building process</t>
+      <c r="C54" s="90" t="inlineStr">
+        <is>
+          <t>Prior belief
+Names variable(s) predicted to determine recommendability — based on intuition, any answer ok</t>
+        </is>
+      </c>
+      <c r="D54" s="90" t="inlineStr">
+        <is>
+          <t>Data-based exploration
+Names variable(s) based on data WITH graph/visualization evidence (not just intuition)</t>
+        </is>
+      </c>
+      <c r="E54" s="90" t="inlineStr">
+        <is>
+          <t>Meaningful difference found
+Yes/No response AND references actual data to support the answer</t>
+        </is>
+      </c>
+      <c r="F54" s="90" t="inlineStr">
+        <is>
+          <t>First variable justification
+Justifies first-variable choice using data evidence (not general knowledge such as 'fat is unhealthy')</t>
+        </is>
+      </c>
+      <c r="G54" s="90" t="inlineStr">
+        <is>
+          <t>Tree 1 — build + EMIT
+Builds single-level tree with one variable, records EMIT accuracy result</t>
+        </is>
+      </c>
+      <c r="H54" s="90" t="inlineStr">
+        <is>
+          <t>Tree 2 — build + EMIT
+Builds second single-level tree with a different variable, records EMIT</t>
+        </is>
+      </c>
+      <c r="I54" s="90" t="inlineStr">
+        <is>
+          <t>Tree 3 — build + EMIT
+Builds third single-level tree with yet another variable, records EMIT</t>
+        </is>
+      </c>
+      <c r="J54" s="90" t="inlineStr">
+        <is>
+          <t>Best tree + criteria
+Identifies best tree among B1-B3 AND lists criteria used for comparison</t>
+        </is>
+      </c>
+      <c r="K54" s="90" t="inlineStr">
+        <is>
+          <t>Threshold optimization
+Tries different threshold values for best variable from B; saves best with EMIT</t>
+        </is>
+      </c>
+      <c r="L54" s="90" t="inlineStr">
+        <is>
+          <t>Threshold effect
+Explains how changing the threshold value affects decision tree performance</t>
+        </is>
+      </c>
+      <c r="M54" s="90" t="inlineStr">
+        <is>
+          <t>Best threshold + reasoning
+Identifies best threshold and explains how that conclusion was reached</t>
+        </is>
+      </c>
+      <c r="N54" s="90" t="inlineStr">
+        <is>
+          <t>Two-level tree — build + EMIT
+Adds a second variable to create a two-level tree; saves with EMIT</t>
+        </is>
+      </c>
+      <c r="O54" s="90" t="inlineStr">
+        <is>
+          <t>Second level effect
+Explains whether and how the second variable improved classification</t>
+        </is>
+      </c>
+      <c r="P54" s="90" t="inlineStr">
+        <is>
+          <t>Best variable combination
+States which variable combination produced the best result</t>
+        </is>
+      </c>
+      <c r="Q54" s="90" t="inlineStr">
+        <is>
+          <t>Stopping criterion
+Explains how they decided they had reached their best decision tree</t>
+        </is>
+      </c>
+      <c r="R54" s="90" t="inlineStr">
+        <is>
+          <t>Metrics
+E (intro): Records Sensitivity and MCR values from EMIT for the best tree</t>
+        </is>
+      </c>
+      <c r="S54" s="90" t="inlineStr">
+        <is>
+          <t>Metric interpretation
+Explains which metric matters more for this model's purpose and why</t>
+        </is>
+      </c>
+      <c r="T54" s="90" t="inlineStr">
+        <is>
+          <t>Error type analysis
+Identifies whether the model made more false positives or false negatives</t>
+        </is>
+      </c>
+      <c r="U54" s="90" t="inlineStr">
+        <is>
+          <t>Good-enough criterion
+Reflects on how software / they would decide when a tree is good enough</t>
+        </is>
+      </c>
+      <c r="V54" s="90" t="inlineStr">
+        <is>
+          <t>Perfect classification
+Reflects on whether DTs can achieve zero error; gives a reasoned answer</t>
+        </is>
+      </c>
+      <c r="W54" s="90" t="inlineStr">
+        <is>
+          <t>Test set application
+Applies best tree to test dataset, evaluates with EMIT, records result</t>
+        </is>
+      </c>
+      <c r="X54" s="90" t="inlineStr">
+        <is>
+          <t>Train vs test comparison
+Compares test vs. training performance and explains any difference</t>
+        </is>
+      </c>
+      <c r="Y54" s="90" t="inlineStr">
+        <is>
+          <t>What the model learned
+Explains what the decision tree model 'learned' from the training data</t>
+        </is>
+      </c>
+      <c r="Z54" s="90" t="inlineStr">
+        <is>
+          <t>Personal reflection
+Reflects on personal learning during the tree-building process</t>
         </is>
       </c>
       <c r="AA54" s="85" t="inlineStr">
@@ -3735,78 +3766,67 @@
       <c r="C3" s="82" t="inlineStr">
         <is>
           <t>Blank 1
-Target Label
-Determining the final classification result (e.g., 'not recommendable')</t>
+Target Label</t>
         </is>
       </c>
       <c r="D3" s="82" t="inlineStr">
         <is>
           <t>Blank 2
-Data Object
-Recognizing the fundamental data entity or item (e.g., 'Hazelnut Wafer')</t>
+Data Object</t>
         </is>
       </c>
       <c r="E3" s="82" t="inlineStr">
         <is>
           <t>Blank 3
-Feature Name
-Identifying the name of the independent variable (e.g., 'Fat')</t>
+Feature Name</t>
         </is>
       </c>
       <c r="F3" s="82" t="inlineStr">
         <is>
           <t>Blank 4
-Feature Value
-Extracting the specific quantitative measurement for an attribute (e.g., '31.9 g')</t>
+Feature Value</t>
         </is>
       </c>
       <c r="G3" s="82" t="inlineStr">
         <is>
           <t>Blank 5
-Data Instance
-Comprehending that an item acts as a single row or data point in a dataset (e.g., 'Individual foods are called objects...')</t>
+Data Instance</t>
         </is>
       </c>
       <c r="H3" s="82" t="inlineStr">
         <is>
           <t>Blank 6
-Specific Object
-Mapping a concrete, real-world example to the concept of a data object (e.g., 'A hazelnut wafer is an object')</t>
+Specific Object</t>
         </is>
       </c>
       <c r="I3" s="82" t="inlineStr">
         <is>
           <t>Blank 7
-Feature Variable
-Understanding the structural attributes (columns) that describe the data (e.g., 'features are located in the left column')</t>
+Feature Variable</t>
         </is>
       </c>
       <c r="J3" s="82" t="inlineStr">
         <is>
           <t>Blank 8
-Feature Count
-Calculating the dimensionality or total number of variables in the dataset (e.g., 'there are 7 features')</t>
+Feature Count</t>
         </is>
       </c>
       <c r="K3" s="82" t="inlineStr">
         <is>
           <t>Blank 9
-Feature List
-Enumerating all the independent variables that can be extracted (e.g., 'Energy, Fat, Saturated Fat...')</t>
+Feature List</t>
         </is>
       </c>
       <c r="L3" s="82" t="inlineStr">
         <is>
           <t>Blank 10
-Instance Name
-Associating a specific data value (like 31.9 g) back to the specific object it belongs to (e.g., 'Hazelnut Wafer contains 31.9 g of fat')</t>
+Instance Name</t>
         </is>
       </c>
       <c r="M3" s="82" t="inlineStr">
         <is>
           <t>Blank 11
-Assigned Label
-Grasping that the target variable serves as the final decision or output for that specific item (e.g., 'given the note not recommendable as a label...')</t>
+Assigned Label</t>
         </is>
       </c>
       <c r="N3" s="82" t="inlineStr">
@@ -3833,20 +3853,20 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="B5" s="84" t="n"/>
-      <c r="C5" s="84" t="n"/>
-      <c r="D5" s="84" t="n"/>
-      <c r="E5" s="84" t="n"/>
-      <c r="F5" s="84" t="n"/>
-      <c r="G5" s="84" t="n"/>
-      <c r="H5" s="84" t="n"/>
-      <c r="I5" s="84" t="n"/>
-      <c r="J5" s="84" t="n"/>
-      <c r="K5" s="84" t="n"/>
-      <c r="L5" s="84" t="n"/>
-      <c r="M5" s="84" t="n"/>
-      <c r="N5" s="84" t="n"/>
-      <c r="O5" s="84" t="n"/>
+      <c r="B5" s="86" t="n"/>
+      <c r="C5" s="86" t="n"/>
+      <c r="D5" s="86" t="n"/>
+      <c r="E5" s="86" t="n"/>
+      <c r="F5" s="86" t="n"/>
+      <c r="G5" s="86" t="n"/>
+      <c r="H5" s="86" t="n"/>
+      <c r="I5" s="86" t="n"/>
+      <c r="J5" s="86" t="n"/>
+      <c r="K5" s="86" t="n"/>
+      <c r="L5" s="86" t="n"/>
+      <c r="M5" s="86" t="n"/>
+      <c r="N5" s="86" t="n"/>
+      <c r="O5" s="87" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1" s="51">
       <c r="A6" s="85" t="inlineStr">
@@ -4582,20 +4602,20 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="B36" s="84" t="n"/>
-      <c r="C36" s="84" t="n"/>
-      <c r="D36" s="84" t="n"/>
-      <c r="E36" s="84" t="n"/>
-      <c r="F36" s="84" t="n"/>
-      <c r="G36" s="84" t="n"/>
-      <c r="H36" s="84" t="n"/>
-      <c r="I36" s="84" t="n"/>
-      <c r="J36" s="84" t="n"/>
-      <c r="K36" s="84" t="n"/>
-      <c r="L36" s="84" t="n"/>
-      <c r="M36" s="84" t="n"/>
-      <c r="N36" s="84" t="n"/>
-      <c r="O36" s="84" t="n"/>
+      <c r="B36" s="86" t="n"/>
+      <c r="C36" s="86" t="n"/>
+      <c r="D36" s="86" t="n"/>
+      <c r="E36" s="86" t="n"/>
+      <c r="F36" s="86" t="n"/>
+      <c r="G36" s="86" t="n"/>
+      <c r="H36" s="86" t="n"/>
+      <c r="I36" s="86" t="n"/>
+      <c r="J36" s="86" t="n"/>
+      <c r="K36" s="86" t="n"/>
+      <c r="L36" s="86" t="n"/>
+      <c r="M36" s="86" t="n"/>
+      <c r="N36" s="86" t="n"/>
+      <c r="O36" s="87" t="n"/>
     </row>
     <row r="37" ht="18" customHeight="1" s="51">
       <c r="A37" s="85" t="inlineStr">
@@ -4972,27 +4992,26 @@
       <c r="N51" s="85" t="n"/>
       <c r="O51" s="85" t="n"/>
     </row>
-    <row r="52"/>
     <row r="53">
       <c r="A53" s="84" t="inlineStr">
         <is>
           <t>Dropdown values: Acquire | Deepen | Create | ? (unscorable/blank)</t>
         </is>
       </c>
-      <c r="B53" s="84" t="n"/>
-      <c r="C53" s="84" t="n"/>
-      <c r="D53" s="84" t="n"/>
-      <c r="E53" s="84" t="n"/>
-      <c r="F53" s="84" t="n"/>
-      <c r="G53" s="84" t="n"/>
-      <c r="H53" s="84" t="n"/>
-      <c r="I53" s="84" t="n"/>
-      <c r="J53" s="84" t="n"/>
-      <c r="K53" s="84" t="n"/>
-      <c r="L53" s="84" t="n"/>
-      <c r="M53" s="84" t="n"/>
-      <c r="N53" s="84" t="n"/>
-      <c r="O53" s="84" t="n"/>
+      <c r="B53" s="86" t="n"/>
+      <c r="C53" s="86" t="n"/>
+      <c r="D53" s="86" t="n"/>
+      <c r="E53" s="86" t="n"/>
+      <c r="F53" s="86" t="n"/>
+      <c r="G53" s="86" t="n"/>
+      <c r="H53" s="86" t="n"/>
+      <c r="I53" s="86" t="n"/>
+      <c r="J53" s="86" t="n"/>
+      <c r="K53" s="86" t="n"/>
+      <c r="L53" s="86" t="n"/>
+      <c r="M53" s="86" t="n"/>
+      <c r="N53" s="86" t="n"/>
+      <c r="O53" s="87" t="n"/>
     </row>
     <row r="54" ht="40" customHeight="1" s="51">
       <c r="A54" s="85" t="inlineStr">
@@ -5001,59 +5020,70 @@
         </is>
       </c>
       <c r="B54" s="85" t="n"/>
-      <c r="C54" s="85" t="inlineStr">
-        <is>
-          <t>Diagram arrow pointing to food card name -&gt; 'label' (etiket)</t>
-        </is>
-      </c>
-      <c r="D54" s="85" t="inlineStr">
-        <is>
-          <t>Diagram arrow pointing to 'Findikli Gofret' card -&gt; 'object' (nesne)</t>
-        </is>
-      </c>
-      <c r="E54" s="85" t="inlineStr">
-        <is>
-          <t>Diagram arrow pointing to left column of card -&gt; 'feature / variable / characteristic'</t>
-        </is>
-      </c>
-      <c r="F54" s="85" t="inlineStr">
-        <is>
-          <t>Diagram arrow pointing to a numeric cell -&gt; 'value of the feature / characteristic'</t>
-        </is>
-      </c>
-      <c r="G54" s="85" t="inlineStr">
-        <is>
-          <t>Cloze: 'Individual foods are called ___' -&gt; object (nesne)</t>
-        </is>
-      </c>
-      <c r="H54" s="85" t="inlineStr">
-        <is>
-          <t>Cloze: 'Hazelnut wafer is a ___' -&gt; object (nesne)</t>
-        </is>
-      </c>
-      <c r="I54" s="85" t="inlineStr">
-        <is>
-          <t>Cloze: left-column names are called '___ / characteristic / variable'</t>
-        </is>
-      </c>
-      <c r="J54" s="85" t="inlineStr">
-        <is>
-          <t>Cloze: 'How many features? ___' -&gt; 7 (yedi / seven)</t>
-        </is>
-      </c>
-      <c r="K54" s="85" t="inlineStr">
-        <is>
-          <t>Cloze: student writes all feature names: Energy, Fat, Saturated Fat, Carbohydrates, Sugar, Protein, Salt</t>
-        </is>
-      </c>
-      <c r="L54" s="85" t="inlineStr">
-        <is>
-          <t>Cloze: 'For example ___ contains 31.9g fat' -&gt; Hazelnut Wafer (Findikli Gofret)</t>
-        </is>
-      </c>
-      <c r="M54" s="85" t="inlineStr">
-        <is>
-          <t>Cloze: 'Hazelnut wafer has been given ___ as label' -&gt; not recommended (tavsiye edilemez)</t>
+      <c r="C54" s="90" t="inlineStr">
+        <is>
+          <t>Target Label
+Diagram arrow pointing to food card name → 'label' (etiket)</t>
+        </is>
+      </c>
+      <c r="D54" s="90" t="inlineStr">
+        <is>
+          <t>Data Object
+Diagram arrow pointing to 'Findikli Gofret' card → 'object' (nesne)</t>
+        </is>
+      </c>
+      <c r="E54" s="90" t="inlineStr">
+        <is>
+          <t>Feature Name
+Diagram arrow pointing to left column of card → 'feature / variable / characteristic'</t>
+        </is>
+      </c>
+      <c r="F54" s="90" t="inlineStr">
+        <is>
+          <t>Feature Value
+Diagram arrow pointing to a numeric cell → 'value of the feature / characteristic'</t>
+        </is>
+      </c>
+      <c r="G54" s="90" t="inlineStr">
+        <is>
+          <t>Data Instance
+Cloze: 'Individual foods are called ___' → object (nesne)</t>
+        </is>
+      </c>
+      <c r="H54" s="90" t="inlineStr">
+        <is>
+          <t>Specific Object
+Cloze: 'Hazelnut wafer is a ___' → object (nesne)</t>
+        </is>
+      </c>
+      <c r="I54" s="90" t="inlineStr">
+        <is>
+          <t>Feature Variable
+Cloze: left-column names are called '___ / characteristic / variable'</t>
+        </is>
+      </c>
+      <c r="J54" s="90" t="inlineStr">
+        <is>
+          <t>Feature Count
+Cloze: 'How many features? ___' → 7 (yedi / seven)</t>
+        </is>
+      </c>
+      <c r="K54" s="90" t="inlineStr">
+        <is>
+          <t>Feature List
+Cloze: student writes all feature names: Energy, Fat, Saturated Fat, Carbohydrates, Sugar, Protein, Salt</t>
+        </is>
+      </c>
+      <c r="L54" s="90" t="inlineStr">
+        <is>
+          <t>Instance Name
+Cloze: 'For example ___ contains 31.9g fat' → Hazelnut Wafer (Findikli Gofret)</t>
+        </is>
+      </c>
+      <c r="M54" s="90" t="inlineStr">
+        <is>
+          <t>Assigned Label
+Cloze: 'Hazelnut wafer has been given ___ as label' → not recommended (tavsiye edilemez)</t>
         </is>
       </c>
       <c r="N54" s="85" t="inlineStr">
@@ -6430,25 +6460,25 @@
       </c>
       <c r="C3" s="82" t="inlineStr">
         <is>
-          <t>Task 1
+          <t>Blank 1
 Circle 4 misclassified</t>
         </is>
       </c>
       <c r="D3" s="82" t="inlineStr">
         <is>
-          <t>Task 2
+          <t>Blank 2
 Better threshold position</t>
         </is>
       </c>
       <c r="E3" s="82" t="inlineStr">
         <is>
-          <t>Exercise 3
+          <t>Blank 3
 Pia correct?</t>
         </is>
       </c>
       <c r="F3" s="82" t="inlineStr">
         <is>
-          <t>Task 4
+          <t>Blank 4
 Best energy threshold</t>
         </is>
       </c>
@@ -6476,13 +6506,13 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="B5" s="84" t="n"/>
-      <c r="C5" s="84" t="n"/>
-      <c r="D5" s="84" t="n"/>
-      <c r="E5" s="84" t="n"/>
-      <c r="F5" s="84" t="n"/>
-      <c r="G5" s="84" t="n"/>
-      <c r="H5" s="84" t="n"/>
+      <c r="B5" s="86" t="n"/>
+      <c r="C5" s="86" t="n"/>
+      <c r="D5" s="86" t="n"/>
+      <c r="E5" s="86" t="n"/>
+      <c r="F5" s="86" t="n"/>
+      <c r="G5" s="86" t="n"/>
+      <c r="H5" s="87" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1" s="51">
       <c r="A6" s="85" t="inlineStr">
@@ -7015,13 +7045,13 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="B36" s="84" t="n"/>
-      <c r="C36" s="84" t="n"/>
-      <c r="D36" s="84" t="n"/>
-      <c r="E36" s="84" t="n"/>
-      <c r="F36" s="84" t="n"/>
-      <c r="G36" s="84" t="n"/>
-      <c r="H36" s="84" t="n"/>
+      <c r="B36" s="86" t="n"/>
+      <c r="C36" s="86" t="n"/>
+      <c r="D36" s="86" t="n"/>
+      <c r="E36" s="86" t="n"/>
+      <c r="F36" s="86" t="n"/>
+      <c r="G36" s="86" t="n"/>
+      <c r="H36" s="87" t="n"/>
     </row>
     <row r="37" ht="18" customHeight="1" s="51">
       <c r="A37" s="85" t="inlineStr">
@@ -7293,20 +7323,19 @@
       <c r="G51" s="85" t="n"/>
       <c r="H51" s="85" t="n"/>
     </row>
-    <row r="52"/>
     <row r="53">
       <c r="A53" s="84" t="inlineStr">
         <is>
           <t>Dropdown values: Acquire | Deepen | Create | ? (unscorable/blank)</t>
         </is>
       </c>
-      <c r="B53" s="84" t="n"/>
-      <c r="C53" s="84" t="n"/>
-      <c r="D53" s="84" t="n"/>
-      <c r="E53" s="84" t="n"/>
-      <c r="F53" s="84" t="n"/>
-      <c r="G53" s="84" t="n"/>
-      <c r="H53" s="84" t="n"/>
+      <c r="B53" s="86" t="n"/>
+      <c r="C53" s="86" t="n"/>
+      <c r="D53" s="86" t="n"/>
+      <c r="E53" s="86" t="n"/>
+      <c r="F53" s="86" t="n"/>
+      <c r="G53" s="86" t="n"/>
+      <c r="H53" s="87" t="n"/>
     </row>
     <row r="54" ht="40" customHeight="1" s="51">
       <c r="A54" s="85" t="inlineStr">
@@ -7315,24 +7344,28 @@
         </is>
       </c>
       <c r="B54" s="85" t="n"/>
-      <c r="C54" s="85" t="inlineStr">
-        <is>
-          <t>Task 1: Circles all 4 incorrectly classified food cards at Leo's threshold</t>
-        </is>
-      </c>
-      <c r="D54" s="85" t="inlineStr">
-        <is>
-          <t>Task 2: Places threshold between two adjacent distinct fat values; written justification present</t>
-        </is>
-      </c>
-      <c r="E54" s="85" t="inlineStr">
-        <is>
-          <t>Exercise 3: Explains why equal-valued items cannot be split (Pia is correct; equal values cannot be separated)</t>
-        </is>
-      </c>
-      <c r="F54" s="85" t="inlineStr">
-        <is>
-          <t>Task 4: Sorts cards, fills table, writes best energy threshold in final blank</t>
+      <c r="C54" s="90" t="inlineStr">
+        <is>
+          <t>Circle 4 misclassified
+Circles all 4 incorrectly classified food cards at Leo's threshold</t>
+        </is>
+      </c>
+      <c r="D54" s="90" t="inlineStr">
+        <is>
+          <t>Better threshold position
+Places threshold between two adjacent distinct fat values; written justification present</t>
+        </is>
+      </c>
+      <c r="E54" s="90" t="inlineStr">
+        <is>
+          <t>Pia correct?
+Explains why equal-valued items cannot be split (Pia is correct; equal values cannot be separated)</t>
+        </is>
+      </c>
+      <c r="F54" s="90" t="inlineStr">
+        <is>
+          <t>Best energy threshold
+Sorts cards, fills table, writes best energy threshold in final blank</t>
         </is>
       </c>
       <c r="G54" s="85" t="inlineStr">
@@ -7463,43 +7496,43 @@
       </c>
       <c r="C3" s="82" t="inlineStr">
         <is>
-          <t>Block 1
+          <t>Blank 1
 Variable + threshold</t>
         </is>
       </c>
       <c r="D3" s="82" t="inlineStr">
         <is>
-          <t>Block 1
+          <t>Blank 2
 Count consistency</t>
         </is>
       </c>
       <c r="E3" s="82" t="inlineStr">
         <is>
-          <t>Block 2
+          <t>Blank 3
 Variable + threshold</t>
         </is>
       </c>
       <c r="F3" s="82" t="inlineStr">
         <is>
-          <t>Block 2
+          <t>Blank 4
 Count consistency</t>
         </is>
       </c>
       <c r="G3" s="82" t="inlineStr">
         <is>
-          <t>Block 3
+          <t>Blank 5
 Variable + threshold</t>
         </is>
       </c>
       <c r="H3" s="82" t="inlineStr">
         <is>
-          <t>Block 3
+          <t>Blank 6
 Count consistency</t>
         </is>
       </c>
       <c r="I3" s="82" t="inlineStr">
         <is>
-          <t>Final blank
+          <t>Blank 7
 Chosen threshold</t>
         </is>
       </c>
@@ -7527,16 +7560,16 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="B5" s="84" t="n"/>
-      <c r="C5" s="84" t="n"/>
-      <c r="D5" s="84" t="n"/>
-      <c r="E5" s="84" t="n"/>
-      <c r="F5" s="84" t="n"/>
-      <c r="G5" s="84" t="n"/>
-      <c r="H5" s="84" t="n"/>
-      <c r="I5" s="84" t="n"/>
-      <c r="J5" s="84" t="n"/>
-      <c r="K5" s="84" t="n"/>
+      <c r="B5" s="86" t="n"/>
+      <c r="C5" s="86" t="n"/>
+      <c r="D5" s="86" t="n"/>
+      <c r="E5" s="86" t="n"/>
+      <c r="F5" s="86" t="n"/>
+      <c r="G5" s="86" t="n"/>
+      <c r="H5" s="86" t="n"/>
+      <c r="I5" s="86" t="n"/>
+      <c r="J5" s="86" t="n"/>
+      <c r="K5" s="87" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1" s="51">
       <c r="A6" s="85" t="inlineStr">
@@ -8156,16 +8189,16 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="B36" s="84" t="n"/>
-      <c r="C36" s="84" t="n"/>
-      <c r="D36" s="84" t="n"/>
-      <c r="E36" s="84" t="n"/>
-      <c r="F36" s="84" t="n"/>
-      <c r="G36" s="84" t="n"/>
-      <c r="H36" s="84" t="n"/>
-      <c r="I36" s="84" t="n"/>
-      <c r="J36" s="84" t="n"/>
-      <c r="K36" s="84" t="n"/>
+      <c r="B36" s="86" t="n"/>
+      <c r="C36" s="86" t="n"/>
+      <c r="D36" s="86" t="n"/>
+      <c r="E36" s="86" t="n"/>
+      <c r="F36" s="86" t="n"/>
+      <c r="G36" s="86" t="n"/>
+      <c r="H36" s="86" t="n"/>
+      <c r="I36" s="86" t="n"/>
+      <c r="J36" s="86" t="n"/>
+      <c r="K36" s="87" t="n"/>
     </row>
     <row r="37" ht="18" customHeight="1" s="51">
       <c r="A37" s="85" t="inlineStr">
@@ -8482,23 +8515,22 @@
       <c r="J51" s="85" t="n"/>
       <c r="K51" s="85" t="n"/>
     </row>
-    <row r="52"/>
     <row r="53">
       <c r="A53" s="84" t="inlineStr">
         <is>
           <t>Dropdown values: Acquire | Deepen | Create | ? (unscorable/blank)</t>
         </is>
       </c>
-      <c r="B53" s="84" t="n"/>
-      <c r="C53" s="84" t="n"/>
-      <c r="D53" s="84" t="n"/>
-      <c r="E53" s="84" t="n"/>
-      <c r="F53" s="84" t="n"/>
-      <c r="G53" s="84" t="n"/>
-      <c r="H53" s="84" t="n"/>
-      <c r="I53" s="84" t="n"/>
-      <c r="J53" s="84" t="n"/>
-      <c r="K53" s="84" t="n"/>
+      <c r="B53" s="86" t="n"/>
+      <c r="C53" s="86" t="n"/>
+      <c r="D53" s="86" t="n"/>
+      <c r="E53" s="86" t="n"/>
+      <c r="F53" s="86" t="n"/>
+      <c r="G53" s="86" t="n"/>
+      <c r="H53" s="86" t="n"/>
+      <c r="I53" s="86" t="n"/>
+      <c r="J53" s="86" t="n"/>
+      <c r="K53" s="87" t="n"/>
     </row>
     <row r="54" ht="40" customHeight="1" s="51">
       <c r="A54" s="85" t="inlineStr">
@@ -8507,39 +8539,46 @@
         </is>
       </c>
       <c r="B54" s="85" t="n"/>
-      <c r="C54" s="85" t="inlineStr">
-        <is>
-          <t>Block 1: Names a valid dataset variable and fills in threshold value(s)</t>
-        </is>
-      </c>
-      <c r="D54" s="85" t="inlineStr">
-        <is>
-          <t>Block 1: Recommended + not-recommended counts sum correctly to total number of cards</t>
-        </is>
-      </c>
-      <c r="E54" s="85" t="inlineStr">
-        <is>
-          <t>Block 2: Names a different valid variable and fills in threshold value(s)</t>
-        </is>
-      </c>
-      <c r="F54" s="85" t="inlineStr">
-        <is>
-          <t>Block 2: Counts sum correctly</t>
-        </is>
-      </c>
-      <c r="G54" s="85" t="inlineStr">
-        <is>
-          <t>Block 3: Names a third valid variable and fills in threshold value(s)</t>
-        </is>
-      </c>
-      <c r="H54" s="85" t="inlineStr">
-        <is>
-          <t>Block 3: Counts sum correctly</t>
-        </is>
-      </c>
-      <c r="I54" s="85" t="inlineStr">
-        <is>
-          <t>Final line: states which variable and threshold they selected and records it</t>
+      <c r="C54" s="90" t="inlineStr">
+        <is>
+          <t>Variable + threshold
+Names a valid dataset variable and fills in threshold value(s)</t>
+        </is>
+      </c>
+      <c r="D54" s="90" t="inlineStr">
+        <is>
+          <t>Count consistency
+Recommended + not-recommended counts sum correctly to total number of cards</t>
+        </is>
+      </c>
+      <c r="E54" s="90" t="inlineStr">
+        <is>
+          <t>Variable + threshold
+Names a different valid variable and fills in threshold value(s)</t>
+        </is>
+      </c>
+      <c r="F54" s="90" t="inlineStr">
+        <is>
+          <t>Count consistency
+Counts sum correctly</t>
+        </is>
+      </c>
+      <c r="G54" s="90" t="inlineStr">
+        <is>
+          <t>Variable + threshold
+Names a third valid variable and fills in threshold value(s)</t>
+        </is>
+      </c>
+      <c r="H54" s="90" t="inlineStr">
+        <is>
+          <t>Count consistency
+Counts sum correctly</t>
+        </is>
+      </c>
+      <c r="I54" s="90" t="inlineStr">
+        <is>
+          <t>Chosen threshold
+Final line: states which variable and threshold they selected and records it</t>
         </is>
       </c>
       <c r="J54" s="85" t="inlineStr">
@@ -8670,43 +8709,43 @@
       </c>
       <c r="C3" s="82" t="inlineStr">
         <is>
-          <t>Root node
+          <t>Blank 1
 Variable</t>
         </is>
       </c>
       <c r="D3" s="82" t="inlineStr">
         <is>
-          <t>Branch labels
+          <t>Blank 2
 &lt;= and &gt;</t>
         </is>
       </c>
       <c r="E3" s="82" t="inlineStr">
         <is>
-          <t>Left leaf
+          <t>Blank 3
 Classification</t>
         </is>
       </c>
       <c r="F3" s="82" t="inlineStr">
         <is>
-          <t>Left leaf
+          <t>Blank 4
 Counts</t>
         </is>
       </c>
       <c r="G3" s="82" t="inlineStr">
         <is>
-          <t>Right leaf
+          <t>Blank 5
 Classification</t>
         </is>
       </c>
       <c r="H3" s="82" t="inlineStr">
         <is>
-          <t>Right leaf
+          <t>Blank 6
 Counts</t>
         </is>
       </c>
       <c r="I3" s="82" t="inlineStr">
         <is>
-          <t>2nd level node
+          <t>Blank 7
 Variable (if present)</t>
         </is>
       </c>
@@ -8734,16 +8773,16 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="B5" s="84" t="n"/>
-      <c r="C5" s="84" t="n"/>
-      <c r="D5" s="84" t="n"/>
-      <c r="E5" s="84" t="n"/>
-      <c r="F5" s="84" t="n"/>
-      <c r="G5" s="84" t="n"/>
-      <c r="H5" s="84" t="n"/>
-      <c r="I5" s="84" t="n"/>
-      <c r="J5" s="84" t="n"/>
-      <c r="K5" s="84" t="n"/>
+      <c r="B5" s="86" t="n"/>
+      <c r="C5" s="86" t="n"/>
+      <c r="D5" s="86" t="n"/>
+      <c r="E5" s="86" t="n"/>
+      <c r="F5" s="86" t="n"/>
+      <c r="G5" s="86" t="n"/>
+      <c r="H5" s="86" t="n"/>
+      <c r="I5" s="86" t="n"/>
+      <c r="J5" s="86" t="n"/>
+      <c r="K5" s="87" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1" s="51">
       <c r="A6" s="85" t="inlineStr">
@@ -9363,16 +9402,16 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="B36" s="84" t="n"/>
-      <c r="C36" s="84" t="n"/>
-      <c r="D36" s="84" t="n"/>
-      <c r="E36" s="84" t="n"/>
-      <c r="F36" s="84" t="n"/>
-      <c r="G36" s="84" t="n"/>
-      <c r="H36" s="84" t="n"/>
-      <c r="I36" s="84" t="n"/>
-      <c r="J36" s="84" t="n"/>
-      <c r="K36" s="84" t="n"/>
+      <c r="B36" s="86" t="n"/>
+      <c r="C36" s="86" t="n"/>
+      <c r="D36" s="86" t="n"/>
+      <c r="E36" s="86" t="n"/>
+      <c r="F36" s="86" t="n"/>
+      <c r="G36" s="86" t="n"/>
+      <c r="H36" s="86" t="n"/>
+      <c r="I36" s="86" t="n"/>
+      <c r="J36" s="86" t="n"/>
+      <c r="K36" s="87" t="n"/>
     </row>
     <row r="37" ht="18" customHeight="1" s="51">
       <c r="A37" s="85" t="inlineStr">
@@ -9689,23 +9728,22 @@
       <c r="J51" s="85" t="n"/>
       <c r="K51" s="85" t="n"/>
     </row>
-    <row r="52"/>
     <row r="53">
       <c r="A53" s="84" t="inlineStr">
         <is>
           <t>Dropdown values: Acquire | Deepen | Create | ? (unscorable/blank)</t>
         </is>
       </c>
-      <c r="B53" s="84" t="n"/>
-      <c r="C53" s="84" t="n"/>
-      <c r="D53" s="84" t="n"/>
-      <c r="E53" s="84" t="n"/>
-      <c r="F53" s="84" t="n"/>
-      <c r="G53" s="84" t="n"/>
-      <c r="H53" s="84" t="n"/>
-      <c r="I53" s="84" t="n"/>
-      <c r="J53" s="84" t="n"/>
-      <c r="K53" s="84" t="n"/>
+      <c r="B53" s="86" t="n"/>
+      <c r="C53" s="86" t="n"/>
+      <c r="D53" s="86" t="n"/>
+      <c r="E53" s="86" t="n"/>
+      <c r="F53" s="86" t="n"/>
+      <c r="G53" s="86" t="n"/>
+      <c r="H53" s="86" t="n"/>
+      <c r="I53" s="86" t="n"/>
+      <c r="J53" s="86" t="n"/>
+      <c r="K53" s="87" t="n"/>
     </row>
     <row r="54" ht="40" customHeight="1" s="51">
       <c r="A54" s="85" t="inlineStr">
@@ -9714,39 +9752,46 @@
         </is>
       </c>
       <c r="B54" s="85" t="n"/>
-      <c r="C54" s="85" t="inlineStr">
-        <is>
-          <t>Root node blank: names a variable for the first split</t>
-        </is>
-      </c>
-      <c r="D54" s="85" t="inlineStr">
-        <is>
-          <t>Branch labels: writes &lt;= and &gt; with threshold values on both branches</t>
-        </is>
-      </c>
-      <c r="E54" s="85" t="inlineStr">
-        <is>
-          <t>Left leaf: correct classification label (recommended / not recommended)</t>
-        </is>
-      </c>
-      <c r="F54" s="85" t="inlineStr">
-        <is>
-          <t>Left leaf: correct counts in brackets [recommended] [not-recommended]</t>
-        </is>
-      </c>
-      <c r="G54" s="85" t="inlineStr">
-        <is>
-          <t>Right leaf: correct classification label</t>
-        </is>
-      </c>
-      <c r="H54" s="85" t="inlineStr">
-        <is>
-          <t>Right leaf: correct counts in brackets</t>
-        </is>
-      </c>
-      <c r="I54" s="85" t="inlineStr">
-        <is>
-          <t>Second-level node: names a valid variable for further split (score if present)</t>
+      <c r="C54" s="90" t="inlineStr">
+        <is>
+          <t>Variable
+Root node blank: names a variable for the first split</t>
+        </is>
+      </c>
+      <c r="D54" s="90" t="inlineStr">
+        <is>
+          <t>&lt;= and &gt;
+Branch labels: writes &lt;= and &gt; with threshold values on both branches</t>
+        </is>
+      </c>
+      <c r="E54" s="90" t="inlineStr">
+        <is>
+          <t>Classification
+Left leaf: correct classification label (recommended / not recommended)</t>
+        </is>
+      </c>
+      <c r="F54" s="90" t="inlineStr">
+        <is>
+          <t>Counts
+Left leaf: correct counts in brackets [recommended] [not-recommended]</t>
+        </is>
+      </c>
+      <c r="G54" s="90" t="inlineStr">
+        <is>
+          <t>Classification
+Right leaf: correct classification label</t>
+        </is>
+      </c>
+      <c r="H54" s="90" t="inlineStr">
+        <is>
+          <t>Counts
+Right leaf: correct counts in brackets</t>
+        </is>
+      </c>
+      <c r="I54" s="90" t="inlineStr">
+        <is>
+          <t>Variable (if present)
+Second-level node: names a valid variable for further split (score if present)</t>
         </is>
       </c>
       <c r="J54" s="85" t="inlineStr">
@@ -9877,43 +9922,43 @@
       </c>
       <c r="C3" s="82" t="inlineStr">
         <is>
-          <t>Page 1
+          <t>Blank 1
 Path A match</t>
         </is>
       </c>
       <c r="D3" s="82" t="inlineStr">
         <is>
-          <t>Page 1
+          <t>Blank 2
 Path B match</t>
         </is>
       </c>
       <c r="E3" s="82" t="inlineStr">
         <is>
-          <t>Page 1
+          <t>Blank 3
 Path C match</t>
         </is>
       </c>
       <c r="F3" s="82" t="inlineStr">
         <is>
-          <t>Page 2
+          <t>Blank 4
 Path count</t>
         </is>
       </c>
       <c r="G3" s="82" t="inlineStr">
         <is>
-          <t>Page 2
+          <t>Blank 5
 Rule 1</t>
         </is>
       </c>
       <c r="H3" s="82" t="inlineStr">
         <is>
-          <t>Page 2
+          <t>Blank 6
 Rule 2</t>
         </is>
       </c>
       <c r="I3" s="82" t="inlineStr">
         <is>
-          <t>Page 2
+          <t>Blank 7
 Rules 3-6</t>
         </is>
       </c>
@@ -9941,16 +9986,16 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="B5" s="84" t="n"/>
-      <c r="C5" s="84" t="n"/>
-      <c r="D5" s="84" t="n"/>
-      <c r="E5" s="84" t="n"/>
-      <c r="F5" s="84" t="n"/>
-      <c r="G5" s="84" t="n"/>
-      <c r="H5" s="84" t="n"/>
-      <c r="I5" s="84" t="n"/>
-      <c r="J5" s="84" t="n"/>
-      <c r="K5" s="84" t="n"/>
+      <c r="B5" s="86" t="n"/>
+      <c r="C5" s="86" t="n"/>
+      <c r="D5" s="86" t="n"/>
+      <c r="E5" s="86" t="n"/>
+      <c r="F5" s="86" t="n"/>
+      <c r="G5" s="86" t="n"/>
+      <c r="H5" s="86" t="n"/>
+      <c r="I5" s="86" t="n"/>
+      <c r="J5" s="86" t="n"/>
+      <c r="K5" s="87" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1" s="51">
       <c r="A6" s="85" t="inlineStr">
@@ -10570,16 +10615,16 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="B36" s="84" t="n"/>
-      <c r="C36" s="84" t="n"/>
-      <c r="D36" s="84" t="n"/>
-      <c r="E36" s="84" t="n"/>
-      <c r="F36" s="84" t="n"/>
-      <c r="G36" s="84" t="n"/>
-      <c r="H36" s="84" t="n"/>
-      <c r="I36" s="84" t="n"/>
-      <c r="J36" s="84" t="n"/>
-      <c r="K36" s="84" t="n"/>
+      <c r="B36" s="86" t="n"/>
+      <c r="C36" s="86" t="n"/>
+      <c r="D36" s="86" t="n"/>
+      <c r="E36" s="86" t="n"/>
+      <c r="F36" s="86" t="n"/>
+      <c r="G36" s="86" t="n"/>
+      <c r="H36" s="86" t="n"/>
+      <c r="I36" s="86" t="n"/>
+      <c r="J36" s="86" t="n"/>
+      <c r="K36" s="87" t="n"/>
     </row>
     <row r="37" ht="18" customHeight="1" s="51">
       <c r="A37" s="85" t="inlineStr">
@@ -10896,23 +10941,22 @@
       <c r="J51" s="85" t="n"/>
       <c r="K51" s="85" t="n"/>
     </row>
-    <row r="52"/>
     <row r="53">
       <c r="A53" s="84" t="inlineStr">
         <is>
           <t>Dropdown values: Acquire | Deepen | Create | ? (unscorable/blank)</t>
         </is>
       </c>
-      <c r="B53" s="84" t="n"/>
-      <c r="C53" s="84" t="n"/>
-      <c r="D53" s="84" t="n"/>
-      <c r="E53" s="84" t="n"/>
-      <c r="F53" s="84" t="n"/>
-      <c r="G53" s="84" t="n"/>
-      <c r="H53" s="84" t="n"/>
-      <c r="I53" s="84" t="n"/>
-      <c r="J53" s="84" t="n"/>
-      <c r="K53" s="84" t="n"/>
+      <c r="B53" s="86" t="n"/>
+      <c r="C53" s="86" t="n"/>
+      <c r="D53" s="86" t="n"/>
+      <c r="E53" s="86" t="n"/>
+      <c r="F53" s="86" t="n"/>
+      <c r="G53" s="86" t="n"/>
+      <c r="H53" s="86" t="n"/>
+      <c r="I53" s="86" t="n"/>
+      <c r="J53" s="86" t="n"/>
+      <c r="K53" s="87" t="n"/>
     </row>
     <row r="54" ht="40" customHeight="1" s="51">
       <c r="A54" s="85" t="inlineStr">
@@ -10921,39 +10965,46 @@
         </is>
       </c>
       <c r="B54" s="85" t="n"/>
-      <c r="C54" s="85" t="inlineStr">
-        <is>
-          <t>Page 1 matching: assigns correct rule to Path A (energy &lt; 180 kcal -&gt; recommended)</t>
-        </is>
-      </c>
-      <c r="D54" s="85" t="inlineStr">
-        <is>
-          <t>Page 1 matching: assigns correct rule to Path B (energy &gt;= 180 AND protein &lt; 7.7 -&gt; not recommended)</t>
-        </is>
-      </c>
-      <c r="E54" s="85" t="inlineStr">
-        <is>
-          <t>Page 1 matching: assigns correct rule to Path C (energy &gt;= 180 AND protein &gt;= 7.7 -&gt; recommended)</t>
-        </is>
-      </c>
-      <c r="F54" s="85" t="inlineStr">
-        <is>
-          <t>Page 2 blank: 'My tree contains ___ paths' — states correct number of paths</t>
-        </is>
-      </c>
-      <c r="G54" s="85" t="inlineStr">
-        <is>
-          <t>Page 2 Rule 1: writes a complete if-then rule logically consistent with their WS6 tree</t>
-        </is>
-      </c>
-      <c r="H54" s="85" t="inlineStr">
-        <is>
-          <t>Page 2 Rule 2: second rule consistent with tree</t>
-        </is>
-      </c>
-      <c r="I54" s="85" t="inlineStr">
-        <is>
-          <t>Page 2 Rules 3-6: additional rules present and consistent (score if all paths covered)</t>
+      <c r="C54" s="90" t="inlineStr">
+        <is>
+          <t>Path A match
+Page 1 matching: assigns correct rule to Path A (energy &lt; 180 kcal -&gt; recommended)</t>
+        </is>
+      </c>
+      <c r="D54" s="90" t="inlineStr">
+        <is>
+          <t>Path B match
+Page 1 matching: assigns correct rule to Path B (energy &gt;= 180 AND protein &lt; 7.7 -&gt; not recommended)</t>
+        </is>
+      </c>
+      <c r="E54" s="90" t="inlineStr">
+        <is>
+          <t>Path C match
+Page 1 matching: assigns correct rule to Path C (energy &gt;= 180 AND protein &gt;= 7.7 -&gt; recommended)</t>
+        </is>
+      </c>
+      <c r="F54" s="90" t="inlineStr">
+        <is>
+          <t>Path count
+Page 2 blank: 'My tree contains ___ paths' — states correct number of paths</t>
+        </is>
+      </c>
+      <c r="G54" s="90" t="inlineStr">
+        <is>
+          <t>Rule 1
+Page 2 Rule 1: writes a complete if-then rule logically consistent with their WS6 tree</t>
+        </is>
+      </c>
+      <c r="H54" s="90" t="inlineStr">
+        <is>
+          <t>Rule 2
+Page 2 Rule 2: second rule consistent with tree</t>
+        </is>
+      </c>
+      <c r="I54" s="90" t="inlineStr">
+        <is>
+          <t>Rules 3-6
+Page 2 Rules 3-6: additional rules present and consistent (score if all paths covered)</t>
         </is>
       </c>
       <c r="J54" s="85" t="inlineStr">
@@ -11060,19 +11111,19 @@
       </c>
       <c r="C3" s="82" t="inlineStr">
         <is>
-          <t>Table
+          <t>Blank 1
 Misclassification counts</t>
         </is>
       </c>
       <c r="D3" s="82" t="inlineStr">
         <is>
-          <t>Final blank
+          <t>Blank 2
 Optimum threshold</t>
         </is>
       </c>
       <c r="E3" s="82" t="inlineStr">
         <is>
-          <t>Reasoning
+          <t>Blank 3
 Why optimum</t>
         </is>
       </c>
@@ -11100,12 +11151,12 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="B5" s="84" t="n"/>
-      <c r="C5" s="84" t="n"/>
-      <c r="D5" s="84" t="n"/>
-      <c r="E5" s="84" t="n"/>
-      <c r="F5" s="84" t="n"/>
-      <c r="G5" s="84" t="n"/>
+      <c r="B5" s="86" t="n"/>
+      <c r="C5" s="86" t="n"/>
+      <c r="D5" s="86" t="n"/>
+      <c r="E5" s="86" t="n"/>
+      <c r="F5" s="86" t="n"/>
+      <c r="G5" s="87" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1" s="51">
       <c r="A6" s="85" t="inlineStr">
@@ -11609,12 +11660,12 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="B36" s="84" t="n"/>
-      <c r="C36" s="84" t="n"/>
-      <c r="D36" s="84" t="n"/>
-      <c r="E36" s="84" t="n"/>
-      <c r="F36" s="84" t="n"/>
-      <c r="G36" s="84" t="n"/>
+      <c r="B36" s="86" t="n"/>
+      <c r="C36" s="86" t="n"/>
+      <c r="D36" s="86" t="n"/>
+      <c r="E36" s="86" t="n"/>
+      <c r="F36" s="86" t="n"/>
+      <c r="G36" s="87" t="n"/>
     </row>
     <row r="37" ht="18" customHeight="1" s="51">
       <c r="A37" s="85" t="inlineStr">
@@ -11871,19 +11922,18 @@
       <c r="F51" s="85" t="n"/>
       <c r="G51" s="85" t="n"/>
     </row>
-    <row r="52"/>
     <row r="53">
       <c r="A53" s="84" t="inlineStr">
         <is>
           <t>Dropdown values: Acquire | Deepen | Create | ? (unscorable/blank)</t>
         </is>
       </c>
-      <c r="B53" s="84" t="n"/>
-      <c r="C53" s="84" t="n"/>
-      <c r="D53" s="84" t="n"/>
-      <c r="E53" s="84" t="n"/>
-      <c r="F53" s="84" t="n"/>
-      <c r="G53" s="84" t="n"/>
+      <c r="B53" s="86" t="n"/>
+      <c r="C53" s="86" t="n"/>
+      <c r="D53" s="86" t="n"/>
+      <c r="E53" s="86" t="n"/>
+      <c r="F53" s="86" t="n"/>
+      <c r="G53" s="87" t="n"/>
     </row>
     <row r="54" ht="40" customHeight="1" s="51">
       <c r="A54" s="85" t="inlineStr">
@@ -11892,19 +11942,22 @@
         </is>
       </c>
       <c r="B54" s="85" t="n"/>
-      <c r="C54" s="85" t="inlineStr">
-        <is>
-          <t>Table: correctly counts misclassifications for each of the 7 candidate thresholds</t>
-        </is>
-      </c>
-      <c r="D54" s="85" t="inlineStr">
-        <is>
-          <t>Final blank: 'The optimum threshold is: ___' — selects threshold with fewest errors</t>
-        </is>
-      </c>
-      <c r="E54" s="85" t="inlineStr">
-        <is>
-          <t>Written justification: explains why this threshold minimizes error (score if present)</t>
+      <c r="C54" s="90" t="inlineStr">
+        <is>
+          <t>Misclassification counts
+Table: correctly counts misclassifications for each of the 7 candidate thresholds</t>
+        </is>
+      </c>
+      <c r="D54" s="90" t="inlineStr">
+        <is>
+          <t>Optimum threshold
+Final blank: 'The optimum threshold is: ___' — selects threshold with fewest errors</t>
+        </is>
+      </c>
+      <c r="E54" s="90" t="inlineStr">
+        <is>
+          <t>Why optimum
+Written justification: explains why this threshold minimizes error (score if present)</t>
         </is>
       </c>
       <c r="F54" s="85" t="inlineStr">
@@ -12035,43 +12088,43 @@
       </c>
       <c r="C3" s="82" t="inlineStr">
         <is>
-          <t>Q4
+          <t>Blank 1
 Can explain DT</t>
         </is>
       </c>
       <c r="D3" s="82" t="inlineStr">
         <is>
-          <t>Q8a
+          <t>Blank 2
 Classify strawberry</t>
         </is>
       </c>
       <c r="E3" s="82" t="inlineStr">
         <is>
-          <t>Q8b
+          <t>Blank 3
 Decision rule</t>
         </is>
       </c>
       <c r="F3" s="82" t="inlineStr">
         <is>
-          <t>Q9
+          <t>Blank 4
 What is data</t>
         </is>
       </c>
       <c r="G3" s="82" t="inlineStr">
         <is>
-          <t>Q10
+          <t>Blank 5
 DT capabilities</t>
         </is>
       </c>
       <c r="H3" s="82" t="inlineStr">
         <is>
-          <t>Q11
+          <t>Blank 6
 Step ordering</t>
         </is>
       </c>
       <c r="I3" s="82" t="inlineStr">
         <is>
-          <t>Q12
+          <t>Blank 7
 Why is DT AI</t>
         </is>
       </c>
@@ -12099,16 +12152,16 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="B5" s="84" t="n"/>
-      <c r="C5" s="84" t="n"/>
-      <c r="D5" s="84" t="n"/>
-      <c r="E5" s="84" t="n"/>
-      <c r="F5" s="84" t="n"/>
-      <c r="G5" s="84" t="n"/>
-      <c r="H5" s="84" t="n"/>
-      <c r="I5" s="84" t="n"/>
-      <c r="J5" s="84" t="n"/>
-      <c r="K5" s="84" t="n"/>
+      <c r="B5" s="86" t="n"/>
+      <c r="C5" s="86" t="n"/>
+      <c r="D5" s="86" t="n"/>
+      <c r="E5" s="86" t="n"/>
+      <c r="F5" s="86" t="n"/>
+      <c r="G5" s="86" t="n"/>
+      <c r="H5" s="86" t="n"/>
+      <c r="I5" s="86" t="n"/>
+      <c r="J5" s="86" t="n"/>
+      <c r="K5" s="87" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1" s="51">
       <c r="A6" s="85" t="inlineStr">
@@ -12728,16 +12781,16 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="B36" s="84" t="n"/>
-      <c r="C36" s="84" t="n"/>
-      <c r="D36" s="84" t="n"/>
-      <c r="E36" s="84" t="n"/>
-      <c r="F36" s="84" t="n"/>
-      <c r="G36" s="84" t="n"/>
-      <c r="H36" s="84" t="n"/>
-      <c r="I36" s="84" t="n"/>
-      <c r="J36" s="84" t="n"/>
-      <c r="K36" s="84" t="n"/>
+      <c r="B36" s="86" t="n"/>
+      <c r="C36" s="86" t="n"/>
+      <c r="D36" s="86" t="n"/>
+      <c r="E36" s="86" t="n"/>
+      <c r="F36" s="86" t="n"/>
+      <c r="G36" s="86" t="n"/>
+      <c r="H36" s="86" t="n"/>
+      <c r="I36" s="86" t="n"/>
+      <c r="J36" s="86" t="n"/>
+      <c r="K36" s="87" t="n"/>
     </row>
     <row r="37" ht="18" customHeight="1" s="51">
       <c r="A37" s="85" t="inlineStr">
@@ -13054,23 +13107,22 @@
       <c r="J51" s="85" t="n"/>
       <c r="K51" s="85" t="n"/>
     </row>
-    <row r="52"/>
     <row r="53">
       <c r="A53" s="84" t="inlineStr">
         <is>
           <t>Dropdown values: Acquire | Deepen | Create | ? (unscorable/blank)</t>
         </is>
       </c>
-      <c r="B53" s="84" t="n"/>
-      <c r="C53" s="84" t="n"/>
-      <c r="D53" s="84" t="n"/>
-      <c r="E53" s="84" t="n"/>
-      <c r="F53" s="84" t="n"/>
-      <c r="G53" s="84" t="n"/>
-      <c r="H53" s="84" t="n"/>
-      <c r="I53" s="84" t="n"/>
-      <c r="J53" s="84" t="n"/>
-      <c r="K53" s="84" t="n"/>
+      <c r="B53" s="86" t="n"/>
+      <c r="C53" s="86" t="n"/>
+      <c r="D53" s="86" t="n"/>
+      <c r="E53" s="86" t="n"/>
+      <c r="F53" s="86" t="n"/>
+      <c r="G53" s="86" t="n"/>
+      <c r="H53" s="86" t="n"/>
+      <c r="I53" s="86" t="n"/>
+      <c r="J53" s="86" t="n"/>
+      <c r="K53" s="87" t="n"/>
     </row>
     <row r="54" ht="40" customHeight="1" s="51">
       <c r="A54" s="85" t="inlineStr">
@@ -13079,39 +13131,46 @@
         </is>
       </c>
       <c r="B54" s="85" t="n"/>
-      <c r="C54" s="85" t="inlineStr">
-        <is>
-          <t>Q4 (yes/no): Can you explain how a decision tree works? Score as Acquire if 'Yes'</t>
-        </is>
-      </c>
-      <c r="D54" s="85" t="inlineStr">
-        <is>
-          <t>Q8a: Uses the given decision tree to classify strawberries correctly</t>
-        </is>
-      </c>
-      <c r="E54" s="85" t="inlineStr">
-        <is>
-          <t>Q8b: Writes correct decision rule for strawberry classification (blank: ___ because ___)</t>
-        </is>
-      </c>
-      <c r="F54" s="85" t="inlineStr">
-        <is>
-          <t>Q9: Open-ended (6 lines) — explains what data is and why we need it</t>
-        </is>
-      </c>
-      <c r="G54" s="85" t="inlineStr">
-        <is>
-          <t>Q10: Multi-select T/F table — marks correct statements about what DTs can do</t>
-        </is>
-      </c>
-      <c r="H54" s="85" t="inlineStr">
-        <is>
-          <t>Q11: Orders the 4 steps for building a decision rule correctly (1-4)</t>
-        </is>
-      </c>
-      <c r="I54" s="85" t="inlineStr">
-        <is>
-          <t>Q12: Multi-select T/F table — marks correct reasons why a DT is considered AI</t>
+      <c r="C54" s="90" t="inlineStr">
+        <is>
+          <t>Can explain DT
+Q4 (yes/no): Can you explain how a decision tree works? Score as Acquire if 'Yes'</t>
+        </is>
+      </c>
+      <c r="D54" s="90" t="inlineStr">
+        <is>
+          <t>Classify strawberry
+Uses the given decision tree to classify strawberries correctly</t>
+        </is>
+      </c>
+      <c r="E54" s="90" t="inlineStr">
+        <is>
+          <t>Decision rule
+Writes correct decision rule for strawberry classification (blank: ___ because ___)</t>
+        </is>
+      </c>
+      <c r="F54" s="90" t="inlineStr">
+        <is>
+          <t>What is data
+Open-ended (6 lines) — explains what data is and why we need it</t>
+        </is>
+      </c>
+      <c r="G54" s="90" t="inlineStr">
+        <is>
+          <t>DT capabilities
+Multi-select T/F table — marks correct statements about what DTs can do</t>
+        </is>
+      </c>
+      <c r="H54" s="90" t="inlineStr">
+        <is>
+          <t>Step ordering
+Orders the 4 steps for building a decision rule correctly (1-4)</t>
+        </is>
+      </c>
+      <c r="I54" s="90" t="inlineStr">
+        <is>
+          <t>Why is DT AI
+Multi-select T/F table — marks correct reasons why a DT is considered AI</t>
         </is>
       </c>
       <c r="J54" s="85" t="inlineStr">

--- a/AI_CFT_Labeling.xlsx
+++ b/AI_CFT_Labeling.xlsx
@@ -25,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="25">
+  <fonts count="27">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -178,6 +178,18 @@
       <name val="Calibri"/>
       <i val="1"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF1F3864"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <i val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="26">
@@ -422,7 +434,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -668,6 +680,11 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="23" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1330,7 +1347,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB54"/>
+  <dimension ref="A1:AG54"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" style="51" min="1" max="1"/>
@@ -1359,24 +1376,29 @@
     <col width="18" customWidth="1" style="51" min="24" max="24"/>
     <col width="18" customWidth="1" style="51" min="25" max="25"/>
     <col width="18" customWidth="1" style="51" min="26" max="26"/>
-    <col width="14" customWidth="1" style="51" min="27" max="27"/>
-    <col width="22" customWidth="1" style="51" min="28" max="28"/>
+    <col width="18" customWidth="1" style="51" min="27" max="27"/>
+    <col width="18" customWidth="1" style="51" min="28" max="28"/>
+    <col width="18" customWidth="1" style="51" min="29" max="29"/>
+    <col width="18" customWidth="1" style="51" min="30" max="30"/>
+    <col width="18" customWidth="1" style="51" min="31" max="31"/>
+    <col width="14" customWidth="1" style="51" min="32" max="32"/>
+    <col width="22" customWidth="1" style="51" min="33" max="33"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" s="51">
       <c r="A1" s="77" t="inlineStr">
         <is>
-          <t>AI-CFT Labeling — WS_DT - CODAP Arbor</t>
+          <t>AI-CFT Labeling — WS_DT</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1" s="51">
-      <c r="A2" s="78" t="inlineStr">
+      <c r="A2" s="91" t="inlineStr">
         <is>
           <t>Cohort</t>
         </is>
       </c>
-      <c r="B2" s="78" t="inlineStr">
+      <c r="B2" s="91" t="inlineStr">
         <is>
           <t>Student</t>
         </is>
@@ -1386,127 +1408,152 @@
           <t>Acquire</t>
         </is>
       </c>
-      <c r="D2" s="79" t="inlineStr">
-        <is>
-          <t>Acquire</t>
-        </is>
-      </c>
-      <c r="E2" s="79" t="inlineStr">
-        <is>
-          <t>Acquire</t>
-        </is>
-      </c>
-      <c r="F2" s="88" t="inlineStr">
+      <c r="D2" s="88" t="inlineStr">
         <is>
           <t>Deepen</t>
         </is>
       </c>
-      <c r="G2" s="88" t="inlineStr">
+      <c r="E2" s="88" t="inlineStr">
         <is>
           <t>Deepen</t>
         </is>
       </c>
-      <c r="H2" s="88" t="inlineStr">
+      <c r="F2" s="89" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="G2" s="89" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="H2" s="89" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="I2" s="89" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="J2" s="88" t="inlineStr">
         <is>
           <t>Deepen</t>
         </is>
       </c>
-      <c r="I2" s="88" t="inlineStr">
+      <c r="K2" s="89" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="L2" s="88" t="inlineStr">
         <is>
           <t>Deepen</t>
         </is>
       </c>
-      <c r="J2" s="88" t="inlineStr">
+      <c r="M2" s="88" t="inlineStr">
         <is>
           <t>Deepen</t>
         </is>
       </c>
-      <c r="K2" s="88" t="inlineStr">
+      <c r="N2" s="89" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="O2" s="88" t="inlineStr">
         <is>
           <t>Deepen</t>
         </is>
       </c>
-      <c r="L2" s="88" t="inlineStr">
+      <c r="P2" s="89" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="Q2" s="89" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="R2" s="88" t="inlineStr">
         <is>
           <t>Deepen</t>
         </is>
       </c>
-      <c r="M2" s="88" t="inlineStr">
+      <c r="S2" s="88" t="inlineStr">
         <is>
           <t>Deepen</t>
         </is>
       </c>
-      <c r="N2" s="89" t="inlineStr">
+      <c r="T2" s="88" t="inlineStr">
+        <is>
+          <t>Deepen</t>
+        </is>
+      </c>
+      <c r="U2" s="88" t="inlineStr">
+        <is>
+          <t>Deepen</t>
+        </is>
+      </c>
+      <c r="V2" s="88" t="inlineStr">
+        <is>
+          <t>Deepen</t>
+        </is>
+      </c>
+      <c r="W2" s="88" t="inlineStr">
+        <is>
+          <t>Deepen</t>
+        </is>
+      </c>
+      <c r="X2" s="89" t="inlineStr">
         <is>
           <t>Create</t>
         </is>
       </c>
-      <c r="O2" s="89" t="inlineStr">
+      <c r="Y2" s="88" t="inlineStr">
+        <is>
+          <t>Deepen</t>
+        </is>
+      </c>
+      <c r="Z2" s="89" t="inlineStr">
         <is>
           <t>Create</t>
         </is>
       </c>
-      <c r="P2" s="89" t="inlineStr">
+      <c r="AA2" s="88" t="inlineStr">
+        <is>
+          <t>Deepen</t>
+        </is>
+      </c>
+      <c r="AB2" s="89" t="inlineStr">
         <is>
           <t>Create</t>
         </is>
       </c>
-      <c r="Q2" s="89" t="inlineStr">
+      <c r="AC2" s="88" t="inlineStr">
+        <is>
+          <t>Deepen</t>
+        </is>
+      </c>
+      <c r="AD2" s="89" t="inlineStr">
         <is>
           <t>Create</t>
         </is>
       </c>
-      <c r="R2" s="88" t="inlineStr">
-        <is>
-          <t>Deepen</t>
-        </is>
-      </c>
-      <c r="S2" s="89" t="inlineStr">
+      <c r="AE2" s="89" t="inlineStr">
         <is>
           <t>Create</t>
         </is>
       </c>
-      <c r="T2" s="88" t="inlineStr">
-        <is>
-          <t>Deepen</t>
-        </is>
-      </c>
-      <c r="U2" s="89" t="inlineStr">
-        <is>
-          <t>Create</t>
-        </is>
-      </c>
-      <c r="V2" s="89" t="inlineStr">
-        <is>
-          <t>Create</t>
-        </is>
-      </c>
-      <c r="W2" s="89" t="inlineStr">
-        <is>
-          <t>Create</t>
-        </is>
-      </c>
-      <c r="X2" s="89" t="inlineStr">
-        <is>
-          <t>Create</t>
-        </is>
-      </c>
-      <c r="Y2" s="89" t="inlineStr">
-        <is>
-          <t>Create</t>
-        </is>
-      </c>
-      <c r="Z2" s="89" t="inlineStr">
-        <is>
-          <t>Create</t>
-        </is>
-      </c>
-      <c r="AA2" s="80" t="inlineStr">
+      <c r="AF2" s="80" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AB2" s="80" t="inlineStr">
+      <c r="AG2" s="80" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1526,153 +1573,183 @@
       <c r="C3" s="82" t="inlineStr">
         <is>
           <t>Blank 1
-Prior belief</t>
+A1 – Prior belief</t>
         </is>
       </c>
       <c r="D3" s="82" t="inlineStr">
         <is>
           <t>Blank 2
-Data-based exploration</t>
+A2 – Data-based exploration</t>
         </is>
       </c>
       <c r="E3" s="82" t="inlineStr">
         <is>
           <t>Blank 3
-Meaningful difference found</t>
+A3 – Meaningful difference</t>
         </is>
       </c>
       <c r="F3" s="82" t="inlineStr">
         <is>
           <t>Blank 4
-First variable justification</t>
+A4 – First variable justification</t>
         </is>
       </c>
       <c r="G3" s="82" t="inlineStr">
         <is>
           <t>Blank 5
-Tree 1 — build + EMIT</t>
+B1 – Tree 1 build + EMIT</t>
         </is>
       </c>
       <c r="H3" s="82" t="inlineStr">
         <is>
           <t>Blank 6
-Tree 2 — build + EMIT</t>
+B2 – Tree 2 build + EMIT</t>
         </is>
       </c>
       <c r="I3" s="82" t="inlineStr">
         <is>
           <t>Blank 7
-Tree 3 — build + EMIT</t>
+B3 – Tree 3 build + EMIT</t>
         </is>
       </c>
       <c r="J3" s="82" t="inlineStr">
         <is>
           <t>Blank 8
-Best tree + criteria</t>
+B4 – Best tree + criteria</t>
         </is>
       </c>
       <c r="K3" s="82" t="inlineStr">
         <is>
           <t>Blank 9
-Threshold optimization</t>
+C1 – Threshold optimization</t>
         </is>
       </c>
       <c r="L3" s="82" t="inlineStr">
         <is>
           <t>Blank 10
-Threshold effect</t>
+C2 – Threshold effect</t>
         </is>
       </c>
       <c r="M3" s="82" t="inlineStr">
         <is>
           <t>Blank 11
-Best threshold + reasoning</t>
+C3 – Best threshold + reasoning</t>
         </is>
       </c>
       <c r="N3" s="82" t="inlineStr">
         <is>
           <t>Blank 12
-Two-level tree — build + EMIT</t>
+D1 – Two-level tree build + EMIT</t>
         </is>
       </c>
       <c r="O3" s="82" t="inlineStr">
         <is>
           <t>Blank 13
-Second level effect</t>
+D2 – Second level effect</t>
         </is>
       </c>
       <c r="P3" s="82" t="inlineStr">
         <is>
           <t>Blank 14
-Best variable combination</t>
+D3 – Best variable combination</t>
         </is>
       </c>
       <c r="Q3" s="82" t="inlineStr">
         <is>
           <t>Blank 15
-Stopping criterion</t>
+D4 – Stopping criterion</t>
         </is>
       </c>
       <c r="R3" s="82" t="inlineStr">
         <is>
           <t>Blank 16
-Metrics</t>
+E – Sensitivity value</t>
         </is>
       </c>
       <c r="S3" s="82" t="inlineStr">
         <is>
           <t>Blank 17
-Metric interpretation</t>
+E – MCR value</t>
         </is>
       </c>
       <c r="T3" s="82" t="inlineStr">
         <is>
           <t>Blank 18
-Error type analysis</t>
+E – True Positives</t>
         </is>
       </c>
       <c r="U3" s="82" t="inlineStr">
         <is>
           <t>Blank 19
-Good-enough criterion</t>
+E – False Positives</t>
         </is>
       </c>
       <c r="V3" s="82" t="inlineStr">
         <is>
           <t>Blank 20
-Perfect classification</t>
+E – True Negatives</t>
         </is>
       </c>
       <c r="W3" s="82" t="inlineStr">
         <is>
           <t>Blank 21
-Test set application</t>
+E – False Negatives</t>
         </is>
       </c>
       <c r="X3" s="82" t="inlineStr">
         <is>
           <t>Blank 22
-Train vs test comparison</t>
+E1 – Metric interpretation</t>
         </is>
       </c>
       <c r="Y3" s="82" t="inlineStr">
         <is>
           <t>Blank 23
-What the model learned</t>
+E2 – Error type analysis</t>
         </is>
       </c>
       <c r="Z3" s="82" t="inlineStr">
         <is>
           <t>Blank 24
-Personal reflection</t>
+E3 – Good-enough criterion</t>
         </is>
       </c>
       <c r="AA3" s="82" t="inlineStr">
         <is>
+          <t>Blank 25
+E4 – Perfect classification</t>
+        </is>
+      </c>
+      <c r="AB3" s="82" t="inlineStr">
+        <is>
+          <t>Blank 26
+F1 – Test set application</t>
+        </is>
+      </c>
+      <c r="AC3" s="82" t="inlineStr">
+        <is>
+          <t>Blank 27
+F2 – Train vs test comparison</t>
+        </is>
+      </c>
+      <c r="AD3" s="82" t="inlineStr">
+        <is>
+          <t>Blank 28
+G1 – What the model learned</t>
+        </is>
+      </c>
+      <c r="AE3" s="82" t="inlineStr">
+        <is>
+          <t>Blank 29
+G2 – Personal reflection</t>
+        </is>
+      </c>
+      <c r="AF3" s="82" t="inlineStr">
+        <is>
           <t>Overall WS_DT</t>
         </is>
       </c>
-      <c r="AB3" s="82" t="inlineStr">
+      <c r="AG3" s="82" t="inlineStr">
         <is>
           <t>Notes WS_DT</t>
         </is>
@@ -1691,33 +1768,42 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="B5" s="86" t="n"/>
-      <c r="C5" s="86" t="n"/>
-      <c r="D5" s="86" t="n"/>
-      <c r="E5" s="86" t="n"/>
-      <c r="F5" s="86" t="n"/>
-      <c r="G5" s="86" t="n"/>
-      <c r="H5" s="86" t="n"/>
-      <c r="I5" s="86" t="n"/>
-      <c r="J5" s="86" t="n"/>
-      <c r="K5" s="86" t="n"/>
-      <c r="L5" s="86" t="n"/>
-      <c r="M5" s="86" t="n"/>
-      <c r="N5" s="86" t="n"/>
-      <c r="O5" s="86" t="n"/>
-      <c r="P5" s="86" t="n"/>
-      <c r="Q5" s="86" t="n"/>
-      <c r="R5" s="86" t="n"/>
-      <c r="S5" s="86" t="n"/>
-      <c r="T5" s="86" t="n"/>
-      <c r="U5" s="86" t="n"/>
-      <c r="V5" s="86" t="n"/>
-      <c r="W5" s="86" t="n"/>
-      <c r="X5" s="86" t="n"/>
-      <c r="Y5" s="86" t="n"/>
-      <c r="Z5" s="86" t="n"/>
-      <c r="AA5" s="86" t="n"/>
-      <c r="AB5" s="87" t="n"/>
+      <c r="B5" s="84" t="inlineStr">
+        <is>
+          <t>Ozzy</t>
+        </is>
+      </c>
+      <c r="C5" s="84" t="n"/>
+      <c r="D5" s="84" t="n"/>
+      <c r="E5" s="84" t="n"/>
+      <c r="F5" s="84" t="n"/>
+      <c r="G5" s="84" t="n"/>
+      <c r="H5" s="84" t="n"/>
+      <c r="I5" s="84" t="n"/>
+      <c r="J5" s="84" t="n"/>
+      <c r="K5" s="84" t="n"/>
+      <c r="L5" s="84" t="n"/>
+      <c r="M5" s="84" t="n"/>
+      <c r="N5" s="84" t="n"/>
+      <c r="O5" s="84" t="n"/>
+      <c r="P5" s="84" t="n"/>
+      <c r="Q5" s="84" t="n"/>
+      <c r="R5" s="84" t="n"/>
+      <c r="S5" s="84" t="n"/>
+      <c r="T5" s="84" t="n"/>
+      <c r="U5" s="84" t="n"/>
+      <c r="V5" s="84" t="n"/>
+      <c r="W5" s="84" t="n"/>
+      <c r="X5" s="84" t="n"/>
+      <c r="Y5" s="84" t="n"/>
+      <c r="Z5" s="84" t="n"/>
+      <c r="AA5" s="84" t="n"/>
+      <c r="AB5" s="84" t="n"/>
+      <c r="AC5" s="84" t="n"/>
+      <c r="AD5" s="84" t="n"/>
+      <c r="AE5" s="84" t="n"/>
+      <c r="AF5" s="84" t="n"/>
+      <c r="AG5" s="84" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1" s="51">
       <c r="A6" s="85" t="inlineStr">
@@ -1756,6 +1842,11 @@
       <c r="Z6" s="85" t="n"/>
       <c r="AA6" s="85" t="n"/>
       <c r="AB6" s="85" t="n"/>
+      <c r="AC6" s="85" t="n"/>
+      <c r="AD6" s="85" t="n"/>
+      <c r="AE6" s="85" t="n"/>
+      <c r="AF6" s="85" t="n"/>
+      <c r="AG6" s="85" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1" s="51">
       <c r="A7" s="84" t="inlineStr">
@@ -1794,6 +1885,11 @@
       <c r="Z7" s="84" t="n"/>
       <c r="AA7" s="84" t="n"/>
       <c r="AB7" s="84" t="n"/>
+      <c r="AC7" s="84" t="n"/>
+      <c r="AD7" s="84" t="n"/>
+      <c r="AE7" s="84" t="n"/>
+      <c r="AF7" s="84" t="n"/>
+      <c r="AG7" s="84" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1" s="51">
       <c r="A8" s="85" t="inlineStr">
@@ -1832,6 +1928,11 @@
       <c r="Z8" s="85" t="n"/>
       <c r="AA8" s="85" t="n"/>
       <c r="AB8" s="85" t="n"/>
+      <c r="AC8" s="85" t="n"/>
+      <c r="AD8" s="85" t="n"/>
+      <c r="AE8" s="85" t="n"/>
+      <c r="AF8" s="85" t="n"/>
+      <c r="AG8" s="85" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1" s="51">
       <c r="A9" s="84" t="inlineStr">
@@ -1870,6 +1971,11 @@
       <c r="Z9" s="84" t="n"/>
       <c r="AA9" s="84" t="n"/>
       <c r="AB9" s="84" t="n"/>
+      <c r="AC9" s="84" t="n"/>
+      <c r="AD9" s="84" t="n"/>
+      <c r="AE9" s="84" t="n"/>
+      <c r="AF9" s="84" t="n"/>
+      <c r="AG9" s="84" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1" s="51">
       <c r="A10" s="85" t="inlineStr">
@@ -1908,6 +2014,11 @@
       <c r="Z10" s="85" t="n"/>
       <c r="AA10" s="85" t="n"/>
       <c r="AB10" s="85" t="n"/>
+      <c r="AC10" s="85" t="n"/>
+      <c r="AD10" s="85" t="n"/>
+      <c r="AE10" s="85" t="n"/>
+      <c r="AF10" s="85" t="n"/>
+      <c r="AG10" s="85" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1" s="51">
       <c r="A11" s="84" t="inlineStr">
@@ -1946,6 +2057,11 @@
       <c r="Z11" s="84" t="n"/>
       <c r="AA11" s="84" t="n"/>
       <c r="AB11" s="84" t="n"/>
+      <c r="AC11" s="84" t="n"/>
+      <c r="AD11" s="84" t="n"/>
+      <c r="AE11" s="84" t="n"/>
+      <c r="AF11" s="84" t="n"/>
+      <c r="AG11" s="84" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1" s="51">
       <c r="A12" s="85" t="inlineStr">
@@ -1984,6 +2100,11 @@
       <c r="Z12" s="85" t="n"/>
       <c r="AA12" s="85" t="n"/>
       <c r="AB12" s="85" t="n"/>
+      <c r="AC12" s="85" t="n"/>
+      <c r="AD12" s="85" t="n"/>
+      <c r="AE12" s="85" t="n"/>
+      <c r="AF12" s="85" t="n"/>
+      <c r="AG12" s="85" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1" s="51">
       <c r="A13" s="84" t="inlineStr">
@@ -2022,6 +2143,11 @@
       <c r="Z13" s="84" t="n"/>
       <c r="AA13" s="84" t="n"/>
       <c r="AB13" s="84" t="n"/>
+      <c r="AC13" s="84" t="n"/>
+      <c r="AD13" s="84" t="n"/>
+      <c r="AE13" s="84" t="n"/>
+      <c r="AF13" s="84" t="n"/>
+      <c r="AG13" s="84" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1" s="51">
       <c r="A14" s="85" t="inlineStr">
@@ -2060,6 +2186,11 @@
       <c r="Z14" s="85" t="n"/>
       <c r="AA14" s="85" t="n"/>
       <c r="AB14" s="85" t="n"/>
+      <c r="AC14" s="85" t="n"/>
+      <c r="AD14" s="85" t="n"/>
+      <c r="AE14" s="85" t="n"/>
+      <c r="AF14" s="85" t="n"/>
+      <c r="AG14" s="85" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1" s="51">
       <c r="A15" s="84" t="inlineStr">
@@ -2098,6 +2229,11 @@
       <c r="Z15" s="84" t="n"/>
       <c r="AA15" s="84" t="n"/>
       <c r="AB15" s="84" t="n"/>
+      <c r="AC15" s="84" t="n"/>
+      <c r="AD15" s="84" t="n"/>
+      <c r="AE15" s="84" t="n"/>
+      <c r="AF15" s="84" t="n"/>
+      <c r="AG15" s="84" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1" s="51">
       <c r="A16" s="85" t="inlineStr">
@@ -2136,6 +2272,11 @@
       <c r="Z16" s="85" t="n"/>
       <c r="AA16" s="85" t="n"/>
       <c r="AB16" s="85" t="n"/>
+      <c r="AC16" s="85" t="n"/>
+      <c r="AD16" s="85" t="n"/>
+      <c r="AE16" s="85" t="n"/>
+      <c r="AF16" s="85" t="n"/>
+      <c r="AG16" s="85" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1" s="51">
       <c r="A17" s="84" t="inlineStr">
@@ -2174,6 +2315,11 @@
       <c r="Z17" s="84" t="n"/>
       <c r="AA17" s="84" t="n"/>
       <c r="AB17" s="84" t="n"/>
+      <c r="AC17" s="84" t="n"/>
+      <c r="AD17" s="84" t="n"/>
+      <c r="AE17" s="84" t="n"/>
+      <c r="AF17" s="84" t="n"/>
+      <c r="AG17" s="84" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1" s="51">
       <c r="A18" s="85" t="inlineStr">
@@ -2212,6 +2358,11 @@
       <c r="Z18" s="85" t="n"/>
       <c r="AA18" s="85" t="n"/>
       <c r="AB18" s="85" t="n"/>
+      <c r="AC18" s="85" t="n"/>
+      <c r="AD18" s="85" t="n"/>
+      <c r="AE18" s="85" t="n"/>
+      <c r="AF18" s="85" t="n"/>
+      <c r="AG18" s="85" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1" s="51">
       <c r="A19" s="84" t="inlineStr">
@@ -2250,6 +2401,11 @@
       <c r="Z19" s="84" t="n"/>
       <c r="AA19" s="84" t="n"/>
       <c r="AB19" s="84" t="n"/>
+      <c r="AC19" s="84" t="n"/>
+      <c r="AD19" s="84" t="n"/>
+      <c r="AE19" s="84" t="n"/>
+      <c r="AF19" s="84" t="n"/>
+      <c r="AG19" s="84" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1" s="51">
       <c r="A20" s="85" t="inlineStr">
@@ -2288,6 +2444,11 @@
       <c r="Z20" s="85" t="n"/>
       <c r="AA20" s="85" t="n"/>
       <c r="AB20" s="85" t="n"/>
+      <c r="AC20" s="85" t="n"/>
+      <c r="AD20" s="85" t="n"/>
+      <c r="AE20" s="85" t="n"/>
+      <c r="AF20" s="85" t="n"/>
+      <c r="AG20" s="85" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1" s="51">
       <c r="A21" s="84" t="inlineStr">
@@ -2326,6 +2487,11 @@
       <c r="Z21" s="84" t="n"/>
       <c r="AA21" s="84" t="n"/>
       <c r="AB21" s="84" t="n"/>
+      <c r="AC21" s="84" t="n"/>
+      <c r="AD21" s="84" t="n"/>
+      <c r="AE21" s="84" t="n"/>
+      <c r="AF21" s="84" t="n"/>
+      <c r="AG21" s="84" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1" s="51">
       <c r="A22" s="85" t="inlineStr">
@@ -2364,6 +2530,11 @@
       <c r="Z22" s="85" t="n"/>
       <c r="AA22" s="85" t="n"/>
       <c r="AB22" s="85" t="n"/>
+      <c r="AC22" s="85" t="n"/>
+      <c r="AD22" s="85" t="n"/>
+      <c r="AE22" s="85" t="n"/>
+      <c r="AF22" s="85" t="n"/>
+      <c r="AG22" s="85" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1" s="51">
       <c r="A23" s="84" t="inlineStr">
@@ -2402,6 +2573,11 @@
       <c r="Z23" s="84" t="n"/>
       <c r="AA23" s="84" t="n"/>
       <c r="AB23" s="84" t="n"/>
+      <c r="AC23" s="84" t="n"/>
+      <c r="AD23" s="84" t="n"/>
+      <c r="AE23" s="84" t="n"/>
+      <c r="AF23" s="84" t="n"/>
+      <c r="AG23" s="84" t="n"/>
     </row>
     <row r="24" ht="18" customHeight="1" s="51">
       <c r="A24" s="85" t="inlineStr">
@@ -2440,6 +2616,11 @@
       <c r="Z24" s="85" t="n"/>
       <c r="AA24" s="85" t="n"/>
       <c r="AB24" s="85" t="n"/>
+      <c r="AC24" s="85" t="n"/>
+      <c r="AD24" s="85" t="n"/>
+      <c r="AE24" s="85" t="n"/>
+      <c r="AF24" s="85" t="n"/>
+      <c r="AG24" s="85" t="n"/>
     </row>
     <row r="25" ht="18" customHeight="1" s="51">
       <c r="A25" s="84" t="inlineStr">
@@ -2478,6 +2659,11 @@
       <c r="Z25" s="84" t="n"/>
       <c r="AA25" s="84" t="n"/>
       <c r="AB25" s="84" t="n"/>
+      <c r="AC25" s="84" t="n"/>
+      <c r="AD25" s="84" t="n"/>
+      <c r="AE25" s="84" t="n"/>
+      <c r="AF25" s="84" t="n"/>
+      <c r="AG25" s="84" t="n"/>
     </row>
     <row r="26" ht="18" customHeight="1" s="51">
       <c r="A26" s="85" t="inlineStr">
@@ -2516,6 +2702,11 @@
       <c r="Z26" s="85" t="n"/>
       <c r="AA26" s="85" t="n"/>
       <c r="AB26" s="85" t="n"/>
+      <c r="AC26" s="85" t="n"/>
+      <c r="AD26" s="85" t="n"/>
+      <c r="AE26" s="85" t="n"/>
+      <c r="AF26" s="85" t="n"/>
+      <c r="AG26" s="85" t="n"/>
     </row>
     <row r="27" ht="18" customHeight="1" s="51">
       <c r="A27" s="84" t="inlineStr">
@@ -2554,6 +2745,11 @@
       <c r="Z27" s="84" t="n"/>
       <c r="AA27" s="84" t="n"/>
       <c r="AB27" s="84" t="n"/>
+      <c r="AC27" s="84" t="n"/>
+      <c r="AD27" s="84" t="n"/>
+      <c r="AE27" s="84" t="n"/>
+      <c r="AF27" s="84" t="n"/>
+      <c r="AG27" s="84" t="n"/>
     </row>
     <row r="28" ht="18" customHeight="1" s="51">
       <c r="A28" s="85" t="inlineStr">
@@ -2592,6 +2788,11 @@
       <c r="Z28" s="85" t="n"/>
       <c r="AA28" s="85" t="n"/>
       <c r="AB28" s="85" t="n"/>
+      <c r="AC28" s="85" t="n"/>
+      <c r="AD28" s="85" t="n"/>
+      <c r="AE28" s="85" t="n"/>
+      <c r="AF28" s="85" t="n"/>
+      <c r="AG28" s="85" t="n"/>
     </row>
     <row r="29" ht="18" customHeight="1" s="51">
       <c r="A29" s="84" t="inlineStr">
@@ -2630,6 +2831,11 @@
       <c r="Z29" s="84" t="n"/>
       <c r="AA29" s="84" t="n"/>
       <c r="AB29" s="84" t="n"/>
+      <c r="AC29" s="84" t="n"/>
+      <c r="AD29" s="84" t="n"/>
+      <c r="AE29" s="84" t="n"/>
+      <c r="AF29" s="84" t="n"/>
+      <c r="AG29" s="84" t="n"/>
     </row>
     <row r="30" ht="18" customHeight="1" s="51">
       <c r="A30" s="85" t="inlineStr">
@@ -2668,6 +2874,11 @@
       <c r="Z30" s="85" t="n"/>
       <c r="AA30" s="85" t="n"/>
       <c r="AB30" s="85" t="n"/>
+      <c r="AC30" s="85" t="n"/>
+      <c r="AD30" s="85" t="n"/>
+      <c r="AE30" s="85" t="n"/>
+      <c r="AF30" s="85" t="n"/>
+      <c r="AG30" s="85" t="n"/>
     </row>
     <row r="31" ht="18" customHeight="1" s="51">
       <c r="A31" s="84" t="inlineStr">
@@ -2706,6 +2917,11 @@
       <c r="Z31" s="84" t="n"/>
       <c r="AA31" s="84" t="n"/>
       <c r="AB31" s="84" t="n"/>
+      <c r="AC31" s="84" t="n"/>
+      <c r="AD31" s="84" t="n"/>
+      <c r="AE31" s="84" t="n"/>
+      <c r="AF31" s="84" t="n"/>
+      <c r="AG31" s="84" t="n"/>
     </row>
     <row r="32" ht="18" customHeight="1" s="51">
       <c r="A32" s="85" t="inlineStr">
@@ -2744,6 +2960,11 @@
       <c r="Z32" s="85" t="n"/>
       <c r="AA32" s="85" t="n"/>
       <c r="AB32" s="85" t="n"/>
+      <c r="AC32" s="85" t="n"/>
+      <c r="AD32" s="85" t="n"/>
+      <c r="AE32" s="85" t="n"/>
+      <c r="AF32" s="85" t="n"/>
+      <c r="AG32" s="85" t="n"/>
     </row>
     <row r="33" ht="18" customHeight="1" s="51">
       <c r="A33" s="84" t="inlineStr">
@@ -2782,6 +3003,11 @@
       <c r="Z33" s="84" t="n"/>
       <c r="AA33" s="84" t="n"/>
       <c r="AB33" s="84" t="n"/>
+      <c r="AC33" s="84" t="n"/>
+      <c r="AD33" s="84" t="n"/>
+      <c r="AE33" s="84" t="n"/>
+      <c r="AF33" s="84" t="n"/>
+      <c r="AG33" s="84" t="n"/>
     </row>
     <row r="34" ht="18" customHeight="1" s="51">
       <c r="A34" s="85" t="inlineStr">
@@ -2789,7 +3015,11 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="B34" s="85" t="n"/>
+      <c r="B34" s="85" t="inlineStr">
+        <is>
+          <t>Sabrina</t>
+        </is>
+      </c>
       <c r="C34" s="85" t="n"/>
       <c r="D34" s="85" t="n"/>
       <c r="E34" s="85" t="n"/>
@@ -2816,6 +3046,11 @@
       <c r="Z34" s="85" t="n"/>
       <c r="AA34" s="85" t="n"/>
       <c r="AB34" s="85" t="n"/>
+      <c r="AC34" s="85" t="n"/>
+      <c r="AD34" s="85" t="n"/>
+      <c r="AE34" s="85" t="n"/>
+      <c r="AF34" s="85" t="n"/>
+      <c r="AG34" s="85" t="n"/>
     </row>
     <row r="35" ht="20" customHeight="1" s="51">
       <c r="A35" s="83" t="inlineStr">
@@ -2830,33 +3065,42 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="B36" s="86" t="n"/>
-      <c r="C36" s="86" t="n"/>
-      <c r="D36" s="86" t="n"/>
-      <c r="E36" s="86" t="n"/>
-      <c r="F36" s="86" t="n"/>
-      <c r="G36" s="86" t="n"/>
-      <c r="H36" s="86" t="n"/>
-      <c r="I36" s="86" t="n"/>
-      <c r="J36" s="86" t="n"/>
-      <c r="K36" s="86" t="n"/>
-      <c r="L36" s="86" t="n"/>
-      <c r="M36" s="86" t="n"/>
-      <c r="N36" s="86" t="n"/>
-      <c r="O36" s="86" t="n"/>
-      <c r="P36" s="86" t="n"/>
-      <c r="Q36" s="86" t="n"/>
-      <c r="R36" s="86" t="n"/>
-      <c r="S36" s="86" t="n"/>
-      <c r="T36" s="86" t="n"/>
-      <c r="U36" s="86" t="n"/>
-      <c r="V36" s="86" t="n"/>
-      <c r="W36" s="86" t="n"/>
-      <c r="X36" s="86" t="n"/>
-      <c r="Y36" s="86" t="n"/>
-      <c r="Z36" s="86" t="n"/>
-      <c r="AA36" s="86" t="n"/>
-      <c r="AB36" s="87" t="n"/>
+      <c r="B36" s="84" t="inlineStr">
+        <is>
+          <t>Sheila</t>
+        </is>
+      </c>
+      <c r="C36" s="84" t="n"/>
+      <c r="D36" s="84" t="n"/>
+      <c r="E36" s="84" t="n"/>
+      <c r="F36" s="84" t="n"/>
+      <c r="G36" s="84" t="n"/>
+      <c r="H36" s="84" t="n"/>
+      <c r="I36" s="84" t="n"/>
+      <c r="J36" s="84" t="n"/>
+      <c r="K36" s="84" t="n"/>
+      <c r="L36" s="84" t="n"/>
+      <c r="M36" s="84" t="n"/>
+      <c r="N36" s="84" t="n"/>
+      <c r="O36" s="84" t="n"/>
+      <c r="P36" s="84" t="n"/>
+      <c r="Q36" s="84" t="n"/>
+      <c r="R36" s="84" t="n"/>
+      <c r="S36" s="84" t="n"/>
+      <c r="T36" s="84" t="n"/>
+      <c r="U36" s="84" t="n"/>
+      <c r="V36" s="84" t="n"/>
+      <c r="W36" s="84" t="n"/>
+      <c r="X36" s="84" t="n"/>
+      <c r="Y36" s="84" t="n"/>
+      <c r="Z36" s="84" t="n"/>
+      <c r="AA36" s="84" t="n"/>
+      <c r="AB36" s="84" t="n"/>
+      <c r="AC36" s="84" t="n"/>
+      <c r="AD36" s="84" t="n"/>
+      <c r="AE36" s="84" t="n"/>
+      <c r="AF36" s="84" t="n"/>
+      <c r="AG36" s="84" t="n"/>
     </row>
     <row r="37" ht="18" customHeight="1" s="51">
       <c r="A37" s="85" t="inlineStr">
@@ -2895,6 +3139,11 @@
       <c r="Z37" s="85" t="n"/>
       <c r="AA37" s="85" t="n"/>
       <c r="AB37" s="85" t="n"/>
+      <c r="AC37" s="85" t="n"/>
+      <c r="AD37" s="85" t="n"/>
+      <c r="AE37" s="85" t="n"/>
+      <c r="AF37" s="85" t="n"/>
+      <c r="AG37" s="85" t="n"/>
     </row>
     <row r="38" ht="18" customHeight="1" s="51">
       <c r="A38" s="84" t="inlineStr">
@@ -2933,6 +3182,11 @@
       <c r="Z38" s="84" t="n"/>
       <c r="AA38" s="84" t="n"/>
       <c r="AB38" s="84" t="n"/>
+      <c r="AC38" s="84" t="n"/>
+      <c r="AD38" s="84" t="n"/>
+      <c r="AE38" s="84" t="n"/>
+      <c r="AF38" s="84" t="n"/>
+      <c r="AG38" s="84" t="n"/>
     </row>
     <row r="39" ht="18" customHeight="1" s="51">
       <c r="A39" s="85" t="inlineStr">
@@ -2971,6 +3225,11 @@
       <c r="Z39" s="85" t="n"/>
       <c r="AA39" s="85" t="n"/>
       <c r="AB39" s="85" t="n"/>
+      <c r="AC39" s="85" t="n"/>
+      <c r="AD39" s="85" t="n"/>
+      <c r="AE39" s="85" t="n"/>
+      <c r="AF39" s="85" t="n"/>
+      <c r="AG39" s="85" t="n"/>
     </row>
     <row r="40" ht="18" customHeight="1" s="51">
       <c r="A40" s="84" t="inlineStr">
@@ -3009,6 +3268,11 @@
       <c r="Z40" s="84" t="n"/>
       <c r="AA40" s="84" t="n"/>
       <c r="AB40" s="84" t="n"/>
+      <c r="AC40" s="84" t="n"/>
+      <c r="AD40" s="84" t="n"/>
+      <c r="AE40" s="84" t="n"/>
+      <c r="AF40" s="84" t="n"/>
+      <c r="AG40" s="84" t="n"/>
     </row>
     <row r="41" ht="18" customHeight="1" s="51">
       <c r="A41" s="85" t="inlineStr">
@@ -3047,6 +3311,11 @@
       <c r="Z41" s="85" t="n"/>
       <c r="AA41" s="85" t="n"/>
       <c r="AB41" s="85" t="n"/>
+      <c r="AC41" s="85" t="n"/>
+      <c r="AD41" s="85" t="n"/>
+      <c r="AE41" s="85" t="n"/>
+      <c r="AF41" s="85" t="n"/>
+      <c r="AG41" s="85" t="n"/>
     </row>
     <row r="42" ht="18" customHeight="1" s="51">
       <c r="A42" s="84" t="inlineStr">
@@ -3085,6 +3354,11 @@
       <c r="Z42" s="84" t="n"/>
       <c r="AA42" s="84" t="n"/>
       <c r="AB42" s="84" t="n"/>
+      <c r="AC42" s="84" t="n"/>
+      <c r="AD42" s="84" t="n"/>
+      <c r="AE42" s="84" t="n"/>
+      <c r="AF42" s="84" t="n"/>
+      <c r="AG42" s="84" t="n"/>
     </row>
     <row r="43" ht="18" customHeight="1" s="51">
       <c r="A43" s="85" t="inlineStr">
@@ -3123,6 +3397,11 @@
       <c r="Z43" s="85" t="n"/>
       <c r="AA43" s="85" t="n"/>
       <c r="AB43" s="85" t="n"/>
+      <c r="AC43" s="85" t="n"/>
+      <c r="AD43" s="85" t="n"/>
+      <c r="AE43" s="85" t="n"/>
+      <c r="AF43" s="85" t="n"/>
+      <c r="AG43" s="85" t="n"/>
     </row>
     <row r="44" ht="18" customHeight="1" s="51">
       <c r="A44" s="84" t="inlineStr">
@@ -3161,6 +3440,11 @@
       <c r="Z44" s="84" t="n"/>
       <c r="AA44" s="84" t="n"/>
       <c r="AB44" s="84" t="n"/>
+      <c r="AC44" s="84" t="n"/>
+      <c r="AD44" s="84" t="n"/>
+      <c r="AE44" s="84" t="n"/>
+      <c r="AF44" s="84" t="n"/>
+      <c r="AG44" s="84" t="n"/>
     </row>
     <row r="45" ht="18" customHeight="1" s="51">
       <c r="A45" s="85" t="inlineStr">
@@ -3199,6 +3483,11 @@
       <c r="Z45" s="85" t="n"/>
       <c r="AA45" s="85" t="n"/>
       <c r="AB45" s="85" t="n"/>
+      <c r="AC45" s="85" t="n"/>
+      <c r="AD45" s="85" t="n"/>
+      <c r="AE45" s="85" t="n"/>
+      <c r="AF45" s="85" t="n"/>
+      <c r="AG45" s="85" t="n"/>
     </row>
     <row r="46" ht="18" customHeight="1" s="51">
       <c r="A46" s="84" t="inlineStr">
@@ -3237,6 +3526,11 @@
       <c r="Z46" s="84" t="n"/>
       <c r="AA46" s="84" t="n"/>
       <c r="AB46" s="84" t="n"/>
+      <c r="AC46" s="84" t="n"/>
+      <c r="AD46" s="84" t="n"/>
+      <c r="AE46" s="84" t="n"/>
+      <c r="AF46" s="84" t="n"/>
+      <c r="AG46" s="84" t="n"/>
     </row>
     <row r="47" ht="18" customHeight="1" s="51">
       <c r="A47" s="85" t="inlineStr">
@@ -3275,6 +3569,11 @@
       <c r="Z47" s="85" t="n"/>
       <c r="AA47" s="85" t="n"/>
       <c r="AB47" s="85" t="n"/>
+      <c r="AC47" s="85" t="n"/>
+      <c r="AD47" s="85" t="n"/>
+      <c r="AE47" s="85" t="n"/>
+      <c r="AF47" s="85" t="n"/>
+      <c r="AG47" s="85" t="n"/>
     </row>
     <row r="48" ht="18" customHeight="1" s="51">
       <c r="A48" s="84" t="inlineStr">
@@ -3313,6 +3612,11 @@
       <c r="Z48" s="84" t="n"/>
       <c r="AA48" s="84" t="n"/>
       <c r="AB48" s="84" t="n"/>
+      <c r="AC48" s="84" t="n"/>
+      <c r="AD48" s="84" t="n"/>
+      <c r="AE48" s="84" t="n"/>
+      <c r="AF48" s="84" t="n"/>
+      <c r="AG48" s="84" t="n"/>
     </row>
     <row r="49" ht="18" customHeight="1" s="51">
       <c r="A49" s="85" t="inlineStr">
@@ -3351,6 +3655,11 @@
       <c r="Z49" s="85" t="n"/>
       <c r="AA49" s="85" t="n"/>
       <c r="AB49" s="85" t="n"/>
+      <c r="AC49" s="85" t="n"/>
+      <c r="AD49" s="85" t="n"/>
+      <c r="AE49" s="85" t="n"/>
+      <c r="AF49" s="85" t="n"/>
+      <c r="AG49" s="85" t="n"/>
     </row>
     <row r="50" ht="18" customHeight="1" s="51">
       <c r="A50" s="84" t="inlineStr">
@@ -3389,6 +3698,11 @@
       <c r="Z50" s="84" t="n"/>
       <c r="AA50" s="84" t="n"/>
       <c r="AB50" s="84" t="n"/>
+      <c r="AC50" s="84" t="n"/>
+      <c r="AD50" s="84" t="n"/>
+      <c r="AE50" s="84" t="n"/>
+      <c r="AF50" s="84" t="n"/>
+      <c r="AG50" s="84" t="n"/>
     </row>
     <row r="51" ht="18" customHeight="1" s="51">
       <c r="A51" s="85" t="inlineStr">
@@ -3427,214 +3741,212 @@
       <c r="Z51" s="85" t="n"/>
       <c r="AA51" s="85" t="n"/>
       <c r="AB51" s="85" t="n"/>
+      <c r="AC51" s="85" t="n"/>
+      <c r="AD51" s="85" t="n"/>
+      <c r="AE51" s="85" t="n"/>
+      <c r="AF51" s="85" t="n"/>
+      <c r="AG51" s="85" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="84" t="inlineStr">
-        <is>
-          <t>Dropdown values: Acquire | Deepen | Create | ? (unscorable/blank)</t>
-        </is>
-      </c>
-      <c r="B53" s="86" t="n"/>
-      <c r="C53" s="86" t="n"/>
-      <c r="D53" s="86" t="n"/>
-      <c r="E53" s="86" t="n"/>
-      <c r="F53" s="86" t="n"/>
-      <c r="G53" s="86" t="n"/>
-      <c r="H53" s="86" t="n"/>
-      <c r="I53" s="86" t="n"/>
-      <c r="J53" s="86" t="n"/>
-      <c r="K53" s="86" t="n"/>
-      <c r="L53" s="86" t="n"/>
-      <c r="M53" s="86" t="n"/>
-      <c r="N53" s="86" t="n"/>
-      <c r="O53" s="86" t="n"/>
-      <c r="P53" s="86" t="n"/>
-      <c r="Q53" s="86" t="n"/>
-      <c r="R53" s="86" t="n"/>
-      <c r="S53" s="86" t="n"/>
-      <c r="T53" s="86" t="n"/>
-      <c r="U53" s="86" t="n"/>
-      <c r="V53" s="86" t="n"/>
-      <c r="W53" s="86" t="n"/>
-      <c r="X53" s="86" t="n"/>
-      <c r="Y53" s="86" t="n"/>
-      <c r="Z53" s="86" t="n"/>
-      <c r="AA53" s="86" t="n"/>
-      <c r="AB53" s="87" t="n"/>
-    </row>
-    <row r="54" ht="40" customHeight="1" s="51">
-      <c r="A54" s="85" t="inlineStr">
+      <c r="A53" s="92" t="inlineStr">
         <is>
           <t>Task descriptions:</t>
         </is>
       </c>
-      <c r="B54" s="85" t="n"/>
-      <c r="C54" s="90" t="inlineStr">
-        <is>
-          <t>Prior belief
-Names variable(s) predicted to determine recommendability — based on intuition, any answer ok</t>
-        </is>
-      </c>
-      <c r="D54" s="90" t="inlineStr">
-        <is>
-          <t>Data-based exploration
-Names variable(s) based on data WITH graph/visualization evidence (not just intuition)</t>
-        </is>
-      </c>
-      <c r="E54" s="90" t="inlineStr">
-        <is>
-          <t>Meaningful difference found
-Yes/No response AND references actual data to support the answer</t>
-        </is>
-      </c>
-      <c r="F54" s="90" t="inlineStr">
-        <is>
-          <t>First variable justification
-Justifies first-variable choice using data evidence (not general knowledge such as 'fat is unhealthy')</t>
-        </is>
-      </c>
-      <c r="G54" s="90" t="inlineStr">
-        <is>
-          <t>Tree 1 — build + EMIT
-Builds single-level tree with one variable, records EMIT accuracy result</t>
-        </is>
-      </c>
-      <c r="H54" s="90" t="inlineStr">
-        <is>
-          <t>Tree 2 — build + EMIT
-Builds second single-level tree with a different variable, records EMIT</t>
-        </is>
-      </c>
-      <c r="I54" s="90" t="inlineStr">
-        <is>
-          <t>Tree 3 — build + EMIT
-Builds third single-level tree with yet another variable, records EMIT</t>
-        </is>
-      </c>
-      <c r="J54" s="90" t="inlineStr">
-        <is>
-          <t>Best tree + criteria
-Identifies best tree among B1-B3 AND lists criteria used for comparison</t>
-        </is>
-      </c>
-      <c r="K54" s="90" t="inlineStr">
-        <is>
-          <t>Threshold optimization
-Tries different threshold values for best variable from B; saves best with EMIT</t>
-        </is>
-      </c>
-      <c r="L54" s="90" t="inlineStr">
-        <is>
-          <t>Threshold effect
-Explains how changing the threshold value affects decision tree performance</t>
-        </is>
-      </c>
-      <c r="M54" s="90" t="inlineStr">
-        <is>
-          <t>Best threshold + reasoning
-Identifies best threshold and explains how that conclusion was reached</t>
-        </is>
-      </c>
-      <c r="N54" s="90" t="inlineStr">
-        <is>
-          <t>Two-level tree — build + EMIT
-Adds a second variable to create a two-level tree; saves with EMIT</t>
-        </is>
-      </c>
-      <c r="O54" s="90" t="inlineStr">
-        <is>
-          <t>Second level effect
-Explains whether and how the second variable improved classification</t>
-        </is>
-      </c>
-      <c r="P54" s="90" t="inlineStr">
-        <is>
-          <t>Best variable combination
-States which variable combination produced the best result</t>
-        </is>
-      </c>
-      <c r="Q54" s="90" t="inlineStr">
-        <is>
-          <t>Stopping criterion
-Explains how they decided they had reached their best decision tree</t>
-        </is>
-      </c>
-      <c r="R54" s="90" t="inlineStr">
-        <is>
-          <t>Metrics
-E (intro): Records Sensitivity and MCR values from EMIT for the best tree</t>
-        </is>
-      </c>
-      <c r="S54" s="90" t="inlineStr">
-        <is>
-          <t>Metric interpretation
-Explains which metric matters more for this model's purpose and why</t>
-        </is>
-      </c>
-      <c r="T54" s="90" t="inlineStr">
-        <is>
-          <t>Error type analysis
-Identifies whether the model made more false positives or false negatives</t>
-        </is>
-      </c>
-      <c r="U54" s="90" t="inlineStr">
-        <is>
-          <t>Good-enough criterion
-Reflects on how software / they would decide when a tree is good enough</t>
-        </is>
-      </c>
-      <c r="V54" s="90" t="inlineStr">
-        <is>
-          <t>Perfect classification
-Reflects on whether DTs can achieve zero error; gives a reasoned answer</t>
-        </is>
-      </c>
-      <c r="W54" s="90" t="inlineStr">
-        <is>
-          <t>Test set application
-Applies best tree to test dataset, evaluates with EMIT, records result</t>
-        </is>
-      </c>
-      <c r="X54" s="90" t="inlineStr">
-        <is>
-          <t>Train vs test comparison
-Compares test vs. training performance and explains any difference</t>
-        </is>
-      </c>
-      <c r="Y54" s="90" t="inlineStr">
-        <is>
-          <t>What the model learned
-Explains what the decision tree model 'learned' from the training data</t>
-        </is>
-      </c>
-      <c r="Z54" s="90" t="inlineStr">
-        <is>
-          <t>Personal reflection
-Reflects on personal learning during the tree-building process</t>
-        </is>
-      </c>
-      <c r="AA54" s="85" t="inlineStr">
-        <is>
-          <t>Overall AI-CFT level for WS_DT as a whole</t>
-        </is>
-      </c>
-      <c r="AB54" s="85" t="inlineStr">
-        <is>
-          <t>Free notes</t>
+    </row>
+    <row r="54" ht="60" customHeight="1" s="51">
+      <c r="C54" s="93" t="inlineStr">
+        <is>
+          <t>A1 – Prior belief
+Which variables do you predict will determine recommendability? (intuition, no analysis yet)</t>
+        </is>
+      </c>
+      <c r="D54" s="93" t="inlineStr">
+        <is>
+          <t>A2 – Data-based exploration
+Which variables actually influence recommendability based on data? (with graph evidence)</t>
+        </is>
+      </c>
+      <c r="E54" s="93" t="inlineStr">
+        <is>
+          <t>A3 – Meaningful difference
+Did you find a variable showing meaningful difference between groups? Explain with data.</t>
+        </is>
+      </c>
+      <c r="F54" s="93" t="inlineStr">
+        <is>
+          <t>A4 – First variable justification
+Which variable would you use first in a prediction model? Justify using data evidence.</t>
+        </is>
+      </c>
+      <c r="G54" s="93" t="inlineStr">
+        <is>
+          <t>B1 – Tree 1 build + EMIT
+Build single-level tree with variable 1; record EMIT accuracy result</t>
+        </is>
+      </c>
+      <c r="H54" s="93" t="inlineStr">
+        <is>
+          <t>B2 – Tree 2 build + EMIT
+Build single-level tree with variable 2; record EMIT accuracy result</t>
+        </is>
+      </c>
+      <c r="I54" s="93" t="inlineStr">
+        <is>
+          <t>B3 – Tree 3 build + EMIT
+Build single-level tree with variable 3; record EMIT accuracy result</t>
+        </is>
+      </c>
+      <c r="J54" s="93" t="inlineStr">
+        <is>
+          <t>B4 – Best tree + criteria
+Which variable gave best result? What criteria used to judge?</t>
+        </is>
+      </c>
+      <c r="K54" s="93" t="inlineStr">
+        <is>
+          <t>C1 – Threshold optimization
+Try different thresholds for best variable; save best result with EMIT</t>
+        </is>
+      </c>
+      <c r="L54" s="93" t="inlineStr">
+        <is>
+          <t>C2 – Threshold effect
+How does changing the threshold value affect decision tree performance?</t>
+        </is>
+      </c>
+      <c r="M54" s="93" t="inlineStr">
+        <is>
+          <t>C3 – Best threshold + reasoning
+Which threshold best separates the groups? How did you decide?</t>
+        </is>
+      </c>
+      <c r="N54" s="93" t="inlineStr">
+        <is>
+          <t>D1 – Two-level tree build + EMIT
+Add second variable to create a two-level tree; save result with EMIT</t>
+        </is>
+      </c>
+      <c r="O54" s="93" t="inlineStr">
+        <is>
+          <t>D2 – Second level effect
+Did the second level improve classification? How and in what ways?</t>
+        </is>
+      </c>
+      <c r="P54" s="93" t="inlineStr">
+        <is>
+          <t>D3 – Best variable combination
+Which variable combination produced the best result?</t>
+        </is>
+      </c>
+      <c r="Q54" s="93" t="inlineStr">
+        <is>
+          <t>D4 – Stopping criterion
+How did you decide you had reached your best decision tree?</t>
+        </is>
+      </c>
+      <c r="R54" s="93" t="inlineStr">
+        <is>
+          <t>E – Sensitivity value
+Fill in Sensitivity (Duyarlılık) value from EMIT for best tree</t>
+        </is>
+      </c>
+      <c r="S54" s="93" t="inlineStr">
+        <is>
+          <t>E – MCR value
+Fill in Misclassification Rate (MCR) value from EMIT for best tree</t>
+        </is>
+      </c>
+      <c r="T54" s="93" t="inlineStr">
+        <is>
+          <t>E – True Positives
+Count of True Positives (TP) from confusion matrix</t>
+        </is>
+      </c>
+      <c r="U54" s="93" t="inlineStr">
+        <is>
+          <t>E – False Positives
+Count of False Positives (FP) from confusion matrix</t>
+        </is>
+      </c>
+      <c r="V54" s="93" t="inlineStr">
+        <is>
+          <t>E – True Negatives
+Count of True Negatives (TN) from confusion matrix</t>
+        </is>
+      </c>
+      <c r="W54" s="93" t="inlineStr">
+        <is>
+          <t>E – False Negatives
+Count of False Negatives (FN) from confusion matrix</t>
+        </is>
+      </c>
+      <c r="X54" s="93" t="inlineStr">
+        <is>
+          <t>E1 – Metric interpretation
+Which metric matters most for this model's purpose: sensitivity, MCR, or other? Why?</t>
+        </is>
+      </c>
+      <c r="Y54" s="93" t="inlineStr">
+        <is>
+          <t>E2 – Error type analysis
+Did model make more false positives or false negatives?</t>
+        </is>
+      </c>
+      <c r="Z54" s="93" t="inlineStr">
+        <is>
+          <t>E3 – Good-enough criterion
+How would software / you decide when a tree is good enough?</t>
+        </is>
+      </c>
+      <c r="AA54" s="93" t="inlineStr">
+        <is>
+          <t>E4 – Perfect classification
+Do you think decision trees can ever classify perfectly? Reasoned answer.</t>
+        </is>
+      </c>
+      <c r="AB54" s="93" t="inlineStr">
+        <is>
+          <t>F1 – Test set application
+Apply best tree to test dataset; evaluate with EMIT; record result</t>
+        </is>
+      </c>
+      <c r="AC54" s="93" t="inlineStr">
+        <is>
+          <t>F2 – Train vs test comparison
+Compare test vs. training performance and explain any difference</t>
+        </is>
+      </c>
+      <c r="AD54" s="93" t="inlineStr">
+        <is>
+          <t>G1 – What the model learned
+What did the decision tree model 'learn' from the training data?</t>
+        </is>
+      </c>
+      <c r="AE54" s="93" t="inlineStr">
+        <is>
+          <t>G2 – Personal reflection
+What did you personally learn while building decision trees?</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="9">
+    <mergeCell ref="A1:AG1"/>
+    <mergeCell ref="A35:AG35"/>
     <mergeCell ref="A5:AB5"/>
+    <mergeCell ref="A4:AG4"/>
     <mergeCell ref="A36:AB36"/>
     <mergeCell ref="A1:AB1"/>
     <mergeCell ref="A53:AB53"/>
     <mergeCell ref="A35:AB35"/>
     <mergeCell ref="A4:AB4"/>
   </mergeCells>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation sqref="C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 C17 C18 C19 C20 C21 C22 C23 C24 C25 C26 C27 C28 C29 C30 C31 C32 C33 C34 C36 C37 C38 C39 C40 C41 C42 C43 C44 C45 C46 C47 C48 C49 C50 C51 D5 D6 D7 D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19 D20 D21 D22 D23 D24 D25 D26 D27 D28 D29 D30 D31 D32 D33 D34 D36 D37 D38 D39 D40 D41 D42 D43 D44 D45 D46 D47 D48 D49 D50 D51 E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E24 E25 E26 E27 E28 E29 E30 E31 E32 E33 E34 E36 E37 E38 E39 E40 E41 E42 E43 E44 E45 E46 E47 E48 E49 E50 E51 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34 F36 F37 F38 F39 F40 F41 F42 F43 F44 F45 F46 F47 F48 F49 F50 F51 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 G31 G32 G33 G34 G36 G37 G38 G39 G40 G41 G42 G43 G44 G45 G46 G47 G48 G49 G50 G51 H5 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27 H28 H29 H30 H31 H32 H33 H34 H36 H37 H38 H39 H40 H41 H42 H43 H44 H45 H46 H47 H48 H49 H50 H51 I5 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I24 I25 I26 I27 I28 I29 I30 I31 I32 I33 I34 I36 I37 I38 I39 I40 I41 I42 I43 I44 I45 I46 I47 I48 I49 I50 I51 J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25 J26 J27 J28 J29 J30 J31 J32 J33 J34 J36 J37 J38 J39 J40 J41 J42 J43 J44 J45 J46 J47 J48 J49 J50 J51 K5 K6 K7 K8 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 K19 K20 K21 K22 K23 K24 K25 K26 K27 K28 K29 K30 K31 K32 K33 K34 K36 K37 K38 K39 K40 K41 K42 K43 K44 K45 K46 K47 K48 K49 K50 K51 L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26 L27 L28 L29 L30 L31 L32 L33 L34 L36 L37 L38 L39 L40 L41 L42 L43 L44 L45 L46 L47 L48 L49 L50 L51 M5 M6 M7 M8 M9 M10 M11 M12 M13 M14 M15 M16 M17 M18 M19 M20 M21 M22 M23 M24 M25 M26 M27 M28 M29 M30 M31 M32 M33 M34 M36 M37 M38 M39 M40 M41 M42 M43 M44 M45 M46 M47 M48 M49 M50 M51 N5 N6 N7 N8 N9 N10 N11 N12 N13 N14 N15 N16 N17 N18 N19 N20 N21 N22 N23 N24 N25 N26 N27 N28 N29 N30 N31 N32 N33 N34 N36 N37 N38 N39 N40 N41 N42 N43 N44 N45 N46 N47 N48 N49 N50 N51 O5 O6 O7 O8 O9 O10 O11 O12 O13 O14 O15 O16 O17 O18 O19 O20 O21 O22 O23 O24 O25 O26 O27 O28 O29 O30 O31 O32 O33 O34 O36 O37 O38 O39 O40 O41 O42 O43 O44 O45 O46 O47 O48 O49 O50 O51 P5 P6 P7 P8 P9 P10 P11 P12 P13 P14 P15 P16 P17 P18 P19 P20 P21 P22 P23 P24 P25 P26 P27 P28 P29 P30 P31 P32 P33 P34 P36 P37 P38 P39 P40 P41 P42 P43 P44 P45 P46 P47 P48 P49 P50 P51 Q5 Q6 Q7 Q8 Q9 Q10 Q11 Q12 Q13 Q14 Q15 Q16 Q17 Q18 Q19 Q20 Q21 Q22 Q23 Q24 Q25 Q26 Q27 Q28 Q29 Q30 Q31 Q32 Q33 Q34 Q36 Q37 Q38 Q39 Q40 Q41 Q42 Q43 Q44 Q45 Q46 Q47 Q48 Q49 Q50 Q51 R5 R6 R7 R8 R9 R10 R11 R12 R13 R14 R15 R16 R17 R18 R19 R20 R21 R22 R23 R24 R25 R26 R27 R28 R29 R30 R31 R32 R33 R34 R36 R37 R38 R39 R40 R41 R42 R43 R44 R45 R46 R47 R48 R49 R50 R51 S5 S6 S7 S8 S9 S10 S11 S12 S13 S14 S15 S16 S17 S18 S19 S20 S21 S22 S23 S24 S25 S26 S27 S28 S29 S30 S31 S32 S33 S34 S36 S37 S38 S39 S40 S41 S42 S43 S44 S45 S46 S47 S48 S49 S50 S51 T5 T6 T7 T8 T9 T10 T11 T12 T13 T14 T15 T16 T17 T18 T19 T20 T21 T22 T23 T24 T25 T26 T27 T28 T29 T30 T31 T32 T33 T34 T36 T37 T38 T39 T40 T41 T42 T43 T44 T45 T46 T47 T48 T49 T50 T51 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U36 U37 U38 U39 U40 U41 U42 U43 U44 U45 U46 U47 U48 U49 U50 U51 V5 V6 V7 V8 V9 V10 V11 V12 V13 V14 V15 V16 V17 V18 V19 V20 V21 V22 V23 V24 V25 V26 V27 V28 V29 V30 V31 V32 V33 V34 V36 V37 V38 V39 V40 V41 V42 V43 V44 V45 V46 V47 V48 V49 V50 V51 W5 W6 W7 W8 W9 W10 W11 W12 W13 W14 W15 W16 W17 W18 W19 W20 W21 W22 W23 W24 W25 W26 W27 W28 W29 W30 W31 W32 W33 W34 W36 W37 W38 W39 W40 W41 W42 W43 W44 W45 W46 W47 W48 W49 W50 W51 X5 X6 X7 X8 X9 X10 X11 X12 X13 X14 X15 X16 X17 X18 X19 X20 X21 X22 X23 X24 X25 X26 X27 X28 X29 X30 X31 X32 X33 X34 X36 X37 X38 X39 X40 X41 X42 X43 X44 X45 X46 X47 X48 X49 X50 X51 Y5 Y6 Y7 Y8 Y9 Y10 Y11 Y12 Y13 Y14 Y15 Y16 Y17 Y18 Y19 Y20 Y21 Y22 Y23 Y24 Y25 Y26 Y27 Y28 Y29 Y30 Y31 Y32 Y33 Y34 Y36 Y37 Y38 Y39 Y40 Y41 Y42 Y43 Y44 Y45 Y46 Y47 Y48 Y49 Y50 Y51 Z5 Z6 Z7 Z8 Z9 Z10 Z11 Z12 Z13 Z14 Z15 Z16 Z17 Z18 Z19 Z20 Z21 Z22 Z23 Z24 Z25 Z26 Z27 Z28 Z29 Z30 Z31 Z32 Z33 Z34 Z36 Z37 Z38 Z39 Z40 Z41 Z42 Z43 Z44 Z45 Z46 Z47 Z48 Z49 Z50 Z51 AA5 AA6 AA7 AA8 AA9 AA10 AA11 AA12 AA13 AA14 AA15 AA16 AA17 AA18 AA19 AA20 AA21 AA22 AA23 AA24 AA25 AA26 AA27 AA28 AA29 AA30 AA31 AA32 AA33 AA34 AA36 AA37 AA38 AA39 AA40 AA41 AA42 AA43 AA44 AA45 AA46 AA47 AA48 AA49 AA50 AA51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Choose: Acquire, Deepen, Create, or ?" promptTitle="Select level" prompt="AI-CFT level" type="list">
+      <formula1>"Acquire,Deepen,Create,?"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 C17 C18 C19 C20 C21 C22 C23 C24 C25 C26 C27 C28 C29 C30 C31 C32 C33 C34 C36 C37 C38 C39 C40 C41 C42 C43 C44 C45 C46 C47 C48 C49 C50 C51 D5 D6 D7 D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19 D20 D21 D22 D23 D24 D25 D26 D27 D28 D29 D30 D31 D32 D33 D34 D36 D37 D38 D39 D40 D41 D42 D43 D44 D45 D46 D47 D48 D49 D50 D51 E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E24 E25 E26 E27 E28 E29 E30 E31 E32 E33 E34 E36 E37 E38 E39 E40 E41 E42 E43 E44 E45 E46 E47 E48 E49 E50 E51 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34 F36 F37 F38 F39 F40 F41 F42 F43 F44 F45 F46 F47 F48 F49 F50 F51 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 G31 G32 G33 G34 G36 G37 G38 G39 G40 G41 G42 G43 G44 G45 G46 G47 G48 G49 G50 G51 H5 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27 H28 H29 H30 H31 H32 H33 H34 H36 H37 H38 H39 H40 H41 H42 H43 H44 H45 H46 H47 H48 H49 H50 H51 I5 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I24 I25 I26 I27 I28 I29 I30 I31 I32 I33 I34 I36 I37 I38 I39 I40 I41 I42 I43 I44 I45 I46 I47 I48 I49 I50 I51 J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25 J26 J27 J28 J29 J30 J31 J32 J33 J34 J36 J37 J38 J39 J40 J41 J42 J43 J44 J45 J46 J47 J48 J49 J50 J51 K5 K6 K7 K8 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 K19 K20 K21 K22 K23 K24 K25 K26 K27 K28 K29 K30 K31 K32 K33 K34 K36 K37 K38 K39 K40 K41 K42 K43 K44 K45 K46 K47 K48 K49 K50 K51 L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26 L27 L28 L29 L30 L31 L32 L33 L34 L36 L37 L38 L39 L40 L41 L42 L43 L44 L45 L46 L47 L48 L49 L50 L51 M5 M6 M7 M8 M9 M10 M11 M12 M13 M14 M15 M16 M17 M18 M19 M20 M21 M22 M23 M24 M25 M26 M27 M28 M29 M30 M31 M32 M33 M34 M36 M37 M38 M39 M40 M41 M42 M43 M44 M45 M46 M47 M48 M49 M50 M51 N5 N6 N7 N8 N9 N10 N11 N12 N13 N14 N15 N16 N17 N18 N19 N20 N21 N22 N23 N24 N25 N26 N27 N28 N29 N30 N31 N32 N33 N34 N36 N37 N38 N39 N40 N41 N42 N43 N44 N45 N46 N47 N48 N49 N50 N51 O5 O6 O7 O8 O9 O10 O11 O12 O13 O14 O15 O16 O17 O18 O19 O20 O21 O22 O23 O24 O25 O26 O27 O28 O29 O30 O31 O32 O33 O34 O36 O37 O38 O39 O40 O41 O42 O43 O44 O45 O46 O47 O48 O49 O50 O51 P5 P6 P7 P8 P9 P10 P11 P12 P13 P14 P15 P16 P17 P18 P19 P20 P21 P22 P23 P24 P25 P26 P27 P28 P29 P30 P31 P32 P33 P34 P36 P37 P38 P39 P40 P41 P42 P43 P44 P45 P46 P47 P48 P49 P50 P51 Q5 Q6 Q7 Q8 Q9 Q10 Q11 Q12 Q13 Q14 Q15 Q16 Q17 Q18 Q19 Q20 Q21 Q22 Q23 Q24 Q25 Q26 Q27 Q28 Q29 Q30 Q31 Q32 Q33 Q34 Q36 Q37 Q38 Q39 Q40 Q41 Q42 Q43 Q44 Q45 Q46 Q47 Q48 Q49 Q50 Q51 R5 R6 R7 R8 R9 R10 R11 R12 R13 R14 R15 R16 R17 R18 R19 R20 R21 R22 R23 R24 R25 R26 R27 R28 R29 R30 R31 R32 R33 R34 R36 R37 R38 R39 R40 R41 R42 R43 R44 R45 R46 R47 R48 R49 R50 R51 S5 S6 S7 S8 S9 S10 S11 S12 S13 S14 S15 S16 S17 S18 S19 S20 S21 S22 S23 S24 S25 S26 S27 S28 S29 S30 S31 S32 S33 S34 S36 S37 S38 S39 S40 S41 S42 S43 S44 S45 S46 S47 S48 S49 S50 S51 T5 T6 T7 T8 T9 T10 T11 T12 T13 T14 T15 T16 T17 T18 T19 T20 T21 T22 T23 T24 T25 T26 T27 T28 T29 T30 T31 T32 T33 T34 T36 T37 T38 T39 T40 T41 T42 T43 T44 T45 T46 T47 T48 T49 T50 T51 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U36 U37 U38 U39 U40 U41 U42 U43 U44 U45 U46 U47 U48 U49 U50 U51 V5 V6 V7 V8 V9 V10 V11 V12 V13 V14 V15 V16 V17 V18 V19 V20 V21 V22 V23 V24 V25 V26 V27 V28 V29 V30 V31 V32 V33 V34 V36 V37 V38 V39 V40 V41 V42 V43 V44 V45 V46 V47 V48 V49 V50 V51 W5 W6 W7 W8 W9 W10 W11 W12 W13 W14 W15 W16 W17 W18 W19 W20 W21 W22 W23 W24 W25 W26 W27 W28 W29 W30 W31 W32 W33 W34 W36 W37 W38 W39 W40 W41 W42 W43 W44 W45 W46 W47 W48 W49 W50 W51 X5 X6 X7 X8 X9 X10 X11 X12 X13 X14 X15 X16 X17 X18 X19 X20 X21 X22 X23 X24 X25 X26 X27 X28 X29 X30 X31 X32 X33 X34 X36 X37 X38 X39 X40 X41 X42 X43 X44 X45 X46 X47 X48 X49 X50 X51 Y5 Y6 Y7 Y8 Y9 Y10 Y11 Y12 Y13 Y14 Y15 Y16 Y17 Y18 Y19 Y20 Y21 Y22 Y23 Y24 Y25 Y26 Y27 Y28 Y29 Y30 Y31 Y32 Y33 Y34 Y36 Y37 Y38 Y39 Y40 Y41 Y42 Y43 Y44 Y45 Y46 Y47 Y48 Y49 Y50 Y51 Z5 Z6 Z7 Z8 Z9 Z10 Z11 Z12 Z13 Z14 Z15 Z16 Z17 Z18 Z19 Z20 Z21 Z22 Z23 Z24 Z25 Z26 Z27 Z28 Z29 Z30 Z31 Z32 Z33 Z34 Z36 Z37 Z38 Z39 Z40 Z41 Z42 Z43 Z44 Z45 Z46 Z47 Z48 Z49 Z50 Z51 AA5 AA6 AA7 AA8 AA9 AA10 AA11 AA12 AA13 AA14 AA15 AA16 AA17 AA18 AA19 AA20 AA21 AA22 AA23 AA24 AA25 AA26 AA27 AA28 AA29 AA30 AA31 AA32 AA33 AA34 AA36 AA37 AA38 AA39 AA40 AA41 AA42 AA43 AA44 AA45 AA46 AA47 AA48 AA49 AA50 AA51 AB5 AB6 AB7 AB8 AB9 AB10 AB11 AB12 AB13 AB14 AB15 AB16 AB17 AB18 AB19 AB20 AB21 AB22 AB23 AB24 AB25 AB26 AB27 AB28 AB29 AB30 AB31 AB32 AB33 AB34 AB36 AB37 AB38 AB39 AB40 AB41 AB42 AB43 AB44 AB45 AB46 AB47 AB48 AB49 AB50 AB51 AC5 AC6 AC7 AC8 AC9 AC10 AC11 AC12 AC13 AC14 AC15 AC16 AC17 AC18 AC19 AC20 AC21 AC22 AC23 AC24 AC25 AC26 AC27 AC28 AC29 AC30 AC31 AC32 AC33 AC34 AC36 AC37 AC38 AC39 AC40 AC41 AC42 AC43 AC44 AC45 AC46 AC47 AC48 AC49 AC50 AC51 AD5 AD6 AD7 AD8 AD9 AD10 AD11 AD12 AD13 AD14 AD15 AD16 AD17 AD18 AD19 AD20 AD21 AD22 AD23 AD24 AD25 AD26 AD27 AD28 AD29 AD30 AD31 AD32 AD33 AD34 AD36 AD37 AD38 AD39 AD40 AD41 AD42 AD43 AD44 AD45 AD46 AD47 AD48 AD49 AD50 AD51 AE5 AE6 AE7 AE8 AE9 AE10 AE11 AE12 AE13 AE14 AE15 AE16 AE17 AE18 AE19 AE20 AE21 AE22 AE23 AE24 AE25 AE26 AE27 AE28 AE29 AE30 AE31 AE32 AE33 AE34 AE36 AE37 AE38 AE39 AE40 AE41 AE42 AE43 AE44 AE45 AE46 AE47 AE48 AE49 AE50 AE51 AF5 AF6 AF7 AF8 AF9 AF10 AF11 AF12 AF13 AF14 AF15 AF16 AF17 AF18 AF19 AF20 AF21 AF22 AF23 AF24 AF25 AF26 AF27 AF28 AF29 AF30 AF31 AF32 AF33 AF34 AF36 AF37 AF38 AF39 AF40 AF41 AF42 AF43 AF44 AF45 AF46 AF47 AF48 AF49 AF50 AF51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Acquire,Deepen,Create,?"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6385,7 +6697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H54"/>
+  <dimension ref="A1:J54"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" style="51" min="1" max="1"/>
@@ -6394,31 +6706,33 @@
     <col width="18" customWidth="1" style="51" min="4" max="4"/>
     <col width="18" customWidth="1" style="51" min="5" max="5"/>
     <col width="18" customWidth="1" style="51" min="6" max="6"/>
-    <col width="14" customWidth="1" style="51" min="7" max="7"/>
-    <col width="22" customWidth="1" style="51" min="8" max="8"/>
+    <col width="18" customWidth="1" style="51" min="7" max="7"/>
+    <col width="18" customWidth="1" style="51" min="8" max="8"/>
+    <col width="14" customWidth="1" style="51" min="9" max="9"/>
+    <col width="22" customWidth="1" style="51" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" s="51">
       <c r="A1" s="77" t="inlineStr">
         <is>
-          <t>AI-CFT Labeling — WS4 - Best Threshold</t>
+          <t>AI-CFT Labeling — WS4</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1" s="51">
-      <c r="A2" s="78" t="inlineStr">
+      <c r="A2" s="91" t="inlineStr">
         <is>
           <t>Cohort</t>
         </is>
       </c>
-      <c r="B2" s="78" t="inlineStr">
+      <c r="B2" s="91" t="inlineStr">
         <is>
           <t>Student</t>
         </is>
       </c>
-      <c r="C2" s="79" t="inlineStr">
-        <is>
-          <t>Acquire</t>
+      <c r="C2" s="88" t="inlineStr">
+        <is>
+          <t>Deepen</t>
         </is>
       </c>
       <c r="D2" s="88" t="inlineStr">
@@ -6436,12 +6750,22 @@
           <t>Deepen</t>
         </is>
       </c>
-      <c r="G2" s="80" t="inlineStr">
+      <c r="G2" s="88" t="inlineStr">
+        <is>
+          <t>Deepen</t>
+        </is>
+      </c>
+      <c r="H2" s="88" t="inlineStr">
+        <is>
+          <t>Deepen</t>
+        </is>
+      </c>
+      <c r="I2" s="80" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H2" s="80" t="inlineStr">
+      <c r="J2" s="80" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6473,21 +6797,33 @@
       <c r="E3" s="82" t="inlineStr">
         <is>
           <t>Blank 3
+Threshold justification</t>
+        </is>
+      </c>
+      <c r="F3" s="82" t="inlineStr">
+        <is>
+          <t>Blank 4
 Pia correct?</t>
         </is>
       </c>
-      <c r="F3" s="82" t="inlineStr">
-        <is>
-          <t>Blank 4
-Best energy threshold</t>
-        </is>
-      </c>
       <c r="G3" s="82" t="inlineStr">
         <is>
+          <t>Blank 5
+Sorted cards annotation</t>
+        </is>
+      </c>
+      <c r="H3" s="82" t="inlineStr">
+        <is>
+          <t>Blank 6
+Best energy threshold value</t>
+        </is>
+      </c>
+      <c r="I3" s="82" t="inlineStr">
+        <is>
           <t>Overall WS4</t>
         </is>
       </c>
-      <c r="H3" s="82" t="inlineStr">
+      <c r="J3" s="82" t="inlineStr">
         <is>
           <t>Notes WS4</t>
         </is>
@@ -6506,13 +6842,19 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="B5" s="86" t="n"/>
-      <c r="C5" s="86" t="n"/>
-      <c r="D5" s="86" t="n"/>
-      <c r="E5" s="86" t="n"/>
-      <c r="F5" s="86" t="n"/>
-      <c r="G5" s="86" t="n"/>
-      <c r="H5" s="87" t="n"/>
+      <c r="B5" s="84" t="inlineStr">
+        <is>
+          <t>Ozzy</t>
+        </is>
+      </c>
+      <c r="C5" s="84" t="n"/>
+      <c r="D5" s="84" t="n"/>
+      <c r="E5" s="84" t="n"/>
+      <c r="F5" s="84" t="n"/>
+      <c r="G5" s="84" t="n"/>
+      <c r="H5" s="84" t="n"/>
+      <c r="I5" s="84" t="n"/>
+      <c r="J5" s="84" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1" s="51">
       <c r="A6" s="85" t="inlineStr">
@@ -6531,6 +6873,8 @@
       <c r="F6" s="85" t="n"/>
       <c r="G6" s="85" t="n"/>
       <c r="H6" s="85" t="n"/>
+      <c r="I6" s="85" t="n"/>
+      <c r="J6" s="85" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1" s="51">
       <c r="A7" s="84" t="inlineStr">
@@ -6549,6 +6893,8 @@
       <c r="F7" s="84" t="n"/>
       <c r="G7" s="84" t="n"/>
       <c r="H7" s="84" t="n"/>
+      <c r="I7" s="84" t="n"/>
+      <c r="J7" s="84" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1" s="51">
       <c r="A8" s="85" t="inlineStr">
@@ -6567,6 +6913,8 @@
       <c r="F8" s="85" t="n"/>
       <c r="G8" s="85" t="n"/>
       <c r="H8" s="85" t="n"/>
+      <c r="I8" s="85" t="n"/>
+      <c r="J8" s="85" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1" s="51">
       <c r="A9" s="84" t="inlineStr">
@@ -6585,6 +6933,8 @@
       <c r="F9" s="84" t="n"/>
       <c r="G9" s="84" t="n"/>
       <c r="H9" s="84" t="n"/>
+      <c r="I9" s="84" t="n"/>
+      <c r="J9" s="84" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1" s="51">
       <c r="A10" s="85" t="inlineStr">
@@ -6603,6 +6953,8 @@
       <c r="F10" s="85" t="n"/>
       <c r="G10" s="85" t="n"/>
       <c r="H10" s="85" t="n"/>
+      <c r="I10" s="85" t="n"/>
+      <c r="J10" s="85" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1" s="51">
       <c r="A11" s="84" t="inlineStr">
@@ -6621,6 +6973,8 @@
       <c r="F11" s="84" t="n"/>
       <c r="G11" s="84" t="n"/>
       <c r="H11" s="84" t="n"/>
+      <c r="I11" s="84" t="n"/>
+      <c r="J11" s="84" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1" s="51">
       <c r="A12" s="85" t="inlineStr">
@@ -6639,6 +6993,8 @@
       <c r="F12" s="85" t="n"/>
       <c r="G12" s="85" t="n"/>
       <c r="H12" s="85" t="n"/>
+      <c r="I12" s="85" t="n"/>
+      <c r="J12" s="85" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1" s="51">
       <c r="A13" s="84" t="inlineStr">
@@ -6657,6 +7013,8 @@
       <c r="F13" s="84" t="n"/>
       <c r="G13" s="84" t="n"/>
       <c r="H13" s="84" t="n"/>
+      <c r="I13" s="84" t="n"/>
+      <c r="J13" s="84" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1" s="51">
       <c r="A14" s="85" t="inlineStr">
@@ -6675,6 +7033,8 @@
       <c r="F14" s="85" t="n"/>
       <c r="G14" s="85" t="n"/>
       <c r="H14" s="85" t="n"/>
+      <c r="I14" s="85" t="n"/>
+      <c r="J14" s="85" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1" s="51">
       <c r="A15" s="84" t="inlineStr">
@@ -6693,6 +7053,8 @@
       <c r="F15" s="84" t="n"/>
       <c r="G15" s="84" t="n"/>
       <c r="H15" s="84" t="n"/>
+      <c r="I15" s="84" t="n"/>
+      <c r="J15" s="84" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1" s="51">
       <c r="A16" s="85" t="inlineStr">
@@ -6711,6 +7073,8 @@
       <c r="F16" s="85" t="n"/>
       <c r="G16" s="85" t="n"/>
       <c r="H16" s="85" t="n"/>
+      <c r="I16" s="85" t="n"/>
+      <c r="J16" s="85" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1" s="51">
       <c r="A17" s="84" t="inlineStr">
@@ -6729,6 +7093,8 @@
       <c r="F17" s="84" t="n"/>
       <c r="G17" s="84" t="n"/>
       <c r="H17" s="84" t="n"/>
+      <c r="I17" s="84" t="n"/>
+      <c r="J17" s="84" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1" s="51">
       <c r="A18" s="85" t="inlineStr">
@@ -6747,6 +7113,8 @@
       <c r="F18" s="85" t="n"/>
       <c r="G18" s="85" t="n"/>
       <c r="H18" s="85" t="n"/>
+      <c r="I18" s="85" t="n"/>
+      <c r="J18" s="85" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1" s="51">
       <c r="A19" s="84" t="inlineStr">
@@ -6765,6 +7133,8 @@
       <c r="F19" s="84" t="n"/>
       <c r="G19" s="84" t="n"/>
       <c r="H19" s="84" t="n"/>
+      <c r="I19" s="84" t="n"/>
+      <c r="J19" s="84" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1" s="51">
       <c r="A20" s="85" t="inlineStr">
@@ -6783,6 +7153,8 @@
       <c r="F20" s="85" t="n"/>
       <c r="G20" s="85" t="n"/>
       <c r="H20" s="85" t="n"/>
+      <c r="I20" s="85" t="n"/>
+      <c r="J20" s="85" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1" s="51">
       <c r="A21" s="84" t="inlineStr">
@@ -6801,6 +7173,8 @@
       <c r="F21" s="84" t="n"/>
       <c r="G21" s="84" t="n"/>
       <c r="H21" s="84" t="n"/>
+      <c r="I21" s="84" t="n"/>
+      <c r="J21" s="84" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1" s="51">
       <c r="A22" s="85" t="inlineStr">
@@ -6819,6 +7193,8 @@
       <c r="F22" s="85" t="n"/>
       <c r="G22" s="85" t="n"/>
       <c r="H22" s="85" t="n"/>
+      <c r="I22" s="85" t="n"/>
+      <c r="J22" s="85" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1" s="51">
       <c r="A23" s="84" t="inlineStr">
@@ -6837,6 +7213,8 @@
       <c r="F23" s="84" t="n"/>
       <c r="G23" s="84" t="n"/>
       <c r="H23" s="84" t="n"/>
+      <c r="I23" s="84" t="n"/>
+      <c r="J23" s="84" t="n"/>
     </row>
     <row r="24" ht="18" customHeight="1" s="51">
       <c r="A24" s="85" t="inlineStr">
@@ -6855,6 +7233,8 @@
       <c r="F24" s="85" t="n"/>
       <c r="G24" s="85" t="n"/>
       <c r="H24" s="85" t="n"/>
+      <c r="I24" s="85" t="n"/>
+      <c r="J24" s="85" t="n"/>
     </row>
     <row r="25" ht="18" customHeight="1" s="51">
       <c r="A25" s="84" t="inlineStr">
@@ -6873,6 +7253,8 @@
       <c r="F25" s="84" t="n"/>
       <c r="G25" s="84" t="n"/>
       <c r="H25" s="84" t="n"/>
+      <c r="I25" s="84" t="n"/>
+      <c r="J25" s="84" t="n"/>
     </row>
     <row r="26" ht="18" customHeight="1" s="51">
       <c r="A26" s="85" t="inlineStr">
@@ -6891,6 +7273,8 @@
       <c r="F26" s="85" t="n"/>
       <c r="G26" s="85" t="n"/>
       <c r="H26" s="85" t="n"/>
+      <c r="I26" s="85" t="n"/>
+      <c r="J26" s="85" t="n"/>
     </row>
     <row r="27" ht="18" customHeight="1" s="51">
       <c r="A27" s="84" t="inlineStr">
@@ -6909,6 +7293,8 @@
       <c r="F27" s="84" t="n"/>
       <c r="G27" s="84" t="n"/>
       <c r="H27" s="84" t="n"/>
+      <c r="I27" s="84" t="n"/>
+      <c r="J27" s="84" t="n"/>
     </row>
     <row r="28" ht="18" customHeight="1" s="51">
       <c r="A28" s="85" t="inlineStr">
@@ -6927,6 +7313,8 @@
       <c r="F28" s="85" t="n"/>
       <c r="G28" s="85" t="n"/>
       <c r="H28" s="85" t="n"/>
+      <c r="I28" s="85" t="n"/>
+      <c r="J28" s="85" t="n"/>
     </row>
     <row r="29" ht="18" customHeight="1" s="51">
       <c r="A29" s="84" t="inlineStr">
@@ -6945,6 +7333,8 @@
       <c r="F29" s="84" t="n"/>
       <c r="G29" s="84" t="n"/>
       <c r="H29" s="84" t="n"/>
+      <c r="I29" s="84" t="n"/>
+      <c r="J29" s="84" t="n"/>
     </row>
     <row r="30" ht="18" customHeight="1" s="51">
       <c r="A30" s="85" t="inlineStr">
@@ -6963,6 +7353,8 @@
       <c r="F30" s="85" t="n"/>
       <c r="G30" s="85" t="n"/>
       <c r="H30" s="85" t="n"/>
+      <c r="I30" s="85" t="n"/>
+      <c r="J30" s="85" t="n"/>
     </row>
     <row r="31" ht="18" customHeight="1" s="51">
       <c r="A31" s="84" t="inlineStr">
@@ -6981,6 +7373,8 @@
       <c r="F31" s="84" t="n"/>
       <c r="G31" s="84" t="n"/>
       <c r="H31" s="84" t="n"/>
+      <c r="I31" s="84" t="n"/>
+      <c r="J31" s="84" t="n"/>
     </row>
     <row r="32" ht="18" customHeight="1" s="51">
       <c r="A32" s="85" t="inlineStr">
@@ -6999,6 +7393,8 @@
       <c r="F32" s="85" t="n"/>
       <c r="G32" s="85" t="n"/>
       <c r="H32" s="85" t="n"/>
+      <c r="I32" s="85" t="n"/>
+      <c r="J32" s="85" t="n"/>
     </row>
     <row r="33" ht="18" customHeight="1" s="51">
       <c r="A33" s="84" t="inlineStr">
@@ -7017,6 +7413,8 @@
       <c r="F33" s="84" t="n"/>
       <c r="G33" s="84" t="n"/>
       <c r="H33" s="84" t="n"/>
+      <c r="I33" s="84" t="n"/>
+      <c r="J33" s="84" t="n"/>
     </row>
     <row r="34" ht="18" customHeight="1" s="51">
       <c r="A34" s="85" t="inlineStr">
@@ -7024,13 +7422,19 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="B34" s="85" t="n"/>
+      <c r="B34" s="85" t="inlineStr">
+        <is>
+          <t>Sabrina</t>
+        </is>
+      </c>
       <c r="C34" s="85" t="n"/>
       <c r="D34" s="85" t="n"/>
       <c r="E34" s="85" t="n"/>
       <c r="F34" s="85" t="n"/>
       <c r="G34" s="85" t="n"/>
       <c r="H34" s="85" t="n"/>
+      <c r="I34" s="85" t="n"/>
+      <c r="J34" s="85" t="n"/>
     </row>
     <row r="35" ht="20" customHeight="1" s="51">
       <c r="A35" s="83" t="inlineStr">
@@ -7045,13 +7449,19 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="B36" s="86" t="n"/>
-      <c r="C36" s="86" t="n"/>
-      <c r="D36" s="86" t="n"/>
-      <c r="E36" s="86" t="n"/>
-      <c r="F36" s="86" t="n"/>
-      <c r="G36" s="86" t="n"/>
-      <c r="H36" s="87" t="n"/>
+      <c r="B36" s="84" t="inlineStr">
+        <is>
+          <t>Sheila</t>
+        </is>
+      </c>
+      <c r="C36" s="84" t="n"/>
+      <c r="D36" s="84" t="n"/>
+      <c r="E36" s="84" t="n"/>
+      <c r="F36" s="84" t="n"/>
+      <c r="G36" s="84" t="n"/>
+      <c r="H36" s="84" t="n"/>
+      <c r="I36" s="84" t="n"/>
+      <c r="J36" s="84" t="n"/>
     </row>
     <row r="37" ht="18" customHeight="1" s="51">
       <c r="A37" s="85" t="inlineStr">
@@ -7070,6 +7480,8 @@
       <c r="F37" s="85" t="n"/>
       <c r="G37" s="85" t="n"/>
       <c r="H37" s="85" t="n"/>
+      <c r="I37" s="85" t="n"/>
+      <c r="J37" s="85" t="n"/>
     </row>
     <row r="38" ht="18" customHeight="1" s="51">
       <c r="A38" s="84" t="inlineStr">
@@ -7088,6 +7500,8 @@
       <c r="F38" s="84" t="n"/>
       <c r="G38" s="84" t="n"/>
       <c r="H38" s="84" t="n"/>
+      <c r="I38" s="84" t="n"/>
+      <c r="J38" s="84" t="n"/>
     </row>
     <row r="39" ht="18" customHeight="1" s="51">
       <c r="A39" s="85" t="inlineStr">
@@ -7106,6 +7520,8 @@
       <c r="F39" s="85" t="n"/>
       <c r="G39" s="85" t="n"/>
       <c r="H39" s="85" t="n"/>
+      <c r="I39" s="85" t="n"/>
+      <c r="J39" s="85" t="n"/>
     </row>
     <row r="40" ht="18" customHeight="1" s="51">
       <c r="A40" s="84" t="inlineStr">
@@ -7124,6 +7540,8 @@
       <c r="F40" s="84" t="n"/>
       <c r="G40" s="84" t="n"/>
       <c r="H40" s="84" t="n"/>
+      <c r="I40" s="84" t="n"/>
+      <c r="J40" s="84" t="n"/>
     </row>
     <row r="41" ht="18" customHeight="1" s="51">
       <c r="A41" s="85" t="inlineStr">
@@ -7142,6 +7560,8 @@
       <c r="F41" s="85" t="n"/>
       <c r="G41" s="85" t="n"/>
       <c r="H41" s="85" t="n"/>
+      <c r="I41" s="85" t="n"/>
+      <c r="J41" s="85" t="n"/>
     </row>
     <row r="42" ht="18" customHeight="1" s="51">
       <c r="A42" s="84" t="inlineStr">
@@ -7160,6 +7580,8 @@
       <c r="F42" s="84" t="n"/>
       <c r="G42" s="84" t="n"/>
       <c r="H42" s="84" t="n"/>
+      <c r="I42" s="84" t="n"/>
+      <c r="J42" s="84" t="n"/>
     </row>
     <row r="43" ht="18" customHeight="1" s="51">
       <c r="A43" s="85" t="inlineStr">
@@ -7178,6 +7600,8 @@
       <c r="F43" s="85" t="n"/>
       <c r="G43" s="85" t="n"/>
       <c r="H43" s="85" t="n"/>
+      <c r="I43" s="85" t="n"/>
+      <c r="J43" s="85" t="n"/>
     </row>
     <row r="44" ht="18" customHeight="1" s="51">
       <c r="A44" s="84" t="inlineStr">
@@ -7196,6 +7620,8 @@
       <c r="F44" s="84" t="n"/>
       <c r="G44" s="84" t="n"/>
       <c r="H44" s="84" t="n"/>
+      <c r="I44" s="84" t="n"/>
+      <c r="J44" s="84" t="n"/>
     </row>
     <row r="45" ht="18" customHeight="1" s="51">
       <c r="A45" s="85" t="inlineStr">
@@ -7214,6 +7640,8 @@
       <c r="F45" s="85" t="n"/>
       <c r="G45" s="85" t="n"/>
       <c r="H45" s="85" t="n"/>
+      <c r="I45" s="85" t="n"/>
+      <c r="J45" s="85" t="n"/>
     </row>
     <row r="46" ht="18" customHeight="1" s="51">
       <c r="A46" s="84" t="inlineStr">
@@ -7232,6 +7660,8 @@
       <c r="F46" s="84" t="n"/>
       <c r="G46" s="84" t="n"/>
       <c r="H46" s="84" t="n"/>
+      <c r="I46" s="84" t="n"/>
+      <c r="J46" s="84" t="n"/>
     </row>
     <row r="47" ht="18" customHeight="1" s="51">
       <c r="A47" s="85" t="inlineStr">
@@ -7250,6 +7680,8 @@
       <c r="F47" s="85" t="n"/>
       <c r="G47" s="85" t="n"/>
       <c r="H47" s="85" t="n"/>
+      <c r="I47" s="85" t="n"/>
+      <c r="J47" s="85" t="n"/>
     </row>
     <row r="48" ht="18" customHeight="1" s="51">
       <c r="A48" s="84" t="inlineStr">
@@ -7268,6 +7700,8 @@
       <c r="F48" s="84" t="n"/>
       <c r="G48" s="84" t="n"/>
       <c r="H48" s="84" t="n"/>
+      <c r="I48" s="84" t="n"/>
+      <c r="J48" s="84" t="n"/>
     </row>
     <row r="49" ht="18" customHeight="1" s="51">
       <c r="A49" s="85" t="inlineStr">
@@ -7286,6 +7720,8 @@
       <c r="F49" s="85" t="n"/>
       <c r="G49" s="85" t="n"/>
       <c r="H49" s="85" t="n"/>
+      <c r="I49" s="85" t="n"/>
+      <c r="J49" s="85" t="n"/>
     </row>
     <row r="50" ht="18" customHeight="1" s="51">
       <c r="A50" s="84" t="inlineStr">
@@ -7304,6 +7740,8 @@
       <c r="F50" s="84" t="n"/>
       <c r="G50" s="84" t="n"/>
       <c r="H50" s="84" t="n"/>
+      <c r="I50" s="84" t="n"/>
+      <c r="J50" s="84" t="n"/>
     </row>
     <row r="51" ht="18" customHeight="1" s="51">
       <c r="A51" s="85" t="inlineStr">
@@ -7322,74 +7760,71 @@
       <c r="F51" s="85" t="n"/>
       <c r="G51" s="85" t="n"/>
       <c r="H51" s="85" t="n"/>
+      <c r="I51" s="85" t="n"/>
+      <c r="J51" s="85" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="84" t="inlineStr">
-        <is>
-          <t>Dropdown values: Acquire | Deepen | Create | ? (unscorable/blank)</t>
-        </is>
-      </c>
-      <c r="B53" s="86" t="n"/>
-      <c r="C53" s="86" t="n"/>
-      <c r="D53" s="86" t="n"/>
-      <c r="E53" s="86" t="n"/>
-      <c r="F53" s="86" t="n"/>
-      <c r="G53" s="86" t="n"/>
-      <c r="H53" s="87" t="n"/>
-    </row>
-    <row r="54" ht="40" customHeight="1" s="51">
-      <c r="A54" s="85" t="inlineStr">
+      <c r="A53" s="92" t="inlineStr">
         <is>
           <t>Task descriptions:</t>
         </is>
       </c>
-      <c r="B54" s="85" t="n"/>
-      <c r="C54" s="90" t="inlineStr">
+    </row>
+    <row r="54" ht="60" customHeight="1" s="51">
+      <c r="C54" s="93" t="inlineStr">
         <is>
           <t>Circle 4 misclassified
-Circles all 4 incorrectly classified food cards at Leo's threshold</t>
-        </is>
-      </c>
-      <c r="D54" s="90" t="inlineStr">
+Identify which 4 food cards are incorrectly classified at Leo's threshold</t>
+        </is>
+      </c>
+      <c r="D54" s="93" t="inlineStr">
         <is>
           <t>Better threshold position
-Places threshold between two adjacent distinct fat values; written justification present</t>
-        </is>
-      </c>
-      <c r="E54" s="90" t="inlineStr">
+Mark a better threshold line between two adjacent foods on the sorted card row</t>
+        </is>
+      </c>
+      <c r="E54" s="93" t="inlineStr">
+        <is>
+          <t>Threshold justification
+Written explanation of why chosen threshold is better than Leo's</t>
+        </is>
+      </c>
+      <c r="F54" s="93" t="inlineStr">
         <is>
           <t>Pia correct?
-Explains why equal-valued items cannot be split (Pia is correct; equal values cannot be separated)</t>
-        </is>
-      </c>
-      <c r="F54" s="90" t="inlineStr">
-        <is>
-          <t>Best energy threshold
-Sorts cards, fills table, writes best energy threshold in final blank</t>
-        </is>
-      </c>
-      <c r="G54" s="85" t="inlineStr">
-        <is>
-          <t>Overall AI-CFT level for WS4 as a whole</t>
-        </is>
-      </c>
-      <c r="H54" s="85" t="inlineStr">
-        <is>
-          <t>Free notes</t>
+Explanation of why Leo's exact pencil placement cannot be a valid threshold (equal values cannot be split)</t>
+        </is>
+      </c>
+      <c r="G54" s="93" t="inlineStr">
+        <is>
+          <t>Sorted cards annotation
+Sort and annotate energy cards with the best threshold line drawn</t>
+        </is>
+      </c>
+      <c r="H54" s="93" t="inlineStr">
+        <is>
+          <t>Best energy threshold value
+Fill in: 'Best threshold value for energy variable: ___' (numerical value)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="9">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="A53:H53"/>
     <mergeCell ref="A35:H35"/>
+    <mergeCell ref="A35:J35"/>
     <mergeCell ref="A36:H36"/>
+    <mergeCell ref="A4:J4"/>
     <mergeCell ref="A5:H5"/>
   </mergeCells>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation sqref="C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 C17 C18 C19 C20 C21 C22 C23 C24 C25 C26 C27 C28 C29 C30 C31 C32 C33 C34 C36 C37 C38 C39 C40 C41 C42 C43 C44 C45 C46 C47 C48 C49 C50 C51 D5 D6 D7 D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19 D20 D21 D22 D23 D24 D25 D26 D27 D28 D29 D30 D31 D32 D33 D34 D36 D37 D38 D39 D40 D41 D42 D43 D44 D45 D46 D47 D48 D49 D50 D51 E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E24 E25 E26 E27 E28 E29 E30 E31 E32 E33 E34 E36 E37 E38 E39 E40 E41 E42 E43 E44 E45 E46 E47 E48 E49 E50 E51 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34 F36 F37 F38 F39 F40 F41 F42 F43 F44 F45 F46 F47 F48 F49 F50 F51 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 G31 G32 G33 G34 G36 G37 G38 G39 G40 G41 G42 G43 G44 G45 G46 G47 G48 G49 G50 G51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Choose: Acquire, Deepen, Create, or ?" promptTitle="Select level" prompt="AI-CFT level" type="list">
+      <formula1>"Acquire,Deepen,Create,?"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 C17 C18 C19 C20 C21 C22 C23 C24 C25 C26 C27 C28 C29 C30 C31 C32 C33 C34 C36 C37 C38 C39 C40 C41 C42 C43 C44 C45 C46 C47 C48 C49 C50 C51 D5 D6 D7 D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19 D20 D21 D22 D23 D24 D25 D26 D27 D28 D29 D30 D31 D32 D33 D34 D36 D37 D38 D39 D40 D41 D42 D43 D44 D45 D46 D47 D48 D49 D50 D51 E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E24 E25 E26 E27 E28 E29 E30 E31 E32 E33 E34 E36 E37 E38 E39 E40 E41 E42 E43 E44 E45 E46 E47 E48 E49 E50 E51 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34 F36 F37 F38 F39 F40 F41 F42 F43 F44 F45 F46 F47 F48 F49 F50 F51 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 G31 G32 G33 G34 G36 G37 G38 G39 G40 G41 G42 G43 G44 G45 G46 G47 G48 G49 G50 G51 H5 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27 H28 H29 H30 H31 H32 H33 H34 H36 H37 H38 H39 H40 H41 H42 H43 H44 H45 H46 H47 H48 H49 H50 H51 I5 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I24 I25 I26 I27 I28 I29 I30 I31 I32 I33 I34 I36 I37 I38 I39 I40 I41 I42 I43 I44 I45 I46 I47 I48 I49 I50 I51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Acquire,Deepen,Create,?"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7403,7 +7838,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K54"/>
+  <dimension ref="A1:AF54"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" style="51" min="1" max="1"/>
@@ -7415,31 +7850,52 @@
     <col width="18" customWidth="1" style="51" min="7" max="7"/>
     <col width="18" customWidth="1" style="51" min="8" max="8"/>
     <col width="18" customWidth="1" style="51" min="9" max="9"/>
-    <col width="14" customWidth="1" style="51" min="10" max="10"/>
-    <col width="22" customWidth="1" style="51" min="11" max="11"/>
+    <col width="18" customWidth="1" style="51" min="10" max="10"/>
+    <col width="18" customWidth="1" style="51" min="11" max="11"/>
+    <col width="18" customWidth="1" style="51" min="12" max="12"/>
+    <col width="18" customWidth="1" style="51" min="13" max="13"/>
+    <col width="18" customWidth="1" style="51" min="14" max="14"/>
+    <col width="18" customWidth="1" style="51" min="15" max="15"/>
+    <col width="18" customWidth="1" style="51" min="16" max="16"/>
+    <col width="18" customWidth="1" style="51" min="17" max="17"/>
+    <col width="18" customWidth="1" style="51" min="18" max="18"/>
+    <col width="18" customWidth="1" style="51" min="19" max="19"/>
+    <col width="18" customWidth="1" style="51" min="20" max="20"/>
+    <col width="18" customWidth="1" style="51" min="21" max="21"/>
+    <col width="18" customWidth="1" style="51" min="22" max="22"/>
+    <col width="18" customWidth="1" style="51" min="23" max="23"/>
+    <col width="18" customWidth="1" style="51" min="24" max="24"/>
+    <col width="18" customWidth="1" style="51" min="25" max="25"/>
+    <col width="18" customWidth="1" style="51" min="26" max="26"/>
+    <col width="18" customWidth="1" style="51" min="27" max="27"/>
+    <col width="18" customWidth="1" style="51" min="28" max="28"/>
+    <col width="18" customWidth="1" style="51" min="29" max="29"/>
+    <col width="18" customWidth="1" style="51" min="30" max="30"/>
+    <col width="14" customWidth="1" style="51" min="31" max="31"/>
+    <col width="22" customWidth="1" style="51" min="32" max="32"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" s="51">
       <c r="A1" s="77" t="inlineStr">
         <is>
-          <t>AI-CFT Labeling — WS5 - Try Thresholds</t>
+          <t>AI-CFT Labeling — WS5</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1" s="51">
-      <c r="A2" s="78" t="inlineStr">
+      <c r="A2" s="91" t="inlineStr">
         <is>
           <t>Cohort</t>
         </is>
       </c>
-      <c r="B2" s="78" t="inlineStr">
+      <c r="B2" s="91" t="inlineStr">
         <is>
           <t>Student</t>
         </is>
       </c>
-      <c r="C2" s="79" t="inlineStr">
-        <is>
-          <t>Acquire</t>
+      <c r="C2" s="88" t="inlineStr">
+        <is>
+          <t>Deepen</t>
         </is>
       </c>
       <c r="D2" s="88" t="inlineStr">
@@ -7447,9 +7903,9 @@
           <t>Deepen</t>
         </is>
       </c>
-      <c r="E2" s="79" t="inlineStr">
-        <is>
-          <t>Acquire</t>
+      <c r="E2" s="88" t="inlineStr">
+        <is>
+          <t>Deepen</t>
         </is>
       </c>
       <c r="F2" s="88" t="inlineStr">
@@ -7457,9 +7913,9 @@
           <t>Deepen</t>
         </is>
       </c>
-      <c r="G2" s="79" t="inlineStr">
-        <is>
-          <t>Acquire</t>
+      <c r="G2" s="88" t="inlineStr">
+        <is>
+          <t>Deepen</t>
         </is>
       </c>
       <c r="H2" s="88" t="inlineStr">
@@ -7472,12 +7928,117 @@
           <t>Deepen</t>
         </is>
       </c>
-      <c r="J2" s="80" t="inlineStr">
+      <c r="J2" s="88" t="inlineStr">
+        <is>
+          <t>Deepen</t>
+        </is>
+      </c>
+      <c r="K2" s="88" t="inlineStr">
+        <is>
+          <t>Deepen</t>
+        </is>
+      </c>
+      <c r="L2" s="88" t="inlineStr">
+        <is>
+          <t>Deepen</t>
+        </is>
+      </c>
+      <c r="M2" s="88" t="inlineStr">
+        <is>
+          <t>Deepen</t>
+        </is>
+      </c>
+      <c r="N2" s="88" t="inlineStr">
+        <is>
+          <t>Deepen</t>
+        </is>
+      </c>
+      <c r="O2" s="88" t="inlineStr">
+        <is>
+          <t>Deepen</t>
+        </is>
+      </c>
+      <c r="P2" s="88" t="inlineStr">
+        <is>
+          <t>Deepen</t>
+        </is>
+      </c>
+      <c r="Q2" s="88" t="inlineStr">
+        <is>
+          <t>Deepen</t>
+        </is>
+      </c>
+      <c r="R2" s="88" t="inlineStr">
+        <is>
+          <t>Deepen</t>
+        </is>
+      </c>
+      <c r="S2" s="88" t="inlineStr">
+        <is>
+          <t>Deepen</t>
+        </is>
+      </c>
+      <c r="T2" s="88" t="inlineStr">
+        <is>
+          <t>Deepen</t>
+        </is>
+      </c>
+      <c r="U2" s="88" t="inlineStr">
+        <is>
+          <t>Deepen</t>
+        </is>
+      </c>
+      <c r="V2" s="88" t="inlineStr">
+        <is>
+          <t>Deepen</t>
+        </is>
+      </c>
+      <c r="W2" s="88" t="inlineStr">
+        <is>
+          <t>Deepen</t>
+        </is>
+      </c>
+      <c r="X2" s="88" t="inlineStr">
+        <is>
+          <t>Deepen</t>
+        </is>
+      </c>
+      <c r="Y2" s="88" t="inlineStr">
+        <is>
+          <t>Deepen</t>
+        </is>
+      </c>
+      <c r="Z2" s="88" t="inlineStr">
+        <is>
+          <t>Deepen</t>
+        </is>
+      </c>
+      <c r="AA2" s="88" t="inlineStr">
+        <is>
+          <t>Deepen</t>
+        </is>
+      </c>
+      <c r="AB2" s="88" t="inlineStr">
+        <is>
+          <t>Deepen</t>
+        </is>
+      </c>
+      <c r="AC2" s="89" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="AD2" s="89" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="AE2" s="80" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K2" s="80" t="inlineStr">
+      <c r="AF2" s="80" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7497,51 +8058,177 @@
       <c r="C3" s="82" t="inlineStr">
         <is>
           <t>Blank 1
-Variable + threshold</t>
+Block 1 – Variable name</t>
         </is>
       </c>
       <c r="D3" s="82" t="inlineStr">
         <is>
           <t>Blank 2
-Count consistency</t>
+Block 1 – Threshold ≤</t>
         </is>
       </c>
       <c r="E3" s="82" t="inlineStr">
         <is>
           <t>Blank 3
-Variable + threshold</t>
+Block 1 – Threshold &gt;</t>
         </is>
       </c>
       <c r="F3" s="82" t="inlineStr">
         <is>
           <t>Blank 4
-Count consistency</t>
+Block 1 – Rec count (left)</t>
         </is>
       </c>
       <c r="G3" s="82" t="inlineStr">
         <is>
           <t>Blank 5
-Variable + threshold</t>
+Block 1 – Not-rec count (left)</t>
         </is>
       </c>
       <c r="H3" s="82" t="inlineStr">
         <is>
           <t>Blank 6
-Count consistency</t>
+Block 1 – Rec count (right)</t>
         </is>
       </c>
       <c r="I3" s="82" t="inlineStr">
         <is>
           <t>Blank 7
-Chosen threshold</t>
+Block 1 – Not-rec count (right)</t>
         </is>
       </c>
       <c r="J3" s="82" t="inlineStr">
         <is>
+          <t>Blank 8
+Block 1 – Misclassification count</t>
+        </is>
+      </c>
+      <c r="K3" s="82" t="inlineStr">
+        <is>
+          <t>Blank 9
+Block 2 – Variable name</t>
+        </is>
+      </c>
+      <c r="L3" s="82" t="inlineStr">
+        <is>
+          <t>Blank 10
+Block 2 – Threshold ≤</t>
+        </is>
+      </c>
+      <c r="M3" s="82" t="inlineStr">
+        <is>
+          <t>Blank 11
+Block 2 – Threshold &gt;</t>
+        </is>
+      </c>
+      <c r="N3" s="82" t="inlineStr">
+        <is>
+          <t>Blank 12
+Block 2 – Rec count (left)</t>
+        </is>
+      </c>
+      <c r="O3" s="82" t="inlineStr">
+        <is>
+          <t>Blank 13
+Block 2 – Not-rec count (left)</t>
+        </is>
+      </c>
+      <c r="P3" s="82" t="inlineStr">
+        <is>
+          <t>Blank 14
+Block 2 – Rec count (right)</t>
+        </is>
+      </c>
+      <c r="Q3" s="82" t="inlineStr">
+        <is>
+          <t>Blank 15
+Block 2 – Not-rec count (right)</t>
+        </is>
+      </c>
+      <c r="R3" s="82" t="inlineStr">
+        <is>
+          <t>Blank 16
+Block 2 – Misclassification count</t>
+        </is>
+      </c>
+      <c r="S3" s="82" t="inlineStr">
+        <is>
+          <t>Blank 17
+Block 3 – Variable name</t>
+        </is>
+      </c>
+      <c r="T3" s="82" t="inlineStr">
+        <is>
+          <t>Blank 18
+Block 3 – Threshold ≤</t>
+        </is>
+      </c>
+      <c r="U3" s="82" t="inlineStr">
+        <is>
+          <t>Blank 19
+Block 3 – Threshold &gt;</t>
+        </is>
+      </c>
+      <c r="V3" s="82" t="inlineStr">
+        <is>
+          <t>Blank 20
+Block 3 – Rec count (left)</t>
+        </is>
+      </c>
+      <c r="W3" s="82" t="inlineStr">
+        <is>
+          <t>Blank 21
+Block 3 – Not-rec count (left)</t>
+        </is>
+      </c>
+      <c r="X3" s="82" t="inlineStr">
+        <is>
+          <t>Blank 22
+Block 3 – Rec count (right)</t>
+        </is>
+      </c>
+      <c r="Y3" s="82" t="inlineStr">
+        <is>
+          <t>Blank 23
+Block 3 – Not-rec count (right)</t>
+        </is>
+      </c>
+      <c r="Z3" s="82" t="inlineStr">
+        <is>
+          <t>Blank 24
+Block 3 – Rec total</t>
+        </is>
+      </c>
+      <c r="AA3" s="82" t="inlineStr">
+        <is>
+          <t>Blank 25
+Block 3 – Not-rec total</t>
+        </is>
+      </c>
+      <c r="AB3" s="82" t="inlineStr">
+        <is>
+          <t>Blank 26
+Block 3 – Misclassification count</t>
+        </is>
+      </c>
+      <c r="AC3" s="82" t="inlineStr">
+        <is>
+          <t>Blank 27
+Chosen variable</t>
+        </is>
+      </c>
+      <c r="AD3" s="82" t="inlineStr">
+        <is>
+          <t>Blank 28
+Selected threshold value</t>
+        </is>
+      </c>
+      <c r="AE3" s="82" t="inlineStr">
+        <is>
           <t>Overall WS5</t>
         </is>
       </c>
-      <c r="K3" s="82" t="inlineStr">
+      <c r="AF3" s="82" t="inlineStr">
         <is>
           <t>Notes WS5</t>
         </is>
@@ -7560,16 +8247,41 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="B5" s="86" t="n"/>
-      <c r="C5" s="86" t="n"/>
-      <c r="D5" s="86" t="n"/>
-      <c r="E5" s="86" t="n"/>
-      <c r="F5" s="86" t="n"/>
-      <c r="G5" s="86" t="n"/>
-      <c r="H5" s="86" t="n"/>
-      <c r="I5" s="86" t="n"/>
-      <c r="J5" s="86" t="n"/>
-      <c r="K5" s="87" t="n"/>
+      <c r="B5" s="84" t="inlineStr">
+        <is>
+          <t>Ozzy</t>
+        </is>
+      </c>
+      <c r="C5" s="84" t="n"/>
+      <c r="D5" s="84" t="n"/>
+      <c r="E5" s="84" t="n"/>
+      <c r="F5" s="84" t="n"/>
+      <c r="G5" s="84" t="n"/>
+      <c r="H5" s="84" t="n"/>
+      <c r="I5" s="84" t="n"/>
+      <c r="J5" s="84" t="n"/>
+      <c r="K5" s="84" t="n"/>
+      <c r="L5" s="84" t="n"/>
+      <c r="M5" s="84" t="n"/>
+      <c r="N5" s="84" t="n"/>
+      <c r="O5" s="84" t="n"/>
+      <c r="P5" s="84" t="n"/>
+      <c r="Q5" s="84" t="n"/>
+      <c r="R5" s="84" t="n"/>
+      <c r="S5" s="84" t="n"/>
+      <c r="T5" s="84" t="n"/>
+      <c r="U5" s="84" t="n"/>
+      <c r="V5" s="84" t="n"/>
+      <c r="W5" s="84" t="n"/>
+      <c r="X5" s="84" t="n"/>
+      <c r="Y5" s="84" t="n"/>
+      <c r="Z5" s="84" t="n"/>
+      <c r="AA5" s="84" t="n"/>
+      <c r="AB5" s="84" t="n"/>
+      <c r="AC5" s="84" t="n"/>
+      <c r="AD5" s="84" t="n"/>
+      <c r="AE5" s="84" t="n"/>
+      <c r="AF5" s="84" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1" s="51">
       <c r="A6" s="85" t="inlineStr">
@@ -7591,6 +8303,27 @@
       <c r="I6" s="85" t="n"/>
       <c r="J6" s="85" t="n"/>
       <c r="K6" s="85" t="n"/>
+      <c r="L6" s="85" t="n"/>
+      <c r="M6" s="85" t="n"/>
+      <c r="N6" s="85" t="n"/>
+      <c r="O6" s="85" t="n"/>
+      <c r="P6" s="85" t="n"/>
+      <c r="Q6" s="85" t="n"/>
+      <c r="R6" s="85" t="n"/>
+      <c r="S6" s="85" t="n"/>
+      <c r="T6" s="85" t="n"/>
+      <c r="U6" s="85" t="n"/>
+      <c r="V6" s="85" t="n"/>
+      <c r="W6" s="85" t="n"/>
+      <c r="X6" s="85" t="n"/>
+      <c r="Y6" s="85" t="n"/>
+      <c r="Z6" s="85" t="n"/>
+      <c r="AA6" s="85" t="n"/>
+      <c r="AB6" s="85" t="n"/>
+      <c r="AC6" s="85" t="n"/>
+      <c r="AD6" s="85" t="n"/>
+      <c r="AE6" s="85" t="n"/>
+      <c r="AF6" s="85" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1" s="51">
       <c r="A7" s="84" t="inlineStr">
@@ -7612,6 +8345,27 @@
       <c r="I7" s="84" t="n"/>
       <c r="J7" s="84" t="n"/>
       <c r="K7" s="84" t="n"/>
+      <c r="L7" s="84" t="n"/>
+      <c r="M7" s="84" t="n"/>
+      <c r="N7" s="84" t="n"/>
+      <c r="O7" s="84" t="n"/>
+      <c r="P7" s="84" t="n"/>
+      <c r="Q7" s="84" t="n"/>
+      <c r="R7" s="84" t="n"/>
+      <c r="S7" s="84" t="n"/>
+      <c r="T7" s="84" t="n"/>
+      <c r="U7" s="84" t="n"/>
+      <c r="V7" s="84" t="n"/>
+      <c r="W7" s="84" t="n"/>
+      <c r="X7" s="84" t="n"/>
+      <c r="Y7" s="84" t="n"/>
+      <c r="Z7" s="84" t="n"/>
+      <c r="AA7" s="84" t="n"/>
+      <c r="AB7" s="84" t="n"/>
+      <c r="AC7" s="84" t="n"/>
+      <c r="AD7" s="84" t="n"/>
+      <c r="AE7" s="84" t="n"/>
+      <c r="AF7" s="84" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1" s="51">
       <c r="A8" s="85" t="inlineStr">
@@ -7633,6 +8387,27 @@
       <c r="I8" s="85" t="n"/>
       <c r="J8" s="85" t="n"/>
       <c r="K8" s="85" t="n"/>
+      <c r="L8" s="85" t="n"/>
+      <c r="M8" s="85" t="n"/>
+      <c r="N8" s="85" t="n"/>
+      <c r="O8" s="85" t="n"/>
+      <c r="P8" s="85" t="n"/>
+      <c r="Q8" s="85" t="n"/>
+      <c r="R8" s="85" t="n"/>
+      <c r="S8" s="85" t="n"/>
+      <c r="T8" s="85" t="n"/>
+      <c r="U8" s="85" t="n"/>
+      <c r="V8" s="85" t="n"/>
+      <c r="W8" s="85" t="n"/>
+      <c r="X8" s="85" t="n"/>
+      <c r="Y8" s="85" t="n"/>
+      <c r="Z8" s="85" t="n"/>
+      <c r="AA8" s="85" t="n"/>
+      <c r="AB8" s="85" t="n"/>
+      <c r="AC8" s="85" t="n"/>
+      <c r="AD8" s="85" t="n"/>
+      <c r="AE8" s="85" t="n"/>
+      <c r="AF8" s="85" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1" s="51">
       <c r="A9" s="84" t="inlineStr">
@@ -7654,6 +8429,27 @@
       <c r="I9" s="84" t="n"/>
       <c r="J9" s="84" t="n"/>
       <c r="K9" s="84" t="n"/>
+      <c r="L9" s="84" t="n"/>
+      <c r="M9" s="84" t="n"/>
+      <c r="N9" s="84" t="n"/>
+      <c r="O9" s="84" t="n"/>
+      <c r="P9" s="84" t="n"/>
+      <c r="Q9" s="84" t="n"/>
+      <c r="R9" s="84" t="n"/>
+      <c r="S9" s="84" t="n"/>
+      <c r="T9" s="84" t="n"/>
+      <c r="U9" s="84" t="n"/>
+      <c r="V9" s="84" t="n"/>
+      <c r="W9" s="84" t="n"/>
+      <c r="X9" s="84" t="n"/>
+      <c r="Y9" s="84" t="n"/>
+      <c r="Z9" s="84" t="n"/>
+      <c r="AA9" s="84" t="n"/>
+      <c r="AB9" s="84" t="n"/>
+      <c r="AC9" s="84" t="n"/>
+      <c r="AD9" s="84" t="n"/>
+      <c r="AE9" s="84" t="n"/>
+      <c r="AF9" s="84" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1" s="51">
       <c r="A10" s="85" t="inlineStr">
@@ -7675,6 +8471,27 @@
       <c r="I10" s="85" t="n"/>
       <c r="J10" s="85" t="n"/>
       <c r="K10" s="85" t="n"/>
+      <c r="L10" s="85" t="n"/>
+      <c r="M10" s="85" t="n"/>
+      <c r="N10" s="85" t="n"/>
+      <c r="O10" s="85" t="n"/>
+      <c r="P10" s="85" t="n"/>
+      <c r="Q10" s="85" t="n"/>
+      <c r="R10" s="85" t="n"/>
+      <c r="S10" s="85" t="n"/>
+      <c r="T10" s="85" t="n"/>
+      <c r="U10" s="85" t="n"/>
+      <c r="V10" s="85" t="n"/>
+      <c r="W10" s="85" t="n"/>
+      <c r="X10" s="85" t="n"/>
+      <c r="Y10" s="85" t="n"/>
+      <c r="Z10" s="85" t="n"/>
+      <c r="AA10" s="85" t="n"/>
+      <c r="AB10" s="85" t="n"/>
+      <c r="AC10" s="85" t="n"/>
+      <c r="AD10" s="85" t="n"/>
+      <c r="AE10" s="85" t="n"/>
+      <c r="AF10" s="85" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1" s="51">
       <c r="A11" s="84" t="inlineStr">
@@ -7696,6 +8513,27 @@
       <c r="I11" s="84" t="n"/>
       <c r="J11" s="84" t="n"/>
       <c r="K11" s="84" t="n"/>
+      <c r="L11" s="84" t="n"/>
+      <c r="M11" s="84" t="n"/>
+      <c r="N11" s="84" t="n"/>
+      <c r="O11" s="84" t="n"/>
+      <c r="P11" s="84" t="n"/>
+      <c r="Q11" s="84" t="n"/>
+      <c r="R11" s="84" t="n"/>
+      <c r="S11" s="84" t="n"/>
+      <c r="T11" s="84" t="n"/>
+      <c r="U11" s="84" t="n"/>
+      <c r="V11" s="84" t="n"/>
+      <c r="W11" s="84" t="n"/>
+      <c r="X11" s="84" t="n"/>
+      <c r="Y11" s="84" t="n"/>
+      <c r="Z11" s="84" t="n"/>
+      <c r="AA11" s="84" t="n"/>
+      <c r="AB11" s="84" t="n"/>
+      <c r="AC11" s="84" t="n"/>
+      <c r="AD11" s="84" t="n"/>
+      <c r="AE11" s="84" t="n"/>
+      <c r="AF11" s="84" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1" s="51">
       <c r="A12" s="85" t="inlineStr">
@@ -7717,6 +8555,27 @@
       <c r="I12" s="85" t="n"/>
       <c r="J12" s="85" t="n"/>
       <c r="K12" s="85" t="n"/>
+      <c r="L12" s="85" t="n"/>
+      <c r="M12" s="85" t="n"/>
+      <c r="N12" s="85" t="n"/>
+      <c r="O12" s="85" t="n"/>
+      <c r="P12" s="85" t="n"/>
+      <c r="Q12" s="85" t="n"/>
+      <c r="R12" s="85" t="n"/>
+      <c r="S12" s="85" t="n"/>
+      <c r="T12" s="85" t="n"/>
+      <c r="U12" s="85" t="n"/>
+      <c r="V12" s="85" t="n"/>
+      <c r="W12" s="85" t="n"/>
+      <c r="X12" s="85" t="n"/>
+      <c r="Y12" s="85" t="n"/>
+      <c r="Z12" s="85" t="n"/>
+      <c r="AA12" s="85" t="n"/>
+      <c r="AB12" s="85" t="n"/>
+      <c r="AC12" s="85" t="n"/>
+      <c r="AD12" s="85" t="n"/>
+      <c r="AE12" s="85" t="n"/>
+      <c r="AF12" s="85" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1" s="51">
       <c r="A13" s="84" t="inlineStr">
@@ -7738,6 +8597,27 @@
       <c r="I13" s="84" t="n"/>
       <c r="J13" s="84" t="n"/>
       <c r="K13" s="84" t="n"/>
+      <c r="L13" s="84" t="n"/>
+      <c r="M13" s="84" t="n"/>
+      <c r="N13" s="84" t="n"/>
+      <c r="O13" s="84" t="n"/>
+      <c r="P13" s="84" t="n"/>
+      <c r="Q13" s="84" t="n"/>
+      <c r="R13" s="84" t="n"/>
+      <c r="S13" s="84" t="n"/>
+      <c r="T13" s="84" t="n"/>
+      <c r="U13" s="84" t="n"/>
+      <c r="V13" s="84" t="n"/>
+      <c r="W13" s="84" t="n"/>
+      <c r="X13" s="84" t="n"/>
+      <c r="Y13" s="84" t="n"/>
+      <c r="Z13" s="84" t="n"/>
+      <c r="AA13" s="84" t="n"/>
+      <c r="AB13" s="84" t="n"/>
+      <c r="AC13" s="84" t="n"/>
+      <c r="AD13" s="84" t="n"/>
+      <c r="AE13" s="84" t="n"/>
+      <c r="AF13" s="84" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1" s="51">
       <c r="A14" s="85" t="inlineStr">
@@ -7759,6 +8639,27 @@
       <c r="I14" s="85" t="n"/>
       <c r="J14" s="85" t="n"/>
       <c r="K14" s="85" t="n"/>
+      <c r="L14" s="85" t="n"/>
+      <c r="M14" s="85" t="n"/>
+      <c r="N14" s="85" t="n"/>
+      <c r="O14" s="85" t="n"/>
+      <c r="P14" s="85" t="n"/>
+      <c r="Q14" s="85" t="n"/>
+      <c r="R14" s="85" t="n"/>
+      <c r="S14" s="85" t="n"/>
+      <c r="T14" s="85" t="n"/>
+      <c r="U14" s="85" t="n"/>
+      <c r="V14" s="85" t="n"/>
+      <c r="W14" s="85" t="n"/>
+      <c r="X14" s="85" t="n"/>
+      <c r="Y14" s="85" t="n"/>
+      <c r="Z14" s="85" t="n"/>
+      <c r="AA14" s="85" t="n"/>
+      <c r="AB14" s="85" t="n"/>
+      <c r="AC14" s="85" t="n"/>
+      <c r="AD14" s="85" t="n"/>
+      <c r="AE14" s="85" t="n"/>
+      <c r="AF14" s="85" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1" s="51">
       <c r="A15" s="84" t="inlineStr">
@@ -7780,6 +8681,27 @@
       <c r="I15" s="84" t="n"/>
       <c r="J15" s="84" t="n"/>
       <c r="K15" s="84" t="n"/>
+      <c r="L15" s="84" t="n"/>
+      <c r="M15" s="84" t="n"/>
+      <c r="N15" s="84" t="n"/>
+      <c r="O15" s="84" t="n"/>
+      <c r="P15" s="84" t="n"/>
+      <c r="Q15" s="84" t="n"/>
+      <c r="R15" s="84" t="n"/>
+      <c r="S15" s="84" t="n"/>
+      <c r="T15" s="84" t="n"/>
+      <c r="U15" s="84" t="n"/>
+      <c r="V15" s="84" t="n"/>
+      <c r="W15" s="84" t="n"/>
+      <c r="X15" s="84" t="n"/>
+      <c r="Y15" s="84" t="n"/>
+      <c r="Z15" s="84" t="n"/>
+      <c r="AA15" s="84" t="n"/>
+      <c r="AB15" s="84" t="n"/>
+      <c r="AC15" s="84" t="n"/>
+      <c r="AD15" s="84" t="n"/>
+      <c r="AE15" s="84" t="n"/>
+      <c r="AF15" s="84" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1" s="51">
       <c r="A16" s="85" t="inlineStr">
@@ -7801,6 +8723,27 @@
       <c r="I16" s="85" t="n"/>
       <c r="J16" s="85" t="n"/>
       <c r="K16" s="85" t="n"/>
+      <c r="L16" s="85" t="n"/>
+      <c r="M16" s="85" t="n"/>
+      <c r="N16" s="85" t="n"/>
+      <c r="O16" s="85" t="n"/>
+      <c r="P16" s="85" t="n"/>
+      <c r="Q16" s="85" t="n"/>
+      <c r="R16" s="85" t="n"/>
+      <c r="S16" s="85" t="n"/>
+      <c r="T16" s="85" t="n"/>
+      <c r="U16" s="85" t="n"/>
+      <c r="V16" s="85" t="n"/>
+      <c r="W16" s="85" t="n"/>
+      <c r="X16" s="85" t="n"/>
+      <c r="Y16" s="85" t="n"/>
+      <c r="Z16" s="85" t="n"/>
+      <c r="AA16" s="85" t="n"/>
+      <c r="AB16" s="85" t="n"/>
+      <c r="AC16" s="85" t="n"/>
+      <c r="AD16" s="85" t="n"/>
+      <c r="AE16" s="85" t="n"/>
+      <c r="AF16" s="85" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1" s="51">
       <c r="A17" s="84" t="inlineStr">
@@ -7822,6 +8765,27 @@
       <c r="I17" s="84" t="n"/>
       <c r="J17" s="84" t="n"/>
       <c r="K17" s="84" t="n"/>
+      <c r="L17" s="84" t="n"/>
+      <c r="M17" s="84" t="n"/>
+      <c r="N17" s="84" t="n"/>
+      <c r="O17" s="84" t="n"/>
+      <c r="P17" s="84" t="n"/>
+      <c r="Q17" s="84" t="n"/>
+      <c r="R17" s="84" t="n"/>
+      <c r="S17" s="84" t="n"/>
+      <c r="T17" s="84" t="n"/>
+      <c r="U17" s="84" t="n"/>
+      <c r="V17" s="84" t="n"/>
+      <c r="W17" s="84" t="n"/>
+      <c r="X17" s="84" t="n"/>
+      <c r="Y17" s="84" t="n"/>
+      <c r="Z17" s="84" t="n"/>
+      <c r="AA17" s="84" t="n"/>
+      <c r="AB17" s="84" t="n"/>
+      <c r="AC17" s="84" t="n"/>
+      <c r="AD17" s="84" t="n"/>
+      <c r="AE17" s="84" t="n"/>
+      <c r="AF17" s="84" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1" s="51">
       <c r="A18" s="85" t="inlineStr">
@@ -7843,6 +8807,27 @@
       <c r="I18" s="85" t="n"/>
       <c r="J18" s="85" t="n"/>
       <c r="K18" s="85" t="n"/>
+      <c r="L18" s="85" t="n"/>
+      <c r="M18" s="85" t="n"/>
+      <c r="N18" s="85" t="n"/>
+      <c r="O18" s="85" t="n"/>
+      <c r="P18" s="85" t="n"/>
+      <c r="Q18" s="85" t="n"/>
+      <c r="R18" s="85" t="n"/>
+      <c r="S18" s="85" t="n"/>
+      <c r="T18" s="85" t="n"/>
+      <c r="U18" s="85" t="n"/>
+      <c r="V18" s="85" t="n"/>
+      <c r="W18" s="85" t="n"/>
+      <c r="X18" s="85" t="n"/>
+      <c r="Y18" s="85" t="n"/>
+      <c r="Z18" s="85" t="n"/>
+      <c r="AA18" s="85" t="n"/>
+      <c r="AB18" s="85" t="n"/>
+      <c r="AC18" s="85" t="n"/>
+      <c r="AD18" s="85" t="n"/>
+      <c r="AE18" s="85" t="n"/>
+      <c r="AF18" s="85" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1" s="51">
       <c r="A19" s="84" t="inlineStr">
@@ -7864,6 +8849,27 @@
       <c r="I19" s="84" t="n"/>
       <c r="J19" s="84" t="n"/>
       <c r="K19" s="84" t="n"/>
+      <c r="L19" s="84" t="n"/>
+      <c r="M19" s="84" t="n"/>
+      <c r="N19" s="84" t="n"/>
+      <c r="O19" s="84" t="n"/>
+      <c r="P19" s="84" t="n"/>
+      <c r="Q19" s="84" t="n"/>
+      <c r="R19" s="84" t="n"/>
+      <c r="S19" s="84" t="n"/>
+      <c r="T19" s="84" t="n"/>
+      <c r="U19" s="84" t="n"/>
+      <c r="V19" s="84" t="n"/>
+      <c r="W19" s="84" t="n"/>
+      <c r="X19" s="84" t="n"/>
+      <c r="Y19" s="84" t="n"/>
+      <c r="Z19" s="84" t="n"/>
+      <c r="AA19" s="84" t="n"/>
+      <c r="AB19" s="84" t="n"/>
+      <c r="AC19" s="84" t="n"/>
+      <c r="AD19" s="84" t="n"/>
+      <c r="AE19" s="84" t="n"/>
+      <c r="AF19" s="84" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1" s="51">
       <c r="A20" s="85" t="inlineStr">
@@ -7885,6 +8891,27 @@
       <c r="I20" s="85" t="n"/>
       <c r="J20" s="85" t="n"/>
       <c r="K20" s="85" t="n"/>
+      <c r="L20" s="85" t="n"/>
+      <c r="M20" s="85" t="n"/>
+      <c r="N20" s="85" t="n"/>
+      <c r="O20" s="85" t="n"/>
+      <c r="P20" s="85" t="n"/>
+      <c r="Q20" s="85" t="n"/>
+      <c r="R20" s="85" t="n"/>
+      <c r="S20" s="85" t="n"/>
+      <c r="T20" s="85" t="n"/>
+      <c r="U20" s="85" t="n"/>
+      <c r="V20" s="85" t="n"/>
+      <c r="W20" s="85" t="n"/>
+      <c r="X20" s="85" t="n"/>
+      <c r="Y20" s="85" t="n"/>
+      <c r="Z20" s="85" t="n"/>
+      <c r="AA20" s="85" t="n"/>
+      <c r="AB20" s="85" t="n"/>
+      <c r="AC20" s="85" t="n"/>
+      <c r="AD20" s="85" t="n"/>
+      <c r="AE20" s="85" t="n"/>
+      <c r="AF20" s="85" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1" s="51">
       <c r="A21" s="84" t="inlineStr">
@@ -7906,6 +8933,27 @@
       <c r="I21" s="84" t="n"/>
       <c r="J21" s="84" t="n"/>
       <c r="K21" s="84" t="n"/>
+      <c r="L21" s="84" t="n"/>
+      <c r="M21" s="84" t="n"/>
+      <c r="N21" s="84" t="n"/>
+      <c r="O21" s="84" t="n"/>
+      <c r="P21" s="84" t="n"/>
+      <c r="Q21" s="84" t="n"/>
+      <c r="R21" s="84" t="n"/>
+      <c r="S21" s="84" t="n"/>
+      <c r="T21" s="84" t="n"/>
+      <c r="U21" s="84" t="n"/>
+      <c r="V21" s="84" t="n"/>
+      <c r="W21" s="84" t="n"/>
+      <c r="X21" s="84" t="n"/>
+      <c r="Y21" s="84" t="n"/>
+      <c r="Z21" s="84" t="n"/>
+      <c r="AA21" s="84" t="n"/>
+      <c r="AB21" s="84" t="n"/>
+      <c r="AC21" s="84" t="n"/>
+      <c r="AD21" s="84" t="n"/>
+      <c r="AE21" s="84" t="n"/>
+      <c r="AF21" s="84" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1" s="51">
       <c r="A22" s="85" t="inlineStr">
@@ -7927,6 +8975,27 @@
       <c r="I22" s="85" t="n"/>
       <c r="J22" s="85" t="n"/>
       <c r="K22" s="85" t="n"/>
+      <c r="L22" s="85" t="n"/>
+      <c r="M22" s="85" t="n"/>
+      <c r="N22" s="85" t="n"/>
+      <c r="O22" s="85" t="n"/>
+      <c r="P22" s="85" t="n"/>
+      <c r="Q22" s="85" t="n"/>
+      <c r="R22" s="85" t="n"/>
+      <c r="S22" s="85" t="n"/>
+      <c r="T22" s="85" t="n"/>
+      <c r="U22" s="85" t="n"/>
+      <c r="V22" s="85" t="n"/>
+      <c r="W22" s="85" t="n"/>
+      <c r="X22" s="85" t="n"/>
+      <c r="Y22" s="85" t="n"/>
+      <c r="Z22" s="85" t="n"/>
+      <c r="AA22" s="85" t="n"/>
+      <c r="AB22" s="85" t="n"/>
+      <c r="AC22" s="85" t="n"/>
+      <c r="AD22" s="85" t="n"/>
+      <c r="AE22" s="85" t="n"/>
+      <c r="AF22" s="85" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1" s="51">
       <c r="A23" s="84" t="inlineStr">
@@ -7948,6 +9017,27 @@
       <c r="I23" s="84" t="n"/>
       <c r="J23" s="84" t="n"/>
       <c r="K23" s="84" t="n"/>
+      <c r="L23" s="84" t="n"/>
+      <c r="M23" s="84" t="n"/>
+      <c r="N23" s="84" t="n"/>
+      <c r="O23" s="84" t="n"/>
+      <c r="P23" s="84" t="n"/>
+      <c r="Q23" s="84" t="n"/>
+      <c r="R23" s="84" t="n"/>
+      <c r="S23" s="84" t="n"/>
+      <c r="T23" s="84" t="n"/>
+      <c r="U23" s="84" t="n"/>
+      <c r="V23" s="84" t="n"/>
+      <c r="W23" s="84" t="n"/>
+      <c r="X23" s="84" t="n"/>
+      <c r="Y23" s="84" t="n"/>
+      <c r="Z23" s="84" t="n"/>
+      <c r="AA23" s="84" t="n"/>
+      <c r="AB23" s="84" t="n"/>
+      <c r="AC23" s="84" t="n"/>
+      <c r="AD23" s="84" t="n"/>
+      <c r="AE23" s="84" t="n"/>
+      <c r="AF23" s="84" t="n"/>
     </row>
     <row r="24" ht="18" customHeight="1" s="51">
       <c r="A24" s="85" t="inlineStr">
@@ -7969,6 +9059,27 @@
       <c r="I24" s="85" t="n"/>
       <c r="J24" s="85" t="n"/>
       <c r="K24" s="85" t="n"/>
+      <c r="L24" s="85" t="n"/>
+      <c r="M24" s="85" t="n"/>
+      <c r="N24" s="85" t="n"/>
+      <c r="O24" s="85" t="n"/>
+      <c r="P24" s="85" t="n"/>
+      <c r="Q24" s="85" t="n"/>
+      <c r="R24" s="85" t="n"/>
+      <c r="S24" s="85" t="n"/>
+      <c r="T24" s="85" t="n"/>
+      <c r="U24" s="85" t="n"/>
+      <c r="V24" s="85" t="n"/>
+      <c r="W24" s="85" t="n"/>
+      <c r="X24" s="85" t="n"/>
+      <c r="Y24" s="85" t="n"/>
+      <c r="Z24" s="85" t="n"/>
+      <c r="AA24" s="85" t="n"/>
+      <c r="AB24" s="85" t="n"/>
+      <c r="AC24" s="85" t="n"/>
+      <c r="AD24" s="85" t="n"/>
+      <c r="AE24" s="85" t="n"/>
+      <c r="AF24" s="85" t="n"/>
     </row>
     <row r="25" ht="18" customHeight="1" s="51">
       <c r="A25" s="84" t="inlineStr">
@@ -7990,6 +9101,27 @@
       <c r="I25" s="84" t="n"/>
       <c r="J25" s="84" t="n"/>
       <c r="K25" s="84" t="n"/>
+      <c r="L25" s="84" t="n"/>
+      <c r="M25" s="84" t="n"/>
+      <c r="N25" s="84" t="n"/>
+      <c r="O25" s="84" t="n"/>
+      <c r="P25" s="84" t="n"/>
+      <c r="Q25" s="84" t="n"/>
+      <c r="R25" s="84" t="n"/>
+      <c r="S25" s="84" t="n"/>
+      <c r="T25" s="84" t="n"/>
+      <c r="U25" s="84" t="n"/>
+      <c r="V25" s="84" t="n"/>
+      <c r="W25" s="84" t="n"/>
+      <c r="X25" s="84" t="n"/>
+      <c r="Y25" s="84" t="n"/>
+      <c r="Z25" s="84" t="n"/>
+      <c r="AA25" s="84" t="n"/>
+      <c r="AB25" s="84" t="n"/>
+      <c r="AC25" s="84" t="n"/>
+      <c r="AD25" s="84" t="n"/>
+      <c r="AE25" s="84" t="n"/>
+      <c r="AF25" s="84" t="n"/>
     </row>
     <row r="26" ht="18" customHeight="1" s="51">
       <c r="A26" s="85" t="inlineStr">
@@ -8011,6 +9143,27 @@
       <c r="I26" s="85" t="n"/>
       <c r="J26" s="85" t="n"/>
       <c r="K26" s="85" t="n"/>
+      <c r="L26" s="85" t="n"/>
+      <c r="M26" s="85" t="n"/>
+      <c r="N26" s="85" t="n"/>
+      <c r="O26" s="85" t="n"/>
+      <c r="P26" s="85" t="n"/>
+      <c r="Q26" s="85" t="n"/>
+      <c r="R26" s="85" t="n"/>
+      <c r="S26" s="85" t="n"/>
+      <c r="T26" s="85" t="n"/>
+      <c r="U26" s="85" t="n"/>
+      <c r="V26" s="85" t="n"/>
+      <c r="W26" s="85" t="n"/>
+      <c r="X26" s="85" t="n"/>
+      <c r="Y26" s="85" t="n"/>
+      <c r="Z26" s="85" t="n"/>
+      <c r="AA26" s="85" t="n"/>
+      <c r="AB26" s="85" t="n"/>
+      <c r="AC26" s="85" t="n"/>
+      <c r="AD26" s="85" t="n"/>
+      <c r="AE26" s="85" t="n"/>
+      <c r="AF26" s="85" t="n"/>
     </row>
     <row r="27" ht="18" customHeight="1" s="51">
       <c r="A27" s="84" t="inlineStr">
@@ -8032,6 +9185,27 @@
       <c r="I27" s="84" t="n"/>
       <c r="J27" s="84" t="n"/>
       <c r="K27" s="84" t="n"/>
+      <c r="L27" s="84" t="n"/>
+      <c r="M27" s="84" t="n"/>
+      <c r="N27" s="84" t="n"/>
+      <c r="O27" s="84" t="n"/>
+      <c r="P27" s="84" t="n"/>
+      <c r="Q27" s="84" t="n"/>
+      <c r="R27" s="84" t="n"/>
+      <c r="S27" s="84" t="n"/>
+      <c r="T27" s="84" t="n"/>
+      <c r="U27" s="84" t="n"/>
+      <c r="V27" s="84" t="n"/>
+      <c r="W27" s="84" t="n"/>
+      <c r="X27" s="84" t="n"/>
+      <c r="Y27" s="84" t="n"/>
+      <c r="Z27" s="84" t="n"/>
+      <c r="AA27" s="84" t="n"/>
+      <c r="AB27" s="84" t="n"/>
+      <c r="AC27" s="84" t="n"/>
+      <c r="AD27" s="84" t="n"/>
+      <c r="AE27" s="84" t="n"/>
+      <c r="AF27" s="84" t="n"/>
     </row>
     <row r="28" ht="18" customHeight="1" s="51">
       <c r="A28" s="85" t="inlineStr">
@@ -8053,6 +9227,27 @@
       <c r="I28" s="85" t="n"/>
       <c r="J28" s="85" t="n"/>
       <c r="K28" s="85" t="n"/>
+      <c r="L28" s="85" t="n"/>
+      <c r="M28" s="85" t="n"/>
+      <c r="N28" s="85" t="n"/>
+      <c r="O28" s="85" t="n"/>
+      <c r="P28" s="85" t="n"/>
+      <c r="Q28" s="85" t="n"/>
+      <c r="R28" s="85" t="n"/>
+      <c r="S28" s="85" t="n"/>
+      <c r="T28" s="85" t="n"/>
+      <c r="U28" s="85" t="n"/>
+      <c r="V28" s="85" t="n"/>
+      <c r="W28" s="85" t="n"/>
+      <c r="X28" s="85" t="n"/>
+      <c r="Y28" s="85" t="n"/>
+      <c r="Z28" s="85" t="n"/>
+      <c r="AA28" s="85" t="n"/>
+      <c r="AB28" s="85" t="n"/>
+      <c r="AC28" s="85" t="n"/>
+      <c r="AD28" s="85" t="n"/>
+      <c r="AE28" s="85" t="n"/>
+      <c r="AF28" s="85" t="n"/>
     </row>
     <row r="29" ht="18" customHeight="1" s="51">
       <c r="A29" s="84" t="inlineStr">
@@ -8074,6 +9269,27 @@
       <c r="I29" s="84" t="n"/>
       <c r="J29" s="84" t="n"/>
       <c r="K29" s="84" t="n"/>
+      <c r="L29" s="84" t="n"/>
+      <c r="M29" s="84" t="n"/>
+      <c r="N29" s="84" t="n"/>
+      <c r="O29" s="84" t="n"/>
+      <c r="P29" s="84" t="n"/>
+      <c r="Q29" s="84" t="n"/>
+      <c r="R29" s="84" t="n"/>
+      <c r="S29" s="84" t="n"/>
+      <c r="T29" s="84" t="n"/>
+      <c r="U29" s="84" t="n"/>
+      <c r="V29" s="84" t="n"/>
+      <c r="W29" s="84" t="n"/>
+      <c r="X29" s="84" t="n"/>
+      <c r="Y29" s="84" t="n"/>
+      <c r="Z29" s="84" t="n"/>
+      <c r="AA29" s="84" t="n"/>
+      <c r="AB29" s="84" t="n"/>
+      <c r="AC29" s="84" t="n"/>
+      <c r="AD29" s="84" t="n"/>
+      <c r="AE29" s="84" t="n"/>
+      <c r="AF29" s="84" t="n"/>
     </row>
     <row r="30" ht="18" customHeight="1" s="51">
       <c r="A30" s="85" t="inlineStr">
@@ -8095,6 +9311,27 @@
       <c r="I30" s="85" t="n"/>
       <c r="J30" s="85" t="n"/>
       <c r="K30" s="85" t="n"/>
+      <c r="L30" s="85" t="n"/>
+      <c r="M30" s="85" t="n"/>
+      <c r="N30" s="85" t="n"/>
+      <c r="O30" s="85" t="n"/>
+      <c r="P30" s="85" t="n"/>
+      <c r="Q30" s="85" t="n"/>
+      <c r="R30" s="85" t="n"/>
+      <c r="S30" s="85" t="n"/>
+      <c r="T30" s="85" t="n"/>
+      <c r="U30" s="85" t="n"/>
+      <c r="V30" s="85" t="n"/>
+      <c r="W30" s="85" t="n"/>
+      <c r="X30" s="85" t="n"/>
+      <c r="Y30" s="85" t="n"/>
+      <c r="Z30" s="85" t="n"/>
+      <c r="AA30" s="85" t="n"/>
+      <c r="AB30" s="85" t="n"/>
+      <c r="AC30" s="85" t="n"/>
+      <c r="AD30" s="85" t="n"/>
+      <c r="AE30" s="85" t="n"/>
+      <c r="AF30" s="85" t="n"/>
     </row>
     <row r="31" ht="18" customHeight="1" s="51">
       <c r="A31" s="84" t="inlineStr">
@@ -8116,6 +9353,27 @@
       <c r="I31" s="84" t="n"/>
       <c r="J31" s="84" t="n"/>
       <c r="K31" s="84" t="n"/>
+      <c r="L31" s="84" t="n"/>
+      <c r="M31" s="84" t="n"/>
+      <c r="N31" s="84" t="n"/>
+      <c r="O31" s="84" t="n"/>
+      <c r="P31" s="84" t="n"/>
+      <c r="Q31" s="84" t="n"/>
+      <c r="R31" s="84" t="n"/>
+      <c r="S31" s="84" t="n"/>
+      <c r="T31" s="84" t="n"/>
+      <c r="U31" s="84" t="n"/>
+      <c r="V31" s="84" t="n"/>
+      <c r="W31" s="84" t="n"/>
+      <c r="X31" s="84" t="n"/>
+      <c r="Y31" s="84" t="n"/>
+      <c r="Z31" s="84" t="n"/>
+      <c r="AA31" s="84" t="n"/>
+      <c r="AB31" s="84" t="n"/>
+      <c r="AC31" s="84" t="n"/>
+      <c r="AD31" s="84" t="n"/>
+      <c r="AE31" s="84" t="n"/>
+      <c r="AF31" s="84" t="n"/>
     </row>
     <row r="32" ht="18" customHeight="1" s="51">
       <c r="A32" s="85" t="inlineStr">
@@ -8137,6 +9395,27 @@
       <c r="I32" s="85" t="n"/>
       <c r="J32" s="85" t="n"/>
       <c r="K32" s="85" t="n"/>
+      <c r="L32" s="85" t="n"/>
+      <c r="M32" s="85" t="n"/>
+      <c r="N32" s="85" t="n"/>
+      <c r="O32" s="85" t="n"/>
+      <c r="P32" s="85" t="n"/>
+      <c r="Q32" s="85" t="n"/>
+      <c r="R32" s="85" t="n"/>
+      <c r="S32" s="85" t="n"/>
+      <c r="T32" s="85" t="n"/>
+      <c r="U32" s="85" t="n"/>
+      <c r="V32" s="85" t="n"/>
+      <c r="W32" s="85" t="n"/>
+      <c r="X32" s="85" t="n"/>
+      <c r="Y32" s="85" t="n"/>
+      <c r="Z32" s="85" t="n"/>
+      <c r="AA32" s="85" t="n"/>
+      <c r="AB32" s="85" t="n"/>
+      <c r="AC32" s="85" t="n"/>
+      <c r="AD32" s="85" t="n"/>
+      <c r="AE32" s="85" t="n"/>
+      <c r="AF32" s="85" t="n"/>
     </row>
     <row r="33" ht="18" customHeight="1" s="51">
       <c r="A33" s="84" t="inlineStr">
@@ -8158,6 +9437,27 @@
       <c r="I33" s="84" t="n"/>
       <c r="J33" s="84" t="n"/>
       <c r="K33" s="84" t="n"/>
+      <c r="L33" s="84" t="n"/>
+      <c r="M33" s="84" t="n"/>
+      <c r="N33" s="84" t="n"/>
+      <c r="O33" s="84" t="n"/>
+      <c r="P33" s="84" t="n"/>
+      <c r="Q33" s="84" t="n"/>
+      <c r="R33" s="84" t="n"/>
+      <c r="S33" s="84" t="n"/>
+      <c r="T33" s="84" t="n"/>
+      <c r="U33" s="84" t="n"/>
+      <c r="V33" s="84" t="n"/>
+      <c r="W33" s="84" t="n"/>
+      <c r="X33" s="84" t="n"/>
+      <c r="Y33" s="84" t="n"/>
+      <c r="Z33" s="84" t="n"/>
+      <c r="AA33" s="84" t="n"/>
+      <c r="AB33" s="84" t="n"/>
+      <c r="AC33" s="84" t="n"/>
+      <c r="AD33" s="84" t="n"/>
+      <c r="AE33" s="84" t="n"/>
+      <c r="AF33" s="84" t="n"/>
     </row>
     <row r="34" ht="18" customHeight="1" s="51">
       <c r="A34" s="85" t="inlineStr">
@@ -8165,7 +9465,11 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="B34" s="85" t="n"/>
+      <c r="B34" s="85" t="inlineStr">
+        <is>
+          <t>Sabrina</t>
+        </is>
+      </c>
       <c r="C34" s="85" t="n"/>
       <c r="D34" s="85" t="n"/>
       <c r="E34" s="85" t="n"/>
@@ -8175,6 +9479,27 @@
       <c r="I34" s="85" t="n"/>
       <c r="J34" s="85" t="n"/>
       <c r="K34" s="85" t="n"/>
+      <c r="L34" s="85" t="n"/>
+      <c r="M34" s="85" t="n"/>
+      <c r="N34" s="85" t="n"/>
+      <c r="O34" s="85" t="n"/>
+      <c r="P34" s="85" t="n"/>
+      <c r="Q34" s="85" t="n"/>
+      <c r="R34" s="85" t="n"/>
+      <c r="S34" s="85" t="n"/>
+      <c r="T34" s="85" t="n"/>
+      <c r="U34" s="85" t="n"/>
+      <c r="V34" s="85" t="n"/>
+      <c r="W34" s="85" t="n"/>
+      <c r="X34" s="85" t="n"/>
+      <c r="Y34" s="85" t="n"/>
+      <c r="Z34" s="85" t="n"/>
+      <c r="AA34" s="85" t="n"/>
+      <c r="AB34" s="85" t="n"/>
+      <c r="AC34" s="85" t="n"/>
+      <c r="AD34" s="85" t="n"/>
+      <c r="AE34" s="85" t="n"/>
+      <c r="AF34" s="85" t="n"/>
     </row>
     <row r="35" ht="20" customHeight="1" s="51">
       <c r="A35" s="83" t="inlineStr">
@@ -8189,16 +9514,41 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="B36" s="86" t="n"/>
-      <c r="C36" s="86" t="n"/>
-      <c r="D36" s="86" t="n"/>
-      <c r="E36" s="86" t="n"/>
-      <c r="F36" s="86" t="n"/>
-      <c r="G36" s="86" t="n"/>
-      <c r="H36" s="86" t="n"/>
-      <c r="I36" s="86" t="n"/>
-      <c r="J36" s="86" t="n"/>
-      <c r="K36" s="87" t="n"/>
+      <c r="B36" s="84" t="inlineStr">
+        <is>
+          <t>Sheila</t>
+        </is>
+      </c>
+      <c r="C36" s="84" t="n"/>
+      <c r="D36" s="84" t="n"/>
+      <c r="E36" s="84" t="n"/>
+      <c r="F36" s="84" t="n"/>
+      <c r="G36" s="84" t="n"/>
+      <c r="H36" s="84" t="n"/>
+      <c r="I36" s="84" t="n"/>
+      <c r="J36" s="84" t="n"/>
+      <c r="K36" s="84" t="n"/>
+      <c r="L36" s="84" t="n"/>
+      <c r="M36" s="84" t="n"/>
+      <c r="N36" s="84" t="n"/>
+      <c r="O36" s="84" t="n"/>
+      <c r="P36" s="84" t="n"/>
+      <c r="Q36" s="84" t="n"/>
+      <c r="R36" s="84" t="n"/>
+      <c r="S36" s="84" t="n"/>
+      <c r="T36" s="84" t="n"/>
+      <c r="U36" s="84" t="n"/>
+      <c r="V36" s="84" t="n"/>
+      <c r="W36" s="84" t="n"/>
+      <c r="X36" s="84" t="n"/>
+      <c r="Y36" s="84" t="n"/>
+      <c r="Z36" s="84" t="n"/>
+      <c r="AA36" s="84" t="n"/>
+      <c r="AB36" s="84" t="n"/>
+      <c r="AC36" s="84" t="n"/>
+      <c r="AD36" s="84" t="n"/>
+      <c r="AE36" s="84" t="n"/>
+      <c r="AF36" s="84" t="n"/>
     </row>
     <row r="37" ht="18" customHeight="1" s="51">
       <c r="A37" s="85" t="inlineStr">
@@ -8220,6 +9570,27 @@
       <c r="I37" s="85" t="n"/>
       <c r="J37" s="85" t="n"/>
       <c r="K37" s="85" t="n"/>
+      <c r="L37" s="85" t="n"/>
+      <c r="M37" s="85" t="n"/>
+      <c r="N37" s="85" t="n"/>
+      <c r="O37" s="85" t="n"/>
+      <c r="P37" s="85" t="n"/>
+      <c r="Q37" s="85" t="n"/>
+      <c r="R37" s="85" t="n"/>
+      <c r="S37" s="85" t="n"/>
+      <c r="T37" s="85" t="n"/>
+      <c r="U37" s="85" t="n"/>
+      <c r="V37" s="85" t="n"/>
+      <c r="W37" s="85" t="n"/>
+      <c r="X37" s="85" t="n"/>
+      <c r="Y37" s="85" t="n"/>
+      <c r="Z37" s="85" t="n"/>
+      <c r="AA37" s="85" t="n"/>
+      <c r="AB37" s="85" t="n"/>
+      <c r="AC37" s="85" t="n"/>
+      <c r="AD37" s="85" t="n"/>
+      <c r="AE37" s="85" t="n"/>
+      <c r="AF37" s="85" t="n"/>
     </row>
     <row r="38" ht="18" customHeight="1" s="51">
       <c r="A38" s="84" t="inlineStr">
@@ -8241,6 +9612,27 @@
       <c r="I38" s="84" t="n"/>
       <c r="J38" s="84" t="n"/>
       <c r="K38" s="84" t="n"/>
+      <c r="L38" s="84" t="n"/>
+      <c r="M38" s="84" t="n"/>
+      <c r="N38" s="84" t="n"/>
+      <c r="O38" s="84" t="n"/>
+      <c r="P38" s="84" t="n"/>
+      <c r="Q38" s="84" t="n"/>
+      <c r="R38" s="84" t="n"/>
+      <c r="S38" s="84" t="n"/>
+      <c r="T38" s="84" t="n"/>
+      <c r="U38" s="84" t="n"/>
+      <c r="V38" s="84" t="n"/>
+      <c r="W38" s="84" t="n"/>
+      <c r="X38" s="84" t="n"/>
+      <c r="Y38" s="84" t="n"/>
+      <c r="Z38" s="84" t="n"/>
+      <c r="AA38" s="84" t="n"/>
+      <c r="AB38" s="84" t="n"/>
+      <c r="AC38" s="84" t="n"/>
+      <c r="AD38" s="84" t="n"/>
+      <c r="AE38" s="84" t="n"/>
+      <c r="AF38" s="84" t="n"/>
     </row>
     <row r="39" ht="18" customHeight="1" s="51">
       <c r="A39" s="85" t="inlineStr">
@@ -8262,6 +9654,27 @@
       <c r="I39" s="85" t="n"/>
       <c r="J39" s="85" t="n"/>
       <c r="K39" s="85" t="n"/>
+      <c r="L39" s="85" t="n"/>
+      <c r="M39" s="85" t="n"/>
+      <c r="N39" s="85" t="n"/>
+      <c r="O39" s="85" t="n"/>
+      <c r="P39" s="85" t="n"/>
+      <c r="Q39" s="85" t="n"/>
+      <c r="R39" s="85" t="n"/>
+      <c r="S39" s="85" t="n"/>
+      <c r="T39" s="85" t="n"/>
+      <c r="U39" s="85" t="n"/>
+      <c r="V39" s="85" t="n"/>
+      <c r="W39" s="85" t="n"/>
+      <c r="X39" s="85" t="n"/>
+      <c r="Y39" s="85" t="n"/>
+      <c r="Z39" s="85" t="n"/>
+      <c r="AA39" s="85" t="n"/>
+      <c r="AB39" s="85" t="n"/>
+      <c r="AC39" s="85" t="n"/>
+      <c r="AD39" s="85" t="n"/>
+      <c r="AE39" s="85" t="n"/>
+      <c r="AF39" s="85" t="n"/>
     </row>
     <row r="40" ht="18" customHeight="1" s="51">
       <c r="A40" s="84" t="inlineStr">
@@ -8283,6 +9696,27 @@
       <c r="I40" s="84" t="n"/>
       <c r="J40" s="84" t="n"/>
       <c r="K40" s="84" t="n"/>
+      <c r="L40" s="84" t="n"/>
+      <c r="M40" s="84" t="n"/>
+      <c r="N40" s="84" t="n"/>
+      <c r="O40" s="84" t="n"/>
+      <c r="P40" s="84" t="n"/>
+      <c r="Q40" s="84" t="n"/>
+      <c r="R40" s="84" t="n"/>
+      <c r="S40" s="84" t="n"/>
+      <c r="T40" s="84" t="n"/>
+      <c r="U40" s="84" t="n"/>
+      <c r="V40" s="84" t="n"/>
+      <c r="W40" s="84" t="n"/>
+      <c r="X40" s="84" t="n"/>
+      <c r="Y40" s="84" t="n"/>
+      <c r="Z40" s="84" t="n"/>
+      <c r="AA40" s="84" t="n"/>
+      <c r="AB40" s="84" t="n"/>
+      <c r="AC40" s="84" t="n"/>
+      <c r="AD40" s="84" t="n"/>
+      <c r="AE40" s="84" t="n"/>
+      <c r="AF40" s="84" t="n"/>
     </row>
     <row r="41" ht="18" customHeight="1" s="51">
       <c r="A41" s="85" t="inlineStr">
@@ -8304,6 +9738,27 @@
       <c r="I41" s="85" t="n"/>
       <c r="J41" s="85" t="n"/>
       <c r="K41" s="85" t="n"/>
+      <c r="L41" s="85" t="n"/>
+      <c r="M41" s="85" t="n"/>
+      <c r="N41" s="85" t="n"/>
+      <c r="O41" s="85" t="n"/>
+      <c r="P41" s="85" t="n"/>
+      <c r="Q41" s="85" t="n"/>
+      <c r="R41" s="85" t="n"/>
+      <c r="S41" s="85" t="n"/>
+      <c r="T41" s="85" t="n"/>
+      <c r="U41" s="85" t="n"/>
+      <c r="V41" s="85" t="n"/>
+      <c r="W41" s="85" t="n"/>
+      <c r="X41" s="85" t="n"/>
+      <c r="Y41" s="85" t="n"/>
+      <c r="Z41" s="85" t="n"/>
+      <c r="AA41" s="85" t="n"/>
+      <c r="AB41" s="85" t="n"/>
+      <c r="AC41" s="85" t="n"/>
+      <c r="AD41" s="85" t="n"/>
+      <c r="AE41" s="85" t="n"/>
+      <c r="AF41" s="85" t="n"/>
     </row>
     <row r="42" ht="18" customHeight="1" s="51">
       <c r="A42" s="84" t="inlineStr">
@@ -8325,6 +9780,27 @@
       <c r="I42" s="84" t="n"/>
       <c r="J42" s="84" t="n"/>
       <c r="K42" s="84" t="n"/>
+      <c r="L42" s="84" t="n"/>
+      <c r="M42" s="84" t="n"/>
+      <c r="N42" s="84" t="n"/>
+      <c r="O42" s="84" t="n"/>
+      <c r="P42" s="84" t="n"/>
+      <c r="Q42" s="84" t="n"/>
+      <c r="R42" s="84" t="n"/>
+      <c r="S42" s="84" t="n"/>
+      <c r="T42" s="84" t="n"/>
+      <c r="U42" s="84" t="n"/>
+      <c r="V42" s="84" t="n"/>
+      <c r="W42" s="84" t="n"/>
+      <c r="X42" s="84" t="n"/>
+      <c r="Y42" s="84" t="n"/>
+      <c r="Z42" s="84" t="n"/>
+      <c r="AA42" s="84" t="n"/>
+      <c r="AB42" s="84" t="n"/>
+      <c r="AC42" s="84" t="n"/>
+      <c r="AD42" s="84" t="n"/>
+      <c r="AE42" s="84" t="n"/>
+      <c r="AF42" s="84" t="n"/>
     </row>
     <row r="43" ht="18" customHeight="1" s="51">
       <c r="A43" s="85" t="inlineStr">
@@ -8346,6 +9822,27 @@
       <c r="I43" s="85" t="n"/>
       <c r="J43" s="85" t="n"/>
       <c r="K43" s="85" t="n"/>
+      <c r="L43" s="85" t="n"/>
+      <c r="M43" s="85" t="n"/>
+      <c r="N43" s="85" t="n"/>
+      <c r="O43" s="85" t="n"/>
+      <c r="P43" s="85" t="n"/>
+      <c r="Q43" s="85" t="n"/>
+      <c r="R43" s="85" t="n"/>
+      <c r="S43" s="85" t="n"/>
+      <c r="T43" s="85" t="n"/>
+      <c r="U43" s="85" t="n"/>
+      <c r="V43" s="85" t="n"/>
+      <c r="W43" s="85" t="n"/>
+      <c r="X43" s="85" t="n"/>
+      <c r="Y43" s="85" t="n"/>
+      <c r="Z43" s="85" t="n"/>
+      <c r="AA43" s="85" t="n"/>
+      <c r="AB43" s="85" t="n"/>
+      <c r="AC43" s="85" t="n"/>
+      <c r="AD43" s="85" t="n"/>
+      <c r="AE43" s="85" t="n"/>
+      <c r="AF43" s="85" t="n"/>
     </row>
     <row r="44" ht="18" customHeight="1" s="51">
       <c r="A44" s="84" t="inlineStr">
@@ -8367,6 +9864,27 @@
       <c r="I44" s="84" t="n"/>
       <c r="J44" s="84" t="n"/>
       <c r="K44" s="84" t="n"/>
+      <c r="L44" s="84" t="n"/>
+      <c r="M44" s="84" t="n"/>
+      <c r="N44" s="84" t="n"/>
+      <c r="O44" s="84" t="n"/>
+      <c r="P44" s="84" t="n"/>
+      <c r="Q44" s="84" t="n"/>
+      <c r="R44" s="84" t="n"/>
+      <c r="S44" s="84" t="n"/>
+      <c r="T44" s="84" t="n"/>
+      <c r="U44" s="84" t="n"/>
+      <c r="V44" s="84" t="n"/>
+      <c r="W44" s="84" t="n"/>
+      <c r="X44" s="84" t="n"/>
+      <c r="Y44" s="84" t="n"/>
+      <c r="Z44" s="84" t="n"/>
+      <c r="AA44" s="84" t="n"/>
+      <c r="AB44" s="84" t="n"/>
+      <c r="AC44" s="84" t="n"/>
+      <c r="AD44" s="84" t="n"/>
+      <c r="AE44" s="84" t="n"/>
+      <c r="AF44" s="84" t="n"/>
     </row>
     <row r="45" ht="18" customHeight="1" s="51">
       <c r="A45" s="85" t="inlineStr">
@@ -8388,6 +9906,27 @@
       <c r="I45" s="85" t="n"/>
       <c r="J45" s="85" t="n"/>
       <c r="K45" s="85" t="n"/>
+      <c r="L45" s="85" t="n"/>
+      <c r="M45" s="85" t="n"/>
+      <c r="N45" s="85" t="n"/>
+      <c r="O45" s="85" t="n"/>
+      <c r="P45" s="85" t="n"/>
+      <c r="Q45" s="85" t="n"/>
+      <c r="R45" s="85" t="n"/>
+      <c r="S45" s="85" t="n"/>
+      <c r="T45" s="85" t="n"/>
+      <c r="U45" s="85" t="n"/>
+      <c r="V45" s="85" t="n"/>
+      <c r="W45" s="85" t="n"/>
+      <c r="X45" s="85" t="n"/>
+      <c r="Y45" s="85" t="n"/>
+      <c r="Z45" s="85" t="n"/>
+      <c r="AA45" s="85" t="n"/>
+      <c r="AB45" s="85" t="n"/>
+      <c r="AC45" s="85" t="n"/>
+      <c r="AD45" s="85" t="n"/>
+      <c r="AE45" s="85" t="n"/>
+      <c r="AF45" s="85" t="n"/>
     </row>
     <row r="46" ht="18" customHeight="1" s="51">
       <c r="A46" s="84" t="inlineStr">
@@ -8409,6 +9948,27 @@
       <c r="I46" s="84" t="n"/>
       <c r="J46" s="84" t="n"/>
       <c r="K46" s="84" t="n"/>
+      <c r="L46" s="84" t="n"/>
+      <c r="M46" s="84" t="n"/>
+      <c r="N46" s="84" t="n"/>
+      <c r="O46" s="84" t="n"/>
+      <c r="P46" s="84" t="n"/>
+      <c r="Q46" s="84" t="n"/>
+      <c r="R46" s="84" t="n"/>
+      <c r="S46" s="84" t="n"/>
+      <c r="T46" s="84" t="n"/>
+      <c r="U46" s="84" t="n"/>
+      <c r="V46" s="84" t="n"/>
+      <c r="W46" s="84" t="n"/>
+      <c r="X46" s="84" t="n"/>
+      <c r="Y46" s="84" t="n"/>
+      <c r="Z46" s="84" t="n"/>
+      <c r="AA46" s="84" t="n"/>
+      <c r="AB46" s="84" t="n"/>
+      <c r="AC46" s="84" t="n"/>
+      <c r="AD46" s="84" t="n"/>
+      <c r="AE46" s="84" t="n"/>
+      <c r="AF46" s="84" t="n"/>
     </row>
     <row r="47" ht="18" customHeight="1" s="51">
       <c r="A47" s="85" t="inlineStr">
@@ -8430,6 +9990,27 @@
       <c r="I47" s="85" t="n"/>
       <c r="J47" s="85" t="n"/>
       <c r="K47" s="85" t="n"/>
+      <c r="L47" s="85" t="n"/>
+      <c r="M47" s="85" t="n"/>
+      <c r="N47" s="85" t="n"/>
+      <c r="O47" s="85" t="n"/>
+      <c r="P47" s="85" t="n"/>
+      <c r="Q47" s="85" t="n"/>
+      <c r="R47" s="85" t="n"/>
+      <c r="S47" s="85" t="n"/>
+      <c r="T47" s="85" t="n"/>
+      <c r="U47" s="85" t="n"/>
+      <c r="V47" s="85" t="n"/>
+      <c r="W47" s="85" t="n"/>
+      <c r="X47" s="85" t="n"/>
+      <c r="Y47" s="85" t="n"/>
+      <c r="Z47" s="85" t="n"/>
+      <c r="AA47" s="85" t="n"/>
+      <c r="AB47" s="85" t="n"/>
+      <c r="AC47" s="85" t="n"/>
+      <c r="AD47" s="85" t="n"/>
+      <c r="AE47" s="85" t="n"/>
+      <c r="AF47" s="85" t="n"/>
     </row>
     <row r="48" ht="18" customHeight="1" s="51">
       <c r="A48" s="84" t="inlineStr">
@@ -8451,6 +10032,27 @@
       <c r="I48" s="84" t="n"/>
       <c r="J48" s="84" t="n"/>
       <c r="K48" s="84" t="n"/>
+      <c r="L48" s="84" t="n"/>
+      <c r="M48" s="84" t="n"/>
+      <c r="N48" s="84" t="n"/>
+      <c r="O48" s="84" t="n"/>
+      <c r="P48" s="84" t="n"/>
+      <c r="Q48" s="84" t="n"/>
+      <c r="R48" s="84" t="n"/>
+      <c r="S48" s="84" t="n"/>
+      <c r="T48" s="84" t="n"/>
+      <c r="U48" s="84" t="n"/>
+      <c r="V48" s="84" t="n"/>
+      <c r="W48" s="84" t="n"/>
+      <c r="X48" s="84" t="n"/>
+      <c r="Y48" s="84" t="n"/>
+      <c r="Z48" s="84" t="n"/>
+      <c r="AA48" s="84" t="n"/>
+      <c r="AB48" s="84" t="n"/>
+      <c r="AC48" s="84" t="n"/>
+      <c r="AD48" s="84" t="n"/>
+      <c r="AE48" s="84" t="n"/>
+      <c r="AF48" s="84" t="n"/>
     </row>
     <row r="49" ht="18" customHeight="1" s="51">
       <c r="A49" s="85" t="inlineStr">
@@ -8472,6 +10074,27 @@
       <c r="I49" s="85" t="n"/>
       <c r="J49" s="85" t="n"/>
       <c r="K49" s="85" t="n"/>
+      <c r="L49" s="85" t="n"/>
+      <c r="M49" s="85" t="n"/>
+      <c r="N49" s="85" t="n"/>
+      <c r="O49" s="85" t="n"/>
+      <c r="P49" s="85" t="n"/>
+      <c r="Q49" s="85" t="n"/>
+      <c r="R49" s="85" t="n"/>
+      <c r="S49" s="85" t="n"/>
+      <c r="T49" s="85" t="n"/>
+      <c r="U49" s="85" t="n"/>
+      <c r="V49" s="85" t="n"/>
+      <c r="W49" s="85" t="n"/>
+      <c r="X49" s="85" t="n"/>
+      <c r="Y49" s="85" t="n"/>
+      <c r="Z49" s="85" t="n"/>
+      <c r="AA49" s="85" t="n"/>
+      <c r="AB49" s="85" t="n"/>
+      <c r="AC49" s="85" t="n"/>
+      <c r="AD49" s="85" t="n"/>
+      <c r="AE49" s="85" t="n"/>
+      <c r="AF49" s="85" t="n"/>
     </row>
     <row r="50" ht="18" customHeight="1" s="51">
       <c r="A50" s="84" t="inlineStr">
@@ -8493,6 +10116,27 @@
       <c r="I50" s="84" t="n"/>
       <c r="J50" s="84" t="n"/>
       <c r="K50" s="84" t="n"/>
+      <c r="L50" s="84" t="n"/>
+      <c r="M50" s="84" t="n"/>
+      <c r="N50" s="84" t="n"/>
+      <c r="O50" s="84" t="n"/>
+      <c r="P50" s="84" t="n"/>
+      <c r="Q50" s="84" t="n"/>
+      <c r="R50" s="84" t="n"/>
+      <c r="S50" s="84" t="n"/>
+      <c r="T50" s="84" t="n"/>
+      <c r="U50" s="84" t="n"/>
+      <c r="V50" s="84" t="n"/>
+      <c r="W50" s="84" t="n"/>
+      <c r="X50" s="84" t="n"/>
+      <c r="Y50" s="84" t="n"/>
+      <c r="Z50" s="84" t="n"/>
+      <c r="AA50" s="84" t="n"/>
+      <c r="AB50" s="84" t="n"/>
+      <c r="AC50" s="84" t="n"/>
+      <c r="AD50" s="84" t="n"/>
+      <c r="AE50" s="84" t="n"/>
+      <c r="AF50" s="84" t="n"/>
     </row>
     <row r="51" ht="18" customHeight="1" s="51">
       <c r="A51" s="85" t="inlineStr">
@@ -8514,95 +10158,222 @@
       <c r="I51" s="85" t="n"/>
       <c r="J51" s="85" t="n"/>
       <c r="K51" s="85" t="n"/>
+      <c r="L51" s="85" t="n"/>
+      <c r="M51" s="85" t="n"/>
+      <c r="N51" s="85" t="n"/>
+      <c r="O51" s="85" t="n"/>
+      <c r="P51" s="85" t="n"/>
+      <c r="Q51" s="85" t="n"/>
+      <c r="R51" s="85" t="n"/>
+      <c r="S51" s="85" t="n"/>
+      <c r="T51" s="85" t="n"/>
+      <c r="U51" s="85" t="n"/>
+      <c r="V51" s="85" t="n"/>
+      <c r="W51" s="85" t="n"/>
+      <c r="X51" s="85" t="n"/>
+      <c r="Y51" s="85" t="n"/>
+      <c r="Z51" s="85" t="n"/>
+      <c r="AA51" s="85" t="n"/>
+      <c r="AB51" s="85" t="n"/>
+      <c r="AC51" s="85" t="n"/>
+      <c r="AD51" s="85" t="n"/>
+      <c r="AE51" s="85" t="n"/>
+      <c r="AF51" s="85" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="84" t="inlineStr">
-        <is>
-          <t>Dropdown values: Acquire | Deepen | Create | ? (unscorable/blank)</t>
-        </is>
-      </c>
-      <c r="B53" s="86" t="n"/>
-      <c r="C53" s="86" t="n"/>
-      <c r="D53" s="86" t="n"/>
-      <c r="E53" s="86" t="n"/>
-      <c r="F53" s="86" t="n"/>
-      <c r="G53" s="86" t="n"/>
-      <c r="H53" s="86" t="n"/>
-      <c r="I53" s="86" t="n"/>
-      <c r="J53" s="86" t="n"/>
-      <c r="K53" s="87" t="n"/>
-    </row>
-    <row r="54" ht="40" customHeight="1" s="51">
-      <c r="A54" s="85" t="inlineStr">
+      <c r="A53" s="92" t="inlineStr">
         <is>
           <t>Task descriptions:</t>
         </is>
       </c>
-      <c r="B54" s="85" t="n"/>
-      <c r="C54" s="90" t="inlineStr">
-        <is>
-          <t>Variable + threshold
-Names a valid dataset variable and fills in threshold value(s)</t>
-        </is>
-      </c>
-      <c r="D54" s="90" t="inlineStr">
-        <is>
-          <t>Count consistency
-Recommended + not-recommended counts sum correctly to total number of cards</t>
-        </is>
-      </c>
-      <c r="E54" s="90" t="inlineStr">
-        <is>
-          <t>Variable + threshold
-Names a different valid variable and fills in threshold value(s)</t>
-        </is>
-      </c>
-      <c r="F54" s="90" t="inlineStr">
-        <is>
-          <t>Count consistency
-Counts sum correctly</t>
-        </is>
-      </c>
-      <c r="G54" s="90" t="inlineStr">
-        <is>
-          <t>Variable + threshold
-Names a third valid variable and fills in threshold value(s)</t>
-        </is>
-      </c>
-      <c r="H54" s="90" t="inlineStr">
-        <is>
-          <t>Count consistency
-Counts sum correctly</t>
-        </is>
-      </c>
-      <c r="I54" s="90" t="inlineStr">
-        <is>
-          <t>Chosen threshold
-Final line: states which variable and threshold they selected and records it</t>
-        </is>
-      </c>
-      <c r="J54" s="85" t="inlineStr">
-        <is>
-          <t>Overall AI-CFT level for WS5 as a whole</t>
-        </is>
-      </c>
-      <c r="K54" s="85" t="inlineStr">
-        <is>
-          <t>Free notes</t>
+    </row>
+    <row r="54" ht="60" customHeight="1" s="51">
+      <c r="C54" s="93" t="inlineStr">
+        <is>
+          <t>Block 1 – Variable name
+Name of first chosen variable for threshold exploration</t>
+        </is>
+      </c>
+      <c r="D54" s="93" t="inlineStr">
+        <is>
+          <t>Block 1 – Threshold ≤
+Left threshold value (≤ side) for variable 1</t>
+        </is>
+      </c>
+      <c r="E54" s="93" t="inlineStr">
+        <is>
+          <t>Block 1 – Threshold &gt;
+Right threshold value (&gt; side) for variable 1</t>
+        </is>
+      </c>
+      <c r="F54" s="93" t="inlineStr">
+        <is>
+          <t>Block 1 – Rec count (left)
+Count of recommended foods in left branch (variable 1)</t>
+        </is>
+      </c>
+      <c r="G54" s="93" t="inlineStr">
+        <is>
+          <t>Block 1 – Not-rec count (left)
+Count of not-recommended foods in left branch (variable 1)</t>
+        </is>
+      </c>
+      <c r="H54" s="93" t="inlineStr">
+        <is>
+          <t>Block 1 – Rec count (right)
+Count of recommended foods in right branch (variable 1)</t>
+        </is>
+      </c>
+      <c r="I54" s="93" t="inlineStr">
+        <is>
+          <t>Block 1 – Not-rec count (right)
+Count of not-recommended foods in right branch (variable 1)</t>
+        </is>
+      </c>
+      <c r="J54" s="93" t="inlineStr">
+        <is>
+          <t>Block 1 – Misclassification count
+Total misclassified foods for variable 1 threshold</t>
+        </is>
+      </c>
+      <c r="K54" s="93" t="inlineStr">
+        <is>
+          <t>Block 2 – Variable name
+Name of second chosen variable</t>
+        </is>
+      </c>
+      <c r="L54" s="93" t="inlineStr">
+        <is>
+          <t>Block 2 – Threshold ≤
+Left threshold value (≤ side) for variable 2</t>
+        </is>
+      </c>
+      <c r="M54" s="93" t="inlineStr">
+        <is>
+          <t>Block 2 – Threshold &gt;
+Right threshold value (&gt; side) for variable 2</t>
+        </is>
+      </c>
+      <c r="N54" s="93" t="inlineStr">
+        <is>
+          <t>Block 2 – Rec count (left)
+Count of recommended foods in left branch (variable 2)</t>
+        </is>
+      </c>
+      <c r="O54" s="93" t="inlineStr">
+        <is>
+          <t>Block 2 – Not-rec count (left)
+Count of not-recommended foods in left branch (variable 2)</t>
+        </is>
+      </c>
+      <c r="P54" s="93" t="inlineStr">
+        <is>
+          <t>Block 2 – Rec count (right)
+Count of recommended foods in right branch (variable 2)</t>
+        </is>
+      </c>
+      <c r="Q54" s="93" t="inlineStr">
+        <is>
+          <t>Block 2 – Not-rec count (right)
+Count of not-recommended foods in right branch (variable 2)</t>
+        </is>
+      </c>
+      <c r="R54" s="93" t="inlineStr">
+        <is>
+          <t>Block 2 – Misclassification count
+Total misclassified foods for variable 2 threshold</t>
+        </is>
+      </c>
+      <c r="S54" s="93" t="inlineStr">
+        <is>
+          <t>Block 3 – Variable name
+Name of third chosen variable</t>
+        </is>
+      </c>
+      <c r="T54" s="93" t="inlineStr">
+        <is>
+          <t>Block 3 – Threshold ≤
+Left threshold value (≤ side) for variable 3</t>
+        </is>
+      </c>
+      <c r="U54" s="93" t="inlineStr">
+        <is>
+          <t>Block 3 – Threshold &gt;
+Right threshold value (&gt; side) for variable 3</t>
+        </is>
+      </c>
+      <c r="V54" s="93" t="inlineStr">
+        <is>
+          <t>Block 3 – Rec count (left)
+Count of recommended foods in left branch (variable 3)</t>
+        </is>
+      </c>
+      <c r="W54" s="93" t="inlineStr">
+        <is>
+          <t>Block 3 – Not-rec count (left)
+Count of not-recommended foods in left branch (variable 3)</t>
+        </is>
+      </c>
+      <c r="X54" s="93" t="inlineStr">
+        <is>
+          <t>Block 3 – Rec count (right)
+Count of recommended foods in right branch (variable 3)</t>
+        </is>
+      </c>
+      <c r="Y54" s="93" t="inlineStr">
+        <is>
+          <t>Block 3 – Not-rec count (right)
+Count of not-recommended foods in right branch (variable 3)</t>
+        </is>
+      </c>
+      <c r="Z54" s="93" t="inlineStr">
+        <is>
+          <t>Block 3 – Rec total
+Total recommended count across all branches (variable 3)</t>
+        </is>
+      </c>
+      <c r="AA54" s="93" t="inlineStr">
+        <is>
+          <t>Block 3 – Not-rec total
+Total not-recommended count across all branches (variable 3)</t>
+        </is>
+      </c>
+      <c r="AB54" s="93" t="inlineStr">
+        <is>
+          <t>Block 3 – Misclassification count
+Total misclassified foods for variable 3 threshold</t>
+        </is>
+      </c>
+      <c r="AC54" s="93" t="inlineStr">
+        <is>
+          <t>Chosen variable
+Variable name selected as best for final threshold</t>
+        </is>
+      </c>
+      <c r="AD54" s="93" t="inlineStr">
+        <is>
+          <t>Selected threshold value
+'Which threshold do you choose for ___ variable?' — final numerical answer</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="9">
     <mergeCell ref="A53:K53"/>
     <mergeCell ref="A35:K35"/>
     <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A1:AF1"/>
     <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A35:AF35"/>
+    <mergeCell ref="A4:AF4"/>
     <mergeCell ref="A36:K36"/>
     <mergeCell ref="A5:K5"/>
   </mergeCells>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation sqref="C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 C17 C18 C19 C20 C21 C22 C23 C24 C25 C26 C27 C28 C29 C30 C31 C32 C33 C34 C36 C37 C38 C39 C40 C41 C42 C43 C44 C45 C46 C47 C48 C49 C50 C51 D5 D6 D7 D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19 D20 D21 D22 D23 D24 D25 D26 D27 D28 D29 D30 D31 D32 D33 D34 D36 D37 D38 D39 D40 D41 D42 D43 D44 D45 D46 D47 D48 D49 D50 D51 E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E24 E25 E26 E27 E28 E29 E30 E31 E32 E33 E34 E36 E37 E38 E39 E40 E41 E42 E43 E44 E45 E46 E47 E48 E49 E50 E51 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34 F36 F37 F38 F39 F40 F41 F42 F43 F44 F45 F46 F47 F48 F49 F50 F51 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 G31 G32 G33 G34 G36 G37 G38 G39 G40 G41 G42 G43 G44 G45 G46 G47 G48 G49 G50 G51 H5 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27 H28 H29 H30 H31 H32 H33 H34 H36 H37 H38 H39 H40 H41 H42 H43 H44 H45 H46 H47 H48 H49 H50 H51 I5 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I24 I25 I26 I27 I28 I29 I30 I31 I32 I33 I34 I36 I37 I38 I39 I40 I41 I42 I43 I44 I45 I46 I47 I48 I49 I50 I51 J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25 J26 J27 J28 J29 J30 J31 J32 J33 J34 J36 J37 J38 J39 J40 J41 J42 J43 J44 J45 J46 J47 J48 J49 J50 J51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Choose: Acquire, Deepen, Create, or ?" promptTitle="Select level" prompt="AI-CFT level" type="list">
+      <formula1>"Acquire,Deepen,Create,?"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 C17 C18 C19 C20 C21 C22 C23 C24 C25 C26 C27 C28 C29 C30 C31 C32 C33 C34 C36 C37 C38 C39 C40 C41 C42 C43 C44 C45 C46 C47 C48 C49 C50 C51 D5 D6 D7 D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19 D20 D21 D22 D23 D24 D25 D26 D27 D28 D29 D30 D31 D32 D33 D34 D36 D37 D38 D39 D40 D41 D42 D43 D44 D45 D46 D47 D48 D49 D50 D51 E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E24 E25 E26 E27 E28 E29 E30 E31 E32 E33 E34 E36 E37 E38 E39 E40 E41 E42 E43 E44 E45 E46 E47 E48 E49 E50 E51 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34 F36 F37 F38 F39 F40 F41 F42 F43 F44 F45 F46 F47 F48 F49 F50 F51 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 G31 G32 G33 G34 G36 G37 G38 G39 G40 G41 G42 G43 G44 G45 G46 G47 G48 G49 G50 G51 H5 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27 H28 H29 H30 H31 H32 H33 H34 H36 H37 H38 H39 H40 H41 H42 H43 H44 H45 H46 H47 H48 H49 H50 H51 I5 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I24 I25 I26 I27 I28 I29 I30 I31 I32 I33 I34 I36 I37 I38 I39 I40 I41 I42 I43 I44 I45 I46 I47 I48 I49 I50 I51 J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25 J26 J27 J28 J29 J30 J31 J32 J33 J34 J36 J37 J38 J39 J40 J41 J42 J43 J44 J45 J46 J47 J48 J49 J50 J51 K5 K6 K7 K8 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 K19 K20 K21 K22 K23 K24 K25 K26 K27 K28 K29 K30 K31 K32 K33 K34 K36 K37 K38 K39 K40 K41 K42 K43 K44 K45 K46 K47 K48 K49 K50 K51 L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26 L27 L28 L29 L30 L31 L32 L33 L34 L36 L37 L38 L39 L40 L41 L42 L43 L44 L45 L46 L47 L48 L49 L50 L51 M5 M6 M7 M8 M9 M10 M11 M12 M13 M14 M15 M16 M17 M18 M19 M20 M21 M22 M23 M24 M25 M26 M27 M28 M29 M30 M31 M32 M33 M34 M36 M37 M38 M39 M40 M41 M42 M43 M44 M45 M46 M47 M48 M49 M50 M51 N5 N6 N7 N8 N9 N10 N11 N12 N13 N14 N15 N16 N17 N18 N19 N20 N21 N22 N23 N24 N25 N26 N27 N28 N29 N30 N31 N32 N33 N34 N36 N37 N38 N39 N40 N41 N42 N43 N44 N45 N46 N47 N48 N49 N50 N51 O5 O6 O7 O8 O9 O10 O11 O12 O13 O14 O15 O16 O17 O18 O19 O20 O21 O22 O23 O24 O25 O26 O27 O28 O29 O30 O31 O32 O33 O34 O36 O37 O38 O39 O40 O41 O42 O43 O44 O45 O46 O47 O48 O49 O50 O51 P5 P6 P7 P8 P9 P10 P11 P12 P13 P14 P15 P16 P17 P18 P19 P20 P21 P22 P23 P24 P25 P26 P27 P28 P29 P30 P31 P32 P33 P34 P36 P37 P38 P39 P40 P41 P42 P43 P44 P45 P46 P47 P48 P49 P50 P51 Q5 Q6 Q7 Q8 Q9 Q10 Q11 Q12 Q13 Q14 Q15 Q16 Q17 Q18 Q19 Q20 Q21 Q22 Q23 Q24 Q25 Q26 Q27 Q28 Q29 Q30 Q31 Q32 Q33 Q34 Q36 Q37 Q38 Q39 Q40 Q41 Q42 Q43 Q44 Q45 Q46 Q47 Q48 Q49 Q50 Q51 R5 R6 R7 R8 R9 R10 R11 R12 R13 R14 R15 R16 R17 R18 R19 R20 R21 R22 R23 R24 R25 R26 R27 R28 R29 R30 R31 R32 R33 R34 R36 R37 R38 R39 R40 R41 R42 R43 R44 R45 R46 R47 R48 R49 R50 R51 S5 S6 S7 S8 S9 S10 S11 S12 S13 S14 S15 S16 S17 S18 S19 S20 S21 S22 S23 S24 S25 S26 S27 S28 S29 S30 S31 S32 S33 S34 S36 S37 S38 S39 S40 S41 S42 S43 S44 S45 S46 S47 S48 S49 S50 S51 T5 T6 T7 T8 T9 T10 T11 T12 T13 T14 T15 T16 T17 T18 T19 T20 T21 T22 T23 T24 T25 T26 T27 T28 T29 T30 T31 T32 T33 T34 T36 T37 T38 T39 T40 T41 T42 T43 T44 T45 T46 T47 T48 T49 T50 T51 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U36 U37 U38 U39 U40 U41 U42 U43 U44 U45 U46 U47 U48 U49 U50 U51 V5 V6 V7 V8 V9 V10 V11 V12 V13 V14 V15 V16 V17 V18 V19 V20 V21 V22 V23 V24 V25 V26 V27 V28 V29 V30 V31 V32 V33 V34 V36 V37 V38 V39 V40 V41 V42 V43 V44 V45 V46 V47 V48 V49 V50 V51 W5 W6 W7 W8 W9 W10 W11 W12 W13 W14 W15 W16 W17 W18 W19 W20 W21 W22 W23 W24 W25 W26 W27 W28 W29 W30 W31 W32 W33 W34 W36 W37 W38 W39 W40 W41 W42 W43 W44 W45 W46 W47 W48 W49 W50 W51 X5 X6 X7 X8 X9 X10 X11 X12 X13 X14 X15 X16 X17 X18 X19 X20 X21 X22 X23 X24 X25 X26 X27 X28 X29 X30 X31 X32 X33 X34 X36 X37 X38 X39 X40 X41 X42 X43 X44 X45 X46 X47 X48 X49 X50 X51 Y5 Y6 Y7 Y8 Y9 Y10 Y11 Y12 Y13 Y14 Y15 Y16 Y17 Y18 Y19 Y20 Y21 Y22 Y23 Y24 Y25 Y26 Y27 Y28 Y29 Y30 Y31 Y32 Y33 Y34 Y36 Y37 Y38 Y39 Y40 Y41 Y42 Y43 Y44 Y45 Y46 Y47 Y48 Y49 Y50 Y51 Z5 Z6 Z7 Z8 Z9 Z10 Z11 Z12 Z13 Z14 Z15 Z16 Z17 Z18 Z19 Z20 Z21 Z22 Z23 Z24 Z25 Z26 Z27 Z28 Z29 Z30 Z31 Z32 Z33 Z34 Z36 Z37 Z38 Z39 Z40 Z41 Z42 Z43 Z44 Z45 Z46 Z47 Z48 Z49 Z50 Z51 AA5 AA6 AA7 AA8 AA9 AA10 AA11 AA12 AA13 AA14 AA15 AA16 AA17 AA18 AA19 AA20 AA21 AA22 AA23 AA24 AA25 AA26 AA27 AA28 AA29 AA30 AA31 AA32 AA33 AA34 AA36 AA37 AA38 AA39 AA40 AA41 AA42 AA43 AA44 AA45 AA46 AA47 AA48 AA49 AA50 AA51 AB5 AB6 AB7 AB8 AB9 AB10 AB11 AB12 AB13 AB14 AB15 AB16 AB17 AB18 AB19 AB20 AB21 AB22 AB23 AB24 AB25 AB26 AB27 AB28 AB29 AB30 AB31 AB32 AB33 AB34 AB36 AB37 AB38 AB39 AB40 AB41 AB42 AB43 AB44 AB45 AB46 AB47 AB48 AB49 AB50 AB51 AC5 AC6 AC7 AC8 AC9 AC10 AC11 AC12 AC13 AC14 AC15 AC16 AC17 AC18 AC19 AC20 AC21 AC22 AC23 AC24 AC25 AC26 AC27 AC28 AC29 AC30 AC31 AC32 AC33 AC34 AC36 AC37 AC38 AC39 AC40 AC41 AC42 AC43 AC44 AC45 AC46 AC47 AC48 AC49 AC50 AC51 AD5 AD6 AD7 AD8 AD9 AD10 AD11 AD12 AD13 AD14 AD15 AD16 AD17 AD18 AD19 AD20 AD21 AD22 AD23 AD24 AD25 AD26 AD27 AD28 AD29 AD30 AD31 AD32 AD33 AD34 AD36 AD37 AD38 AD39 AD40 AD41 AD42 AD43 AD44 AD45 AD46 AD47 AD48 AD49 AD50 AD51 AE5 AE6 AE7 AE8 AE9 AE10 AE11 AE12 AE13 AE14 AE15 AE16 AE17 AE18 AE19 AE20 AE21 AE22 AE23 AE24 AE25 AE26 AE27 AE28 AE29 AE30 AE31 AE32 AE33 AE34 AE36 AE37 AE38 AE39 AE40 AE41 AE42 AE43 AE44 AE45 AE46 AE47 AE48 AE49 AE50 AE51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Acquire,Deepen,Create,?"</formula1>
     </dataValidation>
   </dataValidations>
@@ -8616,7 +10387,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K54"/>
+  <dimension ref="A1:Y54"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" style="51" min="1" max="1"/>
@@ -8628,69 +10399,153 @@
     <col width="18" customWidth="1" style="51" min="7" max="7"/>
     <col width="18" customWidth="1" style="51" min="8" max="8"/>
     <col width="18" customWidth="1" style="51" min="9" max="9"/>
-    <col width="14" customWidth="1" style="51" min="10" max="10"/>
-    <col width="22" customWidth="1" style="51" min="11" max="11"/>
+    <col width="18" customWidth="1" style="51" min="10" max="10"/>
+    <col width="18" customWidth="1" style="51" min="11" max="11"/>
+    <col width="18" customWidth="1" style="51" min="12" max="12"/>
+    <col width="18" customWidth="1" style="51" min="13" max="13"/>
+    <col width="18" customWidth="1" style="51" min="14" max="14"/>
+    <col width="18" customWidth="1" style="51" min="15" max="15"/>
+    <col width="18" customWidth="1" style="51" min="16" max="16"/>
+    <col width="18" customWidth="1" style="51" min="17" max="17"/>
+    <col width="18" customWidth="1" style="51" min="18" max="18"/>
+    <col width="18" customWidth="1" style="51" min="19" max="19"/>
+    <col width="18" customWidth="1" style="51" min="20" max="20"/>
+    <col width="18" customWidth="1" style="51" min="21" max="21"/>
+    <col width="18" customWidth="1" style="51" min="22" max="22"/>
+    <col width="18" customWidth="1" style="51" min="23" max="23"/>
+    <col width="14" customWidth="1" style="51" min="24" max="24"/>
+    <col width="22" customWidth="1" style="51" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" s="51">
       <c r="A1" s="77" t="inlineStr">
         <is>
-          <t>AI-CFT Labeling — WS6 - Draw Tree</t>
+          <t>AI-CFT Labeling — WS6</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1" s="51">
-      <c r="A2" s="78" t="inlineStr">
+      <c r="A2" s="91" t="inlineStr">
         <is>
           <t>Cohort</t>
         </is>
       </c>
-      <c r="B2" s="78" t="inlineStr">
+      <c r="B2" s="91" t="inlineStr">
         <is>
           <t>Student</t>
         </is>
       </c>
-      <c r="C2" s="88" t="inlineStr">
-        <is>
-          <t>Deepen</t>
-        </is>
-      </c>
-      <c r="D2" s="79" t="inlineStr">
-        <is>
-          <t>Acquire</t>
-        </is>
-      </c>
-      <c r="E2" s="79" t="inlineStr">
-        <is>
-          <t>Acquire</t>
-        </is>
-      </c>
-      <c r="F2" s="88" t="inlineStr">
-        <is>
-          <t>Deepen</t>
-        </is>
-      </c>
-      <c r="G2" s="79" t="inlineStr">
-        <is>
-          <t>Acquire</t>
-        </is>
-      </c>
-      <c r="H2" s="88" t="inlineStr">
-        <is>
-          <t>Deepen</t>
-        </is>
-      </c>
-      <c r="I2" s="88" t="inlineStr">
-        <is>
-          <t>Deepen</t>
-        </is>
-      </c>
-      <c r="J2" s="80" t="inlineStr">
+      <c r="C2" s="89" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D2" s="89" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="E2" s="89" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="F2" s="89" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="G2" s="89" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="H2" s="89" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="I2" s="89" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="J2" s="89" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="K2" s="89" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="L2" s="89" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="M2" s="89" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="N2" s="89" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="O2" s="89" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="P2" s="89" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="Q2" s="89" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="R2" s="89" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="S2" s="89" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="T2" s="89" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="U2" s="89" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="V2" s="89" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="W2" s="89" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="X2" s="80" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K2" s="80" t="inlineStr">
+      <c r="Y2" s="80" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -8710,51 +10565,135 @@
       <c r="C3" s="82" t="inlineStr">
         <is>
           <t>Blank 1
-Variable</t>
+Root variable</t>
         </is>
       </c>
       <c r="D3" s="82" t="inlineStr">
         <is>
           <t>Blank 2
-&lt;= and &gt;</t>
+Root threshold ≤</t>
         </is>
       </c>
       <c r="E3" s="82" t="inlineStr">
         <is>
           <t>Blank 3
-Classification</t>
+Root threshold &gt;</t>
         </is>
       </c>
       <c r="F3" s="82" t="inlineStr">
         <is>
           <t>Blank 4
-Counts</t>
+Left branch – next node</t>
         </is>
       </c>
       <c r="G3" s="82" t="inlineStr">
         <is>
           <t>Blank 5
-Classification</t>
+Left leaf – rec count</t>
         </is>
       </c>
       <c r="H3" s="82" t="inlineStr">
         <is>
           <t>Blank 6
-Counts</t>
+Left leaf – not-rec count</t>
         </is>
       </c>
       <c r="I3" s="82" t="inlineStr">
         <is>
           <t>Blank 7
-Variable (if present)</t>
+Right branch – next node</t>
         </is>
       </c>
       <c r="J3" s="82" t="inlineStr">
         <is>
+          <t>Blank 8
+Right leaf – rec count</t>
+        </is>
+      </c>
+      <c r="K3" s="82" t="inlineStr">
+        <is>
+          <t>Blank 9
+Right leaf – not-rec count</t>
+        </is>
+      </c>
+      <c r="L3" s="82" t="inlineStr">
+        <is>
+          <t>Blank 10
+Sub-left-left threshold/label</t>
+        </is>
+      </c>
+      <c r="M3" s="82" t="inlineStr">
+        <is>
+          <t>Blank 11
+Sub-left-right threshold/label</t>
+        </is>
+      </c>
+      <c r="N3" s="82" t="inlineStr">
+        <is>
+          <t>Blank 12
+Sub-right-left threshold/label</t>
+        </is>
+      </c>
+      <c r="O3" s="82" t="inlineStr">
+        <is>
+          <t>Blank 13
+Sub-right-right threshold/label</t>
+        </is>
+      </c>
+      <c r="P3" s="82" t="inlineStr">
+        <is>
+          <t>Blank 14
+Leaf LL – rec count</t>
+        </is>
+      </c>
+      <c r="Q3" s="82" t="inlineStr">
+        <is>
+          <t>Blank 15
+Leaf LL – not-rec count</t>
+        </is>
+      </c>
+      <c r="R3" s="82" t="inlineStr">
+        <is>
+          <t>Blank 16
+Leaf LR – rec count</t>
+        </is>
+      </c>
+      <c r="S3" s="82" t="inlineStr">
+        <is>
+          <t>Blank 17
+Leaf LR – not-rec count</t>
+        </is>
+      </c>
+      <c r="T3" s="82" t="inlineStr">
+        <is>
+          <t>Blank 18
+Leaf RL – rec count</t>
+        </is>
+      </c>
+      <c r="U3" s="82" t="inlineStr">
+        <is>
+          <t>Blank 19
+Leaf RL – not-rec count</t>
+        </is>
+      </c>
+      <c r="V3" s="82" t="inlineStr">
+        <is>
+          <t>Blank 20
+Leaf RR – rec count</t>
+        </is>
+      </c>
+      <c r="W3" s="82" t="inlineStr">
+        <is>
+          <t>Blank 21
+Leaf RR – not-rec count</t>
+        </is>
+      </c>
+      <c r="X3" s="82" t="inlineStr">
+        <is>
           <t>Overall WS6</t>
         </is>
       </c>
-      <c r="K3" s="82" t="inlineStr">
+      <c r="Y3" s="82" t="inlineStr">
         <is>
           <t>Notes WS6</t>
         </is>
@@ -8773,16 +10712,34 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="B5" s="86" t="n"/>
-      <c r="C5" s="86" t="n"/>
-      <c r="D5" s="86" t="n"/>
-      <c r="E5" s="86" t="n"/>
-      <c r="F5" s="86" t="n"/>
-      <c r="G5" s="86" t="n"/>
-      <c r="H5" s="86" t="n"/>
-      <c r="I5" s="86" t="n"/>
-      <c r="J5" s="86" t="n"/>
-      <c r="K5" s="87" t="n"/>
+      <c r="B5" s="84" t="inlineStr">
+        <is>
+          <t>Ozzy</t>
+        </is>
+      </c>
+      <c r="C5" s="84" t="n"/>
+      <c r="D5" s="84" t="n"/>
+      <c r="E5" s="84" t="n"/>
+      <c r="F5" s="84" t="n"/>
+      <c r="G5" s="84" t="n"/>
+      <c r="H5" s="84" t="n"/>
+      <c r="I5" s="84" t="n"/>
+      <c r="J5" s="84" t="n"/>
+      <c r="K5" s="84" t="n"/>
+      <c r="L5" s="84" t="n"/>
+      <c r="M5" s="84" t="n"/>
+      <c r="N5" s="84" t="n"/>
+      <c r="O5" s="84" t="n"/>
+      <c r="P5" s="84" t="n"/>
+      <c r="Q5" s="84" t="n"/>
+      <c r="R5" s="84" t="n"/>
+      <c r="S5" s="84" t="n"/>
+      <c r="T5" s="84" t="n"/>
+      <c r="U5" s="84" t="n"/>
+      <c r="V5" s="84" t="n"/>
+      <c r="W5" s="84" t="n"/>
+      <c r="X5" s="84" t="n"/>
+      <c r="Y5" s="84" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1" s="51">
       <c r="A6" s="85" t="inlineStr">
@@ -8804,6 +10761,20 @@
       <c r="I6" s="85" t="n"/>
       <c r="J6" s="85" t="n"/>
       <c r="K6" s="85" t="n"/>
+      <c r="L6" s="85" t="n"/>
+      <c r="M6" s="85" t="n"/>
+      <c r="N6" s="85" t="n"/>
+      <c r="O6" s="85" t="n"/>
+      <c r="P6" s="85" t="n"/>
+      <c r="Q6" s="85" t="n"/>
+      <c r="R6" s="85" t="n"/>
+      <c r="S6" s="85" t="n"/>
+      <c r="T6" s="85" t="n"/>
+      <c r="U6" s="85" t="n"/>
+      <c r="V6" s="85" t="n"/>
+      <c r="W6" s="85" t="n"/>
+      <c r="X6" s="85" t="n"/>
+      <c r="Y6" s="85" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1" s="51">
       <c r="A7" s="84" t="inlineStr">
@@ -8825,6 +10796,20 @@
       <c r="I7" s="84" t="n"/>
       <c r="J7" s="84" t="n"/>
       <c r="K7" s="84" t="n"/>
+      <c r="L7" s="84" t="n"/>
+      <c r="M7" s="84" t="n"/>
+      <c r="N7" s="84" t="n"/>
+      <c r="O7" s="84" t="n"/>
+      <c r="P7" s="84" t="n"/>
+      <c r="Q7" s="84" t="n"/>
+      <c r="R7" s="84" t="n"/>
+      <c r="S7" s="84" t="n"/>
+      <c r="T7" s="84" t="n"/>
+      <c r="U7" s="84" t="n"/>
+      <c r="V7" s="84" t="n"/>
+      <c r="W7" s="84" t="n"/>
+      <c r="X7" s="84" t="n"/>
+      <c r="Y7" s="84" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1" s="51">
       <c r="A8" s="85" t="inlineStr">
@@ -8846,6 +10831,20 @@
       <c r="I8" s="85" t="n"/>
       <c r="J8" s="85" t="n"/>
       <c r="K8" s="85" t="n"/>
+      <c r="L8" s="85" t="n"/>
+      <c r="M8" s="85" t="n"/>
+      <c r="N8" s="85" t="n"/>
+      <c r="O8" s="85" t="n"/>
+      <c r="P8" s="85" t="n"/>
+      <c r="Q8" s="85" t="n"/>
+      <c r="R8" s="85" t="n"/>
+      <c r="S8" s="85" t="n"/>
+      <c r="T8" s="85" t="n"/>
+      <c r="U8" s="85" t="n"/>
+      <c r="V8" s="85" t="n"/>
+      <c r="W8" s="85" t="n"/>
+      <c r="X8" s="85" t="n"/>
+      <c r="Y8" s="85" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1" s="51">
       <c r="A9" s="84" t="inlineStr">
@@ -8867,6 +10866,20 @@
       <c r="I9" s="84" t="n"/>
       <c r="J9" s="84" t="n"/>
       <c r="K9" s="84" t="n"/>
+      <c r="L9" s="84" t="n"/>
+      <c r="M9" s="84" t="n"/>
+      <c r="N9" s="84" t="n"/>
+      <c r="O9" s="84" t="n"/>
+      <c r="P9" s="84" t="n"/>
+      <c r="Q9" s="84" t="n"/>
+      <c r="R9" s="84" t="n"/>
+      <c r="S9" s="84" t="n"/>
+      <c r="T9" s="84" t="n"/>
+      <c r="U9" s="84" t="n"/>
+      <c r="V9" s="84" t="n"/>
+      <c r="W9" s="84" t="n"/>
+      <c r="X9" s="84" t="n"/>
+      <c r="Y9" s="84" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1" s="51">
       <c r="A10" s="85" t="inlineStr">
@@ -8888,6 +10901,20 @@
       <c r="I10" s="85" t="n"/>
       <c r="J10" s="85" t="n"/>
       <c r="K10" s="85" t="n"/>
+      <c r="L10" s="85" t="n"/>
+      <c r="M10" s="85" t="n"/>
+      <c r="N10" s="85" t="n"/>
+      <c r="O10" s="85" t="n"/>
+      <c r="P10" s="85" t="n"/>
+      <c r="Q10" s="85" t="n"/>
+      <c r="R10" s="85" t="n"/>
+      <c r="S10" s="85" t="n"/>
+      <c r="T10" s="85" t="n"/>
+      <c r="U10" s="85" t="n"/>
+      <c r="V10" s="85" t="n"/>
+      <c r="W10" s="85" t="n"/>
+      <c r="X10" s="85" t="n"/>
+      <c r="Y10" s="85" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1" s="51">
       <c r="A11" s="84" t="inlineStr">
@@ -8909,6 +10936,20 @@
       <c r="I11" s="84" t="n"/>
       <c r="J11" s="84" t="n"/>
       <c r="K11" s="84" t="n"/>
+      <c r="L11" s="84" t="n"/>
+      <c r="M11" s="84" t="n"/>
+      <c r="N11" s="84" t="n"/>
+      <c r="O11" s="84" t="n"/>
+      <c r="P11" s="84" t="n"/>
+      <c r="Q11" s="84" t="n"/>
+      <c r="R11" s="84" t="n"/>
+      <c r="S11" s="84" t="n"/>
+      <c r="T11" s="84" t="n"/>
+      <c r="U11" s="84" t="n"/>
+      <c r="V11" s="84" t="n"/>
+      <c r="W11" s="84" t="n"/>
+      <c r="X11" s="84" t="n"/>
+      <c r="Y11" s="84" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1" s="51">
       <c r="A12" s="85" t="inlineStr">
@@ -8930,6 +10971,20 @@
       <c r="I12" s="85" t="n"/>
       <c r="J12" s="85" t="n"/>
       <c r="K12" s="85" t="n"/>
+      <c r="L12" s="85" t="n"/>
+      <c r="M12" s="85" t="n"/>
+      <c r="N12" s="85" t="n"/>
+      <c r="O12" s="85" t="n"/>
+      <c r="P12" s="85" t="n"/>
+      <c r="Q12" s="85" t="n"/>
+      <c r="R12" s="85" t="n"/>
+      <c r="S12" s="85" t="n"/>
+      <c r="T12" s="85" t="n"/>
+      <c r="U12" s="85" t="n"/>
+      <c r="V12" s="85" t="n"/>
+      <c r="W12" s="85" t="n"/>
+      <c r="X12" s="85" t="n"/>
+      <c r="Y12" s="85" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1" s="51">
       <c r="A13" s="84" t="inlineStr">
@@ -8951,6 +11006,20 @@
       <c r="I13" s="84" t="n"/>
       <c r="J13" s="84" t="n"/>
       <c r="K13" s="84" t="n"/>
+      <c r="L13" s="84" t="n"/>
+      <c r="M13" s="84" t="n"/>
+      <c r="N13" s="84" t="n"/>
+      <c r="O13" s="84" t="n"/>
+      <c r="P13" s="84" t="n"/>
+      <c r="Q13" s="84" t="n"/>
+      <c r="R13" s="84" t="n"/>
+      <c r="S13" s="84" t="n"/>
+      <c r="T13" s="84" t="n"/>
+      <c r="U13" s="84" t="n"/>
+      <c r="V13" s="84" t="n"/>
+      <c r="W13" s="84" t="n"/>
+      <c r="X13" s="84" t="n"/>
+      <c r="Y13" s="84" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1" s="51">
       <c r="A14" s="85" t="inlineStr">
@@ -8972,6 +11041,20 @@
       <c r="I14" s="85" t="n"/>
       <c r="J14" s="85" t="n"/>
       <c r="K14" s="85" t="n"/>
+      <c r="L14" s="85" t="n"/>
+      <c r="M14" s="85" t="n"/>
+      <c r="N14" s="85" t="n"/>
+      <c r="O14" s="85" t="n"/>
+      <c r="P14" s="85" t="n"/>
+      <c r="Q14" s="85" t="n"/>
+      <c r="R14" s="85" t="n"/>
+      <c r="S14" s="85" t="n"/>
+      <c r="T14" s="85" t="n"/>
+      <c r="U14" s="85" t="n"/>
+      <c r="V14" s="85" t="n"/>
+      <c r="W14" s="85" t="n"/>
+      <c r="X14" s="85" t="n"/>
+      <c r="Y14" s="85" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1" s="51">
       <c r="A15" s="84" t="inlineStr">
@@ -8993,6 +11076,20 @@
       <c r="I15" s="84" t="n"/>
       <c r="J15" s="84" t="n"/>
       <c r="K15" s="84" t="n"/>
+      <c r="L15" s="84" t="n"/>
+      <c r="M15" s="84" t="n"/>
+      <c r="N15" s="84" t="n"/>
+      <c r="O15" s="84" t="n"/>
+      <c r="P15" s="84" t="n"/>
+      <c r="Q15" s="84" t="n"/>
+      <c r="R15" s="84" t="n"/>
+      <c r="S15" s="84" t="n"/>
+      <c r="T15" s="84" t="n"/>
+      <c r="U15" s="84" t="n"/>
+      <c r="V15" s="84" t="n"/>
+      <c r="W15" s="84" t="n"/>
+      <c r="X15" s="84" t="n"/>
+      <c r="Y15" s="84" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1" s="51">
       <c r="A16" s="85" t="inlineStr">
@@ -9014,6 +11111,20 @@
       <c r="I16" s="85" t="n"/>
       <c r="J16" s="85" t="n"/>
       <c r="K16" s="85" t="n"/>
+      <c r="L16" s="85" t="n"/>
+      <c r="M16" s="85" t="n"/>
+      <c r="N16" s="85" t="n"/>
+      <c r="O16" s="85" t="n"/>
+      <c r="P16" s="85" t="n"/>
+      <c r="Q16" s="85" t="n"/>
+      <c r="R16" s="85" t="n"/>
+      <c r="S16" s="85" t="n"/>
+      <c r="T16" s="85" t="n"/>
+      <c r="U16" s="85" t="n"/>
+      <c r="V16" s="85" t="n"/>
+      <c r="W16" s="85" t="n"/>
+      <c r="X16" s="85" t="n"/>
+      <c r="Y16" s="85" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1" s="51">
       <c r="A17" s="84" t="inlineStr">
@@ -9035,6 +11146,20 @@
       <c r="I17" s="84" t="n"/>
       <c r="J17" s="84" t="n"/>
       <c r="K17" s="84" t="n"/>
+      <c r="L17" s="84" t="n"/>
+      <c r="M17" s="84" t="n"/>
+      <c r="N17" s="84" t="n"/>
+      <c r="O17" s="84" t="n"/>
+      <c r="P17" s="84" t="n"/>
+      <c r="Q17" s="84" t="n"/>
+      <c r="R17" s="84" t="n"/>
+      <c r="S17" s="84" t="n"/>
+      <c r="T17" s="84" t="n"/>
+      <c r="U17" s="84" t="n"/>
+      <c r="V17" s="84" t="n"/>
+      <c r="W17" s="84" t="n"/>
+      <c r="X17" s="84" t="n"/>
+      <c r="Y17" s="84" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1" s="51">
       <c r="A18" s="85" t="inlineStr">
@@ -9056,6 +11181,20 @@
       <c r="I18" s="85" t="n"/>
       <c r="J18" s="85" t="n"/>
       <c r="K18" s="85" t="n"/>
+      <c r="L18" s="85" t="n"/>
+      <c r="M18" s="85" t="n"/>
+      <c r="N18" s="85" t="n"/>
+      <c r="O18" s="85" t="n"/>
+      <c r="P18" s="85" t="n"/>
+      <c r="Q18" s="85" t="n"/>
+      <c r="R18" s="85" t="n"/>
+      <c r="S18" s="85" t="n"/>
+      <c r="T18" s="85" t="n"/>
+      <c r="U18" s="85" t="n"/>
+      <c r="V18" s="85" t="n"/>
+      <c r="W18" s="85" t="n"/>
+      <c r="X18" s="85" t="n"/>
+      <c r="Y18" s="85" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1" s="51">
       <c r="A19" s="84" t="inlineStr">
@@ -9077,6 +11216,20 @@
       <c r="I19" s="84" t="n"/>
       <c r="J19" s="84" t="n"/>
       <c r="K19" s="84" t="n"/>
+      <c r="L19" s="84" t="n"/>
+      <c r="M19" s="84" t="n"/>
+      <c r="N19" s="84" t="n"/>
+      <c r="O19" s="84" t="n"/>
+      <c r="P19" s="84" t="n"/>
+      <c r="Q19" s="84" t="n"/>
+      <c r="R19" s="84" t="n"/>
+      <c r="S19" s="84" t="n"/>
+      <c r="T19" s="84" t="n"/>
+      <c r="U19" s="84" t="n"/>
+      <c r="V19" s="84" t="n"/>
+      <c r="W19" s="84" t="n"/>
+      <c r="X19" s="84" t="n"/>
+      <c r="Y19" s="84" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1" s="51">
       <c r="A20" s="85" t="inlineStr">
@@ -9098,6 +11251,20 @@
       <c r="I20" s="85" t="n"/>
       <c r="J20" s="85" t="n"/>
       <c r="K20" s="85" t="n"/>
+      <c r="L20" s="85" t="n"/>
+      <c r="M20" s="85" t="n"/>
+      <c r="N20" s="85" t="n"/>
+      <c r="O20" s="85" t="n"/>
+      <c r="P20" s="85" t="n"/>
+      <c r="Q20" s="85" t="n"/>
+      <c r="R20" s="85" t="n"/>
+      <c r="S20" s="85" t="n"/>
+      <c r="T20" s="85" t="n"/>
+      <c r="U20" s="85" t="n"/>
+      <c r="V20" s="85" t="n"/>
+      <c r="W20" s="85" t="n"/>
+      <c r="X20" s="85" t="n"/>
+      <c r="Y20" s="85" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1" s="51">
       <c r="A21" s="84" t="inlineStr">
@@ -9119,6 +11286,20 @@
       <c r="I21" s="84" t="n"/>
       <c r="J21" s="84" t="n"/>
       <c r="K21" s="84" t="n"/>
+      <c r="L21" s="84" t="n"/>
+      <c r="M21" s="84" t="n"/>
+      <c r="N21" s="84" t="n"/>
+      <c r="O21" s="84" t="n"/>
+      <c r="P21" s="84" t="n"/>
+      <c r="Q21" s="84" t="n"/>
+      <c r="R21" s="84" t="n"/>
+      <c r="S21" s="84" t="n"/>
+      <c r="T21" s="84" t="n"/>
+      <c r="U21" s="84" t="n"/>
+      <c r="V21" s="84" t="n"/>
+      <c r="W21" s="84" t="n"/>
+      <c r="X21" s="84" t="n"/>
+      <c r="Y21" s="84" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1" s="51">
       <c r="A22" s="85" t="inlineStr">
@@ -9140,6 +11321,20 @@
       <c r="I22" s="85" t="n"/>
       <c r="J22" s="85" t="n"/>
       <c r="K22" s="85" t="n"/>
+      <c r="L22" s="85" t="n"/>
+      <c r="M22" s="85" t="n"/>
+      <c r="N22" s="85" t="n"/>
+      <c r="O22" s="85" t="n"/>
+      <c r="P22" s="85" t="n"/>
+      <c r="Q22" s="85" t="n"/>
+      <c r="R22" s="85" t="n"/>
+      <c r="S22" s="85" t="n"/>
+      <c r="T22" s="85" t="n"/>
+      <c r="U22" s="85" t="n"/>
+      <c r="V22" s="85" t="n"/>
+      <c r="W22" s="85" t="n"/>
+      <c r="X22" s="85" t="n"/>
+      <c r="Y22" s="85" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1" s="51">
       <c r="A23" s="84" t="inlineStr">
@@ -9161,6 +11356,20 @@
       <c r="I23" s="84" t="n"/>
       <c r="J23" s="84" t="n"/>
       <c r="K23" s="84" t="n"/>
+      <c r="L23" s="84" t="n"/>
+      <c r="M23" s="84" t="n"/>
+      <c r="N23" s="84" t="n"/>
+      <c r="O23" s="84" t="n"/>
+      <c r="P23" s="84" t="n"/>
+      <c r="Q23" s="84" t="n"/>
+      <c r="R23" s="84" t="n"/>
+      <c r="S23" s="84" t="n"/>
+      <c r="T23" s="84" t="n"/>
+      <c r="U23" s="84" t="n"/>
+      <c r="V23" s="84" t="n"/>
+      <c r="W23" s="84" t="n"/>
+      <c r="X23" s="84" t="n"/>
+      <c r="Y23" s="84" t="n"/>
     </row>
     <row r="24" ht="18" customHeight="1" s="51">
       <c r="A24" s="85" t="inlineStr">
@@ -9182,6 +11391,20 @@
       <c r="I24" s="85" t="n"/>
       <c r="J24" s="85" t="n"/>
       <c r="K24" s="85" t="n"/>
+      <c r="L24" s="85" t="n"/>
+      <c r="M24" s="85" t="n"/>
+      <c r="N24" s="85" t="n"/>
+      <c r="O24" s="85" t="n"/>
+      <c r="P24" s="85" t="n"/>
+      <c r="Q24" s="85" t="n"/>
+      <c r="R24" s="85" t="n"/>
+      <c r="S24" s="85" t="n"/>
+      <c r="T24" s="85" t="n"/>
+      <c r="U24" s="85" t="n"/>
+      <c r="V24" s="85" t="n"/>
+      <c r="W24" s="85" t="n"/>
+      <c r="X24" s="85" t="n"/>
+      <c r="Y24" s="85" t="n"/>
     </row>
     <row r="25" ht="18" customHeight="1" s="51">
       <c r="A25" s="84" t="inlineStr">
@@ -9203,6 +11426,20 @@
       <c r="I25" s="84" t="n"/>
       <c r="J25" s="84" t="n"/>
       <c r="K25" s="84" t="n"/>
+      <c r="L25" s="84" t="n"/>
+      <c r="M25" s="84" t="n"/>
+      <c r="N25" s="84" t="n"/>
+      <c r="O25" s="84" t="n"/>
+      <c r="P25" s="84" t="n"/>
+      <c r="Q25" s="84" t="n"/>
+      <c r="R25" s="84" t="n"/>
+      <c r="S25" s="84" t="n"/>
+      <c r="T25" s="84" t="n"/>
+      <c r="U25" s="84" t="n"/>
+      <c r="V25" s="84" t="n"/>
+      <c r="W25" s="84" t="n"/>
+      <c r="X25" s="84" t="n"/>
+      <c r="Y25" s="84" t="n"/>
     </row>
     <row r="26" ht="18" customHeight="1" s="51">
       <c r="A26" s="85" t="inlineStr">
@@ -9224,6 +11461,20 @@
       <c r="I26" s="85" t="n"/>
       <c r="J26" s="85" t="n"/>
       <c r="K26" s="85" t="n"/>
+      <c r="L26" s="85" t="n"/>
+      <c r="M26" s="85" t="n"/>
+      <c r="N26" s="85" t="n"/>
+      <c r="O26" s="85" t="n"/>
+      <c r="P26" s="85" t="n"/>
+      <c r="Q26" s="85" t="n"/>
+      <c r="R26" s="85" t="n"/>
+      <c r="S26" s="85" t="n"/>
+      <c r="T26" s="85" t="n"/>
+      <c r="U26" s="85" t="n"/>
+      <c r="V26" s="85" t="n"/>
+      <c r="W26" s="85" t="n"/>
+      <c r="X26" s="85" t="n"/>
+      <c r="Y26" s="85" t="n"/>
     </row>
     <row r="27" ht="18" customHeight="1" s="51">
       <c r="A27" s="84" t="inlineStr">
@@ -9245,6 +11496,20 @@
       <c r="I27" s="84" t="n"/>
       <c r="J27" s="84" t="n"/>
       <c r="K27" s="84" t="n"/>
+      <c r="L27" s="84" t="n"/>
+      <c r="M27" s="84" t="n"/>
+      <c r="N27" s="84" t="n"/>
+      <c r="O27" s="84" t="n"/>
+      <c r="P27" s="84" t="n"/>
+      <c r="Q27" s="84" t="n"/>
+      <c r="R27" s="84" t="n"/>
+      <c r="S27" s="84" t="n"/>
+      <c r="T27" s="84" t="n"/>
+      <c r="U27" s="84" t="n"/>
+      <c r="V27" s="84" t="n"/>
+      <c r="W27" s="84" t="n"/>
+      <c r="X27" s="84" t="n"/>
+      <c r="Y27" s="84" t="n"/>
     </row>
     <row r="28" ht="18" customHeight="1" s="51">
       <c r="A28" s="85" t="inlineStr">
@@ -9266,6 +11531,20 @@
       <c r="I28" s="85" t="n"/>
       <c r="J28" s="85" t="n"/>
       <c r="K28" s="85" t="n"/>
+      <c r="L28" s="85" t="n"/>
+      <c r="M28" s="85" t="n"/>
+      <c r="N28" s="85" t="n"/>
+      <c r="O28" s="85" t="n"/>
+      <c r="P28" s="85" t="n"/>
+      <c r="Q28" s="85" t="n"/>
+      <c r="R28" s="85" t="n"/>
+      <c r="S28" s="85" t="n"/>
+      <c r="T28" s="85" t="n"/>
+      <c r="U28" s="85" t="n"/>
+      <c r="V28" s="85" t="n"/>
+      <c r="W28" s="85" t="n"/>
+      <c r="X28" s="85" t="n"/>
+      <c r="Y28" s="85" t="n"/>
     </row>
     <row r="29" ht="18" customHeight="1" s="51">
       <c r="A29" s="84" t="inlineStr">
@@ -9287,6 +11566,20 @@
       <c r="I29" s="84" t="n"/>
       <c r="J29" s="84" t="n"/>
       <c r="K29" s="84" t="n"/>
+      <c r="L29" s="84" t="n"/>
+      <c r="M29" s="84" t="n"/>
+      <c r="N29" s="84" t="n"/>
+      <c r="O29" s="84" t="n"/>
+      <c r="P29" s="84" t="n"/>
+      <c r="Q29" s="84" t="n"/>
+      <c r="R29" s="84" t="n"/>
+      <c r="S29" s="84" t="n"/>
+      <c r="T29" s="84" t="n"/>
+      <c r="U29" s="84" t="n"/>
+      <c r="V29" s="84" t="n"/>
+      <c r="W29" s="84" t="n"/>
+      <c r="X29" s="84" t="n"/>
+      <c r="Y29" s="84" t="n"/>
     </row>
     <row r="30" ht="18" customHeight="1" s="51">
       <c r="A30" s="85" t="inlineStr">
@@ -9308,6 +11601,20 @@
       <c r="I30" s="85" t="n"/>
       <c r="J30" s="85" t="n"/>
       <c r="K30" s="85" t="n"/>
+      <c r="L30" s="85" t="n"/>
+      <c r="M30" s="85" t="n"/>
+      <c r="N30" s="85" t="n"/>
+      <c r="O30" s="85" t="n"/>
+      <c r="P30" s="85" t="n"/>
+      <c r="Q30" s="85" t="n"/>
+      <c r="R30" s="85" t="n"/>
+      <c r="S30" s="85" t="n"/>
+      <c r="T30" s="85" t="n"/>
+      <c r="U30" s="85" t="n"/>
+      <c r="V30" s="85" t="n"/>
+      <c r="W30" s="85" t="n"/>
+      <c r="X30" s="85" t="n"/>
+      <c r="Y30" s="85" t="n"/>
     </row>
     <row r="31" ht="18" customHeight="1" s="51">
       <c r="A31" s="84" t="inlineStr">
@@ -9329,6 +11636,20 @@
       <c r="I31" s="84" t="n"/>
       <c r="J31" s="84" t="n"/>
       <c r="K31" s="84" t="n"/>
+      <c r="L31" s="84" t="n"/>
+      <c r="M31" s="84" t="n"/>
+      <c r="N31" s="84" t="n"/>
+      <c r="O31" s="84" t="n"/>
+      <c r="P31" s="84" t="n"/>
+      <c r="Q31" s="84" t="n"/>
+      <c r="R31" s="84" t="n"/>
+      <c r="S31" s="84" t="n"/>
+      <c r="T31" s="84" t="n"/>
+      <c r="U31" s="84" t="n"/>
+      <c r="V31" s="84" t="n"/>
+      <c r="W31" s="84" t="n"/>
+      <c r="X31" s="84" t="n"/>
+      <c r="Y31" s="84" t="n"/>
     </row>
     <row r="32" ht="18" customHeight="1" s="51">
       <c r="A32" s="85" t="inlineStr">
@@ -9350,6 +11671,20 @@
       <c r="I32" s="85" t="n"/>
       <c r="J32" s="85" t="n"/>
       <c r="K32" s="85" t="n"/>
+      <c r="L32" s="85" t="n"/>
+      <c r="M32" s="85" t="n"/>
+      <c r="N32" s="85" t="n"/>
+      <c r="O32" s="85" t="n"/>
+      <c r="P32" s="85" t="n"/>
+      <c r="Q32" s="85" t="n"/>
+      <c r="R32" s="85" t="n"/>
+      <c r="S32" s="85" t="n"/>
+      <c r="T32" s="85" t="n"/>
+      <c r="U32" s="85" t="n"/>
+      <c r="V32" s="85" t="n"/>
+      <c r="W32" s="85" t="n"/>
+      <c r="X32" s="85" t="n"/>
+      <c r="Y32" s="85" t="n"/>
     </row>
     <row r="33" ht="18" customHeight="1" s="51">
       <c r="A33" s="84" t="inlineStr">
@@ -9371,6 +11706,20 @@
       <c r="I33" s="84" t="n"/>
       <c r="J33" s="84" t="n"/>
       <c r="K33" s="84" t="n"/>
+      <c r="L33" s="84" t="n"/>
+      <c r="M33" s="84" t="n"/>
+      <c r="N33" s="84" t="n"/>
+      <c r="O33" s="84" t="n"/>
+      <c r="P33" s="84" t="n"/>
+      <c r="Q33" s="84" t="n"/>
+      <c r="R33" s="84" t="n"/>
+      <c r="S33" s="84" t="n"/>
+      <c r="T33" s="84" t="n"/>
+      <c r="U33" s="84" t="n"/>
+      <c r="V33" s="84" t="n"/>
+      <c r="W33" s="84" t="n"/>
+      <c r="X33" s="84" t="n"/>
+      <c r="Y33" s="84" t="n"/>
     </row>
     <row r="34" ht="18" customHeight="1" s="51">
       <c r="A34" s="85" t="inlineStr">
@@ -9378,7 +11727,11 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="B34" s="85" t="n"/>
+      <c r="B34" s="85" t="inlineStr">
+        <is>
+          <t>Sabrina</t>
+        </is>
+      </c>
       <c r="C34" s="85" t="n"/>
       <c r="D34" s="85" t="n"/>
       <c r="E34" s="85" t="n"/>
@@ -9388,6 +11741,20 @@
       <c r="I34" s="85" t="n"/>
       <c r="J34" s="85" t="n"/>
       <c r="K34" s="85" t="n"/>
+      <c r="L34" s="85" t="n"/>
+      <c r="M34" s="85" t="n"/>
+      <c r="N34" s="85" t="n"/>
+      <c r="O34" s="85" t="n"/>
+      <c r="P34" s="85" t="n"/>
+      <c r="Q34" s="85" t="n"/>
+      <c r="R34" s="85" t="n"/>
+      <c r="S34" s="85" t="n"/>
+      <c r="T34" s="85" t="n"/>
+      <c r="U34" s="85" t="n"/>
+      <c r="V34" s="85" t="n"/>
+      <c r="W34" s="85" t="n"/>
+      <c r="X34" s="85" t="n"/>
+      <c r="Y34" s="85" t="n"/>
     </row>
     <row r="35" ht="20" customHeight="1" s="51">
       <c r="A35" s="83" t="inlineStr">
@@ -9402,16 +11769,34 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="B36" s="86" t="n"/>
-      <c r="C36" s="86" t="n"/>
-      <c r="D36" s="86" t="n"/>
-      <c r="E36" s="86" t="n"/>
-      <c r="F36" s="86" t="n"/>
-      <c r="G36" s="86" t="n"/>
-      <c r="H36" s="86" t="n"/>
-      <c r="I36" s="86" t="n"/>
-      <c r="J36" s="86" t="n"/>
-      <c r="K36" s="87" t="n"/>
+      <c r="B36" s="84" t="inlineStr">
+        <is>
+          <t>Sheila</t>
+        </is>
+      </c>
+      <c r="C36" s="84" t="n"/>
+      <c r="D36" s="84" t="n"/>
+      <c r="E36" s="84" t="n"/>
+      <c r="F36" s="84" t="n"/>
+      <c r="G36" s="84" t="n"/>
+      <c r="H36" s="84" t="n"/>
+      <c r="I36" s="84" t="n"/>
+      <c r="J36" s="84" t="n"/>
+      <c r="K36" s="84" t="n"/>
+      <c r="L36" s="84" t="n"/>
+      <c r="M36" s="84" t="n"/>
+      <c r="N36" s="84" t="n"/>
+      <c r="O36" s="84" t="n"/>
+      <c r="P36" s="84" t="n"/>
+      <c r="Q36" s="84" t="n"/>
+      <c r="R36" s="84" t="n"/>
+      <c r="S36" s="84" t="n"/>
+      <c r="T36" s="84" t="n"/>
+      <c r="U36" s="84" t="n"/>
+      <c r="V36" s="84" t="n"/>
+      <c r="W36" s="84" t="n"/>
+      <c r="X36" s="84" t="n"/>
+      <c r="Y36" s="84" t="n"/>
     </row>
     <row r="37" ht="18" customHeight="1" s="51">
       <c r="A37" s="85" t="inlineStr">
@@ -9433,6 +11818,20 @@
       <c r="I37" s="85" t="n"/>
       <c r="J37" s="85" t="n"/>
       <c r="K37" s="85" t="n"/>
+      <c r="L37" s="85" t="n"/>
+      <c r="M37" s="85" t="n"/>
+      <c r="N37" s="85" t="n"/>
+      <c r="O37" s="85" t="n"/>
+      <c r="P37" s="85" t="n"/>
+      <c r="Q37" s="85" t="n"/>
+      <c r="R37" s="85" t="n"/>
+      <c r="S37" s="85" t="n"/>
+      <c r="T37" s="85" t="n"/>
+      <c r="U37" s="85" t="n"/>
+      <c r="V37" s="85" t="n"/>
+      <c r="W37" s="85" t="n"/>
+      <c r="X37" s="85" t="n"/>
+      <c r="Y37" s="85" t="n"/>
     </row>
     <row r="38" ht="18" customHeight="1" s="51">
       <c r="A38" s="84" t="inlineStr">
@@ -9454,6 +11853,20 @@
       <c r="I38" s="84" t="n"/>
       <c r="J38" s="84" t="n"/>
       <c r="K38" s="84" t="n"/>
+      <c r="L38" s="84" t="n"/>
+      <c r="M38" s="84" t="n"/>
+      <c r="N38" s="84" t="n"/>
+      <c r="O38" s="84" t="n"/>
+      <c r="P38" s="84" t="n"/>
+      <c r="Q38" s="84" t="n"/>
+      <c r="R38" s="84" t="n"/>
+      <c r="S38" s="84" t="n"/>
+      <c r="T38" s="84" t="n"/>
+      <c r="U38" s="84" t="n"/>
+      <c r="V38" s="84" t="n"/>
+      <c r="W38" s="84" t="n"/>
+      <c r="X38" s="84" t="n"/>
+      <c r="Y38" s="84" t="n"/>
     </row>
     <row r="39" ht="18" customHeight="1" s="51">
       <c r="A39" s="85" t="inlineStr">
@@ -9475,6 +11888,20 @@
       <c r="I39" s="85" t="n"/>
       <c r="J39" s="85" t="n"/>
       <c r="K39" s="85" t="n"/>
+      <c r="L39" s="85" t="n"/>
+      <c r="M39" s="85" t="n"/>
+      <c r="N39" s="85" t="n"/>
+      <c r="O39" s="85" t="n"/>
+      <c r="P39" s="85" t="n"/>
+      <c r="Q39" s="85" t="n"/>
+      <c r="R39" s="85" t="n"/>
+      <c r="S39" s="85" t="n"/>
+      <c r="T39" s="85" t="n"/>
+      <c r="U39" s="85" t="n"/>
+      <c r="V39" s="85" t="n"/>
+      <c r="W39" s="85" t="n"/>
+      <c r="X39" s="85" t="n"/>
+      <c r="Y39" s="85" t="n"/>
     </row>
     <row r="40" ht="18" customHeight="1" s="51">
       <c r="A40" s="84" t="inlineStr">
@@ -9496,6 +11923,20 @@
       <c r="I40" s="84" t="n"/>
       <c r="J40" s="84" t="n"/>
       <c r="K40" s="84" t="n"/>
+      <c r="L40" s="84" t="n"/>
+      <c r="M40" s="84" t="n"/>
+      <c r="N40" s="84" t="n"/>
+      <c r="O40" s="84" t="n"/>
+      <c r="P40" s="84" t="n"/>
+      <c r="Q40" s="84" t="n"/>
+      <c r="R40" s="84" t="n"/>
+      <c r="S40" s="84" t="n"/>
+      <c r="T40" s="84" t="n"/>
+      <c r="U40" s="84" t="n"/>
+      <c r="V40" s="84" t="n"/>
+      <c r="W40" s="84" t="n"/>
+      <c r="X40" s="84" t="n"/>
+      <c r="Y40" s="84" t="n"/>
     </row>
     <row r="41" ht="18" customHeight="1" s="51">
       <c r="A41" s="85" t="inlineStr">
@@ -9517,6 +11958,20 @@
       <c r="I41" s="85" t="n"/>
       <c r="J41" s="85" t="n"/>
       <c r="K41" s="85" t="n"/>
+      <c r="L41" s="85" t="n"/>
+      <c r="M41" s="85" t="n"/>
+      <c r="N41" s="85" t="n"/>
+      <c r="O41" s="85" t="n"/>
+      <c r="P41" s="85" t="n"/>
+      <c r="Q41" s="85" t="n"/>
+      <c r="R41" s="85" t="n"/>
+      <c r="S41" s="85" t="n"/>
+      <c r="T41" s="85" t="n"/>
+      <c r="U41" s="85" t="n"/>
+      <c r="V41" s="85" t="n"/>
+      <c r="W41" s="85" t="n"/>
+      <c r="X41" s="85" t="n"/>
+      <c r="Y41" s="85" t="n"/>
     </row>
     <row r="42" ht="18" customHeight="1" s="51">
       <c r="A42" s="84" t="inlineStr">
@@ -9538,6 +11993,20 @@
       <c r="I42" s="84" t="n"/>
       <c r="J42" s="84" t="n"/>
       <c r="K42" s="84" t="n"/>
+      <c r="L42" s="84" t="n"/>
+      <c r="M42" s="84" t="n"/>
+      <c r="N42" s="84" t="n"/>
+      <c r="O42" s="84" t="n"/>
+      <c r="P42" s="84" t="n"/>
+      <c r="Q42" s="84" t="n"/>
+      <c r="R42" s="84" t="n"/>
+      <c r="S42" s="84" t="n"/>
+      <c r="T42" s="84" t="n"/>
+      <c r="U42" s="84" t="n"/>
+      <c r="V42" s="84" t="n"/>
+      <c r="W42" s="84" t="n"/>
+      <c r="X42" s="84" t="n"/>
+      <c r="Y42" s="84" t="n"/>
     </row>
     <row r="43" ht="18" customHeight="1" s="51">
       <c r="A43" s="85" t="inlineStr">
@@ -9559,6 +12028,20 @@
       <c r="I43" s="85" t="n"/>
       <c r="J43" s="85" t="n"/>
       <c r="K43" s="85" t="n"/>
+      <c r="L43" s="85" t="n"/>
+      <c r="M43" s="85" t="n"/>
+      <c r="N43" s="85" t="n"/>
+      <c r="O43" s="85" t="n"/>
+      <c r="P43" s="85" t="n"/>
+      <c r="Q43" s="85" t="n"/>
+      <c r="R43" s="85" t="n"/>
+      <c r="S43" s="85" t="n"/>
+      <c r="T43" s="85" t="n"/>
+      <c r="U43" s="85" t="n"/>
+      <c r="V43" s="85" t="n"/>
+      <c r="W43" s="85" t="n"/>
+      <c r="X43" s="85" t="n"/>
+      <c r="Y43" s="85" t="n"/>
     </row>
     <row r="44" ht="18" customHeight="1" s="51">
       <c r="A44" s="84" t="inlineStr">
@@ -9580,6 +12063,20 @@
       <c r="I44" s="84" t="n"/>
       <c r="J44" s="84" t="n"/>
       <c r="K44" s="84" t="n"/>
+      <c r="L44" s="84" t="n"/>
+      <c r="M44" s="84" t="n"/>
+      <c r="N44" s="84" t="n"/>
+      <c r="O44" s="84" t="n"/>
+      <c r="P44" s="84" t="n"/>
+      <c r="Q44" s="84" t="n"/>
+      <c r="R44" s="84" t="n"/>
+      <c r="S44" s="84" t="n"/>
+      <c r="T44" s="84" t="n"/>
+      <c r="U44" s="84" t="n"/>
+      <c r="V44" s="84" t="n"/>
+      <c r="W44" s="84" t="n"/>
+      <c r="X44" s="84" t="n"/>
+      <c r="Y44" s="84" t="n"/>
     </row>
     <row r="45" ht="18" customHeight="1" s="51">
       <c r="A45" s="85" t="inlineStr">
@@ -9601,6 +12098,20 @@
       <c r="I45" s="85" t="n"/>
       <c r="J45" s="85" t="n"/>
       <c r="K45" s="85" t="n"/>
+      <c r="L45" s="85" t="n"/>
+      <c r="M45" s="85" t="n"/>
+      <c r="N45" s="85" t="n"/>
+      <c r="O45" s="85" t="n"/>
+      <c r="P45" s="85" t="n"/>
+      <c r="Q45" s="85" t="n"/>
+      <c r="R45" s="85" t="n"/>
+      <c r="S45" s="85" t="n"/>
+      <c r="T45" s="85" t="n"/>
+      <c r="U45" s="85" t="n"/>
+      <c r="V45" s="85" t="n"/>
+      <c r="W45" s="85" t="n"/>
+      <c r="X45" s="85" t="n"/>
+      <c r="Y45" s="85" t="n"/>
     </row>
     <row r="46" ht="18" customHeight="1" s="51">
       <c r="A46" s="84" t="inlineStr">
@@ -9622,6 +12133,20 @@
       <c r="I46" s="84" t="n"/>
       <c r="J46" s="84" t="n"/>
       <c r="K46" s="84" t="n"/>
+      <c r="L46" s="84" t="n"/>
+      <c r="M46" s="84" t="n"/>
+      <c r="N46" s="84" t="n"/>
+      <c r="O46" s="84" t="n"/>
+      <c r="P46" s="84" t="n"/>
+      <c r="Q46" s="84" t="n"/>
+      <c r="R46" s="84" t="n"/>
+      <c r="S46" s="84" t="n"/>
+      <c r="T46" s="84" t="n"/>
+      <c r="U46" s="84" t="n"/>
+      <c r="V46" s="84" t="n"/>
+      <c r="W46" s="84" t="n"/>
+      <c r="X46" s="84" t="n"/>
+      <c r="Y46" s="84" t="n"/>
     </row>
     <row r="47" ht="18" customHeight="1" s="51">
       <c r="A47" s="85" t="inlineStr">
@@ -9643,6 +12168,20 @@
       <c r="I47" s="85" t="n"/>
       <c r="J47" s="85" t="n"/>
       <c r="K47" s="85" t="n"/>
+      <c r="L47" s="85" t="n"/>
+      <c r="M47" s="85" t="n"/>
+      <c r="N47" s="85" t="n"/>
+      <c r="O47" s="85" t="n"/>
+      <c r="P47" s="85" t="n"/>
+      <c r="Q47" s="85" t="n"/>
+      <c r="R47" s="85" t="n"/>
+      <c r="S47" s="85" t="n"/>
+      <c r="T47" s="85" t="n"/>
+      <c r="U47" s="85" t="n"/>
+      <c r="V47" s="85" t="n"/>
+      <c r="W47" s="85" t="n"/>
+      <c r="X47" s="85" t="n"/>
+      <c r="Y47" s="85" t="n"/>
     </row>
     <row r="48" ht="18" customHeight="1" s="51">
       <c r="A48" s="84" t="inlineStr">
@@ -9664,6 +12203,20 @@
       <c r="I48" s="84" t="n"/>
       <c r="J48" s="84" t="n"/>
       <c r="K48" s="84" t="n"/>
+      <c r="L48" s="84" t="n"/>
+      <c r="M48" s="84" t="n"/>
+      <c r="N48" s="84" t="n"/>
+      <c r="O48" s="84" t="n"/>
+      <c r="P48" s="84" t="n"/>
+      <c r="Q48" s="84" t="n"/>
+      <c r="R48" s="84" t="n"/>
+      <c r="S48" s="84" t="n"/>
+      <c r="T48" s="84" t="n"/>
+      <c r="U48" s="84" t="n"/>
+      <c r="V48" s="84" t="n"/>
+      <c r="W48" s="84" t="n"/>
+      <c r="X48" s="84" t="n"/>
+      <c r="Y48" s="84" t="n"/>
     </row>
     <row r="49" ht="18" customHeight="1" s="51">
       <c r="A49" s="85" t="inlineStr">
@@ -9685,6 +12238,20 @@
       <c r="I49" s="85" t="n"/>
       <c r="J49" s="85" t="n"/>
       <c r="K49" s="85" t="n"/>
+      <c r="L49" s="85" t="n"/>
+      <c r="M49" s="85" t="n"/>
+      <c r="N49" s="85" t="n"/>
+      <c r="O49" s="85" t="n"/>
+      <c r="P49" s="85" t="n"/>
+      <c r="Q49" s="85" t="n"/>
+      <c r="R49" s="85" t="n"/>
+      <c r="S49" s="85" t="n"/>
+      <c r="T49" s="85" t="n"/>
+      <c r="U49" s="85" t="n"/>
+      <c r="V49" s="85" t="n"/>
+      <c r="W49" s="85" t="n"/>
+      <c r="X49" s="85" t="n"/>
+      <c r="Y49" s="85" t="n"/>
     </row>
     <row r="50" ht="18" customHeight="1" s="51">
       <c r="A50" s="84" t="inlineStr">
@@ -9706,6 +12273,20 @@
       <c r="I50" s="84" t="n"/>
       <c r="J50" s="84" t="n"/>
       <c r="K50" s="84" t="n"/>
+      <c r="L50" s="84" t="n"/>
+      <c r="M50" s="84" t="n"/>
+      <c r="N50" s="84" t="n"/>
+      <c r="O50" s="84" t="n"/>
+      <c r="P50" s="84" t="n"/>
+      <c r="Q50" s="84" t="n"/>
+      <c r="R50" s="84" t="n"/>
+      <c r="S50" s="84" t="n"/>
+      <c r="T50" s="84" t="n"/>
+      <c r="U50" s="84" t="n"/>
+      <c r="V50" s="84" t="n"/>
+      <c r="W50" s="84" t="n"/>
+      <c r="X50" s="84" t="n"/>
+      <c r="Y50" s="84" t="n"/>
     </row>
     <row r="51" ht="18" customHeight="1" s="51">
       <c r="A51" s="85" t="inlineStr">
@@ -9727,95 +12308,173 @@
       <c r="I51" s="85" t="n"/>
       <c r="J51" s="85" t="n"/>
       <c r="K51" s="85" t="n"/>
+      <c r="L51" s="85" t="n"/>
+      <c r="M51" s="85" t="n"/>
+      <c r="N51" s="85" t="n"/>
+      <c r="O51" s="85" t="n"/>
+      <c r="P51" s="85" t="n"/>
+      <c r="Q51" s="85" t="n"/>
+      <c r="R51" s="85" t="n"/>
+      <c r="S51" s="85" t="n"/>
+      <c r="T51" s="85" t="n"/>
+      <c r="U51" s="85" t="n"/>
+      <c r="V51" s="85" t="n"/>
+      <c r="W51" s="85" t="n"/>
+      <c r="X51" s="85" t="n"/>
+      <c r="Y51" s="85" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="84" t="inlineStr">
-        <is>
-          <t>Dropdown values: Acquire | Deepen | Create | ? (unscorable/blank)</t>
-        </is>
-      </c>
-      <c r="B53" s="86" t="n"/>
-      <c r="C53" s="86" t="n"/>
-      <c r="D53" s="86" t="n"/>
-      <c r="E53" s="86" t="n"/>
-      <c r="F53" s="86" t="n"/>
-      <c r="G53" s="86" t="n"/>
-      <c r="H53" s="86" t="n"/>
-      <c r="I53" s="86" t="n"/>
-      <c r="J53" s="86" t="n"/>
-      <c r="K53" s="87" t="n"/>
-    </row>
-    <row r="54" ht="40" customHeight="1" s="51">
-      <c r="A54" s="85" t="inlineStr">
+      <c r="A53" s="92" t="inlineStr">
         <is>
           <t>Task descriptions:</t>
         </is>
       </c>
-      <c r="B54" s="85" t="n"/>
-      <c r="C54" s="90" t="inlineStr">
-        <is>
-          <t>Variable
-Root node blank: names a variable for the first split</t>
-        </is>
-      </c>
-      <c r="D54" s="90" t="inlineStr">
-        <is>
-          <t>&lt;= and &gt;
-Branch labels: writes &lt;= and &gt; with threshold values on both branches</t>
-        </is>
-      </c>
-      <c r="E54" s="90" t="inlineStr">
-        <is>
-          <t>Classification
-Left leaf: correct classification label (recommended / not recommended)</t>
-        </is>
-      </c>
-      <c r="F54" s="90" t="inlineStr">
-        <is>
-          <t>Counts
-Left leaf: correct counts in brackets [recommended] [not-recommended]</t>
-        </is>
-      </c>
-      <c r="G54" s="90" t="inlineStr">
-        <is>
-          <t>Classification
-Right leaf: correct classification label</t>
-        </is>
-      </c>
-      <c r="H54" s="90" t="inlineStr">
-        <is>
-          <t>Counts
-Right leaf: correct counts in brackets</t>
-        </is>
-      </c>
-      <c r="I54" s="90" t="inlineStr">
-        <is>
-          <t>Variable (if present)
-Second-level node: names a valid variable for further split (score if present)</t>
-        </is>
-      </c>
-      <c r="J54" s="85" t="inlineStr">
-        <is>
-          <t>Overall AI-CFT level for WS6 as a whole</t>
-        </is>
-      </c>
-      <c r="K54" s="85" t="inlineStr">
-        <is>
-          <t>Free notes</t>
+    </row>
+    <row r="54" ht="60" customHeight="1" s="51">
+      <c r="C54" s="93" t="inlineStr">
+        <is>
+          <t>Root variable
+Name of variable used at the root (first) split node</t>
+        </is>
+      </c>
+      <c r="D54" s="93" t="inlineStr">
+        <is>
+          <t>Root threshold ≤
+Threshold value on the left (≤) branch of the root</t>
+        </is>
+      </c>
+      <c r="E54" s="93" t="inlineStr">
+        <is>
+          <t>Root threshold &gt;
+Threshold value on the right (&gt;) branch of the root</t>
+        </is>
+      </c>
+      <c r="F54" s="93" t="inlineStr">
+        <is>
+          <t>Left branch – next node
+Either a leaf classification or name of second-level variable (left side)</t>
+        </is>
+      </c>
+      <c r="G54" s="93" t="inlineStr">
+        <is>
+          <t>Left leaf – rec count
+Count of recommended foods in left leaf [ rec ]</t>
+        </is>
+      </c>
+      <c r="H54" s="93" t="inlineStr">
+        <is>
+          <t>Left leaf – not-rec count
+Count of not-recommended foods in left leaf [ not-rec ]</t>
+        </is>
+      </c>
+      <c r="I54" s="93" t="inlineStr">
+        <is>
+          <t>Right branch – next node
+Either a leaf classification or name of second-level variable (right side)</t>
+        </is>
+      </c>
+      <c r="J54" s="93" t="inlineStr">
+        <is>
+          <t>Right leaf – rec count
+Count of recommended foods in right leaf [ rec ]</t>
+        </is>
+      </c>
+      <c r="K54" s="93" t="inlineStr">
+        <is>
+          <t>Right leaf – not-rec count
+Count of not-recommended foods in right leaf [ not-rec ]</t>
+        </is>
+      </c>
+      <c r="L54" s="93" t="inlineStr">
+        <is>
+          <t>Sub-left-left threshold/label
+Threshold or class label for sub-branch: left → left</t>
+        </is>
+      </c>
+      <c r="M54" s="93" t="inlineStr">
+        <is>
+          <t>Sub-left-right threshold/label
+Threshold or class label for sub-branch: left → right</t>
+        </is>
+      </c>
+      <c r="N54" s="93" t="inlineStr">
+        <is>
+          <t>Sub-right-left threshold/label
+Threshold or class label for sub-branch: right → left</t>
+        </is>
+      </c>
+      <c r="O54" s="93" t="inlineStr">
+        <is>
+          <t>Sub-right-right threshold/label
+Threshold or class label for sub-branch: right → right</t>
+        </is>
+      </c>
+      <c r="P54" s="93" t="inlineStr">
+        <is>
+          <t>Leaf LL – rec count
+Recommended count at leaf: left-left</t>
+        </is>
+      </c>
+      <c r="Q54" s="93" t="inlineStr">
+        <is>
+          <t>Leaf LL – not-rec count
+Not-recommended count at leaf: left-left</t>
+        </is>
+      </c>
+      <c r="R54" s="93" t="inlineStr">
+        <is>
+          <t>Leaf LR – rec count
+Recommended count at leaf: left-right</t>
+        </is>
+      </c>
+      <c r="S54" s="93" t="inlineStr">
+        <is>
+          <t>Leaf LR – not-rec count
+Not-recommended count at leaf: left-right</t>
+        </is>
+      </c>
+      <c r="T54" s="93" t="inlineStr">
+        <is>
+          <t>Leaf RL – rec count
+Recommended count at leaf: right-left</t>
+        </is>
+      </c>
+      <c r="U54" s="93" t="inlineStr">
+        <is>
+          <t>Leaf RL – not-rec count
+Not-recommended count at leaf: right-left</t>
+        </is>
+      </c>
+      <c r="V54" s="93" t="inlineStr">
+        <is>
+          <t>Leaf RR – rec count
+Recommended count at leaf: right-right</t>
+        </is>
+      </c>
+      <c r="W54" s="93" t="inlineStr">
+        <is>
+          <t>Leaf RR – not-rec count
+Not-recommended count at leaf: right-right</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="9">
     <mergeCell ref="A53:K53"/>
     <mergeCell ref="A35:K35"/>
     <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A1:Y1"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A36:K36"/>
+    <mergeCell ref="A35:Y35"/>
+    <mergeCell ref="A4:Y4"/>
     <mergeCell ref="A5:K5"/>
   </mergeCells>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation sqref="C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 C17 C18 C19 C20 C21 C22 C23 C24 C25 C26 C27 C28 C29 C30 C31 C32 C33 C34 C36 C37 C38 C39 C40 C41 C42 C43 C44 C45 C46 C47 C48 C49 C50 C51 D5 D6 D7 D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19 D20 D21 D22 D23 D24 D25 D26 D27 D28 D29 D30 D31 D32 D33 D34 D36 D37 D38 D39 D40 D41 D42 D43 D44 D45 D46 D47 D48 D49 D50 D51 E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E24 E25 E26 E27 E28 E29 E30 E31 E32 E33 E34 E36 E37 E38 E39 E40 E41 E42 E43 E44 E45 E46 E47 E48 E49 E50 E51 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34 F36 F37 F38 F39 F40 F41 F42 F43 F44 F45 F46 F47 F48 F49 F50 F51 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 G31 G32 G33 G34 G36 G37 G38 G39 G40 G41 G42 G43 G44 G45 G46 G47 G48 G49 G50 G51 H5 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27 H28 H29 H30 H31 H32 H33 H34 H36 H37 H38 H39 H40 H41 H42 H43 H44 H45 H46 H47 H48 H49 H50 H51 I5 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I24 I25 I26 I27 I28 I29 I30 I31 I32 I33 I34 I36 I37 I38 I39 I40 I41 I42 I43 I44 I45 I46 I47 I48 I49 I50 I51 J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25 J26 J27 J28 J29 J30 J31 J32 J33 J34 J36 J37 J38 J39 J40 J41 J42 J43 J44 J45 J46 J47 J48 J49 J50 J51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Choose: Acquire, Deepen, Create, or ?" promptTitle="Select level" prompt="AI-CFT level" type="list">
+      <formula1>"Acquire,Deepen,Create,?"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 C17 C18 C19 C20 C21 C22 C23 C24 C25 C26 C27 C28 C29 C30 C31 C32 C33 C34 C36 C37 C38 C39 C40 C41 C42 C43 C44 C45 C46 C47 C48 C49 C50 C51 D5 D6 D7 D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19 D20 D21 D22 D23 D24 D25 D26 D27 D28 D29 D30 D31 D32 D33 D34 D36 D37 D38 D39 D40 D41 D42 D43 D44 D45 D46 D47 D48 D49 D50 D51 E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E24 E25 E26 E27 E28 E29 E30 E31 E32 E33 E34 E36 E37 E38 E39 E40 E41 E42 E43 E44 E45 E46 E47 E48 E49 E50 E51 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34 F36 F37 F38 F39 F40 F41 F42 F43 F44 F45 F46 F47 F48 F49 F50 F51 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 G31 G32 G33 G34 G36 G37 G38 G39 G40 G41 G42 G43 G44 G45 G46 G47 G48 G49 G50 G51 H5 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27 H28 H29 H30 H31 H32 H33 H34 H36 H37 H38 H39 H40 H41 H42 H43 H44 H45 H46 H47 H48 H49 H50 H51 I5 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I24 I25 I26 I27 I28 I29 I30 I31 I32 I33 I34 I36 I37 I38 I39 I40 I41 I42 I43 I44 I45 I46 I47 I48 I49 I50 I51 J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25 J26 J27 J28 J29 J30 J31 J32 J33 J34 J36 J37 J38 J39 J40 J41 J42 J43 J44 J45 J46 J47 J48 J49 J50 J51 K5 K6 K7 K8 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 K19 K20 K21 K22 K23 K24 K25 K26 K27 K28 K29 K30 K31 K32 K33 K34 K36 K37 K38 K39 K40 K41 K42 K43 K44 K45 K46 K47 K48 K49 K50 K51 L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26 L27 L28 L29 L30 L31 L32 L33 L34 L36 L37 L38 L39 L40 L41 L42 L43 L44 L45 L46 L47 L48 L49 L50 L51 M5 M6 M7 M8 M9 M10 M11 M12 M13 M14 M15 M16 M17 M18 M19 M20 M21 M22 M23 M24 M25 M26 M27 M28 M29 M30 M31 M32 M33 M34 M36 M37 M38 M39 M40 M41 M42 M43 M44 M45 M46 M47 M48 M49 M50 M51 N5 N6 N7 N8 N9 N10 N11 N12 N13 N14 N15 N16 N17 N18 N19 N20 N21 N22 N23 N24 N25 N26 N27 N28 N29 N30 N31 N32 N33 N34 N36 N37 N38 N39 N40 N41 N42 N43 N44 N45 N46 N47 N48 N49 N50 N51 O5 O6 O7 O8 O9 O10 O11 O12 O13 O14 O15 O16 O17 O18 O19 O20 O21 O22 O23 O24 O25 O26 O27 O28 O29 O30 O31 O32 O33 O34 O36 O37 O38 O39 O40 O41 O42 O43 O44 O45 O46 O47 O48 O49 O50 O51 P5 P6 P7 P8 P9 P10 P11 P12 P13 P14 P15 P16 P17 P18 P19 P20 P21 P22 P23 P24 P25 P26 P27 P28 P29 P30 P31 P32 P33 P34 P36 P37 P38 P39 P40 P41 P42 P43 P44 P45 P46 P47 P48 P49 P50 P51 Q5 Q6 Q7 Q8 Q9 Q10 Q11 Q12 Q13 Q14 Q15 Q16 Q17 Q18 Q19 Q20 Q21 Q22 Q23 Q24 Q25 Q26 Q27 Q28 Q29 Q30 Q31 Q32 Q33 Q34 Q36 Q37 Q38 Q39 Q40 Q41 Q42 Q43 Q44 Q45 Q46 Q47 Q48 Q49 Q50 Q51 R5 R6 R7 R8 R9 R10 R11 R12 R13 R14 R15 R16 R17 R18 R19 R20 R21 R22 R23 R24 R25 R26 R27 R28 R29 R30 R31 R32 R33 R34 R36 R37 R38 R39 R40 R41 R42 R43 R44 R45 R46 R47 R48 R49 R50 R51 S5 S6 S7 S8 S9 S10 S11 S12 S13 S14 S15 S16 S17 S18 S19 S20 S21 S22 S23 S24 S25 S26 S27 S28 S29 S30 S31 S32 S33 S34 S36 S37 S38 S39 S40 S41 S42 S43 S44 S45 S46 S47 S48 S49 S50 S51 T5 T6 T7 T8 T9 T10 T11 T12 T13 T14 T15 T16 T17 T18 T19 T20 T21 T22 T23 T24 T25 T26 T27 T28 T29 T30 T31 T32 T33 T34 T36 T37 T38 T39 T40 T41 T42 T43 T44 T45 T46 T47 T48 T49 T50 T51 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U36 U37 U38 U39 U40 U41 U42 U43 U44 U45 U46 U47 U48 U49 U50 U51 V5 V6 V7 V8 V9 V10 V11 V12 V13 V14 V15 V16 V17 V18 V19 V20 V21 V22 V23 V24 V25 V26 V27 V28 V29 V30 V31 V32 V33 V34 V36 V37 V38 V39 V40 V41 V42 V43 V44 V45 V46 V47 V48 V49 V50 V51 W5 W6 W7 W8 W9 W10 W11 W12 W13 W14 W15 W16 W17 W18 W19 W20 W21 W22 W23 W24 W25 W26 W27 W28 W29 W30 W31 W32 W33 W34 W36 W37 W38 W39 W40 W41 W42 W43 W44 W45 W46 W47 W48 W49 W50 W51 X5 X6 X7 X8 X9 X10 X11 X12 X13 X14 X15 X16 X17 X18 X19 X20 X21 X22 X23 X24 X25 X26 X27 X28 X29 X30 X31 X32 X33 X34 X36 X37 X38 X39 X40 X41 X42 X43 X44 X45 X46 X47 X48 X49 X50 X51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Acquire,Deepen,Create,?"</formula1>
     </dataValidation>
   </dataValidations>
@@ -9829,7 +12488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K54"/>
+  <dimension ref="A1:N54"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" style="51" min="1" max="1"/>
@@ -9841,69 +12500,87 @@
     <col width="18" customWidth="1" style="51" min="7" max="7"/>
     <col width="18" customWidth="1" style="51" min="8" max="8"/>
     <col width="18" customWidth="1" style="51" min="9" max="9"/>
-    <col width="14" customWidth="1" style="51" min="10" max="10"/>
-    <col width="22" customWidth="1" style="51" min="11" max="11"/>
+    <col width="18" customWidth="1" style="51" min="10" max="10"/>
+    <col width="18" customWidth="1" style="51" min="11" max="11"/>
+    <col width="18" customWidth="1" style="51" min="12" max="12"/>
+    <col width="14" customWidth="1" style="51" min="13" max="13"/>
+    <col width="22" customWidth="1" style="51" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" s="51">
       <c r="A1" s="77" t="inlineStr">
         <is>
-          <t>AI-CFT Labeling — WS7 - Rules</t>
+          <t>AI-CFT Labeling — WS7</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1" s="51">
-      <c r="A2" s="78" t="inlineStr">
+      <c r="A2" s="91" t="inlineStr">
         <is>
           <t>Cohort</t>
         </is>
       </c>
-      <c r="B2" s="78" t="inlineStr">
+      <c r="B2" s="91" t="inlineStr">
         <is>
           <t>Student</t>
         </is>
       </c>
-      <c r="C2" s="79" t="inlineStr">
-        <is>
-          <t>Acquire</t>
-        </is>
-      </c>
-      <c r="D2" s="79" t="inlineStr">
-        <is>
-          <t>Acquire</t>
-        </is>
-      </c>
-      <c r="E2" s="79" t="inlineStr">
-        <is>
-          <t>Acquire</t>
-        </is>
-      </c>
-      <c r="F2" s="79" t="inlineStr">
-        <is>
-          <t>Acquire</t>
-        </is>
-      </c>
-      <c r="G2" s="88" t="inlineStr">
+      <c r="C2" s="88" t="inlineStr">
         <is>
           <t>Deepen</t>
         </is>
       </c>
-      <c r="H2" s="88" t="inlineStr">
+      <c r="D2" s="88" t="inlineStr">
         <is>
           <t>Deepen</t>
         </is>
       </c>
-      <c r="I2" s="88" t="inlineStr">
+      <c r="E2" s="88" t="inlineStr">
         <is>
           <t>Deepen</t>
         </is>
       </c>
-      <c r="J2" s="80" t="inlineStr">
+      <c r="F2" s="89" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="G2" s="89" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="H2" s="89" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="I2" s="89" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="J2" s="89" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="K2" s="89" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="L2" s="89" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="M2" s="80" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K2" s="80" t="inlineStr">
+      <c r="N2" s="80" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -9941,7 +12618,7 @@
       <c r="F3" s="82" t="inlineStr">
         <is>
           <t>Blank 4
-Path count</t>
+Number of paths</t>
         </is>
       </c>
       <c r="G3" s="82" t="inlineStr">
@@ -9959,15 +12636,33 @@
       <c r="I3" s="82" t="inlineStr">
         <is>
           <t>Blank 7
-Rules 3-6</t>
+Rule 3</t>
         </is>
       </c>
       <c r="J3" s="82" t="inlineStr">
         <is>
+          <t>Blank 8
+Rule 4</t>
+        </is>
+      </c>
+      <c r="K3" s="82" t="inlineStr">
+        <is>
+          <t>Blank 9
+Rule 5</t>
+        </is>
+      </c>
+      <c r="L3" s="82" t="inlineStr">
+        <is>
+          <t>Blank 10
+Rule 6</t>
+        </is>
+      </c>
+      <c r="M3" s="82" t="inlineStr">
+        <is>
           <t>Overall WS7</t>
         </is>
       </c>
-      <c r="K3" s="82" t="inlineStr">
+      <c r="N3" s="82" t="inlineStr">
         <is>
           <t>Notes WS7</t>
         </is>
@@ -9986,16 +12681,23 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="B5" s="86" t="n"/>
-      <c r="C5" s="86" t="n"/>
-      <c r="D5" s="86" t="n"/>
-      <c r="E5" s="86" t="n"/>
-      <c r="F5" s="86" t="n"/>
-      <c r="G5" s="86" t="n"/>
-      <c r="H5" s="86" t="n"/>
-      <c r="I5" s="86" t="n"/>
-      <c r="J5" s="86" t="n"/>
-      <c r="K5" s="87" t="n"/>
+      <c r="B5" s="84" t="inlineStr">
+        <is>
+          <t>Ozzy</t>
+        </is>
+      </c>
+      <c r="C5" s="84" t="n"/>
+      <c r="D5" s="84" t="n"/>
+      <c r="E5" s="84" t="n"/>
+      <c r="F5" s="84" t="n"/>
+      <c r="G5" s="84" t="n"/>
+      <c r="H5" s="84" t="n"/>
+      <c r="I5" s="84" t="n"/>
+      <c r="J5" s="84" t="n"/>
+      <c r="K5" s="84" t="n"/>
+      <c r="L5" s="84" t="n"/>
+      <c r="M5" s="84" t="n"/>
+      <c r="N5" s="84" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1" s="51">
       <c r="A6" s="85" t="inlineStr">
@@ -10017,6 +12719,9 @@
       <c r="I6" s="85" t="n"/>
       <c r="J6" s="85" t="n"/>
       <c r="K6" s="85" t="n"/>
+      <c r="L6" s="85" t="n"/>
+      <c r="M6" s="85" t="n"/>
+      <c r="N6" s="85" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1" s="51">
       <c r="A7" s="84" t="inlineStr">
@@ -10038,6 +12743,9 @@
       <c r="I7" s="84" t="n"/>
       <c r="J7" s="84" t="n"/>
       <c r="K7" s="84" t="n"/>
+      <c r="L7" s="84" t="n"/>
+      <c r="M7" s="84" t="n"/>
+      <c r="N7" s="84" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1" s="51">
       <c r="A8" s="85" t="inlineStr">
@@ -10059,6 +12767,9 @@
       <c r="I8" s="85" t="n"/>
       <c r="J8" s="85" t="n"/>
       <c r="K8" s="85" t="n"/>
+      <c r="L8" s="85" t="n"/>
+      <c r="M8" s="85" t="n"/>
+      <c r="N8" s="85" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1" s="51">
       <c r="A9" s="84" t="inlineStr">
@@ -10080,6 +12791,9 @@
       <c r="I9" s="84" t="n"/>
       <c r="J9" s="84" t="n"/>
       <c r="K9" s="84" t="n"/>
+      <c r="L9" s="84" t="n"/>
+      <c r="M9" s="84" t="n"/>
+      <c r="N9" s="84" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1" s="51">
       <c r="A10" s="85" t="inlineStr">
@@ -10101,6 +12815,9 @@
       <c r="I10" s="85" t="n"/>
       <c r="J10" s="85" t="n"/>
       <c r="K10" s="85" t="n"/>
+      <c r="L10" s="85" t="n"/>
+      <c r="M10" s="85" t="n"/>
+      <c r="N10" s="85" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1" s="51">
       <c r="A11" s="84" t="inlineStr">
@@ -10122,6 +12839,9 @@
       <c r="I11" s="84" t="n"/>
       <c r="J11" s="84" t="n"/>
       <c r="K11" s="84" t="n"/>
+      <c r="L11" s="84" t="n"/>
+      <c r="M11" s="84" t="n"/>
+      <c r="N11" s="84" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1" s="51">
       <c r="A12" s="85" t="inlineStr">
@@ -10143,6 +12863,9 @@
       <c r="I12" s="85" t="n"/>
       <c r="J12" s="85" t="n"/>
       <c r="K12" s="85" t="n"/>
+      <c r="L12" s="85" t="n"/>
+      <c r="M12" s="85" t="n"/>
+      <c r="N12" s="85" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1" s="51">
       <c r="A13" s="84" t="inlineStr">
@@ -10164,6 +12887,9 @@
       <c r="I13" s="84" t="n"/>
       <c r="J13" s="84" t="n"/>
       <c r="K13" s="84" t="n"/>
+      <c r="L13" s="84" t="n"/>
+      <c r="M13" s="84" t="n"/>
+      <c r="N13" s="84" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1" s="51">
       <c r="A14" s="85" t="inlineStr">
@@ -10185,6 +12911,9 @@
       <c r="I14" s="85" t="n"/>
       <c r="J14" s="85" t="n"/>
       <c r="K14" s="85" t="n"/>
+      <c r="L14" s="85" t="n"/>
+      <c r="M14" s="85" t="n"/>
+      <c r="N14" s="85" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1" s="51">
       <c r="A15" s="84" t="inlineStr">
@@ -10206,6 +12935,9 @@
       <c r="I15" s="84" t="n"/>
       <c r="J15" s="84" t="n"/>
       <c r="K15" s="84" t="n"/>
+      <c r="L15" s="84" t="n"/>
+      <c r="M15" s="84" t="n"/>
+      <c r="N15" s="84" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1" s="51">
       <c r="A16" s="85" t="inlineStr">
@@ -10227,6 +12959,9 @@
       <c r="I16" s="85" t="n"/>
       <c r="J16" s="85" t="n"/>
       <c r="K16" s="85" t="n"/>
+      <c r="L16" s="85" t="n"/>
+      <c r="M16" s="85" t="n"/>
+      <c r="N16" s="85" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1" s="51">
       <c r="A17" s="84" t="inlineStr">
@@ -10248,6 +12983,9 @@
       <c r="I17" s="84" t="n"/>
       <c r="J17" s="84" t="n"/>
       <c r="K17" s="84" t="n"/>
+      <c r="L17" s="84" t="n"/>
+      <c r="M17" s="84" t="n"/>
+      <c r="N17" s="84" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1" s="51">
       <c r="A18" s="85" t="inlineStr">
@@ -10269,6 +13007,9 @@
       <c r="I18" s="85" t="n"/>
       <c r="J18" s="85" t="n"/>
       <c r="K18" s="85" t="n"/>
+      <c r="L18" s="85" t="n"/>
+      <c r="M18" s="85" t="n"/>
+      <c r="N18" s="85" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1" s="51">
       <c r="A19" s="84" t="inlineStr">
@@ -10290,6 +13031,9 @@
       <c r="I19" s="84" t="n"/>
       <c r="J19" s="84" t="n"/>
       <c r="K19" s="84" t="n"/>
+      <c r="L19" s="84" t="n"/>
+      <c r="M19" s="84" t="n"/>
+      <c r="N19" s="84" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1" s="51">
       <c r="A20" s="85" t="inlineStr">
@@ -10311,6 +13055,9 @@
       <c r="I20" s="85" t="n"/>
       <c r="J20" s="85" t="n"/>
       <c r="K20" s="85" t="n"/>
+      <c r="L20" s="85" t="n"/>
+      <c r="M20" s="85" t="n"/>
+      <c r="N20" s="85" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1" s="51">
       <c r="A21" s="84" t="inlineStr">
@@ -10332,6 +13079,9 @@
       <c r="I21" s="84" t="n"/>
       <c r="J21" s="84" t="n"/>
       <c r="K21" s="84" t="n"/>
+      <c r="L21" s="84" t="n"/>
+      <c r="M21" s="84" t="n"/>
+      <c r="N21" s="84" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1" s="51">
       <c r="A22" s="85" t="inlineStr">
@@ -10353,6 +13103,9 @@
       <c r="I22" s="85" t="n"/>
       <c r="J22" s="85" t="n"/>
       <c r="K22" s="85" t="n"/>
+      <c r="L22" s="85" t="n"/>
+      <c r="M22" s="85" t="n"/>
+      <c r="N22" s="85" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1" s="51">
       <c r="A23" s="84" t="inlineStr">
@@ -10374,6 +13127,9 @@
       <c r="I23" s="84" t="n"/>
       <c r="J23" s="84" t="n"/>
       <c r="K23" s="84" t="n"/>
+      <c r="L23" s="84" t="n"/>
+      <c r="M23" s="84" t="n"/>
+      <c r="N23" s="84" t="n"/>
     </row>
     <row r="24" ht="18" customHeight="1" s="51">
       <c r="A24" s="85" t="inlineStr">
@@ -10395,6 +13151,9 @@
       <c r="I24" s="85" t="n"/>
       <c r="J24" s="85" t="n"/>
       <c r="K24" s="85" t="n"/>
+      <c r="L24" s="85" t="n"/>
+      <c r="M24" s="85" t="n"/>
+      <c r="N24" s="85" t="n"/>
     </row>
     <row r="25" ht="18" customHeight="1" s="51">
       <c r="A25" s="84" t="inlineStr">
@@ -10416,6 +13175,9 @@
       <c r="I25" s="84" t="n"/>
       <c r="J25" s="84" t="n"/>
       <c r="K25" s="84" t="n"/>
+      <c r="L25" s="84" t="n"/>
+      <c r="M25" s="84" t="n"/>
+      <c r="N25" s="84" t="n"/>
     </row>
     <row r="26" ht="18" customHeight="1" s="51">
       <c r="A26" s="85" t="inlineStr">
@@ -10437,6 +13199,9 @@
       <c r="I26" s="85" t="n"/>
       <c r="J26" s="85" t="n"/>
       <c r="K26" s="85" t="n"/>
+      <c r="L26" s="85" t="n"/>
+      <c r="M26" s="85" t="n"/>
+      <c r="N26" s="85" t="n"/>
     </row>
     <row r="27" ht="18" customHeight="1" s="51">
       <c r="A27" s="84" t="inlineStr">
@@ -10458,6 +13223,9 @@
       <c r="I27" s="84" t="n"/>
       <c r="J27" s="84" t="n"/>
       <c r="K27" s="84" t="n"/>
+      <c r="L27" s="84" t="n"/>
+      <c r="M27" s="84" t="n"/>
+      <c r="N27" s="84" t="n"/>
     </row>
     <row r="28" ht="18" customHeight="1" s="51">
       <c r="A28" s="85" t="inlineStr">
@@ -10479,6 +13247,9 @@
       <c r="I28" s="85" t="n"/>
       <c r="J28" s="85" t="n"/>
       <c r="K28" s="85" t="n"/>
+      <c r="L28" s="85" t="n"/>
+      <c r="M28" s="85" t="n"/>
+      <c r="N28" s="85" t="n"/>
     </row>
     <row r="29" ht="18" customHeight="1" s="51">
       <c r="A29" s="84" t="inlineStr">
@@ -10500,6 +13271,9 @@
       <c r="I29" s="84" t="n"/>
       <c r="J29" s="84" t="n"/>
       <c r="K29" s="84" t="n"/>
+      <c r="L29" s="84" t="n"/>
+      <c r="M29" s="84" t="n"/>
+      <c r="N29" s="84" t="n"/>
     </row>
     <row r="30" ht="18" customHeight="1" s="51">
       <c r="A30" s="85" t="inlineStr">
@@ -10521,6 +13295,9 @@
       <c r="I30" s="85" t="n"/>
       <c r="J30" s="85" t="n"/>
       <c r="K30" s="85" t="n"/>
+      <c r="L30" s="85" t="n"/>
+      <c r="M30" s="85" t="n"/>
+      <c r="N30" s="85" t="n"/>
     </row>
     <row r="31" ht="18" customHeight="1" s="51">
       <c r="A31" s="84" t="inlineStr">
@@ -10542,6 +13319,9 @@
       <c r="I31" s="84" t="n"/>
       <c r="J31" s="84" t="n"/>
       <c r="K31" s="84" t="n"/>
+      <c r="L31" s="84" t="n"/>
+      <c r="M31" s="84" t="n"/>
+      <c r="N31" s="84" t="n"/>
     </row>
     <row r="32" ht="18" customHeight="1" s="51">
       <c r="A32" s="85" t="inlineStr">
@@ -10563,6 +13343,9 @@
       <c r="I32" s="85" t="n"/>
       <c r="J32" s="85" t="n"/>
       <c r="K32" s="85" t="n"/>
+      <c r="L32" s="85" t="n"/>
+      <c r="M32" s="85" t="n"/>
+      <c r="N32" s="85" t="n"/>
     </row>
     <row r="33" ht="18" customHeight="1" s="51">
       <c r="A33" s="84" t="inlineStr">
@@ -10584,6 +13367,9 @@
       <c r="I33" s="84" t="n"/>
       <c r="J33" s="84" t="n"/>
       <c r="K33" s="84" t="n"/>
+      <c r="L33" s="84" t="n"/>
+      <c r="M33" s="84" t="n"/>
+      <c r="N33" s="84" t="n"/>
     </row>
     <row r="34" ht="18" customHeight="1" s="51">
       <c r="A34" s="85" t="inlineStr">
@@ -10591,7 +13377,11 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="B34" s="85" t="n"/>
+      <c r="B34" s="85" t="inlineStr">
+        <is>
+          <t>Sabrina</t>
+        </is>
+      </c>
       <c r="C34" s="85" t="n"/>
       <c r="D34" s="85" t="n"/>
       <c r="E34" s="85" t="n"/>
@@ -10601,6 +13391,9 @@
       <c r="I34" s="85" t="n"/>
       <c r="J34" s="85" t="n"/>
       <c r="K34" s="85" t="n"/>
+      <c r="L34" s="85" t="n"/>
+      <c r="M34" s="85" t="n"/>
+      <c r="N34" s="85" t="n"/>
     </row>
     <row r="35" ht="20" customHeight="1" s="51">
       <c r="A35" s="83" t="inlineStr">
@@ -10615,16 +13408,23 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="B36" s="86" t="n"/>
-      <c r="C36" s="86" t="n"/>
-      <c r="D36" s="86" t="n"/>
-      <c r="E36" s="86" t="n"/>
-      <c r="F36" s="86" t="n"/>
-      <c r="G36" s="86" t="n"/>
-      <c r="H36" s="86" t="n"/>
-      <c r="I36" s="86" t="n"/>
-      <c r="J36" s="86" t="n"/>
-      <c r="K36" s="87" t="n"/>
+      <c r="B36" s="84" t="inlineStr">
+        <is>
+          <t>Sheila</t>
+        </is>
+      </c>
+      <c r="C36" s="84" t="n"/>
+      <c r="D36" s="84" t="n"/>
+      <c r="E36" s="84" t="n"/>
+      <c r="F36" s="84" t="n"/>
+      <c r="G36" s="84" t="n"/>
+      <c r="H36" s="84" t="n"/>
+      <c r="I36" s="84" t="n"/>
+      <c r="J36" s="84" t="n"/>
+      <c r="K36" s="84" t="n"/>
+      <c r="L36" s="84" t="n"/>
+      <c r="M36" s="84" t="n"/>
+      <c r="N36" s="84" t="n"/>
     </row>
     <row r="37" ht="18" customHeight="1" s="51">
       <c r="A37" s="85" t="inlineStr">
@@ -10646,6 +13446,9 @@
       <c r="I37" s="85" t="n"/>
       <c r="J37" s="85" t="n"/>
       <c r="K37" s="85" t="n"/>
+      <c r="L37" s="85" t="n"/>
+      <c r="M37" s="85" t="n"/>
+      <c r="N37" s="85" t="n"/>
     </row>
     <row r="38" ht="18" customHeight="1" s="51">
       <c r="A38" s="84" t="inlineStr">
@@ -10667,6 +13470,9 @@
       <c r="I38" s="84" t="n"/>
       <c r="J38" s="84" t="n"/>
       <c r="K38" s="84" t="n"/>
+      <c r="L38" s="84" t="n"/>
+      <c r="M38" s="84" t="n"/>
+      <c r="N38" s="84" t="n"/>
     </row>
     <row r="39" ht="18" customHeight="1" s="51">
       <c r="A39" s="85" t="inlineStr">
@@ -10688,6 +13494,9 @@
       <c r="I39" s="85" t="n"/>
       <c r="J39" s="85" t="n"/>
       <c r="K39" s="85" t="n"/>
+      <c r="L39" s="85" t="n"/>
+      <c r="M39" s="85" t="n"/>
+      <c r="N39" s="85" t="n"/>
     </row>
     <row r="40" ht="18" customHeight="1" s="51">
       <c r="A40" s="84" t="inlineStr">
@@ -10709,6 +13518,9 @@
       <c r="I40" s="84" t="n"/>
       <c r="J40" s="84" t="n"/>
       <c r="K40" s="84" t="n"/>
+      <c r="L40" s="84" t="n"/>
+      <c r="M40" s="84" t="n"/>
+      <c r="N40" s="84" t="n"/>
     </row>
     <row r="41" ht="18" customHeight="1" s="51">
       <c r="A41" s="85" t="inlineStr">
@@ -10730,6 +13542,9 @@
       <c r="I41" s="85" t="n"/>
       <c r="J41" s="85" t="n"/>
       <c r="K41" s="85" t="n"/>
+      <c r="L41" s="85" t="n"/>
+      <c r="M41" s="85" t="n"/>
+      <c r="N41" s="85" t="n"/>
     </row>
     <row r="42" ht="18" customHeight="1" s="51">
       <c r="A42" s="84" t="inlineStr">
@@ -10751,6 +13566,9 @@
       <c r="I42" s="84" t="n"/>
       <c r="J42" s="84" t="n"/>
       <c r="K42" s="84" t="n"/>
+      <c r="L42" s="84" t="n"/>
+      <c r="M42" s="84" t="n"/>
+      <c r="N42" s="84" t="n"/>
     </row>
     <row r="43" ht="18" customHeight="1" s="51">
       <c r="A43" s="85" t="inlineStr">
@@ -10772,6 +13590,9 @@
       <c r="I43" s="85" t="n"/>
       <c r="J43" s="85" t="n"/>
       <c r="K43" s="85" t="n"/>
+      <c r="L43" s="85" t="n"/>
+      <c r="M43" s="85" t="n"/>
+      <c r="N43" s="85" t="n"/>
     </row>
     <row r="44" ht="18" customHeight="1" s="51">
       <c r="A44" s="84" t="inlineStr">
@@ -10793,6 +13614,9 @@
       <c r="I44" s="84" t="n"/>
       <c r="J44" s="84" t="n"/>
       <c r="K44" s="84" t="n"/>
+      <c r="L44" s="84" t="n"/>
+      <c r="M44" s="84" t="n"/>
+      <c r="N44" s="84" t="n"/>
     </row>
     <row r="45" ht="18" customHeight="1" s="51">
       <c r="A45" s="85" t="inlineStr">
@@ -10814,6 +13638,9 @@
       <c r="I45" s="85" t="n"/>
       <c r="J45" s="85" t="n"/>
       <c r="K45" s="85" t="n"/>
+      <c r="L45" s="85" t="n"/>
+      <c r="M45" s="85" t="n"/>
+      <c r="N45" s="85" t="n"/>
     </row>
     <row r="46" ht="18" customHeight="1" s="51">
       <c r="A46" s="84" t="inlineStr">
@@ -10835,6 +13662,9 @@
       <c r="I46" s="84" t="n"/>
       <c r="J46" s="84" t="n"/>
       <c r="K46" s="84" t="n"/>
+      <c r="L46" s="84" t="n"/>
+      <c r="M46" s="84" t="n"/>
+      <c r="N46" s="84" t="n"/>
     </row>
     <row r="47" ht="18" customHeight="1" s="51">
       <c r="A47" s="85" t="inlineStr">
@@ -10856,6 +13686,9 @@
       <c r="I47" s="85" t="n"/>
       <c r="J47" s="85" t="n"/>
       <c r="K47" s="85" t="n"/>
+      <c r="L47" s="85" t="n"/>
+      <c r="M47" s="85" t="n"/>
+      <c r="N47" s="85" t="n"/>
     </row>
     <row r="48" ht="18" customHeight="1" s="51">
       <c r="A48" s="84" t="inlineStr">
@@ -10877,6 +13710,9 @@
       <c r="I48" s="84" t="n"/>
       <c r="J48" s="84" t="n"/>
       <c r="K48" s="84" t="n"/>
+      <c r="L48" s="84" t="n"/>
+      <c r="M48" s="84" t="n"/>
+      <c r="N48" s="84" t="n"/>
     </row>
     <row r="49" ht="18" customHeight="1" s="51">
       <c r="A49" s="85" t="inlineStr">
@@ -10898,6 +13734,9 @@
       <c r="I49" s="85" t="n"/>
       <c r="J49" s="85" t="n"/>
       <c r="K49" s="85" t="n"/>
+      <c r="L49" s="85" t="n"/>
+      <c r="M49" s="85" t="n"/>
+      <c r="N49" s="85" t="n"/>
     </row>
     <row r="50" ht="18" customHeight="1" s="51">
       <c r="A50" s="84" t="inlineStr">
@@ -10919,6 +13758,9 @@
       <c r="I50" s="84" t="n"/>
       <c r="J50" s="84" t="n"/>
       <c r="K50" s="84" t="n"/>
+      <c r="L50" s="84" t="n"/>
+      <c r="M50" s="84" t="n"/>
+      <c r="N50" s="84" t="n"/>
     </row>
     <row r="51" ht="18" customHeight="1" s="51">
       <c r="A51" s="85" t="inlineStr">
@@ -10940,95 +13782,96 @@
       <c r="I51" s="85" t="n"/>
       <c r="J51" s="85" t="n"/>
       <c r="K51" s="85" t="n"/>
+      <c r="L51" s="85" t="n"/>
+      <c r="M51" s="85" t="n"/>
+      <c r="N51" s="85" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="84" t="inlineStr">
-        <is>
-          <t>Dropdown values: Acquire | Deepen | Create | ? (unscorable/blank)</t>
-        </is>
-      </c>
-      <c r="B53" s="86" t="n"/>
-      <c r="C53" s="86" t="n"/>
-      <c r="D53" s="86" t="n"/>
-      <c r="E53" s="86" t="n"/>
-      <c r="F53" s="86" t="n"/>
-      <c r="G53" s="86" t="n"/>
-      <c r="H53" s="86" t="n"/>
-      <c r="I53" s="86" t="n"/>
-      <c r="J53" s="86" t="n"/>
-      <c r="K53" s="87" t="n"/>
-    </row>
-    <row r="54" ht="40" customHeight="1" s="51">
-      <c r="A54" s="85" t="inlineStr">
+      <c r="A53" s="92" t="inlineStr">
         <is>
           <t>Task descriptions:</t>
         </is>
       </c>
-      <c r="B54" s="85" t="n"/>
-      <c r="C54" s="90" t="inlineStr">
+    </row>
+    <row r="54" ht="60" customHeight="1" s="51">
+      <c r="C54" s="93" t="inlineStr">
         <is>
           <t>Path A match
-Page 1 matching: assigns correct rule to Path A (energy &lt; 180 kcal -&gt; recommended)</t>
-        </is>
-      </c>
-      <c r="D54" s="90" t="inlineStr">
+Match Rule A to correct path (letter: A, B, or C)</t>
+        </is>
+      </c>
+      <c r="D54" s="93" t="inlineStr">
         <is>
           <t>Path B match
-Page 1 matching: assigns correct rule to Path B (energy &gt;= 180 AND protein &lt; 7.7 -&gt; not recommended)</t>
-        </is>
-      </c>
-      <c r="E54" s="90" t="inlineStr">
+Match Rule B to correct path (letter: A, B, or C)</t>
+        </is>
+      </c>
+      <c r="E54" s="93" t="inlineStr">
         <is>
           <t>Path C match
-Page 1 matching: assigns correct rule to Path C (energy &gt;= 180 AND protein &gt;= 7.7 -&gt; recommended)</t>
-        </is>
-      </c>
-      <c r="F54" s="90" t="inlineStr">
-        <is>
-          <t>Path count
-Page 2 blank: 'My tree contains ___ paths' — states correct number of paths</t>
-        </is>
-      </c>
-      <c r="G54" s="90" t="inlineStr">
+Match Rule C to correct path (letter: A, B, or C)</t>
+        </is>
+      </c>
+      <c r="F54" s="93" t="inlineStr">
+        <is>
+          <t>Number of paths
+'My tree contains ___ paths' — total number of decision paths</t>
+        </is>
+      </c>
+      <c r="G54" s="93" t="inlineStr">
         <is>
           <t>Rule 1
-Page 2 Rule 1: writes a complete if-then rule logically consistent with their WS6 tree</t>
-        </is>
-      </c>
-      <c r="H54" s="90" t="inlineStr">
+Written if-then decision rule for path 1 of own tree</t>
+        </is>
+      </c>
+      <c r="H54" s="93" t="inlineStr">
         <is>
           <t>Rule 2
-Page 2 Rule 2: second rule consistent with tree</t>
-        </is>
-      </c>
-      <c r="I54" s="90" t="inlineStr">
-        <is>
-          <t>Rules 3-6
-Page 2 Rules 3-6: additional rules present and consistent (score if all paths covered)</t>
-        </is>
-      </c>
-      <c r="J54" s="85" t="inlineStr">
-        <is>
-          <t>Overall AI-CFT level for WS7 as a whole</t>
-        </is>
-      </c>
-      <c r="K54" s="85" t="inlineStr">
-        <is>
-          <t>Free notes</t>
+Written if-then decision rule for path 2 of own tree</t>
+        </is>
+      </c>
+      <c r="I54" s="93" t="inlineStr">
+        <is>
+          <t>Rule 3
+Written if-then decision rule for path 3 of own tree</t>
+        </is>
+      </c>
+      <c r="J54" s="93" t="inlineStr">
+        <is>
+          <t>Rule 4
+Written if-then decision rule for path 4 of own tree (if applicable)</t>
+        </is>
+      </c>
+      <c r="K54" s="93" t="inlineStr">
+        <is>
+          <t>Rule 5
+Written if-then decision rule for path 5 of own tree (if applicable)</t>
+        </is>
+      </c>
+      <c r="L54" s="93" t="inlineStr">
+        <is>
+          <t>Rule 6
+Written if-then decision rule for path 6 of own tree (if applicable)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="9">
     <mergeCell ref="A53:K53"/>
     <mergeCell ref="A35:K35"/>
     <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A35:N35"/>
+    <mergeCell ref="A4:N4"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A36:K36"/>
     <mergeCell ref="A5:K5"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation sqref="C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 C17 C18 C19 C20 C21 C22 C23 C24 C25 C26 C27 C28 C29 C30 C31 C32 C33 C34 C36 C37 C38 C39 C40 C41 C42 C43 C44 C45 C46 C47 C48 C49 C50 C51 D5 D6 D7 D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19 D20 D21 D22 D23 D24 D25 D26 D27 D28 D29 D30 D31 D32 D33 D34 D36 D37 D38 D39 D40 D41 D42 D43 D44 D45 D46 D47 D48 D49 D50 D51 E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E24 E25 E26 E27 E28 E29 E30 E31 E32 E33 E34 E36 E37 E38 E39 E40 E41 E42 E43 E44 E45 E46 E47 E48 E49 E50 E51 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34 F36 F37 F38 F39 F40 F41 F42 F43 F44 F45 F46 F47 F48 F49 F50 F51 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 G31 G32 G33 G34 G36 G37 G38 G39 G40 G41 G42 G43 G44 G45 G46 G47 G48 G49 G50 G51 H5 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27 H28 H29 H30 H31 H32 H33 H34 H36 H37 H38 H39 H40 H41 H42 H43 H44 H45 H46 H47 H48 H49 H50 H51 I5 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I24 I25 I26 I27 I28 I29 I30 I31 I32 I33 I34 I36 I37 I38 I39 I40 I41 I42 I43 I44 I45 I46 I47 I48 I49 I50 I51 J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25 J26 J27 J28 J29 J30 J31 J32 J33 J34 J36 J37 J38 J39 J40 J41 J42 J43 J44 J45 J46 J47 J48 J49 J50 J51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Choose: Acquire, Deepen, Create, or ?" promptTitle="Select level" prompt="AI-CFT level" type="list">
+      <formula1>"Acquire,Deepen,Create,?"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 C17 C18 C19 C20 C21 C22 C23 C24 C25 C26 C27 C28 C29 C30 C31 C32 C33 C34 C36 C37 C38 C39 C40 C41 C42 C43 C44 C45 C46 C47 C48 C49 C50 C51 D5 D6 D7 D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19 D20 D21 D22 D23 D24 D25 D26 D27 D28 D29 D30 D31 D32 D33 D34 D36 D37 D38 D39 D40 D41 D42 D43 D44 D45 D46 D47 D48 D49 D50 D51 E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E24 E25 E26 E27 E28 E29 E30 E31 E32 E33 E34 E36 E37 E38 E39 E40 E41 E42 E43 E44 E45 E46 E47 E48 E49 E50 E51 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34 F36 F37 F38 F39 F40 F41 F42 F43 F44 F45 F46 F47 F48 F49 F50 F51 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 G31 G32 G33 G34 G36 G37 G38 G39 G40 G41 G42 G43 G44 G45 G46 G47 G48 G49 G50 G51 H5 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27 H28 H29 H30 H31 H32 H33 H34 H36 H37 H38 H39 H40 H41 H42 H43 H44 H45 H46 H47 H48 H49 H50 H51 I5 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I24 I25 I26 I27 I28 I29 I30 I31 I32 I33 I34 I36 I37 I38 I39 I40 I41 I42 I43 I44 I45 I46 I47 I48 I49 I50 I51 J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25 J26 J27 J28 J29 J30 J31 J32 J33 J34 J36 J37 J38 J39 J40 J41 J42 J43 J44 J45 J46 J47 J48 J49 J50 J51 K5 K6 K7 K8 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 K19 K20 K21 K22 K23 K24 K25 K26 K27 K28 K29 K30 K31 K32 K33 K34 K36 K37 K38 K39 K40 K41 K42 K43 K44 K45 K46 K47 K48 K49 K50 K51 L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26 L27 L28 L29 L30 L31 L32 L33 L34 L36 L37 L38 L39 L40 L41 L42 L43 L44 L45 L46 L47 L48 L49 L50 L51 M5 M6 M7 M8 M9 M10 M11 M12 M13 M14 M15 M16 M17 M18 M19 M20 M21 M22 M23 M24 M25 M26 M27 M28 M29 M30 M31 M32 M33 M34 M36 M37 M38 M39 M40 M41 M42 M43 M44 M45 M46 M47 M48 M49 M50 M51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Acquire,Deepen,Create,?"</formula1>
     </dataValidation>
   </dataValidations>
@@ -11042,7 +13885,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:L54"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" style="51" min="1" max="1"/>
@@ -11050,24 +13893,29 @@
     <col width="18" customWidth="1" style="51" min="3" max="5"/>
     <col width="18" customWidth="1" style="51" min="4" max="4"/>
     <col width="18" customWidth="1" style="51" min="5" max="5"/>
-    <col width="14" customWidth="1" style="51" min="6" max="6"/>
-    <col width="22" customWidth="1" style="51" min="7" max="7"/>
+    <col width="18" customWidth="1" style="51" min="6" max="6"/>
+    <col width="18" customWidth="1" style="51" min="7" max="7"/>
+    <col width="18" customWidth="1" style="51" min="8" max="8"/>
+    <col width="18" customWidth="1" style="51" min="9" max="9"/>
+    <col width="18" customWidth="1" style="51" min="10" max="10"/>
+    <col width="14" customWidth="1" style="51" min="11" max="11"/>
+    <col width="22" customWidth="1" style="51" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" s="51">
       <c r="A1" s="77" t="inlineStr">
         <is>
-          <t>AI-CFT Labeling — WS10 - Systematic</t>
+          <t>AI-CFT Labeling — WS10</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1" s="51">
-      <c r="A2" s="78" t="inlineStr">
+      <c r="A2" s="91" t="inlineStr">
         <is>
           <t>Cohort</t>
         </is>
       </c>
-      <c r="B2" s="78" t="inlineStr">
+      <c r="B2" s="91" t="inlineStr">
         <is>
           <t>Student</t>
         </is>
@@ -11082,17 +13930,42 @@
           <t>Deepen</t>
         </is>
       </c>
-      <c r="E2" s="89" t="inlineStr">
-        <is>
-          <t>Create</t>
-        </is>
-      </c>
-      <c r="F2" s="80" t="inlineStr">
+      <c r="E2" s="88" t="inlineStr">
+        <is>
+          <t>Deepen</t>
+        </is>
+      </c>
+      <c r="F2" s="88" t="inlineStr">
+        <is>
+          <t>Deepen</t>
+        </is>
+      </c>
+      <c r="G2" s="88" t="inlineStr">
+        <is>
+          <t>Deepen</t>
+        </is>
+      </c>
+      <c r="H2" s="88" t="inlineStr">
+        <is>
+          <t>Deepen</t>
+        </is>
+      </c>
+      <c r="I2" s="88" t="inlineStr">
+        <is>
+          <t>Deepen</t>
+        </is>
+      </c>
+      <c r="J2" s="88" t="inlineStr">
+        <is>
+          <t>Deepen</t>
+        </is>
+      </c>
+      <c r="K2" s="80" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G2" s="80" t="inlineStr">
+      <c r="L2" s="80" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -11112,27 +13985,57 @@
       <c r="C3" s="82" t="inlineStr">
         <is>
           <t>Blank 1
-Misclassification counts</t>
+Misclassification @ 28</t>
         </is>
       </c>
       <c r="D3" s="82" t="inlineStr">
         <is>
           <t>Blank 2
-Optimum threshold</t>
+Misclassification @ 69</t>
         </is>
       </c>
       <c r="E3" s="82" t="inlineStr">
         <is>
           <t>Blank 3
-Why optimum</t>
+Misclassification @ 219</t>
         </is>
       </c>
       <c r="F3" s="82" t="inlineStr">
         <is>
+          <t>Blank 4
+Misclassification @ 346</t>
+        </is>
+      </c>
+      <c r="G3" s="82" t="inlineStr">
+        <is>
+          <t>Blank 5
+Misclassification @ 359</t>
+        </is>
+      </c>
+      <c r="H3" s="82" t="inlineStr">
+        <is>
+          <t>Blank 6
+Misclassification @ 408</t>
+        </is>
+      </c>
+      <c r="I3" s="82" t="inlineStr">
+        <is>
+          <t>Blank 7
+Misclassification @ 489</t>
+        </is>
+      </c>
+      <c r="J3" s="82" t="inlineStr">
+        <is>
+          <t>Blank 8
+Optimal threshold value</t>
+        </is>
+      </c>
+      <c r="K3" s="82" t="inlineStr">
+        <is>
           <t>Overall WS10</t>
         </is>
       </c>
-      <c r="G3" s="82" t="inlineStr">
+      <c r="L3" s="82" t="inlineStr">
         <is>
           <t>Notes WS10</t>
         </is>
@@ -11151,12 +14054,21 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="B5" s="86" t="n"/>
-      <c r="C5" s="86" t="n"/>
-      <c r="D5" s="86" t="n"/>
-      <c r="E5" s="86" t="n"/>
-      <c r="F5" s="86" t="n"/>
-      <c r="G5" s="87" t="n"/>
+      <c r="B5" s="84" t="inlineStr">
+        <is>
+          <t>Ozzy</t>
+        </is>
+      </c>
+      <c r="C5" s="84" t="n"/>
+      <c r="D5" s="84" t="n"/>
+      <c r="E5" s="84" t="n"/>
+      <c r="F5" s="84" t="n"/>
+      <c r="G5" s="84" t="n"/>
+      <c r="H5" s="84" t="n"/>
+      <c r="I5" s="84" t="n"/>
+      <c r="J5" s="84" t="n"/>
+      <c r="K5" s="84" t="n"/>
+      <c r="L5" s="84" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1" s="51">
       <c r="A6" s="85" t="inlineStr">
@@ -11174,6 +14086,11 @@
       <c r="E6" s="85" t="n"/>
       <c r="F6" s="85" t="n"/>
       <c r="G6" s="85" t="n"/>
+      <c r="H6" s="85" t="n"/>
+      <c r="I6" s="85" t="n"/>
+      <c r="J6" s="85" t="n"/>
+      <c r="K6" s="85" t="n"/>
+      <c r="L6" s="85" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1" s="51">
       <c r="A7" s="84" t="inlineStr">
@@ -11191,6 +14108,11 @@
       <c r="E7" s="84" t="n"/>
       <c r="F7" s="84" t="n"/>
       <c r="G7" s="84" t="n"/>
+      <c r="H7" s="84" t="n"/>
+      <c r="I7" s="84" t="n"/>
+      <c r="J7" s="84" t="n"/>
+      <c r="K7" s="84" t="n"/>
+      <c r="L7" s="84" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1" s="51">
       <c r="A8" s="85" t="inlineStr">
@@ -11208,6 +14130,11 @@
       <c r="E8" s="85" t="n"/>
       <c r="F8" s="85" t="n"/>
       <c r="G8" s="85" t="n"/>
+      <c r="H8" s="85" t="n"/>
+      <c r="I8" s="85" t="n"/>
+      <c r="J8" s="85" t="n"/>
+      <c r="K8" s="85" t="n"/>
+      <c r="L8" s="85" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1" s="51">
       <c r="A9" s="84" t="inlineStr">
@@ -11225,6 +14152,11 @@
       <c r="E9" s="84" t="n"/>
       <c r="F9" s="84" t="n"/>
       <c r="G9" s="84" t="n"/>
+      <c r="H9" s="84" t="n"/>
+      <c r="I9" s="84" t="n"/>
+      <c r="J9" s="84" t="n"/>
+      <c r="K9" s="84" t="n"/>
+      <c r="L9" s="84" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1" s="51">
       <c r="A10" s="85" t="inlineStr">
@@ -11242,6 +14174,11 @@
       <c r="E10" s="85" t="n"/>
       <c r="F10" s="85" t="n"/>
       <c r="G10" s="85" t="n"/>
+      <c r="H10" s="85" t="n"/>
+      <c r="I10" s="85" t="n"/>
+      <c r="J10" s="85" t="n"/>
+      <c r="K10" s="85" t="n"/>
+      <c r="L10" s="85" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1" s="51">
       <c r="A11" s="84" t="inlineStr">
@@ -11259,6 +14196,11 @@
       <c r="E11" s="84" t="n"/>
       <c r="F11" s="84" t="n"/>
       <c r="G11" s="84" t="n"/>
+      <c r="H11" s="84" t="n"/>
+      <c r="I11" s="84" t="n"/>
+      <c r="J11" s="84" t="n"/>
+      <c r="K11" s="84" t="n"/>
+      <c r="L11" s="84" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1" s="51">
       <c r="A12" s="85" t="inlineStr">
@@ -11276,6 +14218,11 @@
       <c r="E12" s="85" t="n"/>
       <c r="F12" s="85" t="n"/>
       <c r="G12" s="85" t="n"/>
+      <c r="H12" s="85" t="n"/>
+      <c r="I12" s="85" t="n"/>
+      <c r="J12" s="85" t="n"/>
+      <c r="K12" s="85" t="n"/>
+      <c r="L12" s="85" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1" s="51">
       <c r="A13" s="84" t="inlineStr">
@@ -11293,6 +14240,11 @@
       <c r="E13" s="84" t="n"/>
       <c r="F13" s="84" t="n"/>
       <c r="G13" s="84" t="n"/>
+      <c r="H13" s="84" t="n"/>
+      <c r="I13" s="84" t="n"/>
+      <c r="J13" s="84" t="n"/>
+      <c r="K13" s="84" t="n"/>
+      <c r="L13" s="84" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1" s="51">
       <c r="A14" s="85" t="inlineStr">
@@ -11310,6 +14262,11 @@
       <c r="E14" s="85" t="n"/>
       <c r="F14" s="85" t="n"/>
       <c r="G14" s="85" t="n"/>
+      <c r="H14" s="85" t="n"/>
+      <c r="I14" s="85" t="n"/>
+      <c r="J14" s="85" t="n"/>
+      <c r="K14" s="85" t="n"/>
+      <c r="L14" s="85" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1" s="51">
       <c r="A15" s="84" t="inlineStr">
@@ -11327,6 +14284,11 @@
       <c r="E15" s="84" t="n"/>
       <c r="F15" s="84" t="n"/>
       <c r="G15" s="84" t="n"/>
+      <c r="H15" s="84" t="n"/>
+      <c r="I15" s="84" t="n"/>
+      <c r="J15" s="84" t="n"/>
+      <c r="K15" s="84" t="n"/>
+      <c r="L15" s="84" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1" s="51">
       <c r="A16" s="85" t="inlineStr">
@@ -11344,6 +14306,11 @@
       <c r="E16" s="85" t="n"/>
       <c r="F16" s="85" t="n"/>
       <c r="G16" s="85" t="n"/>
+      <c r="H16" s="85" t="n"/>
+      <c r="I16" s="85" t="n"/>
+      <c r="J16" s="85" t="n"/>
+      <c r="K16" s="85" t="n"/>
+      <c r="L16" s="85" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1" s="51">
       <c r="A17" s="84" t="inlineStr">
@@ -11361,6 +14328,11 @@
       <c r="E17" s="84" t="n"/>
       <c r="F17" s="84" t="n"/>
       <c r="G17" s="84" t="n"/>
+      <c r="H17" s="84" t="n"/>
+      <c r="I17" s="84" t="n"/>
+      <c r="J17" s="84" t="n"/>
+      <c r="K17" s="84" t="n"/>
+      <c r="L17" s="84" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1" s="51">
       <c r="A18" s="85" t="inlineStr">
@@ -11378,6 +14350,11 @@
       <c r="E18" s="85" t="n"/>
       <c r="F18" s="85" t="n"/>
       <c r="G18" s="85" t="n"/>
+      <c r="H18" s="85" t="n"/>
+      <c r="I18" s="85" t="n"/>
+      <c r="J18" s="85" t="n"/>
+      <c r="K18" s="85" t="n"/>
+      <c r="L18" s="85" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1" s="51">
       <c r="A19" s="84" t="inlineStr">
@@ -11395,6 +14372,11 @@
       <c r="E19" s="84" t="n"/>
       <c r="F19" s="84" t="n"/>
       <c r="G19" s="84" t="n"/>
+      <c r="H19" s="84" t="n"/>
+      <c r="I19" s="84" t="n"/>
+      <c r="J19" s="84" t="n"/>
+      <c r="K19" s="84" t="n"/>
+      <c r="L19" s="84" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1" s="51">
       <c r="A20" s="85" t="inlineStr">
@@ -11412,6 +14394,11 @@
       <c r="E20" s="85" t="n"/>
       <c r="F20" s="85" t="n"/>
       <c r="G20" s="85" t="n"/>
+      <c r="H20" s="85" t="n"/>
+      <c r="I20" s="85" t="n"/>
+      <c r="J20" s="85" t="n"/>
+      <c r="K20" s="85" t="n"/>
+      <c r="L20" s="85" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1" s="51">
       <c r="A21" s="84" t="inlineStr">
@@ -11429,6 +14416,11 @@
       <c r="E21" s="84" t="n"/>
       <c r="F21" s="84" t="n"/>
       <c r="G21" s="84" t="n"/>
+      <c r="H21" s="84" t="n"/>
+      <c r="I21" s="84" t="n"/>
+      <c r="J21" s="84" t="n"/>
+      <c r="K21" s="84" t="n"/>
+      <c r="L21" s="84" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1" s="51">
       <c r="A22" s="85" t="inlineStr">
@@ -11446,6 +14438,11 @@
       <c r="E22" s="85" t="n"/>
       <c r="F22" s="85" t="n"/>
       <c r="G22" s="85" t="n"/>
+      <c r="H22" s="85" t="n"/>
+      <c r="I22" s="85" t="n"/>
+      <c r="J22" s="85" t="n"/>
+      <c r="K22" s="85" t="n"/>
+      <c r="L22" s="85" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1" s="51">
       <c r="A23" s="84" t="inlineStr">
@@ -11463,6 +14460,11 @@
       <c r="E23" s="84" t="n"/>
       <c r="F23" s="84" t="n"/>
       <c r="G23" s="84" t="n"/>
+      <c r="H23" s="84" t="n"/>
+      <c r="I23" s="84" t="n"/>
+      <c r="J23" s="84" t="n"/>
+      <c r="K23" s="84" t="n"/>
+      <c r="L23" s="84" t="n"/>
     </row>
     <row r="24" ht="18" customHeight="1" s="51">
       <c r="A24" s="85" t="inlineStr">
@@ -11480,6 +14482,11 @@
       <c r="E24" s="85" t="n"/>
       <c r="F24" s="85" t="n"/>
       <c r="G24" s="85" t="n"/>
+      <c r="H24" s="85" t="n"/>
+      <c r="I24" s="85" t="n"/>
+      <c r="J24" s="85" t="n"/>
+      <c r="K24" s="85" t="n"/>
+      <c r="L24" s="85" t="n"/>
     </row>
     <row r="25" ht="18" customHeight="1" s="51">
       <c r="A25" s="84" t="inlineStr">
@@ -11497,6 +14504,11 @@
       <c r="E25" s="84" t="n"/>
       <c r="F25" s="84" t="n"/>
       <c r="G25" s="84" t="n"/>
+      <c r="H25" s="84" t="n"/>
+      <c r="I25" s="84" t="n"/>
+      <c r="J25" s="84" t="n"/>
+      <c r="K25" s="84" t="n"/>
+      <c r="L25" s="84" t="n"/>
     </row>
     <row r="26" ht="18" customHeight="1" s="51">
       <c r="A26" s="85" t="inlineStr">
@@ -11514,6 +14526,11 @@
       <c r="E26" s="85" t="n"/>
       <c r="F26" s="85" t="n"/>
       <c r="G26" s="85" t="n"/>
+      <c r="H26" s="85" t="n"/>
+      <c r="I26" s="85" t="n"/>
+      <c r="J26" s="85" t="n"/>
+      <c r="K26" s="85" t="n"/>
+      <c r="L26" s="85" t="n"/>
     </row>
     <row r="27" ht="18" customHeight="1" s="51">
       <c r="A27" s="84" t="inlineStr">
@@ -11531,6 +14548,11 @@
       <c r="E27" s="84" t="n"/>
       <c r="F27" s="84" t="n"/>
       <c r="G27" s="84" t="n"/>
+      <c r="H27" s="84" t="n"/>
+      <c r="I27" s="84" t="n"/>
+      <c r="J27" s="84" t="n"/>
+      <c r="K27" s="84" t="n"/>
+      <c r="L27" s="84" t="n"/>
     </row>
     <row r="28" ht="18" customHeight="1" s="51">
       <c r="A28" s="85" t="inlineStr">
@@ -11548,6 +14570,11 @@
       <c r="E28" s="85" t="n"/>
       <c r="F28" s="85" t="n"/>
       <c r="G28" s="85" t="n"/>
+      <c r="H28" s="85" t="n"/>
+      <c r="I28" s="85" t="n"/>
+      <c r="J28" s="85" t="n"/>
+      <c r="K28" s="85" t="n"/>
+      <c r="L28" s="85" t="n"/>
     </row>
     <row r="29" ht="18" customHeight="1" s="51">
       <c r="A29" s="84" t="inlineStr">
@@ -11565,6 +14592,11 @@
       <c r="E29" s="84" t="n"/>
       <c r="F29" s="84" t="n"/>
       <c r="G29" s="84" t="n"/>
+      <c r="H29" s="84" t="n"/>
+      <c r="I29" s="84" t="n"/>
+      <c r="J29" s="84" t="n"/>
+      <c r="K29" s="84" t="n"/>
+      <c r="L29" s="84" t="n"/>
     </row>
     <row r="30" ht="18" customHeight="1" s="51">
       <c r="A30" s="85" t="inlineStr">
@@ -11582,6 +14614,11 @@
       <c r="E30" s="85" t="n"/>
       <c r="F30" s="85" t="n"/>
       <c r="G30" s="85" t="n"/>
+      <c r="H30" s="85" t="n"/>
+      <c r="I30" s="85" t="n"/>
+      <c r="J30" s="85" t="n"/>
+      <c r="K30" s="85" t="n"/>
+      <c r="L30" s="85" t="n"/>
     </row>
     <row r="31" ht="18" customHeight="1" s="51">
       <c r="A31" s="84" t="inlineStr">
@@ -11599,6 +14636,11 @@
       <c r="E31" s="84" t="n"/>
       <c r="F31" s="84" t="n"/>
       <c r="G31" s="84" t="n"/>
+      <c r="H31" s="84" t="n"/>
+      <c r="I31" s="84" t="n"/>
+      <c r="J31" s="84" t="n"/>
+      <c r="K31" s="84" t="n"/>
+      <c r="L31" s="84" t="n"/>
     </row>
     <row r="32" ht="18" customHeight="1" s="51">
       <c r="A32" s="85" t="inlineStr">
@@ -11616,6 +14658,11 @@
       <c r="E32" s="85" t="n"/>
       <c r="F32" s="85" t="n"/>
       <c r="G32" s="85" t="n"/>
+      <c r="H32" s="85" t="n"/>
+      <c r="I32" s="85" t="n"/>
+      <c r="J32" s="85" t="n"/>
+      <c r="K32" s="85" t="n"/>
+      <c r="L32" s="85" t="n"/>
     </row>
     <row r="33" ht="18" customHeight="1" s="51">
       <c r="A33" s="84" t="inlineStr">
@@ -11633,6 +14680,11 @@
       <c r="E33" s="84" t="n"/>
       <c r="F33" s="84" t="n"/>
       <c r="G33" s="84" t="n"/>
+      <c r="H33" s="84" t="n"/>
+      <c r="I33" s="84" t="n"/>
+      <c r="J33" s="84" t="n"/>
+      <c r="K33" s="84" t="n"/>
+      <c r="L33" s="84" t="n"/>
     </row>
     <row r="34" ht="18" customHeight="1" s="51">
       <c r="A34" s="85" t="inlineStr">
@@ -11640,12 +14692,21 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="B34" s="85" t="n"/>
+      <c r="B34" s="85" t="inlineStr">
+        <is>
+          <t>Sabrina</t>
+        </is>
+      </c>
       <c r="C34" s="85" t="n"/>
       <c r="D34" s="85" t="n"/>
       <c r="E34" s="85" t="n"/>
       <c r="F34" s="85" t="n"/>
       <c r="G34" s="85" t="n"/>
+      <c r="H34" s="85" t="n"/>
+      <c r="I34" s="85" t="n"/>
+      <c r="J34" s="85" t="n"/>
+      <c r="K34" s="85" t="n"/>
+      <c r="L34" s="85" t="n"/>
     </row>
     <row r="35" ht="20" customHeight="1" s="51">
       <c r="A35" s="83" t="inlineStr">
@@ -11660,12 +14721,21 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="B36" s="86" t="n"/>
-      <c r="C36" s="86" t="n"/>
-      <c r="D36" s="86" t="n"/>
-      <c r="E36" s="86" t="n"/>
-      <c r="F36" s="86" t="n"/>
-      <c r="G36" s="87" t="n"/>
+      <c r="B36" s="84" t="inlineStr">
+        <is>
+          <t>Sheila</t>
+        </is>
+      </c>
+      <c r="C36" s="84" t="n"/>
+      <c r="D36" s="84" t="n"/>
+      <c r="E36" s="84" t="n"/>
+      <c r="F36" s="84" t="n"/>
+      <c r="G36" s="84" t="n"/>
+      <c r="H36" s="84" t="n"/>
+      <c r="I36" s="84" t="n"/>
+      <c r="J36" s="84" t="n"/>
+      <c r="K36" s="84" t="n"/>
+      <c r="L36" s="84" t="n"/>
     </row>
     <row r="37" ht="18" customHeight="1" s="51">
       <c r="A37" s="85" t="inlineStr">
@@ -11683,6 +14753,11 @@
       <c r="E37" s="85" t="n"/>
       <c r="F37" s="85" t="n"/>
       <c r="G37" s="85" t="n"/>
+      <c r="H37" s="85" t="n"/>
+      <c r="I37" s="85" t="n"/>
+      <c r="J37" s="85" t="n"/>
+      <c r="K37" s="85" t="n"/>
+      <c r="L37" s="85" t="n"/>
     </row>
     <row r="38" ht="18" customHeight="1" s="51">
       <c r="A38" s="84" t="inlineStr">
@@ -11700,6 +14775,11 @@
       <c r="E38" s="84" t="n"/>
       <c r="F38" s="84" t="n"/>
       <c r="G38" s="84" t="n"/>
+      <c r="H38" s="84" t="n"/>
+      <c r="I38" s="84" t="n"/>
+      <c r="J38" s="84" t="n"/>
+      <c r="K38" s="84" t="n"/>
+      <c r="L38" s="84" t="n"/>
     </row>
     <row r="39" ht="18" customHeight="1" s="51">
       <c r="A39" s="85" t="inlineStr">
@@ -11717,6 +14797,11 @@
       <c r="E39" s="85" t="n"/>
       <c r="F39" s="85" t="n"/>
       <c r="G39" s="85" t="n"/>
+      <c r="H39" s="85" t="n"/>
+      <c r="I39" s="85" t="n"/>
+      <c r="J39" s="85" t="n"/>
+      <c r="K39" s="85" t="n"/>
+      <c r="L39" s="85" t="n"/>
     </row>
     <row r="40" ht="18" customHeight="1" s="51">
       <c r="A40" s="84" t="inlineStr">
@@ -11734,6 +14819,11 @@
       <c r="E40" s="84" t="n"/>
       <c r="F40" s="84" t="n"/>
       <c r="G40" s="84" t="n"/>
+      <c r="H40" s="84" t="n"/>
+      <c r="I40" s="84" t="n"/>
+      <c r="J40" s="84" t="n"/>
+      <c r="K40" s="84" t="n"/>
+      <c r="L40" s="84" t="n"/>
     </row>
     <row r="41" ht="18" customHeight="1" s="51">
       <c r="A41" s="85" t="inlineStr">
@@ -11751,6 +14841,11 @@
       <c r="E41" s="85" t="n"/>
       <c r="F41" s="85" t="n"/>
       <c r="G41" s="85" t="n"/>
+      <c r="H41" s="85" t="n"/>
+      <c r="I41" s="85" t="n"/>
+      <c r="J41" s="85" t="n"/>
+      <c r="K41" s="85" t="n"/>
+      <c r="L41" s="85" t="n"/>
     </row>
     <row r="42" ht="18" customHeight="1" s="51">
       <c r="A42" s="84" t="inlineStr">
@@ -11768,6 +14863,11 @@
       <c r="E42" s="84" t="n"/>
       <c r="F42" s="84" t="n"/>
       <c r="G42" s="84" t="n"/>
+      <c r="H42" s="84" t="n"/>
+      <c r="I42" s="84" t="n"/>
+      <c r="J42" s="84" t="n"/>
+      <c r="K42" s="84" t="n"/>
+      <c r="L42" s="84" t="n"/>
     </row>
     <row r="43" ht="18" customHeight="1" s="51">
       <c r="A43" s="85" t="inlineStr">
@@ -11785,6 +14885,11 @@
       <c r="E43" s="85" t="n"/>
       <c r="F43" s="85" t="n"/>
       <c r="G43" s="85" t="n"/>
+      <c r="H43" s="85" t="n"/>
+      <c r="I43" s="85" t="n"/>
+      <c r="J43" s="85" t="n"/>
+      <c r="K43" s="85" t="n"/>
+      <c r="L43" s="85" t="n"/>
     </row>
     <row r="44" ht="18" customHeight="1" s="51">
       <c r="A44" s="84" t="inlineStr">
@@ -11802,6 +14907,11 @@
       <c r="E44" s="84" t="n"/>
       <c r="F44" s="84" t="n"/>
       <c r="G44" s="84" t="n"/>
+      <c r="H44" s="84" t="n"/>
+      <c r="I44" s="84" t="n"/>
+      <c r="J44" s="84" t="n"/>
+      <c r="K44" s="84" t="n"/>
+      <c r="L44" s="84" t="n"/>
     </row>
     <row r="45" ht="18" customHeight="1" s="51">
       <c r="A45" s="85" t="inlineStr">
@@ -11819,6 +14929,11 @@
       <c r="E45" s="85" t="n"/>
       <c r="F45" s="85" t="n"/>
       <c r="G45" s="85" t="n"/>
+      <c r="H45" s="85" t="n"/>
+      <c r="I45" s="85" t="n"/>
+      <c r="J45" s="85" t="n"/>
+      <c r="K45" s="85" t="n"/>
+      <c r="L45" s="85" t="n"/>
     </row>
     <row r="46" ht="18" customHeight="1" s="51">
       <c r="A46" s="84" t="inlineStr">
@@ -11836,6 +14951,11 @@
       <c r="E46" s="84" t="n"/>
       <c r="F46" s="84" t="n"/>
       <c r="G46" s="84" t="n"/>
+      <c r="H46" s="84" t="n"/>
+      <c r="I46" s="84" t="n"/>
+      <c r="J46" s="84" t="n"/>
+      <c r="K46" s="84" t="n"/>
+      <c r="L46" s="84" t="n"/>
     </row>
     <row r="47" ht="18" customHeight="1" s="51">
       <c r="A47" s="85" t="inlineStr">
@@ -11853,6 +14973,11 @@
       <c r="E47" s="85" t="n"/>
       <c r="F47" s="85" t="n"/>
       <c r="G47" s="85" t="n"/>
+      <c r="H47" s="85" t="n"/>
+      <c r="I47" s="85" t="n"/>
+      <c r="J47" s="85" t="n"/>
+      <c r="K47" s="85" t="n"/>
+      <c r="L47" s="85" t="n"/>
     </row>
     <row r="48" ht="18" customHeight="1" s="51">
       <c r="A48" s="84" t="inlineStr">
@@ -11870,6 +14995,11 @@
       <c r="E48" s="84" t="n"/>
       <c r="F48" s="84" t="n"/>
       <c r="G48" s="84" t="n"/>
+      <c r="H48" s="84" t="n"/>
+      <c r="I48" s="84" t="n"/>
+      <c r="J48" s="84" t="n"/>
+      <c r="K48" s="84" t="n"/>
+      <c r="L48" s="84" t="n"/>
     </row>
     <row r="49" ht="18" customHeight="1" s="51">
       <c r="A49" s="85" t="inlineStr">
@@ -11887,6 +15017,11 @@
       <c r="E49" s="85" t="n"/>
       <c r="F49" s="85" t="n"/>
       <c r="G49" s="85" t="n"/>
+      <c r="H49" s="85" t="n"/>
+      <c r="I49" s="85" t="n"/>
+      <c r="J49" s="85" t="n"/>
+      <c r="K49" s="85" t="n"/>
+      <c r="L49" s="85" t="n"/>
     </row>
     <row r="50" ht="18" customHeight="1" s="51">
       <c r="A50" s="84" t="inlineStr">
@@ -11904,6 +15039,11 @@
       <c r="E50" s="84" t="n"/>
       <c r="F50" s="84" t="n"/>
       <c r="G50" s="84" t="n"/>
+      <c r="H50" s="84" t="n"/>
+      <c r="I50" s="84" t="n"/>
+      <c r="J50" s="84" t="n"/>
+      <c r="K50" s="84" t="n"/>
+      <c r="L50" s="84" t="n"/>
     </row>
     <row r="51" ht="18" customHeight="1" s="51">
       <c r="A51" s="85" t="inlineStr">
@@ -11921,67 +15061,86 @@
       <c r="E51" s="85" t="n"/>
       <c r="F51" s="85" t="n"/>
       <c r="G51" s="85" t="n"/>
+      <c r="H51" s="85" t="n"/>
+      <c r="I51" s="85" t="n"/>
+      <c r="J51" s="85" t="n"/>
+      <c r="K51" s="85" t="n"/>
+      <c r="L51" s="85" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="84" t="inlineStr">
-        <is>
-          <t>Dropdown values: Acquire | Deepen | Create | ? (unscorable/blank)</t>
-        </is>
-      </c>
-      <c r="B53" s="86" t="n"/>
-      <c r="C53" s="86" t="n"/>
-      <c r="D53" s="86" t="n"/>
-      <c r="E53" s="86" t="n"/>
-      <c r="F53" s="86" t="n"/>
-      <c r="G53" s="87" t="n"/>
-    </row>
-    <row r="54" ht="40" customHeight="1" s="51">
-      <c r="A54" s="85" t="inlineStr">
+      <c r="A53" s="92" t="inlineStr">
         <is>
           <t>Task descriptions:</t>
         </is>
       </c>
-      <c r="B54" s="85" t="n"/>
-      <c r="C54" s="90" t="inlineStr">
-        <is>
-          <t>Misclassification counts
-Table: correctly counts misclassifications for each of the 7 candidate thresholds</t>
-        </is>
-      </c>
-      <c r="D54" s="90" t="inlineStr">
-        <is>
-          <t>Optimum threshold
-Final blank: 'The optimum threshold is: ___' — selects threshold with fewest errors</t>
-        </is>
-      </c>
-      <c r="E54" s="90" t="inlineStr">
-        <is>
-          <t>Why optimum
-Written justification: explains why this threshold minimizes error (score if present)</t>
-        </is>
-      </c>
-      <c r="F54" s="85" t="inlineStr">
-        <is>
-          <t>Overall AI-CFT level for WS10 as a whole</t>
-        </is>
-      </c>
-      <c r="G54" s="85" t="inlineStr">
-        <is>
-          <t>Free notes</t>
+    </row>
+    <row r="54" ht="60" customHeight="1" s="51">
+      <c r="C54" s="93" t="inlineStr">
+        <is>
+          <t>Misclassification @ 28
+Number of misclassified foods if threshold = 28 kcal</t>
+        </is>
+      </c>
+      <c r="D54" s="93" t="inlineStr">
+        <is>
+          <t>Misclassification @ 69
+Number of misclassified foods if threshold = 69 kcal</t>
+        </is>
+      </c>
+      <c r="E54" s="93" t="inlineStr">
+        <is>
+          <t>Misclassification @ 219
+Number of misclassified foods if threshold = 219 kcal</t>
+        </is>
+      </c>
+      <c r="F54" s="93" t="inlineStr">
+        <is>
+          <t>Misclassification @ 346
+Number of misclassified foods if threshold = 346 kcal</t>
+        </is>
+      </c>
+      <c r="G54" s="93" t="inlineStr">
+        <is>
+          <t>Misclassification @ 359
+Number of misclassified foods if threshold = 359 kcal</t>
+        </is>
+      </c>
+      <c r="H54" s="93" t="inlineStr">
+        <is>
+          <t>Misclassification @ 408
+Number of misclassified foods if threshold = 408 kcal</t>
+        </is>
+      </c>
+      <c r="I54" s="93" t="inlineStr">
+        <is>
+          <t>Misclassification @ 489
+Number of misclassified foods if threshold = 489 kcal</t>
+        </is>
+      </c>
+      <c r="J54" s="93" t="inlineStr">
+        <is>
+          <t>Optimal threshold value
+'The optimal threshold value is: ___' — threshold with fewest misclassifications</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="9">
     <mergeCell ref="A36:G36"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A53:G53"/>
+    <mergeCell ref="A1:L1"/>
     <mergeCell ref="A35:G35"/>
     <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A4:L4"/>
+    <mergeCell ref="A35:L35"/>
     <mergeCell ref="A5:G5"/>
   </mergeCells>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation sqref="C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 C17 C18 C19 C20 C21 C22 C23 C24 C25 C26 C27 C28 C29 C30 C31 C32 C33 C34 C36 C37 C38 C39 C40 C41 C42 C43 C44 C45 C46 C47 C48 C49 C50 C51 D5 D6 D7 D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19 D20 D21 D22 D23 D24 D25 D26 D27 D28 D29 D30 D31 D32 D33 D34 D36 D37 D38 D39 D40 D41 D42 D43 D44 D45 D46 D47 D48 D49 D50 D51 E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E24 E25 E26 E27 E28 E29 E30 E31 E32 E33 E34 E36 E37 E38 E39 E40 E41 E42 E43 E44 E45 E46 E47 E48 E49 E50 E51 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34 F36 F37 F38 F39 F40 F41 F42 F43 F44 F45 F46 F47 F48 F49 F50 F51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Choose: Acquire, Deepen, Create, or ?" promptTitle="Select level" prompt="AI-CFT level" type="list">
+      <formula1>"Acquire,Deepen,Create,?"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 C17 C18 C19 C20 C21 C22 C23 C24 C25 C26 C27 C28 C29 C30 C31 C32 C33 C34 C36 C37 C38 C39 C40 C41 C42 C43 C44 C45 C46 C47 C48 C49 C50 C51 D5 D6 D7 D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19 D20 D21 D22 D23 D24 D25 D26 D27 D28 D29 D30 D31 D32 D33 D34 D36 D37 D38 D39 D40 D41 D42 D43 D44 D45 D46 D47 D48 D49 D50 D51 E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E24 E25 E26 E27 E28 E29 E30 E31 E32 E33 E34 E36 E37 E38 E39 E40 E41 E42 E43 E44 E45 E46 E47 E48 E49 E50 E51 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34 F36 F37 F38 F39 F40 F41 F42 F43 F44 F45 F46 F47 F48 F49 F50 F51 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 G31 G32 G33 G34 G36 G37 G38 G39 G40 G41 G42 G43 G44 G45 G46 G47 G48 G49 G50 G51 H5 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27 H28 H29 H30 H31 H32 H33 H34 H36 H37 H38 H39 H40 H41 H42 H43 H44 H45 H46 H47 H48 H49 H50 H51 I5 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I24 I25 I26 I27 I28 I29 I30 I31 I32 I33 I34 I36 I37 I38 I39 I40 I41 I42 I43 I44 I45 I46 I47 I48 I49 I50 I51 J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25 J26 J27 J28 J29 J30 J31 J32 J33 J34 J36 J37 J38 J39 J40 J41 J42 J43 J44 J45 J46 J47 J48 J49 J50 J51 K5 K6 K7 K8 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 K19 K20 K21 K22 K23 K24 K25 K26 K27 K28 K29 K30 K31 K32 K33 K34 K36 K37 K38 K39 K40 K41 K42 K43 K44 K45 K46 K47 K48 K49 K50 K51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Acquire,Deepen,Create,?"</formula1>
     </dataValidation>
   </dataValidations>
@@ -11995,7 +15154,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K54"/>
+  <dimension ref="A1:Y54"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" style="51" min="1" max="1"/>
@@ -12007,24 +15166,38 @@
     <col width="18" customWidth="1" style="51" min="7" max="7"/>
     <col width="18" customWidth="1" style="51" min="8" max="8"/>
     <col width="18" customWidth="1" style="51" min="9" max="9"/>
-    <col width="14" customWidth="1" style="51" min="10" max="10"/>
-    <col width="22" customWidth="1" style="51" min="11" max="11"/>
+    <col width="18" customWidth="1" style="51" min="10" max="10"/>
+    <col width="18" customWidth="1" style="51" min="11" max="11"/>
+    <col width="18" customWidth="1" style="51" min="12" max="12"/>
+    <col width="18" customWidth="1" style="51" min="13" max="13"/>
+    <col width="18" customWidth="1" style="51" min="14" max="14"/>
+    <col width="18" customWidth="1" style="51" min="15" max="15"/>
+    <col width="18" customWidth="1" style="51" min="16" max="16"/>
+    <col width="18" customWidth="1" style="51" min="17" max="17"/>
+    <col width="18" customWidth="1" style="51" min="18" max="18"/>
+    <col width="18" customWidth="1" style="51" min="19" max="19"/>
+    <col width="18" customWidth="1" style="51" min="20" max="20"/>
+    <col width="18" customWidth="1" style="51" min="21" max="21"/>
+    <col width="18" customWidth="1" style="51" min="22" max="22"/>
+    <col width="18" customWidth="1" style="51" min="23" max="23"/>
+    <col width="14" customWidth="1" style="51" min="24" max="24"/>
+    <col width="22" customWidth="1" style="51" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" s="51">
       <c r="A1" s="77" t="inlineStr">
         <is>
-          <t>AI-CFT Labeling — WS11 - Evaluation</t>
+          <t>AI-CFT Labeling — WS11</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1" s="51">
-      <c r="A2" s="78" t="inlineStr">
+      <c r="A2" s="91" t="inlineStr">
         <is>
           <t>Cohort</t>
         </is>
       </c>
-      <c r="B2" s="78" t="inlineStr">
+      <c r="B2" s="91" t="inlineStr">
         <is>
           <t>Student</t>
         </is>
@@ -12034,42 +15207,112 @@
           <t>Acquire</t>
         </is>
       </c>
-      <c r="D2" s="79" t="inlineStr">
+      <c r="D2" s="88" t="inlineStr">
+        <is>
+          <t>Deepen</t>
+        </is>
+      </c>
+      <c r="E2" s="88" t="inlineStr">
+        <is>
+          <t>Deepen</t>
+        </is>
+      </c>
+      <c r="F2" s="79" t="inlineStr">
         <is>
           <t>Acquire</t>
         </is>
       </c>
-      <c r="E2" s="79" t="inlineStr">
+      <c r="G2" s="88" t="inlineStr">
+        <is>
+          <t>Deepen</t>
+        </is>
+      </c>
+      <c r="H2" s="88" t="inlineStr">
+        <is>
+          <t>Deepen</t>
+        </is>
+      </c>
+      <c r="I2" s="88" t="inlineStr">
+        <is>
+          <t>Deepen</t>
+        </is>
+      </c>
+      <c r="J2" s="88" t="inlineStr">
+        <is>
+          <t>Deepen</t>
+        </is>
+      </c>
+      <c r="K2" s="88" t="inlineStr">
+        <is>
+          <t>Deepen</t>
+        </is>
+      </c>
+      <c r="L2" s="88" t="inlineStr">
+        <is>
+          <t>Deepen</t>
+        </is>
+      </c>
+      <c r="M2" s="88" t="inlineStr">
+        <is>
+          <t>Deepen</t>
+        </is>
+      </c>
+      <c r="N2" s="88" t="inlineStr">
+        <is>
+          <t>Deepen</t>
+        </is>
+      </c>
+      <c r="O2" s="88" t="inlineStr">
+        <is>
+          <t>Deepen</t>
+        </is>
+      </c>
+      <c r="P2" s="88" t="inlineStr">
+        <is>
+          <t>Deepen</t>
+        </is>
+      </c>
+      <c r="Q2" s="88" t="inlineStr">
+        <is>
+          <t>Deepen</t>
+        </is>
+      </c>
+      <c r="R2" s="88" t="inlineStr">
+        <is>
+          <t>Deepen</t>
+        </is>
+      </c>
+      <c r="S2" s="79" t="inlineStr">
         <is>
           <t>Acquire</t>
         </is>
       </c>
-      <c r="F2" s="88" t="inlineStr">
-        <is>
-          <t>Deepen</t>
-        </is>
-      </c>
-      <c r="G2" s="88" t="inlineStr">
-        <is>
-          <t>Deepen</t>
-        </is>
-      </c>
-      <c r="H2" s="79" t="inlineStr">
+      <c r="T2" s="79" t="inlineStr">
         <is>
           <t>Acquire</t>
         </is>
       </c>
-      <c r="I2" s="88" t="inlineStr">
-        <is>
-          <t>Deepen</t>
-        </is>
-      </c>
-      <c r="J2" s="80" t="inlineStr">
+      <c r="U2" s="79" t="inlineStr">
+        <is>
+          <t>Acquire</t>
+        </is>
+      </c>
+      <c r="V2" s="79" t="inlineStr">
+        <is>
+          <t>Acquire</t>
+        </is>
+      </c>
+      <c r="W2" s="79" t="inlineStr">
+        <is>
+          <t>Acquire</t>
+        </is>
+      </c>
+      <c r="X2" s="80" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K2" s="80" t="inlineStr">
+      <c r="Y2" s="80" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -12089,51 +15332,135 @@
       <c r="C3" s="82" t="inlineStr">
         <is>
           <t>Blank 1
-Can explain DT</t>
+Q4 – Can explain DT</t>
         </is>
       </c>
       <c r="D3" s="82" t="inlineStr">
         <is>
           <t>Blank 2
-Classify strawberry</t>
+Q8a – Classify strawberry</t>
         </is>
       </c>
       <c r="E3" s="82" t="inlineStr">
         <is>
           <t>Blank 3
-Decision rule</t>
+Q8b – Decision rule sentence</t>
         </is>
       </c>
       <c r="F3" s="82" t="inlineStr">
         <is>
           <t>Blank 4
-What is data</t>
+Q9 – What is data?</t>
         </is>
       </c>
       <c r="G3" s="82" t="inlineStr">
         <is>
           <t>Blank 5
-DT capabilities</t>
+Q10a – DT statement 1</t>
         </is>
       </c>
       <c r="H3" s="82" t="inlineStr">
         <is>
           <t>Blank 6
-Step ordering</t>
+Q10b – DT statement 2</t>
         </is>
       </c>
       <c r="I3" s="82" t="inlineStr">
         <is>
           <t>Blank 7
-Why is DT AI</t>
+Q10c – DT statement 3</t>
         </is>
       </c>
       <c r="J3" s="82" t="inlineStr">
         <is>
+          <t>Blank 8
+Q10d – DT statement 4</t>
+        </is>
+      </c>
+      <c r="K3" s="82" t="inlineStr">
+        <is>
+          <t>Blank 9
+Q10e – DT statement 5</t>
+        </is>
+      </c>
+      <c r="L3" s="82" t="inlineStr">
+        <is>
+          <t>Blank 10
+Q10f – DT statement 6</t>
+        </is>
+      </c>
+      <c r="M3" s="82" t="inlineStr">
+        <is>
+          <t>Blank 11
+Q10g – DT statement 7</t>
+        </is>
+      </c>
+      <c r="N3" s="82" t="inlineStr">
+        <is>
+          <t>Blank 12
+Q10h – DT statement 8</t>
+        </is>
+      </c>
+      <c r="O3" s="82" t="inlineStr">
+        <is>
+          <t>Blank 13
+Q11a – Step order 1</t>
+        </is>
+      </c>
+      <c r="P3" s="82" t="inlineStr">
+        <is>
+          <t>Blank 14
+Q11b – Step order 2</t>
+        </is>
+      </c>
+      <c r="Q3" s="82" t="inlineStr">
+        <is>
+          <t>Blank 15
+Q11c – Step order 3</t>
+        </is>
+      </c>
+      <c r="R3" s="82" t="inlineStr">
+        <is>
+          <t>Blank 16
+Q11d – Step order 4</t>
+        </is>
+      </c>
+      <c r="S3" s="82" t="inlineStr">
+        <is>
+          <t>Blank 17
+Q12a – AI statement 1</t>
+        </is>
+      </c>
+      <c r="T3" s="82" t="inlineStr">
+        <is>
+          <t>Blank 18
+Q12b – AI statement 2</t>
+        </is>
+      </c>
+      <c r="U3" s="82" t="inlineStr">
+        <is>
+          <t>Blank 19
+Q12c – AI statement 3</t>
+        </is>
+      </c>
+      <c r="V3" s="82" t="inlineStr">
+        <is>
+          <t>Blank 20
+Q12d – AI statement 4</t>
+        </is>
+      </c>
+      <c r="W3" s="82" t="inlineStr">
+        <is>
+          <t>Blank 21
+Q12e – AI statement 5</t>
+        </is>
+      </c>
+      <c r="X3" s="82" t="inlineStr">
+        <is>
           <t>Overall WS11</t>
         </is>
       </c>
-      <c r="K3" s="82" t="inlineStr">
+      <c r="Y3" s="82" t="inlineStr">
         <is>
           <t>Notes WS11</t>
         </is>
@@ -12152,16 +15479,34 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="B5" s="86" t="n"/>
-      <c r="C5" s="86" t="n"/>
-      <c r="D5" s="86" t="n"/>
-      <c r="E5" s="86" t="n"/>
-      <c r="F5" s="86" t="n"/>
-      <c r="G5" s="86" t="n"/>
-      <c r="H5" s="86" t="n"/>
-      <c r="I5" s="86" t="n"/>
-      <c r="J5" s="86" t="n"/>
-      <c r="K5" s="87" t="n"/>
+      <c r="B5" s="84" t="inlineStr">
+        <is>
+          <t>Ozzy</t>
+        </is>
+      </c>
+      <c r="C5" s="84" t="n"/>
+      <c r="D5" s="84" t="n"/>
+      <c r="E5" s="84" t="n"/>
+      <c r="F5" s="84" t="n"/>
+      <c r="G5" s="84" t="n"/>
+      <c r="H5" s="84" t="n"/>
+      <c r="I5" s="84" t="n"/>
+      <c r="J5" s="84" t="n"/>
+      <c r="K5" s="84" t="n"/>
+      <c r="L5" s="84" t="n"/>
+      <c r="M5" s="84" t="n"/>
+      <c r="N5" s="84" t="n"/>
+      <c r="O5" s="84" t="n"/>
+      <c r="P5" s="84" t="n"/>
+      <c r="Q5" s="84" t="n"/>
+      <c r="R5" s="84" t="n"/>
+      <c r="S5" s="84" t="n"/>
+      <c r="T5" s="84" t="n"/>
+      <c r="U5" s="84" t="n"/>
+      <c r="V5" s="84" t="n"/>
+      <c r="W5" s="84" t="n"/>
+      <c r="X5" s="84" t="n"/>
+      <c r="Y5" s="84" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1" s="51">
       <c r="A6" s="85" t="inlineStr">
@@ -12183,6 +15528,20 @@
       <c r="I6" s="85" t="n"/>
       <c r="J6" s="85" t="n"/>
       <c r="K6" s="85" t="n"/>
+      <c r="L6" s="85" t="n"/>
+      <c r="M6" s="85" t="n"/>
+      <c r="N6" s="85" t="n"/>
+      <c r="O6" s="85" t="n"/>
+      <c r="P6" s="85" t="n"/>
+      <c r="Q6" s="85" t="n"/>
+      <c r="R6" s="85" t="n"/>
+      <c r="S6" s="85" t="n"/>
+      <c r="T6" s="85" t="n"/>
+      <c r="U6" s="85" t="n"/>
+      <c r="V6" s="85" t="n"/>
+      <c r="W6" s="85" t="n"/>
+      <c r="X6" s="85" t="n"/>
+      <c r="Y6" s="85" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1" s="51">
       <c r="A7" s="84" t="inlineStr">
@@ -12204,6 +15563,20 @@
       <c r="I7" s="84" t="n"/>
       <c r="J7" s="84" t="n"/>
       <c r="K7" s="84" t="n"/>
+      <c r="L7" s="84" t="n"/>
+      <c r="M7" s="84" t="n"/>
+      <c r="N7" s="84" t="n"/>
+      <c r="O7" s="84" t="n"/>
+      <c r="P7" s="84" t="n"/>
+      <c r="Q7" s="84" t="n"/>
+      <c r="R7" s="84" t="n"/>
+      <c r="S7" s="84" t="n"/>
+      <c r="T7" s="84" t="n"/>
+      <c r="U7" s="84" t="n"/>
+      <c r="V7" s="84" t="n"/>
+      <c r="W7" s="84" t="n"/>
+      <c r="X7" s="84" t="n"/>
+      <c r="Y7" s="84" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1" s="51">
       <c r="A8" s="85" t="inlineStr">
@@ -12225,6 +15598,20 @@
       <c r="I8" s="85" t="n"/>
       <c r="J8" s="85" t="n"/>
       <c r="K8" s="85" t="n"/>
+      <c r="L8" s="85" t="n"/>
+      <c r="M8" s="85" t="n"/>
+      <c r="N8" s="85" t="n"/>
+      <c r="O8" s="85" t="n"/>
+      <c r="P8" s="85" t="n"/>
+      <c r="Q8" s="85" t="n"/>
+      <c r="R8" s="85" t="n"/>
+      <c r="S8" s="85" t="n"/>
+      <c r="T8" s="85" t="n"/>
+      <c r="U8" s="85" t="n"/>
+      <c r="V8" s="85" t="n"/>
+      <c r="W8" s="85" t="n"/>
+      <c r="X8" s="85" t="n"/>
+      <c r="Y8" s="85" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1" s="51">
       <c r="A9" s="84" t="inlineStr">
@@ -12246,6 +15633,20 @@
       <c r="I9" s="84" t="n"/>
       <c r="J9" s="84" t="n"/>
       <c r="K9" s="84" t="n"/>
+      <c r="L9" s="84" t="n"/>
+      <c r="M9" s="84" t="n"/>
+      <c r="N9" s="84" t="n"/>
+      <c r="O9" s="84" t="n"/>
+      <c r="P9" s="84" t="n"/>
+      <c r="Q9" s="84" t="n"/>
+      <c r="R9" s="84" t="n"/>
+      <c r="S9" s="84" t="n"/>
+      <c r="T9" s="84" t="n"/>
+      <c r="U9" s="84" t="n"/>
+      <c r="V9" s="84" t="n"/>
+      <c r="W9" s="84" t="n"/>
+      <c r="X9" s="84" t="n"/>
+      <c r="Y9" s="84" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1" s="51">
       <c r="A10" s="85" t="inlineStr">
@@ -12267,6 +15668,20 @@
       <c r="I10" s="85" t="n"/>
       <c r="J10" s="85" t="n"/>
       <c r="K10" s="85" t="n"/>
+      <c r="L10" s="85" t="n"/>
+      <c r="M10" s="85" t="n"/>
+      <c r="N10" s="85" t="n"/>
+      <c r="O10" s="85" t="n"/>
+      <c r="P10" s="85" t="n"/>
+      <c r="Q10" s="85" t="n"/>
+      <c r="R10" s="85" t="n"/>
+      <c r="S10" s="85" t="n"/>
+      <c r="T10" s="85" t="n"/>
+      <c r="U10" s="85" t="n"/>
+      <c r="V10" s="85" t="n"/>
+      <c r="W10" s="85" t="n"/>
+      <c r="X10" s="85" t="n"/>
+      <c r="Y10" s="85" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1" s="51">
       <c r="A11" s="84" t="inlineStr">
@@ -12288,6 +15703,20 @@
       <c r="I11" s="84" t="n"/>
       <c r="J11" s="84" t="n"/>
       <c r="K11" s="84" t="n"/>
+      <c r="L11" s="84" t="n"/>
+      <c r="M11" s="84" t="n"/>
+      <c r="N11" s="84" t="n"/>
+      <c r="O11" s="84" t="n"/>
+      <c r="P11" s="84" t="n"/>
+      <c r="Q11" s="84" t="n"/>
+      <c r="R11" s="84" t="n"/>
+      <c r="S11" s="84" t="n"/>
+      <c r="T11" s="84" t="n"/>
+      <c r="U11" s="84" t="n"/>
+      <c r="V11" s="84" t="n"/>
+      <c r="W11" s="84" t="n"/>
+      <c r="X11" s="84" t="n"/>
+      <c r="Y11" s="84" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1" s="51">
       <c r="A12" s="85" t="inlineStr">
@@ -12309,6 +15738,20 @@
       <c r="I12" s="85" t="n"/>
       <c r="J12" s="85" t="n"/>
       <c r="K12" s="85" t="n"/>
+      <c r="L12" s="85" t="n"/>
+      <c r="M12" s="85" t="n"/>
+      <c r="N12" s="85" t="n"/>
+      <c r="O12" s="85" t="n"/>
+      <c r="P12" s="85" t="n"/>
+      <c r="Q12" s="85" t="n"/>
+      <c r="R12" s="85" t="n"/>
+      <c r="S12" s="85" t="n"/>
+      <c r="T12" s="85" t="n"/>
+      <c r="U12" s="85" t="n"/>
+      <c r="V12" s="85" t="n"/>
+      <c r="W12" s="85" t="n"/>
+      <c r="X12" s="85" t="n"/>
+      <c r="Y12" s="85" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1" s="51">
       <c r="A13" s="84" t="inlineStr">
@@ -12330,6 +15773,20 @@
       <c r="I13" s="84" t="n"/>
       <c r="J13" s="84" t="n"/>
       <c r="K13" s="84" t="n"/>
+      <c r="L13" s="84" t="n"/>
+      <c r="M13" s="84" t="n"/>
+      <c r="N13" s="84" t="n"/>
+      <c r="O13" s="84" t="n"/>
+      <c r="P13" s="84" t="n"/>
+      <c r="Q13" s="84" t="n"/>
+      <c r="R13" s="84" t="n"/>
+      <c r="S13" s="84" t="n"/>
+      <c r="T13" s="84" t="n"/>
+      <c r="U13" s="84" t="n"/>
+      <c r="V13" s="84" t="n"/>
+      <c r="W13" s="84" t="n"/>
+      <c r="X13" s="84" t="n"/>
+      <c r="Y13" s="84" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1" s="51">
       <c r="A14" s="85" t="inlineStr">
@@ -12351,6 +15808,20 @@
       <c r="I14" s="85" t="n"/>
       <c r="J14" s="85" t="n"/>
       <c r="K14" s="85" t="n"/>
+      <c r="L14" s="85" t="n"/>
+      <c r="M14" s="85" t="n"/>
+      <c r="N14" s="85" t="n"/>
+      <c r="O14" s="85" t="n"/>
+      <c r="P14" s="85" t="n"/>
+      <c r="Q14" s="85" t="n"/>
+      <c r="R14" s="85" t="n"/>
+      <c r="S14" s="85" t="n"/>
+      <c r="T14" s="85" t="n"/>
+      <c r="U14" s="85" t="n"/>
+      <c r="V14" s="85" t="n"/>
+      <c r="W14" s="85" t="n"/>
+      <c r="X14" s="85" t="n"/>
+      <c r="Y14" s="85" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1" s="51">
       <c r="A15" s="84" t="inlineStr">
@@ -12372,6 +15843,20 @@
       <c r="I15" s="84" t="n"/>
       <c r="J15" s="84" t="n"/>
       <c r="K15" s="84" t="n"/>
+      <c r="L15" s="84" t="n"/>
+      <c r="M15" s="84" t="n"/>
+      <c r="N15" s="84" t="n"/>
+      <c r="O15" s="84" t="n"/>
+      <c r="P15" s="84" t="n"/>
+      <c r="Q15" s="84" t="n"/>
+      <c r="R15" s="84" t="n"/>
+      <c r="S15" s="84" t="n"/>
+      <c r="T15" s="84" t="n"/>
+      <c r="U15" s="84" t="n"/>
+      <c r="V15" s="84" t="n"/>
+      <c r="W15" s="84" t="n"/>
+      <c r="X15" s="84" t="n"/>
+      <c r="Y15" s="84" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1" s="51">
       <c r="A16" s="85" t="inlineStr">
@@ -12393,6 +15878,20 @@
       <c r="I16" s="85" t="n"/>
       <c r="J16" s="85" t="n"/>
       <c r="K16" s="85" t="n"/>
+      <c r="L16" s="85" t="n"/>
+      <c r="M16" s="85" t="n"/>
+      <c r="N16" s="85" t="n"/>
+      <c r="O16" s="85" t="n"/>
+      <c r="P16" s="85" t="n"/>
+      <c r="Q16" s="85" t="n"/>
+      <c r="R16" s="85" t="n"/>
+      <c r="S16" s="85" t="n"/>
+      <c r="T16" s="85" t="n"/>
+      <c r="U16" s="85" t="n"/>
+      <c r="V16" s="85" t="n"/>
+      <c r="W16" s="85" t="n"/>
+      <c r="X16" s="85" t="n"/>
+      <c r="Y16" s="85" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1" s="51">
       <c r="A17" s="84" t="inlineStr">
@@ -12414,6 +15913,20 @@
       <c r="I17" s="84" t="n"/>
       <c r="J17" s="84" t="n"/>
       <c r="K17" s="84" t="n"/>
+      <c r="L17" s="84" t="n"/>
+      <c r="M17" s="84" t="n"/>
+      <c r="N17" s="84" t="n"/>
+      <c r="O17" s="84" t="n"/>
+      <c r="P17" s="84" t="n"/>
+      <c r="Q17" s="84" t="n"/>
+      <c r="R17" s="84" t="n"/>
+      <c r="S17" s="84" t="n"/>
+      <c r="T17" s="84" t="n"/>
+      <c r="U17" s="84" t="n"/>
+      <c r="V17" s="84" t="n"/>
+      <c r="W17" s="84" t="n"/>
+      <c r="X17" s="84" t="n"/>
+      <c r="Y17" s="84" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1" s="51">
       <c r="A18" s="85" t="inlineStr">
@@ -12435,6 +15948,20 @@
       <c r="I18" s="85" t="n"/>
       <c r="J18" s="85" t="n"/>
       <c r="K18" s="85" t="n"/>
+      <c r="L18" s="85" t="n"/>
+      <c r="M18" s="85" t="n"/>
+      <c r="N18" s="85" t="n"/>
+      <c r="O18" s="85" t="n"/>
+      <c r="P18" s="85" t="n"/>
+      <c r="Q18" s="85" t="n"/>
+      <c r="R18" s="85" t="n"/>
+      <c r="S18" s="85" t="n"/>
+      <c r="T18" s="85" t="n"/>
+      <c r="U18" s="85" t="n"/>
+      <c r="V18" s="85" t="n"/>
+      <c r="W18" s="85" t="n"/>
+      <c r="X18" s="85" t="n"/>
+      <c r="Y18" s="85" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1" s="51">
       <c r="A19" s="84" t="inlineStr">
@@ -12456,6 +15983,20 @@
       <c r="I19" s="84" t="n"/>
       <c r="J19" s="84" t="n"/>
       <c r="K19" s="84" t="n"/>
+      <c r="L19" s="84" t="n"/>
+      <c r="M19" s="84" t="n"/>
+      <c r="N19" s="84" t="n"/>
+      <c r="O19" s="84" t="n"/>
+      <c r="P19" s="84" t="n"/>
+      <c r="Q19" s="84" t="n"/>
+      <c r="R19" s="84" t="n"/>
+      <c r="S19" s="84" t="n"/>
+      <c r="T19" s="84" t="n"/>
+      <c r="U19" s="84" t="n"/>
+      <c r="V19" s="84" t="n"/>
+      <c r="W19" s="84" t="n"/>
+      <c r="X19" s="84" t="n"/>
+      <c r="Y19" s="84" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1" s="51">
       <c r="A20" s="85" t="inlineStr">
@@ -12477,6 +16018,20 @@
       <c r="I20" s="85" t="n"/>
       <c r="J20" s="85" t="n"/>
       <c r="K20" s="85" t="n"/>
+      <c r="L20" s="85" t="n"/>
+      <c r="M20" s="85" t="n"/>
+      <c r="N20" s="85" t="n"/>
+      <c r="O20" s="85" t="n"/>
+      <c r="P20" s="85" t="n"/>
+      <c r="Q20" s="85" t="n"/>
+      <c r="R20" s="85" t="n"/>
+      <c r="S20" s="85" t="n"/>
+      <c r="T20" s="85" t="n"/>
+      <c r="U20" s="85" t="n"/>
+      <c r="V20" s="85" t="n"/>
+      <c r="W20" s="85" t="n"/>
+      <c r="X20" s="85" t="n"/>
+      <c r="Y20" s="85" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1" s="51">
       <c r="A21" s="84" t="inlineStr">
@@ -12498,6 +16053,20 @@
       <c r="I21" s="84" t="n"/>
       <c r="J21" s="84" t="n"/>
       <c r="K21" s="84" t="n"/>
+      <c r="L21" s="84" t="n"/>
+      <c r="M21" s="84" t="n"/>
+      <c r="N21" s="84" t="n"/>
+      <c r="O21" s="84" t="n"/>
+      <c r="P21" s="84" t="n"/>
+      <c r="Q21" s="84" t="n"/>
+      <c r="R21" s="84" t="n"/>
+      <c r="S21" s="84" t="n"/>
+      <c r="T21" s="84" t="n"/>
+      <c r="U21" s="84" t="n"/>
+      <c r="V21" s="84" t="n"/>
+      <c r="W21" s="84" t="n"/>
+      <c r="X21" s="84" t="n"/>
+      <c r="Y21" s="84" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1" s="51">
       <c r="A22" s="85" t="inlineStr">
@@ -12519,6 +16088,20 @@
       <c r="I22" s="85" t="n"/>
       <c r="J22" s="85" t="n"/>
       <c r="K22" s="85" t="n"/>
+      <c r="L22" s="85" t="n"/>
+      <c r="M22" s="85" t="n"/>
+      <c r="N22" s="85" t="n"/>
+      <c r="O22" s="85" t="n"/>
+      <c r="P22" s="85" t="n"/>
+      <c r="Q22" s="85" t="n"/>
+      <c r="R22" s="85" t="n"/>
+      <c r="S22" s="85" t="n"/>
+      <c r="T22" s="85" t="n"/>
+      <c r="U22" s="85" t="n"/>
+      <c r="V22" s="85" t="n"/>
+      <c r="W22" s="85" t="n"/>
+      <c r="X22" s="85" t="n"/>
+      <c r="Y22" s="85" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1" s="51">
       <c r="A23" s="84" t="inlineStr">
@@ -12540,6 +16123,20 @@
       <c r="I23" s="84" t="n"/>
       <c r="J23" s="84" t="n"/>
       <c r="K23" s="84" t="n"/>
+      <c r="L23" s="84" t="n"/>
+      <c r="M23" s="84" t="n"/>
+      <c r="N23" s="84" t="n"/>
+      <c r="O23" s="84" t="n"/>
+      <c r="P23" s="84" t="n"/>
+      <c r="Q23" s="84" t="n"/>
+      <c r="R23" s="84" t="n"/>
+      <c r="S23" s="84" t="n"/>
+      <c r="T23" s="84" t="n"/>
+      <c r="U23" s="84" t="n"/>
+      <c r="V23" s="84" t="n"/>
+      <c r="W23" s="84" t="n"/>
+      <c r="X23" s="84" t="n"/>
+      <c r="Y23" s="84" t="n"/>
     </row>
     <row r="24" ht="18" customHeight="1" s="51">
       <c r="A24" s="85" t="inlineStr">
@@ -12561,6 +16158,20 @@
       <c r="I24" s="85" t="n"/>
       <c r="J24" s="85" t="n"/>
       <c r="K24" s="85" t="n"/>
+      <c r="L24" s="85" t="n"/>
+      <c r="M24" s="85" t="n"/>
+      <c r="N24" s="85" t="n"/>
+      <c r="O24" s="85" t="n"/>
+      <c r="P24" s="85" t="n"/>
+      <c r="Q24" s="85" t="n"/>
+      <c r="R24" s="85" t="n"/>
+      <c r="S24" s="85" t="n"/>
+      <c r="T24" s="85" t="n"/>
+      <c r="U24" s="85" t="n"/>
+      <c r="V24" s="85" t="n"/>
+      <c r="W24" s="85" t="n"/>
+      <c r="X24" s="85" t="n"/>
+      <c r="Y24" s="85" t="n"/>
     </row>
     <row r="25" ht="18" customHeight="1" s="51">
       <c r="A25" s="84" t="inlineStr">
@@ -12582,6 +16193,20 @@
       <c r="I25" s="84" t="n"/>
       <c r="J25" s="84" t="n"/>
       <c r="K25" s="84" t="n"/>
+      <c r="L25" s="84" t="n"/>
+      <c r="M25" s="84" t="n"/>
+      <c r="N25" s="84" t="n"/>
+      <c r="O25" s="84" t="n"/>
+      <c r="P25" s="84" t="n"/>
+      <c r="Q25" s="84" t="n"/>
+      <c r="R25" s="84" t="n"/>
+      <c r="S25" s="84" t="n"/>
+      <c r="T25" s="84" t="n"/>
+      <c r="U25" s="84" t="n"/>
+      <c r="V25" s="84" t="n"/>
+      <c r="W25" s="84" t="n"/>
+      <c r="X25" s="84" t="n"/>
+      <c r="Y25" s="84" t="n"/>
     </row>
     <row r="26" ht="18" customHeight="1" s="51">
       <c r="A26" s="85" t="inlineStr">
@@ -12603,6 +16228,20 @@
       <c r="I26" s="85" t="n"/>
       <c r="J26" s="85" t="n"/>
       <c r="K26" s="85" t="n"/>
+      <c r="L26" s="85" t="n"/>
+      <c r="M26" s="85" t="n"/>
+      <c r="N26" s="85" t="n"/>
+      <c r="O26" s="85" t="n"/>
+      <c r="P26" s="85" t="n"/>
+      <c r="Q26" s="85" t="n"/>
+      <c r="R26" s="85" t="n"/>
+      <c r="S26" s="85" t="n"/>
+      <c r="T26" s="85" t="n"/>
+      <c r="U26" s="85" t="n"/>
+      <c r="V26" s="85" t="n"/>
+      <c r="W26" s="85" t="n"/>
+      <c r="X26" s="85" t="n"/>
+      <c r="Y26" s="85" t="n"/>
     </row>
     <row r="27" ht="18" customHeight="1" s="51">
       <c r="A27" s="84" t="inlineStr">
@@ -12624,6 +16263,20 @@
       <c r="I27" s="84" t="n"/>
       <c r="J27" s="84" t="n"/>
       <c r="K27" s="84" t="n"/>
+      <c r="L27" s="84" t="n"/>
+      <c r="M27" s="84" t="n"/>
+      <c r="N27" s="84" t="n"/>
+      <c r="O27" s="84" t="n"/>
+      <c r="P27" s="84" t="n"/>
+      <c r="Q27" s="84" t="n"/>
+      <c r="R27" s="84" t="n"/>
+      <c r="S27" s="84" t="n"/>
+      <c r="T27" s="84" t="n"/>
+      <c r="U27" s="84" t="n"/>
+      <c r="V27" s="84" t="n"/>
+      <c r="W27" s="84" t="n"/>
+      <c r="X27" s="84" t="n"/>
+      <c r="Y27" s="84" t="n"/>
     </row>
     <row r="28" ht="18" customHeight="1" s="51">
       <c r="A28" s="85" t="inlineStr">
@@ -12645,6 +16298,20 @@
       <c r="I28" s="85" t="n"/>
       <c r="J28" s="85" t="n"/>
       <c r="K28" s="85" t="n"/>
+      <c r="L28" s="85" t="n"/>
+      <c r="M28" s="85" t="n"/>
+      <c r="N28" s="85" t="n"/>
+      <c r="O28" s="85" t="n"/>
+      <c r="P28" s="85" t="n"/>
+      <c r="Q28" s="85" t="n"/>
+      <c r="R28" s="85" t="n"/>
+      <c r="S28" s="85" t="n"/>
+      <c r="T28" s="85" t="n"/>
+      <c r="U28" s="85" t="n"/>
+      <c r="V28" s="85" t="n"/>
+      <c r="W28" s="85" t="n"/>
+      <c r="X28" s="85" t="n"/>
+      <c r="Y28" s="85" t="n"/>
     </row>
     <row r="29" ht="18" customHeight="1" s="51">
       <c r="A29" s="84" t="inlineStr">
@@ -12666,6 +16333,20 @@
       <c r="I29" s="84" t="n"/>
       <c r="J29" s="84" t="n"/>
       <c r="K29" s="84" t="n"/>
+      <c r="L29" s="84" t="n"/>
+      <c r="M29" s="84" t="n"/>
+      <c r="N29" s="84" t="n"/>
+      <c r="O29" s="84" t="n"/>
+      <c r="P29" s="84" t="n"/>
+      <c r="Q29" s="84" t="n"/>
+      <c r="R29" s="84" t="n"/>
+      <c r="S29" s="84" t="n"/>
+      <c r="T29" s="84" t="n"/>
+      <c r="U29" s="84" t="n"/>
+      <c r="V29" s="84" t="n"/>
+      <c r="W29" s="84" t="n"/>
+      <c r="X29" s="84" t="n"/>
+      <c r="Y29" s="84" t="n"/>
     </row>
     <row r="30" ht="18" customHeight="1" s="51">
       <c r="A30" s="85" t="inlineStr">
@@ -12687,6 +16368,20 @@
       <c r="I30" s="85" t="n"/>
       <c r="J30" s="85" t="n"/>
       <c r="K30" s="85" t="n"/>
+      <c r="L30" s="85" t="n"/>
+      <c r="M30" s="85" t="n"/>
+      <c r="N30" s="85" t="n"/>
+      <c r="O30" s="85" t="n"/>
+      <c r="P30" s="85" t="n"/>
+      <c r="Q30" s="85" t="n"/>
+      <c r="R30" s="85" t="n"/>
+      <c r="S30" s="85" t="n"/>
+      <c r="T30" s="85" t="n"/>
+      <c r="U30" s="85" t="n"/>
+      <c r="V30" s="85" t="n"/>
+      <c r="W30" s="85" t="n"/>
+      <c r="X30" s="85" t="n"/>
+      <c r="Y30" s="85" t="n"/>
     </row>
     <row r="31" ht="18" customHeight="1" s="51">
       <c r="A31" s="84" t="inlineStr">
@@ -12708,6 +16403,20 @@
       <c r="I31" s="84" t="n"/>
       <c r="J31" s="84" t="n"/>
       <c r="K31" s="84" t="n"/>
+      <c r="L31" s="84" t="n"/>
+      <c r="M31" s="84" t="n"/>
+      <c r="N31" s="84" t="n"/>
+      <c r="O31" s="84" t="n"/>
+      <c r="P31" s="84" t="n"/>
+      <c r="Q31" s="84" t="n"/>
+      <c r="R31" s="84" t="n"/>
+      <c r="S31" s="84" t="n"/>
+      <c r="T31" s="84" t="n"/>
+      <c r="U31" s="84" t="n"/>
+      <c r="V31" s="84" t="n"/>
+      <c r="W31" s="84" t="n"/>
+      <c r="X31" s="84" t="n"/>
+      <c r="Y31" s="84" t="n"/>
     </row>
     <row r="32" ht="18" customHeight="1" s="51">
       <c r="A32" s="85" t="inlineStr">
@@ -12729,6 +16438,20 @@
       <c r="I32" s="85" t="n"/>
       <c r="J32" s="85" t="n"/>
       <c r="K32" s="85" t="n"/>
+      <c r="L32" s="85" t="n"/>
+      <c r="M32" s="85" t="n"/>
+      <c r="N32" s="85" t="n"/>
+      <c r="O32" s="85" t="n"/>
+      <c r="P32" s="85" t="n"/>
+      <c r="Q32" s="85" t="n"/>
+      <c r="R32" s="85" t="n"/>
+      <c r="S32" s="85" t="n"/>
+      <c r="T32" s="85" t="n"/>
+      <c r="U32" s="85" t="n"/>
+      <c r="V32" s="85" t="n"/>
+      <c r="W32" s="85" t="n"/>
+      <c r="X32" s="85" t="n"/>
+      <c r="Y32" s="85" t="n"/>
     </row>
     <row r="33" ht="18" customHeight="1" s="51">
       <c r="A33" s="84" t="inlineStr">
@@ -12750,6 +16473,20 @@
       <c r="I33" s="84" t="n"/>
       <c r="J33" s="84" t="n"/>
       <c r="K33" s="84" t="n"/>
+      <c r="L33" s="84" t="n"/>
+      <c r="M33" s="84" t="n"/>
+      <c r="N33" s="84" t="n"/>
+      <c r="O33" s="84" t="n"/>
+      <c r="P33" s="84" t="n"/>
+      <c r="Q33" s="84" t="n"/>
+      <c r="R33" s="84" t="n"/>
+      <c r="S33" s="84" t="n"/>
+      <c r="T33" s="84" t="n"/>
+      <c r="U33" s="84" t="n"/>
+      <c r="V33" s="84" t="n"/>
+      <c r="W33" s="84" t="n"/>
+      <c r="X33" s="84" t="n"/>
+      <c r="Y33" s="84" t="n"/>
     </row>
     <row r="34" ht="18" customHeight="1" s="51">
       <c r="A34" s="85" t="inlineStr">
@@ -12757,7 +16494,11 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="B34" s="85" t="n"/>
+      <c r="B34" s="85" t="inlineStr">
+        <is>
+          <t>Sabrina</t>
+        </is>
+      </c>
       <c r="C34" s="85" t="n"/>
       <c r="D34" s="85" t="n"/>
       <c r="E34" s="85" t="n"/>
@@ -12767,6 +16508,20 @@
       <c r="I34" s="85" t="n"/>
       <c r="J34" s="85" t="n"/>
       <c r="K34" s="85" t="n"/>
+      <c r="L34" s="85" t="n"/>
+      <c r="M34" s="85" t="n"/>
+      <c r="N34" s="85" t="n"/>
+      <c r="O34" s="85" t="n"/>
+      <c r="P34" s="85" t="n"/>
+      <c r="Q34" s="85" t="n"/>
+      <c r="R34" s="85" t="n"/>
+      <c r="S34" s="85" t="n"/>
+      <c r="T34" s="85" t="n"/>
+      <c r="U34" s="85" t="n"/>
+      <c r="V34" s="85" t="n"/>
+      <c r="W34" s="85" t="n"/>
+      <c r="X34" s="85" t="n"/>
+      <c r="Y34" s="85" t="n"/>
     </row>
     <row r="35" ht="20" customHeight="1" s="51">
       <c r="A35" s="83" t="inlineStr">
@@ -12781,16 +16536,34 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="B36" s="86" t="n"/>
-      <c r="C36" s="86" t="n"/>
-      <c r="D36" s="86" t="n"/>
-      <c r="E36" s="86" t="n"/>
-      <c r="F36" s="86" t="n"/>
-      <c r="G36" s="86" t="n"/>
-      <c r="H36" s="86" t="n"/>
-      <c r="I36" s="86" t="n"/>
-      <c r="J36" s="86" t="n"/>
-      <c r="K36" s="87" t="n"/>
+      <c r="B36" s="84" t="inlineStr">
+        <is>
+          <t>Sheila</t>
+        </is>
+      </c>
+      <c r="C36" s="84" t="n"/>
+      <c r="D36" s="84" t="n"/>
+      <c r="E36" s="84" t="n"/>
+      <c r="F36" s="84" t="n"/>
+      <c r="G36" s="84" t="n"/>
+      <c r="H36" s="84" t="n"/>
+      <c r="I36" s="84" t="n"/>
+      <c r="J36" s="84" t="n"/>
+      <c r="K36" s="84" t="n"/>
+      <c r="L36" s="84" t="n"/>
+      <c r="M36" s="84" t="n"/>
+      <c r="N36" s="84" t="n"/>
+      <c r="O36" s="84" t="n"/>
+      <c r="P36" s="84" t="n"/>
+      <c r="Q36" s="84" t="n"/>
+      <c r="R36" s="84" t="n"/>
+      <c r="S36" s="84" t="n"/>
+      <c r="T36" s="84" t="n"/>
+      <c r="U36" s="84" t="n"/>
+      <c r="V36" s="84" t="n"/>
+      <c r="W36" s="84" t="n"/>
+      <c r="X36" s="84" t="n"/>
+      <c r="Y36" s="84" t="n"/>
     </row>
     <row r="37" ht="18" customHeight="1" s="51">
       <c r="A37" s="85" t="inlineStr">
@@ -12812,6 +16585,20 @@
       <c r="I37" s="85" t="n"/>
       <c r="J37" s="85" t="n"/>
       <c r="K37" s="85" t="n"/>
+      <c r="L37" s="85" t="n"/>
+      <c r="M37" s="85" t="n"/>
+      <c r="N37" s="85" t="n"/>
+      <c r="O37" s="85" t="n"/>
+      <c r="P37" s="85" t="n"/>
+      <c r="Q37" s="85" t="n"/>
+      <c r="R37" s="85" t="n"/>
+      <c r="S37" s="85" t="n"/>
+      <c r="T37" s="85" t="n"/>
+      <c r="U37" s="85" t="n"/>
+      <c r="V37" s="85" t="n"/>
+      <c r="W37" s="85" t="n"/>
+      <c r="X37" s="85" t="n"/>
+      <c r="Y37" s="85" t="n"/>
     </row>
     <row r="38" ht="18" customHeight="1" s="51">
       <c r="A38" s="84" t="inlineStr">
@@ -12833,6 +16620,20 @@
       <c r="I38" s="84" t="n"/>
       <c r="J38" s="84" t="n"/>
       <c r="K38" s="84" t="n"/>
+      <c r="L38" s="84" t="n"/>
+      <c r="M38" s="84" t="n"/>
+      <c r="N38" s="84" t="n"/>
+      <c r="O38" s="84" t="n"/>
+      <c r="P38" s="84" t="n"/>
+      <c r="Q38" s="84" t="n"/>
+      <c r="R38" s="84" t="n"/>
+      <c r="S38" s="84" t="n"/>
+      <c r="T38" s="84" t="n"/>
+      <c r="U38" s="84" t="n"/>
+      <c r="V38" s="84" t="n"/>
+      <c r="W38" s="84" t="n"/>
+      <c r="X38" s="84" t="n"/>
+      <c r="Y38" s="84" t="n"/>
     </row>
     <row r="39" ht="18" customHeight="1" s="51">
       <c r="A39" s="85" t="inlineStr">
@@ -12854,6 +16655,20 @@
       <c r="I39" s="85" t="n"/>
       <c r="J39" s="85" t="n"/>
       <c r="K39" s="85" t="n"/>
+      <c r="L39" s="85" t="n"/>
+      <c r="M39" s="85" t="n"/>
+      <c r="N39" s="85" t="n"/>
+      <c r="O39" s="85" t="n"/>
+      <c r="P39" s="85" t="n"/>
+      <c r="Q39" s="85" t="n"/>
+      <c r="R39" s="85" t="n"/>
+      <c r="S39" s="85" t="n"/>
+      <c r="T39" s="85" t="n"/>
+      <c r="U39" s="85" t="n"/>
+      <c r="V39" s="85" t="n"/>
+      <c r="W39" s="85" t="n"/>
+      <c r="X39" s="85" t="n"/>
+      <c r="Y39" s="85" t="n"/>
     </row>
     <row r="40" ht="18" customHeight="1" s="51">
       <c r="A40" s="84" t="inlineStr">
@@ -12875,6 +16690,20 @@
       <c r="I40" s="84" t="n"/>
       <c r="J40" s="84" t="n"/>
       <c r="K40" s="84" t="n"/>
+      <c r="L40" s="84" t="n"/>
+      <c r="M40" s="84" t="n"/>
+      <c r="N40" s="84" t="n"/>
+      <c r="O40" s="84" t="n"/>
+      <c r="P40" s="84" t="n"/>
+      <c r="Q40" s="84" t="n"/>
+      <c r="R40" s="84" t="n"/>
+      <c r="S40" s="84" t="n"/>
+      <c r="T40" s="84" t="n"/>
+      <c r="U40" s="84" t="n"/>
+      <c r="V40" s="84" t="n"/>
+      <c r="W40" s="84" t="n"/>
+      <c r="X40" s="84" t="n"/>
+      <c r="Y40" s="84" t="n"/>
     </row>
     <row r="41" ht="18" customHeight="1" s="51">
       <c r="A41" s="85" t="inlineStr">
@@ -12896,6 +16725,20 @@
       <c r="I41" s="85" t="n"/>
       <c r="J41" s="85" t="n"/>
       <c r="K41" s="85" t="n"/>
+      <c r="L41" s="85" t="n"/>
+      <c r="M41" s="85" t="n"/>
+      <c r="N41" s="85" t="n"/>
+      <c r="O41" s="85" t="n"/>
+      <c r="P41" s="85" t="n"/>
+      <c r="Q41" s="85" t="n"/>
+      <c r="R41" s="85" t="n"/>
+      <c r="S41" s="85" t="n"/>
+      <c r="T41" s="85" t="n"/>
+      <c r="U41" s="85" t="n"/>
+      <c r="V41" s="85" t="n"/>
+      <c r="W41" s="85" t="n"/>
+      <c r="X41" s="85" t="n"/>
+      <c r="Y41" s="85" t="n"/>
     </row>
     <row r="42" ht="18" customHeight="1" s="51">
       <c r="A42" s="84" t="inlineStr">
@@ -12917,6 +16760,20 @@
       <c r="I42" s="84" t="n"/>
       <c r="J42" s="84" t="n"/>
       <c r="K42" s="84" t="n"/>
+      <c r="L42" s="84" t="n"/>
+      <c r="M42" s="84" t="n"/>
+      <c r="N42" s="84" t="n"/>
+      <c r="O42" s="84" t="n"/>
+      <c r="P42" s="84" t="n"/>
+      <c r="Q42" s="84" t="n"/>
+      <c r="R42" s="84" t="n"/>
+      <c r="S42" s="84" t="n"/>
+      <c r="T42" s="84" t="n"/>
+      <c r="U42" s="84" t="n"/>
+      <c r="V42" s="84" t="n"/>
+      <c r="W42" s="84" t="n"/>
+      <c r="X42" s="84" t="n"/>
+      <c r="Y42" s="84" t="n"/>
     </row>
     <row r="43" ht="18" customHeight="1" s="51">
       <c r="A43" s="85" t="inlineStr">
@@ -12938,6 +16795,20 @@
       <c r="I43" s="85" t="n"/>
       <c r="J43" s="85" t="n"/>
       <c r="K43" s="85" t="n"/>
+      <c r="L43" s="85" t="n"/>
+      <c r="M43" s="85" t="n"/>
+      <c r="N43" s="85" t="n"/>
+      <c r="O43" s="85" t="n"/>
+      <c r="P43" s="85" t="n"/>
+      <c r="Q43" s="85" t="n"/>
+      <c r="R43" s="85" t="n"/>
+      <c r="S43" s="85" t="n"/>
+      <c r="T43" s="85" t="n"/>
+      <c r="U43" s="85" t="n"/>
+      <c r="V43" s="85" t="n"/>
+      <c r="W43" s="85" t="n"/>
+      <c r="X43" s="85" t="n"/>
+      <c r="Y43" s="85" t="n"/>
     </row>
     <row r="44" ht="18" customHeight="1" s="51">
       <c r="A44" s="84" t="inlineStr">
@@ -12959,6 +16830,20 @@
       <c r="I44" s="84" t="n"/>
       <c r="J44" s="84" t="n"/>
       <c r="K44" s="84" t="n"/>
+      <c r="L44" s="84" t="n"/>
+      <c r="M44" s="84" t="n"/>
+      <c r="N44" s="84" t="n"/>
+      <c r="O44" s="84" t="n"/>
+      <c r="P44" s="84" t="n"/>
+      <c r="Q44" s="84" t="n"/>
+      <c r="R44" s="84" t="n"/>
+      <c r="S44" s="84" t="n"/>
+      <c r="T44" s="84" t="n"/>
+      <c r="U44" s="84" t="n"/>
+      <c r="V44" s="84" t="n"/>
+      <c r="W44" s="84" t="n"/>
+      <c r="X44" s="84" t="n"/>
+      <c r="Y44" s="84" t="n"/>
     </row>
     <row r="45" ht="18" customHeight="1" s="51">
       <c r="A45" s="85" t="inlineStr">
@@ -12980,6 +16865,20 @@
       <c r="I45" s="85" t="n"/>
       <c r="J45" s="85" t="n"/>
       <c r="K45" s="85" t="n"/>
+      <c r="L45" s="85" t="n"/>
+      <c r="M45" s="85" t="n"/>
+      <c r="N45" s="85" t="n"/>
+      <c r="O45" s="85" t="n"/>
+      <c r="P45" s="85" t="n"/>
+      <c r="Q45" s="85" t="n"/>
+      <c r="R45" s="85" t="n"/>
+      <c r="S45" s="85" t="n"/>
+      <c r="T45" s="85" t="n"/>
+      <c r="U45" s="85" t="n"/>
+      <c r="V45" s="85" t="n"/>
+      <c r="W45" s="85" t="n"/>
+      <c r="X45" s="85" t="n"/>
+      <c r="Y45" s="85" t="n"/>
     </row>
     <row r="46" ht="18" customHeight="1" s="51">
       <c r="A46" s="84" t="inlineStr">
@@ -13001,6 +16900,20 @@
       <c r="I46" s="84" t="n"/>
       <c r="J46" s="84" t="n"/>
       <c r="K46" s="84" t="n"/>
+      <c r="L46" s="84" t="n"/>
+      <c r="M46" s="84" t="n"/>
+      <c r="N46" s="84" t="n"/>
+      <c r="O46" s="84" t="n"/>
+      <c r="P46" s="84" t="n"/>
+      <c r="Q46" s="84" t="n"/>
+      <c r="R46" s="84" t="n"/>
+      <c r="S46" s="84" t="n"/>
+      <c r="T46" s="84" t="n"/>
+      <c r="U46" s="84" t="n"/>
+      <c r="V46" s="84" t="n"/>
+      <c r="W46" s="84" t="n"/>
+      <c r="X46" s="84" t="n"/>
+      <c r="Y46" s="84" t="n"/>
     </row>
     <row r="47" ht="18" customHeight="1" s="51">
       <c r="A47" s="85" t="inlineStr">
@@ -13022,6 +16935,20 @@
       <c r="I47" s="85" t="n"/>
       <c r="J47" s="85" t="n"/>
       <c r="K47" s="85" t="n"/>
+      <c r="L47" s="85" t="n"/>
+      <c r="M47" s="85" t="n"/>
+      <c r="N47" s="85" t="n"/>
+      <c r="O47" s="85" t="n"/>
+      <c r="P47" s="85" t="n"/>
+      <c r="Q47" s="85" t="n"/>
+      <c r="R47" s="85" t="n"/>
+      <c r="S47" s="85" t="n"/>
+      <c r="T47" s="85" t="n"/>
+      <c r="U47" s="85" t="n"/>
+      <c r="V47" s="85" t="n"/>
+      <c r="W47" s="85" t="n"/>
+      <c r="X47" s="85" t="n"/>
+      <c r="Y47" s="85" t="n"/>
     </row>
     <row r="48" ht="18" customHeight="1" s="51">
       <c r="A48" s="84" t="inlineStr">
@@ -13043,6 +16970,20 @@
       <c r="I48" s="84" t="n"/>
       <c r="J48" s="84" t="n"/>
       <c r="K48" s="84" t="n"/>
+      <c r="L48" s="84" t="n"/>
+      <c r="M48" s="84" t="n"/>
+      <c r="N48" s="84" t="n"/>
+      <c r="O48" s="84" t="n"/>
+      <c r="P48" s="84" t="n"/>
+      <c r="Q48" s="84" t="n"/>
+      <c r="R48" s="84" t="n"/>
+      <c r="S48" s="84" t="n"/>
+      <c r="T48" s="84" t="n"/>
+      <c r="U48" s="84" t="n"/>
+      <c r="V48" s="84" t="n"/>
+      <c r="W48" s="84" t="n"/>
+      <c r="X48" s="84" t="n"/>
+      <c r="Y48" s="84" t="n"/>
     </row>
     <row r="49" ht="18" customHeight="1" s="51">
       <c r="A49" s="85" t="inlineStr">
@@ -13064,6 +17005,20 @@
       <c r="I49" s="85" t="n"/>
       <c r="J49" s="85" t="n"/>
       <c r="K49" s="85" t="n"/>
+      <c r="L49" s="85" t="n"/>
+      <c r="M49" s="85" t="n"/>
+      <c r="N49" s="85" t="n"/>
+      <c r="O49" s="85" t="n"/>
+      <c r="P49" s="85" t="n"/>
+      <c r="Q49" s="85" t="n"/>
+      <c r="R49" s="85" t="n"/>
+      <c r="S49" s="85" t="n"/>
+      <c r="T49" s="85" t="n"/>
+      <c r="U49" s="85" t="n"/>
+      <c r="V49" s="85" t="n"/>
+      <c r="W49" s="85" t="n"/>
+      <c r="X49" s="85" t="n"/>
+      <c r="Y49" s="85" t="n"/>
     </row>
     <row r="50" ht="18" customHeight="1" s="51">
       <c r="A50" s="84" t="inlineStr">
@@ -13085,6 +17040,20 @@
       <c r="I50" s="84" t="n"/>
       <c r="J50" s="84" t="n"/>
       <c r="K50" s="84" t="n"/>
+      <c r="L50" s="84" t="n"/>
+      <c r="M50" s="84" t="n"/>
+      <c r="N50" s="84" t="n"/>
+      <c r="O50" s="84" t="n"/>
+      <c r="P50" s="84" t="n"/>
+      <c r="Q50" s="84" t="n"/>
+      <c r="R50" s="84" t="n"/>
+      <c r="S50" s="84" t="n"/>
+      <c r="T50" s="84" t="n"/>
+      <c r="U50" s="84" t="n"/>
+      <c r="V50" s="84" t="n"/>
+      <c r="W50" s="84" t="n"/>
+      <c r="X50" s="84" t="n"/>
+      <c r="Y50" s="84" t="n"/>
     </row>
     <row r="51" ht="18" customHeight="1" s="51">
       <c r="A51" s="85" t="inlineStr">
@@ -13106,95 +17075,173 @@
       <c r="I51" s="85" t="n"/>
       <c r="J51" s="85" t="n"/>
       <c r="K51" s="85" t="n"/>
+      <c r="L51" s="85" t="n"/>
+      <c r="M51" s="85" t="n"/>
+      <c r="N51" s="85" t="n"/>
+      <c r="O51" s="85" t="n"/>
+      <c r="P51" s="85" t="n"/>
+      <c r="Q51" s="85" t="n"/>
+      <c r="R51" s="85" t="n"/>
+      <c r="S51" s="85" t="n"/>
+      <c r="T51" s="85" t="n"/>
+      <c r="U51" s="85" t="n"/>
+      <c r="V51" s="85" t="n"/>
+      <c r="W51" s="85" t="n"/>
+      <c r="X51" s="85" t="n"/>
+      <c r="Y51" s="85" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="84" t="inlineStr">
-        <is>
-          <t>Dropdown values: Acquire | Deepen | Create | ? (unscorable/blank)</t>
-        </is>
-      </c>
-      <c r="B53" s="86" t="n"/>
-      <c r="C53" s="86" t="n"/>
-      <c r="D53" s="86" t="n"/>
-      <c r="E53" s="86" t="n"/>
-      <c r="F53" s="86" t="n"/>
-      <c r="G53" s="86" t="n"/>
-      <c r="H53" s="86" t="n"/>
-      <c r="I53" s="86" t="n"/>
-      <c r="J53" s="86" t="n"/>
-      <c r="K53" s="87" t="n"/>
-    </row>
-    <row r="54" ht="40" customHeight="1" s="51">
-      <c r="A54" s="85" t="inlineStr">
+      <c r="A53" s="92" t="inlineStr">
         <is>
           <t>Task descriptions:</t>
         </is>
       </c>
-      <c r="B54" s="85" t="n"/>
-      <c r="C54" s="90" t="inlineStr">
-        <is>
-          <t>Can explain DT
-Q4 (yes/no): Can you explain how a decision tree works? Score as Acquire if 'Yes'</t>
-        </is>
-      </c>
-      <c r="D54" s="90" t="inlineStr">
-        <is>
-          <t>Classify strawberry
-Uses the given decision tree to classify strawberries correctly</t>
-        </is>
-      </c>
-      <c r="E54" s="90" t="inlineStr">
-        <is>
-          <t>Decision rule
-Writes correct decision rule for strawberry classification (blank: ___ because ___)</t>
-        </is>
-      </c>
-      <c r="F54" s="90" t="inlineStr">
-        <is>
-          <t>What is data
-Open-ended (6 lines) — explains what data is and why we need it</t>
-        </is>
-      </c>
-      <c r="G54" s="90" t="inlineStr">
-        <is>
-          <t>DT capabilities
-Multi-select T/F table — marks correct statements about what DTs can do</t>
-        </is>
-      </c>
-      <c r="H54" s="90" t="inlineStr">
-        <is>
-          <t>Step ordering
-Orders the 4 steps for building a decision rule correctly (1-4)</t>
-        </is>
-      </c>
-      <c r="I54" s="90" t="inlineStr">
-        <is>
-          <t>Why is DT AI
-Multi-select T/F table — marks correct reasons why a DT is considered AI</t>
-        </is>
-      </c>
-      <c r="J54" s="85" t="inlineStr">
-        <is>
-          <t>Overall AI-CFT level for WS11 as a whole</t>
-        </is>
-      </c>
-      <c r="K54" s="85" t="inlineStr">
-        <is>
-          <t>Free notes (Q1-Q3 and Q5-Q7 are Likert/demographic, not scored here)</t>
+    </row>
+    <row r="54" ht="60" customHeight="1" s="51">
+      <c r="C54" s="93" t="inlineStr">
+        <is>
+          <t>Q4 – Can explain DT
+Yes/No: Can student explain how a decision tree works?</t>
+        </is>
+      </c>
+      <c r="D54" s="93" t="inlineStr">
+        <is>
+          <t>Q8a – Classify strawberry
+Apply the given decision tree to classify the strawberry card: 'recommended' or 'not recommended'</t>
+        </is>
+      </c>
+      <c r="E54" s="93" t="inlineStr">
+        <is>
+          <t>Q8b – Decision rule sentence
+Complete: 'Strawberry is classified as ___ because ___' — formulate the decision rule</t>
+        </is>
+      </c>
+      <c r="F54" s="93" t="inlineStr">
+        <is>
+          <t>Q9 – What is data?
+Open-ended (6 lines): explain what data is and why we need it</t>
+        </is>
+      </c>
+      <c r="G54" s="93" t="inlineStr">
+        <is>
+          <t>Q10a – DT statement 1
+True/False: DT statement a — what can a decision tree do?</t>
+        </is>
+      </c>
+      <c r="H54" s="93" t="inlineStr">
+        <is>
+          <t>Q10b – DT statement 2
+True/False: DT statement b</t>
+        </is>
+      </c>
+      <c r="I54" s="93" t="inlineStr">
+        <is>
+          <t>Q10c – DT statement 3
+True/False: DT statement c</t>
+        </is>
+      </c>
+      <c r="J54" s="93" t="inlineStr">
+        <is>
+          <t>Q10d – DT statement 4
+True/False: DT statement d</t>
+        </is>
+      </c>
+      <c r="K54" s="93" t="inlineStr">
+        <is>
+          <t>Q10e – DT statement 5
+True/False: DT statement e</t>
+        </is>
+      </c>
+      <c r="L54" s="93" t="inlineStr">
+        <is>
+          <t>Q10f – DT statement 6
+True/False: DT statement f</t>
+        </is>
+      </c>
+      <c r="M54" s="93" t="inlineStr">
+        <is>
+          <t>Q10g – DT statement 7
+True/False: DT statement g</t>
+        </is>
+      </c>
+      <c r="N54" s="93" t="inlineStr">
+        <is>
+          <t>Q10h – DT statement 8
+True/False: DT statement h</t>
+        </is>
+      </c>
+      <c r="O54" s="93" t="inlineStr">
+        <is>
+          <t>Q11a – Step order 1
+Rank step 1 in correct order for building a decision rule (1–4)</t>
+        </is>
+      </c>
+      <c r="P54" s="93" t="inlineStr">
+        <is>
+          <t>Q11b – Step order 2
+Rank step 2 in correct order (1–4)</t>
+        </is>
+      </c>
+      <c r="Q54" s="93" t="inlineStr">
+        <is>
+          <t>Q11c – Step order 3
+Rank step 3 in correct order (1–4)</t>
+        </is>
+      </c>
+      <c r="R54" s="93" t="inlineStr">
+        <is>
+          <t>Q11d – Step order 4
+Rank step 4 in correct order (1–4)</t>
+        </is>
+      </c>
+      <c r="S54" s="93" t="inlineStr">
+        <is>
+          <t>Q12a – AI statement 1
+True/False: Why is a DT considered AI? — statement a</t>
+        </is>
+      </c>
+      <c r="T54" s="93" t="inlineStr">
+        <is>
+          <t>Q12b – AI statement 2
+True/False: AI statement b</t>
+        </is>
+      </c>
+      <c r="U54" s="93" t="inlineStr">
+        <is>
+          <t>Q12c – AI statement 3
+True/False: AI statement c</t>
+        </is>
+      </c>
+      <c r="V54" s="93" t="inlineStr">
+        <is>
+          <t>Q12d – AI statement 4
+True/False: AI statement d</t>
+        </is>
+      </c>
+      <c r="W54" s="93" t="inlineStr">
+        <is>
+          <t>Q12e – AI statement 5
+True/False: AI statement e</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="9">
     <mergeCell ref="A53:K53"/>
     <mergeCell ref="A35:K35"/>
     <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A1:Y1"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A36:K36"/>
+    <mergeCell ref="A35:Y35"/>
+    <mergeCell ref="A4:Y4"/>
     <mergeCell ref="A5:K5"/>
   </mergeCells>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation sqref="C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 C17 C18 C19 C20 C21 C22 C23 C24 C25 C26 C27 C28 C29 C30 C31 C32 C33 C34 C36 C37 C38 C39 C40 C41 C42 C43 C44 C45 C46 C47 C48 C49 C50 C51 D5 D6 D7 D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19 D20 D21 D22 D23 D24 D25 D26 D27 D28 D29 D30 D31 D32 D33 D34 D36 D37 D38 D39 D40 D41 D42 D43 D44 D45 D46 D47 D48 D49 D50 D51 E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E24 E25 E26 E27 E28 E29 E30 E31 E32 E33 E34 E36 E37 E38 E39 E40 E41 E42 E43 E44 E45 E46 E47 E48 E49 E50 E51 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34 F36 F37 F38 F39 F40 F41 F42 F43 F44 F45 F46 F47 F48 F49 F50 F51 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 G31 G32 G33 G34 G36 G37 G38 G39 G40 G41 G42 G43 G44 G45 G46 G47 G48 G49 G50 G51 H5 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27 H28 H29 H30 H31 H32 H33 H34 H36 H37 H38 H39 H40 H41 H42 H43 H44 H45 H46 H47 H48 H49 H50 H51 I5 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I24 I25 I26 I27 I28 I29 I30 I31 I32 I33 I34 I36 I37 I38 I39 I40 I41 I42 I43 I44 I45 I46 I47 I48 I49 I50 I51 J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25 J26 J27 J28 J29 J30 J31 J32 J33 J34 J36 J37 J38 J39 J40 J41 J42 J43 J44 J45 J46 J47 J48 J49 J50 J51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Choose: Acquire, Deepen, Create, or ?" promptTitle="Select level" prompt="AI-CFT level" type="list">
+      <formula1>"Acquire,Deepen,Create,?"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 C17 C18 C19 C20 C21 C22 C23 C24 C25 C26 C27 C28 C29 C30 C31 C32 C33 C34 C36 C37 C38 C39 C40 C41 C42 C43 C44 C45 C46 C47 C48 C49 C50 C51 D5 D6 D7 D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19 D20 D21 D22 D23 D24 D25 D26 D27 D28 D29 D30 D31 D32 D33 D34 D36 D37 D38 D39 D40 D41 D42 D43 D44 D45 D46 D47 D48 D49 D50 D51 E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E24 E25 E26 E27 E28 E29 E30 E31 E32 E33 E34 E36 E37 E38 E39 E40 E41 E42 E43 E44 E45 E46 E47 E48 E49 E50 E51 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34 F36 F37 F38 F39 F40 F41 F42 F43 F44 F45 F46 F47 F48 F49 F50 F51 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 G31 G32 G33 G34 G36 G37 G38 G39 G40 G41 G42 G43 G44 G45 G46 G47 G48 G49 G50 G51 H5 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27 H28 H29 H30 H31 H32 H33 H34 H36 H37 H38 H39 H40 H41 H42 H43 H44 H45 H46 H47 H48 H49 H50 H51 I5 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I24 I25 I26 I27 I28 I29 I30 I31 I32 I33 I34 I36 I37 I38 I39 I40 I41 I42 I43 I44 I45 I46 I47 I48 I49 I50 I51 J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25 J26 J27 J28 J29 J30 J31 J32 J33 J34 J36 J37 J38 J39 J40 J41 J42 J43 J44 J45 J46 J47 J48 J49 J50 J51 K5 K6 K7 K8 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 K19 K20 K21 K22 K23 K24 K25 K26 K27 K28 K29 K30 K31 K32 K33 K34 K36 K37 K38 K39 K40 K41 K42 K43 K44 K45 K46 K47 K48 K49 K50 K51 L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26 L27 L28 L29 L30 L31 L32 L33 L34 L36 L37 L38 L39 L40 L41 L42 L43 L44 L45 L46 L47 L48 L49 L50 L51 M5 M6 M7 M8 M9 M10 M11 M12 M13 M14 M15 M16 M17 M18 M19 M20 M21 M22 M23 M24 M25 M26 M27 M28 M29 M30 M31 M32 M33 M34 M36 M37 M38 M39 M40 M41 M42 M43 M44 M45 M46 M47 M48 M49 M50 M51 N5 N6 N7 N8 N9 N10 N11 N12 N13 N14 N15 N16 N17 N18 N19 N20 N21 N22 N23 N24 N25 N26 N27 N28 N29 N30 N31 N32 N33 N34 N36 N37 N38 N39 N40 N41 N42 N43 N44 N45 N46 N47 N48 N49 N50 N51 O5 O6 O7 O8 O9 O10 O11 O12 O13 O14 O15 O16 O17 O18 O19 O20 O21 O22 O23 O24 O25 O26 O27 O28 O29 O30 O31 O32 O33 O34 O36 O37 O38 O39 O40 O41 O42 O43 O44 O45 O46 O47 O48 O49 O50 O51 P5 P6 P7 P8 P9 P10 P11 P12 P13 P14 P15 P16 P17 P18 P19 P20 P21 P22 P23 P24 P25 P26 P27 P28 P29 P30 P31 P32 P33 P34 P36 P37 P38 P39 P40 P41 P42 P43 P44 P45 P46 P47 P48 P49 P50 P51 Q5 Q6 Q7 Q8 Q9 Q10 Q11 Q12 Q13 Q14 Q15 Q16 Q17 Q18 Q19 Q20 Q21 Q22 Q23 Q24 Q25 Q26 Q27 Q28 Q29 Q30 Q31 Q32 Q33 Q34 Q36 Q37 Q38 Q39 Q40 Q41 Q42 Q43 Q44 Q45 Q46 Q47 Q48 Q49 Q50 Q51 R5 R6 R7 R8 R9 R10 R11 R12 R13 R14 R15 R16 R17 R18 R19 R20 R21 R22 R23 R24 R25 R26 R27 R28 R29 R30 R31 R32 R33 R34 R36 R37 R38 R39 R40 R41 R42 R43 R44 R45 R46 R47 R48 R49 R50 R51 S5 S6 S7 S8 S9 S10 S11 S12 S13 S14 S15 S16 S17 S18 S19 S20 S21 S22 S23 S24 S25 S26 S27 S28 S29 S30 S31 S32 S33 S34 S36 S37 S38 S39 S40 S41 S42 S43 S44 S45 S46 S47 S48 S49 S50 S51 T5 T6 T7 T8 T9 T10 T11 T12 T13 T14 T15 T16 T17 T18 T19 T20 T21 T22 T23 T24 T25 T26 T27 T28 T29 T30 T31 T32 T33 T34 T36 T37 T38 T39 T40 T41 T42 T43 T44 T45 T46 T47 T48 T49 T50 T51 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U36 U37 U38 U39 U40 U41 U42 U43 U44 U45 U46 U47 U48 U49 U50 U51 V5 V6 V7 V8 V9 V10 V11 V12 V13 V14 V15 V16 V17 V18 V19 V20 V21 V22 V23 V24 V25 V26 V27 V28 V29 V30 V31 V32 V33 V34 V36 V37 V38 V39 V40 V41 V42 V43 V44 V45 V46 V47 V48 V49 V50 V51 W5 W6 W7 W8 W9 W10 W11 W12 W13 W14 W15 W16 W17 W18 W19 W20 W21 W22 W23 W24 W25 W26 W27 W28 W29 W30 W31 W32 W33 W34 W36 W37 W38 W39 W40 W41 W42 W43 W44 W45 W46 W47 W48 W49 W50 W51 X5 X6 X7 X8 X9 X10 X11 X12 X13 X14 X15 X16 X17 X18 X19 X20 X21 X22 X23 X24 X25 X26 X27 X28 X29 X30 X31 X32 X33 X34 X36 X37 X38 X39 X40 X41 X42 X43 X44 X45 X46 X47 X48 X49 X50 X51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Acquire,Deepen,Create,?"</formula1>
     </dataValidation>
   </dataValidations>

--- a/AI_CFT_Labeling.xlsx
+++ b/AI_CFT_Labeling.xlsx
@@ -434,7 +434,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -685,6 +685,9 @@
     <xf numFmtId="0" fontId="25" fillId="23" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1768,37 +1771,33 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="B5" s="84" t="inlineStr">
-        <is>
-          <t>Ozzy</t>
-        </is>
-      </c>
-      <c r="C5" s="84" t="n"/>
-      <c r="D5" s="84" t="n"/>
-      <c r="E5" s="84" t="n"/>
-      <c r="F5" s="84" t="n"/>
-      <c r="G5" s="84" t="n"/>
-      <c r="H5" s="84" t="n"/>
-      <c r="I5" s="84" t="n"/>
-      <c r="J5" s="84" t="n"/>
-      <c r="K5" s="84" t="n"/>
-      <c r="L5" s="84" t="n"/>
-      <c r="M5" s="84" t="n"/>
-      <c r="N5" s="84" t="n"/>
-      <c r="O5" s="84" t="n"/>
-      <c r="P5" s="84" t="n"/>
-      <c r="Q5" s="84" t="n"/>
-      <c r="R5" s="84" t="n"/>
-      <c r="S5" s="84" t="n"/>
-      <c r="T5" s="84" t="n"/>
-      <c r="U5" s="84" t="n"/>
-      <c r="V5" s="84" t="n"/>
-      <c r="W5" s="84" t="n"/>
-      <c r="X5" s="84" t="n"/>
-      <c r="Y5" s="84" t="n"/>
-      <c r="Z5" s="84" t="n"/>
-      <c r="AA5" s="84" t="n"/>
-      <c r="AB5" s="84" t="n"/>
+      <c r="B5" s="86" t="n"/>
+      <c r="C5" s="86" t="n"/>
+      <c r="D5" s="86" t="n"/>
+      <c r="E5" s="86" t="n"/>
+      <c r="F5" s="86" t="n"/>
+      <c r="G5" s="86" t="n"/>
+      <c r="H5" s="86" t="n"/>
+      <c r="I5" s="86" t="n"/>
+      <c r="J5" s="86" t="n"/>
+      <c r="K5" s="86" t="n"/>
+      <c r="L5" s="86" t="n"/>
+      <c r="M5" s="86" t="n"/>
+      <c r="N5" s="86" t="n"/>
+      <c r="O5" s="86" t="n"/>
+      <c r="P5" s="86" t="n"/>
+      <c r="Q5" s="86" t="n"/>
+      <c r="R5" s="86" t="n"/>
+      <c r="S5" s="86" t="n"/>
+      <c r="T5" s="86" t="n"/>
+      <c r="U5" s="86" t="n"/>
+      <c r="V5" s="86" t="n"/>
+      <c r="W5" s="86" t="n"/>
+      <c r="X5" s="86" t="n"/>
+      <c r="Y5" s="86" t="n"/>
+      <c r="Z5" s="86" t="n"/>
+      <c r="AA5" s="86" t="n"/>
+      <c r="AB5" s="87" t="n"/>
       <c r="AC5" s="84" t="n"/>
       <c r="AD5" s="84" t="n"/>
       <c r="AE5" s="84" t="n"/>
@@ -3065,37 +3064,33 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="B36" s="84" t="inlineStr">
-        <is>
-          <t>Sheila</t>
-        </is>
-      </c>
-      <c r="C36" s="84" t="n"/>
-      <c r="D36" s="84" t="n"/>
-      <c r="E36" s="84" t="n"/>
-      <c r="F36" s="84" t="n"/>
-      <c r="G36" s="84" t="n"/>
-      <c r="H36" s="84" t="n"/>
-      <c r="I36" s="84" t="n"/>
-      <c r="J36" s="84" t="n"/>
-      <c r="K36" s="84" t="n"/>
-      <c r="L36" s="84" t="n"/>
-      <c r="M36" s="84" t="n"/>
-      <c r="N36" s="84" t="n"/>
-      <c r="O36" s="84" t="n"/>
-      <c r="P36" s="84" t="n"/>
-      <c r="Q36" s="84" t="n"/>
-      <c r="R36" s="84" t="n"/>
-      <c r="S36" s="84" t="n"/>
-      <c r="T36" s="84" t="n"/>
-      <c r="U36" s="84" t="n"/>
-      <c r="V36" s="84" t="n"/>
-      <c r="W36" s="84" t="n"/>
-      <c r="X36" s="84" t="n"/>
-      <c r="Y36" s="84" t="n"/>
-      <c r="Z36" s="84" t="n"/>
-      <c r="AA36" s="84" t="n"/>
-      <c r="AB36" s="84" t="n"/>
+      <c r="B36" s="86" t="n"/>
+      <c r="C36" s="86" t="n"/>
+      <c r="D36" s="86" t="n"/>
+      <c r="E36" s="86" t="n"/>
+      <c r="F36" s="86" t="n"/>
+      <c r="G36" s="86" t="n"/>
+      <c r="H36" s="86" t="n"/>
+      <c r="I36" s="86" t="n"/>
+      <c r="J36" s="86" t="n"/>
+      <c r="K36" s="86" t="n"/>
+      <c r="L36" s="86" t="n"/>
+      <c r="M36" s="86" t="n"/>
+      <c r="N36" s="86" t="n"/>
+      <c r="O36" s="86" t="n"/>
+      <c r="P36" s="86" t="n"/>
+      <c r="Q36" s="86" t="n"/>
+      <c r="R36" s="86" t="n"/>
+      <c r="S36" s="86" t="n"/>
+      <c r="T36" s="86" t="n"/>
+      <c r="U36" s="86" t="n"/>
+      <c r="V36" s="86" t="n"/>
+      <c r="W36" s="86" t="n"/>
+      <c r="X36" s="86" t="n"/>
+      <c r="Y36" s="86" t="n"/>
+      <c r="Z36" s="86" t="n"/>
+      <c r="AA36" s="86" t="n"/>
+      <c r="AB36" s="87" t="n"/>
       <c r="AC36" s="84" t="n"/>
       <c r="AD36" s="84" t="n"/>
       <c r="AE36" s="84" t="n"/>
@@ -3757,176 +3752,147 @@
     <row r="54" ht="60" customHeight="1" s="51">
       <c r="C54" s="93" t="inlineStr">
         <is>
-          <t>A1 – Prior belief
-Which variables do you predict will determine recommendability? (intuition, no analysis yet)</t>
+          <t>Which variables do you predict will determine recommendability? (intuition, no analysis yet)</t>
         </is>
       </c>
       <c r="D54" s="93" t="inlineStr">
         <is>
-          <t>A2 – Data-based exploration
-Which variables actually influence recommendability based on data? (with graph evidence)</t>
+          <t>Which variables actually influence recommendability based on data? (with graph evidence)</t>
         </is>
       </c>
       <c r="E54" s="93" t="inlineStr">
         <is>
-          <t>A3 – Meaningful difference
-Did you find a variable showing meaningful difference between groups? Explain with data.</t>
+          <t>Did you find a variable showing meaningful difference between groups? Explain with data.</t>
         </is>
       </c>
       <c r="F54" s="93" t="inlineStr">
         <is>
-          <t>A4 – First variable justification
-Which variable would you use first in a prediction model? Justify using data evidence.</t>
+          <t>Which variable would you use first in a prediction model? Justify using data evidence.</t>
         </is>
       </c>
       <c r="G54" s="93" t="inlineStr">
         <is>
-          <t>B1 – Tree 1 build + EMIT
-Build single-level tree with variable 1; record EMIT accuracy result</t>
+          <t>Build single-level tree with variable 1; record EMIT accuracy result</t>
         </is>
       </c>
       <c r="H54" s="93" t="inlineStr">
         <is>
-          <t>B2 – Tree 2 build + EMIT
-Build single-level tree with variable 2; record EMIT accuracy result</t>
+          <t>Build single-level tree with variable 2; record EMIT accuracy result</t>
         </is>
       </c>
       <c r="I54" s="93" t="inlineStr">
         <is>
-          <t>B3 – Tree 3 build + EMIT
-Build single-level tree with variable 3; record EMIT accuracy result</t>
+          <t>Build single-level tree with variable 3; record EMIT accuracy result</t>
         </is>
       </c>
       <c r="J54" s="93" t="inlineStr">
         <is>
-          <t>B4 – Best tree + criteria
-Which variable gave best result? What criteria used to judge?</t>
+          <t>Which variable gave best result? What criteria used to judge?</t>
         </is>
       </c>
       <c r="K54" s="93" t="inlineStr">
         <is>
-          <t>C1 – Threshold optimization
-Try different thresholds for best variable; save best result with EMIT</t>
+          <t>Try different thresholds for best variable; save best result with EMIT</t>
         </is>
       </c>
       <c r="L54" s="93" t="inlineStr">
         <is>
-          <t>C2 – Threshold effect
-How does changing the threshold value affect decision tree performance?</t>
+          <t>How does changing the threshold value affect decision tree performance?</t>
         </is>
       </c>
       <c r="M54" s="93" t="inlineStr">
         <is>
-          <t>C3 – Best threshold + reasoning
-Which threshold best separates the groups? How did you decide?</t>
+          <t>Which threshold best separates the groups? How did you decide?</t>
         </is>
       </c>
       <c r="N54" s="93" t="inlineStr">
         <is>
-          <t>D1 – Two-level tree build + EMIT
-Add second variable to create a two-level tree; save result with EMIT</t>
+          <t>Add second variable to create a two-level tree; save result with EMIT</t>
         </is>
       </c>
       <c r="O54" s="93" t="inlineStr">
         <is>
-          <t>D2 – Second level effect
-Did the second level improve classification? How and in what ways?</t>
+          <t>Did the second level improve classification? How and in what ways?</t>
         </is>
       </c>
       <c r="P54" s="93" t="inlineStr">
         <is>
-          <t>D3 – Best variable combination
-Which variable combination produced the best result?</t>
+          <t>Which variable combination produced the best result?</t>
         </is>
       </c>
       <c r="Q54" s="93" t="inlineStr">
         <is>
-          <t>D4 – Stopping criterion
-How did you decide you had reached your best decision tree?</t>
+          <t>How did you decide you had reached your best decision tree?</t>
         </is>
       </c>
       <c r="R54" s="93" t="inlineStr">
         <is>
-          <t>E – Sensitivity value
-Fill in Sensitivity (Duyarlılık) value from EMIT for best tree</t>
+          <t>Fill in Sensitivity (Duyarlılık) value from EMIT for best tree</t>
         </is>
       </c>
       <c r="S54" s="93" t="inlineStr">
         <is>
-          <t>E – MCR value
-Fill in Misclassification Rate (MCR) value from EMIT for best tree</t>
+          <t>Fill in Misclassification Rate (MCR) value from EMIT for best tree</t>
         </is>
       </c>
       <c r="T54" s="93" t="inlineStr">
         <is>
-          <t>E – True Positives
-Count of True Positives (TP) from confusion matrix</t>
+          <t>Count of True Positives (TP) from confusion matrix</t>
         </is>
       </c>
       <c r="U54" s="93" t="inlineStr">
         <is>
-          <t>E – False Positives
-Count of False Positives (FP) from confusion matrix</t>
+          <t>Count of False Positives (FP) from confusion matrix</t>
         </is>
       </c>
       <c r="V54" s="93" t="inlineStr">
         <is>
-          <t>E – True Negatives
-Count of True Negatives (TN) from confusion matrix</t>
+          <t>Count of True Negatives (TN) from confusion matrix</t>
         </is>
       </c>
       <c r="W54" s="93" t="inlineStr">
         <is>
-          <t>E – False Negatives
-Count of False Negatives (FN) from confusion matrix</t>
+          <t>Count of False Negatives (FN) from confusion matrix</t>
         </is>
       </c>
       <c r="X54" s="93" t="inlineStr">
         <is>
-          <t>E1 – Metric interpretation
-Which metric matters most for this model's purpose: sensitivity, MCR, or other? Why?</t>
+          <t>Which metric matters most for this model's purpose: sensitivity, MCR, or other? Why?</t>
         </is>
       </c>
       <c r="Y54" s="93" t="inlineStr">
         <is>
-          <t>E2 – Error type analysis
-Did model make more false positives or false negatives?</t>
+          <t>Did model make more false positives or false negatives?</t>
         </is>
       </c>
       <c r="Z54" s="93" t="inlineStr">
         <is>
-          <t>E3 – Good-enough criterion
-How would software / you decide when a tree is good enough?</t>
+          <t>How would software / you decide when a tree is good enough?</t>
         </is>
       </c>
       <c r="AA54" s="93" t="inlineStr">
         <is>
-          <t>E4 – Perfect classification
-Do you think decision trees can ever classify perfectly? Reasoned answer.</t>
+          <t>Do you think decision trees can ever classify perfectly? Reasoned answer.</t>
         </is>
       </c>
       <c r="AB54" s="93" t="inlineStr">
         <is>
-          <t>F1 – Test set application
-Apply best tree to test dataset; evaluate with EMIT; record result</t>
+          <t>Apply best tree to test dataset; evaluate with EMIT; record result</t>
         </is>
       </c>
       <c r="AC54" s="93" t="inlineStr">
         <is>
-          <t>F2 – Train vs test comparison
-Compare test vs. training performance and explain any difference</t>
+          <t>Compare test vs. training performance and explain any difference</t>
         </is>
       </c>
       <c r="AD54" s="93" t="inlineStr">
         <is>
-          <t>G1 – What the model learned
-What did the decision tree model 'learn' from the training data?</t>
+          <t>What did the decision tree model 'learn' from the training data?</t>
         </is>
       </c>
       <c r="AE54" s="93" t="inlineStr">
         <is>
-          <t>G2 – Personal reflection
-What did you personally learn while building decision trees?</t>
+          <t>What did you personally learn while building decision trees?</t>
         </is>
       </c>
     </row>
@@ -5334,75 +5300,60 @@
       <c r="B54" s="85" t="n"/>
       <c r="C54" s="90" t="inlineStr">
         <is>
-          <t>Target Label
-Diagram arrow pointing to food card name → 'label' (etiket)</t>
+          <t>Diagram arrow pointing to food card name → 'label' (etiket)</t>
         </is>
       </c>
       <c r="D54" s="90" t="inlineStr">
         <is>
-          <t>Data Object
-Diagram arrow pointing to 'Findikli Gofret' card → 'object' (nesne)</t>
+          <t>Diagram arrow pointing to 'Findikli Gofret' card → 'object' (nesne)</t>
         </is>
       </c>
       <c r="E54" s="90" t="inlineStr">
         <is>
-          <t>Feature Name
-Diagram arrow pointing to left column of card → 'feature / variable / characteristic'</t>
+          <t>Diagram arrow pointing to left column of card → 'feature / variable / characteristic'</t>
         </is>
       </c>
       <c r="F54" s="90" t="inlineStr">
         <is>
-          <t>Feature Value
-Diagram arrow pointing to a numeric cell → 'value of the feature / characteristic'</t>
+          <t>Diagram arrow pointing to a numeric cell → 'value of the feature / characteristic'</t>
         </is>
       </c>
       <c r="G54" s="90" t="inlineStr">
         <is>
-          <t>Data Instance
-Cloze: 'Individual foods are called ___' → object (nesne)</t>
+          <t>Cloze: 'Individual foods are called ___' → object (nesne)</t>
         </is>
       </c>
       <c r="H54" s="90" t="inlineStr">
         <is>
-          <t>Specific Object
-Cloze: 'Hazelnut wafer is a ___' → object (nesne)</t>
+          <t>Cloze: 'Hazelnut wafer is a ___' → object (nesne)</t>
         </is>
       </c>
       <c r="I54" s="90" t="inlineStr">
         <is>
-          <t>Feature Variable
-Cloze: left-column names are called '___ / characteristic / variable'</t>
+          <t>Cloze: left-column names are called '___ / characteristic / variable'</t>
         </is>
       </c>
       <c r="J54" s="90" t="inlineStr">
         <is>
-          <t>Feature Count
-Cloze: 'How many features? ___' → 7 (yedi / seven)</t>
+          <t>Cloze: 'How many features? ___' → 7 (yedi / seven)</t>
         </is>
       </c>
       <c r="K54" s="90" t="inlineStr">
         <is>
-          <t>Feature List
-Cloze: student writes all feature names: Energy, Fat, Saturated Fat, Carbohydrates, Sugar, Protein, Salt</t>
+          <t>Cloze: student writes all feature names: Energy, Fat, Saturated Fat, Carbohydrates, Sugar, Protein, Salt</t>
         </is>
       </c>
       <c r="L54" s="90" t="inlineStr">
         <is>
-          <t>Instance Name
-Cloze: 'For example ___ contains 31.9g fat' → Hazelnut Wafer (Findikli Gofret)</t>
+          <t>Cloze: 'For example ___ contains 31.9g fat' → Hazelnut Wafer (Findikli Gofret)</t>
         </is>
       </c>
       <c r="M54" s="90" t="inlineStr">
         <is>
-          <t>Assigned Label
-Cloze: 'Hazelnut wafer has been given ___ as label' → not recommended (tavsiye edilemez)</t>
-        </is>
-      </c>
-      <c r="N54" s="85" t="inlineStr">
-        <is>
-          <t>Overall AI-CFT level for WS1 as a whole</t>
-        </is>
-      </c>
+          <t>Cloze: 'Hazelnut wafer has been given ___ as label' → not recommended (tavsiye edilemez)</t>
+        </is>
+      </c>
+      <c r="N54" s="85" t="n"/>
       <c r="O54" s="85" t="inlineStr">
         <is>
           <t>Free notes: edge cases, illegible answers, etc.</t>
@@ -6632,42 +6583,42 @@
         </is>
       </c>
       <c r="B54" s="25" t="n"/>
-      <c r="C54" s="35" t="inlineStr">
+      <c r="C54" s="94" t="inlineStr">
         <is>
           <t>Applying the established decision rule to predict and assign a target class label to a specific data object (e.g., "tavsiye edilemez").</t>
         </is>
       </c>
-      <c r="D54" s="35" t="inlineStr">
+      <c r="D54" s="94" t="inlineStr">
         <is>
           <t>Justifying the classification outcome by mathematically comparing the object's feature value to the threshold (e.g., "23.0 &gt; 8.0").</t>
         </is>
       </c>
-      <c r="E54" s="35" t="inlineStr">
+      <c r="E54" s="94" t="inlineStr">
         <is>
           <t>Applying the established decision rule to predict and assign a target class label to a specific data object (e.g., "tavsiye edilebilir").</t>
         </is>
       </c>
-      <c r="F54" s="35" t="inlineStr">
+      <c r="F54" s="94" t="inlineStr">
         <is>
           <t>Justifying the classification outcome by mathematically comparing the object's feature value to the threshold (e.g., "8.0 &gt; 0.2").</t>
         </is>
       </c>
-      <c r="G54" s="35" t="inlineStr">
+      <c r="G54" s="94" t="inlineStr">
         <is>
           <t>Applying the established decision rule to predict and assign a target class label to a specific data object (e.g., "tavsiye edilemez").</t>
         </is>
       </c>
-      <c r="H54" s="35" t="inlineStr">
+      <c r="H54" s="94" t="inlineStr">
         <is>
           <t>Justifying the classification outcome by mathematically comparing the object's feature value to the threshold (e.g., "14.0 &gt; 8.0").</t>
         </is>
       </c>
-      <c r="I54" s="36" t="inlineStr">
+      <c r="I54" s="93" t="inlineStr">
         <is>
           <t>Establishing the mathematical boundary expression (≤) for a split node based on the data distribution of the feature (e.g., ≤ 71 kcal).</t>
         </is>
       </c>
-      <c r="J54" s="36" t="inlineStr">
+      <c r="J54" s="93" t="inlineStr">
         <is>
           <t>Establishing the corresponding inverse mathematical expression (&gt;) for a split node to partition the remaining instances in the dataset (e.g., &gt; 71 kcal).</t>
         </is>
@@ -6842,17 +6793,13 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="B5" s="84" t="inlineStr">
-        <is>
-          <t>Ozzy</t>
-        </is>
-      </c>
-      <c r="C5" s="84" t="n"/>
-      <c r="D5" s="84" t="n"/>
-      <c r="E5" s="84" t="n"/>
-      <c r="F5" s="84" t="n"/>
-      <c r="G5" s="84" t="n"/>
-      <c r="H5" s="84" t="n"/>
+      <c r="B5" s="86" t="n"/>
+      <c r="C5" s="86" t="n"/>
+      <c r="D5" s="86" t="n"/>
+      <c r="E5" s="86" t="n"/>
+      <c r="F5" s="86" t="n"/>
+      <c r="G5" s="86" t="n"/>
+      <c r="H5" s="87" t="n"/>
       <c r="I5" s="84" t="n"/>
       <c r="J5" s="84" t="n"/>
     </row>
@@ -7449,17 +7396,13 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="B36" s="84" t="inlineStr">
-        <is>
-          <t>Sheila</t>
-        </is>
-      </c>
-      <c r="C36" s="84" t="n"/>
-      <c r="D36" s="84" t="n"/>
-      <c r="E36" s="84" t="n"/>
-      <c r="F36" s="84" t="n"/>
-      <c r="G36" s="84" t="n"/>
-      <c r="H36" s="84" t="n"/>
+      <c r="B36" s="86" t="n"/>
+      <c r="C36" s="86" t="n"/>
+      <c r="D36" s="86" t="n"/>
+      <c r="E36" s="86" t="n"/>
+      <c r="F36" s="86" t="n"/>
+      <c r="G36" s="86" t="n"/>
+      <c r="H36" s="87" t="n"/>
       <c r="I36" s="84" t="n"/>
       <c r="J36" s="84" t="n"/>
     </row>
@@ -7773,38 +7716,32 @@
     <row r="54" ht="60" customHeight="1" s="51">
       <c r="C54" s="93" t="inlineStr">
         <is>
-          <t>Circle 4 misclassified
-Identify which 4 food cards are incorrectly classified at Leo's threshold</t>
+          <t>Identify which 4 food cards are incorrectly classified at Leo's threshold</t>
         </is>
       </c>
       <c r="D54" s="93" t="inlineStr">
         <is>
-          <t>Better threshold position
-Mark a better threshold line between two adjacent foods on the sorted card row</t>
+          <t>Mark a better threshold line between two adjacent foods on the sorted card row</t>
         </is>
       </c>
       <c r="E54" s="93" t="inlineStr">
         <is>
-          <t>Threshold justification
-Written explanation of why chosen threshold is better than Leo's</t>
+          <t>Written explanation of why chosen threshold is better than Leo's</t>
         </is>
       </c>
       <c r="F54" s="93" t="inlineStr">
         <is>
-          <t>Pia correct?
-Explanation of why Leo's exact pencil placement cannot be a valid threshold (equal values cannot be split)</t>
+          <t>Explanation of why Leo's exact pencil placement cannot be a valid threshold (equal values cannot be split)</t>
         </is>
       </c>
       <c r="G54" s="93" t="inlineStr">
         <is>
-          <t>Sorted cards annotation
-Sort and annotate energy cards with the best threshold line drawn</t>
+          <t>Sort and annotate energy cards with the best threshold line drawn</t>
         </is>
       </c>
       <c r="H54" s="93" t="inlineStr">
         <is>
-          <t>Best energy threshold value
-Fill in: 'Best threshold value for energy variable: ___' (numerical value)</t>
+          <t>Fill in: 'Best threshold value for energy variable: ___' (numerical value)</t>
         </is>
       </c>
     </row>
@@ -8247,20 +8184,16 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="B5" s="84" t="inlineStr">
-        <is>
-          <t>Ozzy</t>
-        </is>
-      </c>
-      <c r="C5" s="84" t="n"/>
-      <c r="D5" s="84" t="n"/>
-      <c r="E5" s="84" t="n"/>
-      <c r="F5" s="84" t="n"/>
-      <c r="G5" s="84" t="n"/>
-      <c r="H5" s="84" t="n"/>
-      <c r="I5" s="84" t="n"/>
-      <c r="J5" s="84" t="n"/>
-      <c r="K5" s="84" t="n"/>
+      <c r="B5" s="86" t="n"/>
+      <c r="C5" s="86" t="n"/>
+      <c r="D5" s="86" t="n"/>
+      <c r="E5" s="86" t="n"/>
+      <c r="F5" s="86" t="n"/>
+      <c r="G5" s="86" t="n"/>
+      <c r="H5" s="86" t="n"/>
+      <c r="I5" s="86" t="n"/>
+      <c r="J5" s="86" t="n"/>
+      <c r="K5" s="87" t="n"/>
       <c r="L5" s="84" t="n"/>
       <c r="M5" s="84" t="n"/>
       <c r="N5" s="84" t="n"/>
@@ -9514,20 +9447,16 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="B36" s="84" t="inlineStr">
-        <is>
-          <t>Sheila</t>
-        </is>
-      </c>
-      <c r="C36" s="84" t="n"/>
-      <c r="D36" s="84" t="n"/>
-      <c r="E36" s="84" t="n"/>
-      <c r="F36" s="84" t="n"/>
-      <c r="G36" s="84" t="n"/>
-      <c r="H36" s="84" t="n"/>
-      <c r="I36" s="84" t="n"/>
-      <c r="J36" s="84" t="n"/>
-      <c r="K36" s="84" t="n"/>
+      <c r="B36" s="86" t="n"/>
+      <c r="C36" s="86" t="n"/>
+      <c r="D36" s="86" t="n"/>
+      <c r="E36" s="86" t="n"/>
+      <c r="F36" s="86" t="n"/>
+      <c r="G36" s="86" t="n"/>
+      <c r="H36" s="86" t="n"/>
+      <c r="I36" s="86" t="n"/>
+      <c r="J36" s="86" t="n"/>
+      <c r="K36" s="87" t="n"/>
       <c r="L36" s="84" t="n"/>
       <c r="M36" s="84" t="n"/>
       <c r="N36" s="84" t="n"/>
@@ -10190,170 +10119,142 @@
     <row r="54" ht="60" customHeight="1" s="51">
       <c r="C54" s="93" t="inlineStr">
         <is>
-          <t>Block 1 – Variable name
-Name of first chosen variable for threshold exploration</t>
+          <t>Name of first chosen variable for threshold exploration</t>
         </is>
       </c>
       <c r="D54" s="93" t="inlineStr">
         <is>
-          <t>Block 1 – Threshold ≤
-Left threshold value (≤ side) for variable 1</t>
+          <t>Left threshold value (≤ side) for variable 1</t>
         </is>
       </c>
       <c r="E54" s="93" t="inlineStr">
         <is>
-          <t>Block 1 – Threshold &gt;
-Right threshold value (&gt; side) for variable 1</t>
+          <t>Right threshold value (&gt; side) for variable 1</t>
         </is>
       </c>
       <c r="F54" s="93" t="inlineStr">
         <is>
-          <t>Block 1 – Rec count (left)
-Count of recommended foods in left branch (variable 1)</t>
+          <t>Count of recommended foods in left branch (variable 1)</t>
         </is>
       </c>
       <c r="G54" s="93" t="inlineStr">
         <is>
-          <t>Block 1 – Not-rec count (left)
-Count of not-recommended foods in left branch (variable 1)</t>
+          <t>Count of not-recommended foods in left branch (variable 1)</t>
         </is>
       </c>
       <c r="H54" s="93" t="inlineStr">
         <is>
-          <t>Block 1 – Rec count (right)
-Count of recommended foods in right branch (variable 1)</t>
+          <t>Count of recommended foods in right branch (variable 1)</t>
         </is>
       </c>
       <c r="I54" s="93" t="inlineStr">
         <is>
-          <t>Block 1 – Not-rec count (right)
-Count of not-recommended foods in right branch (variable 1)</t>
+          <t>Count of not-recommended foods in right branch (variable 1)</t>
         </is>
       </c>
       <c r="J54" s="93" t="inlineStr">
         <is>
-          <t>Block 1 – Misclassification count
-Total misclassified foods for variable 1 threshold</t>
+          <t>Total misclassified foods for variable 1 threshold</t>
         </is>
       </c>
       <c r="K54" s="93" t="inlineStr">
         <is>
-          <t>Block 2 – Variable name
-Name of second chosen variable</t>
+          <t>Name of second chosen variable</t>
         </is>
       </c>
       <c r="L54" s="93" t="inlineStr">
         <is>
-          <t>Block 2 – Threshold ≤
-Left threshold value (≤ side) for variable 2</t>
+          <t>Left threshold value (≤ side) for variable 2</t>
         </is>
       </c>
       <c r="M54" s="93" t="inlineStr">
         <is>
-          <t>Block 2 – Threshold &gt;
-Right threshold value (&gt; side) for variable 2</t>
+          <t>Right threshold value (&gt; side) for variable 2</t>
         </is>
       </c>
       <c r="N54" s="93" t="inlineStr">
         <is>
-          <t>Block 2 – Rec count (left)
-Count of recommended foods in left branch (variable 2)</t>
+          <t>Count of recommended foods in left branch (variable 2)</t>
         </is>
       </c>
       <c r="O54" s="93" t="inlineStr">
         <is>
-          <t>Block 2 – Not-rec count (left)
-Count of not-recommended foods in left branch (variable 2)</t>
+          <t>Count of not-recommended foods in left branch (variable 2)</t>
         </is>
       </c>
       <c r="P54" s="93" t="inlineStr">
         <is>
-          <t>Block 2 – Rec count (right)
-Count of recommended foods in right branch (variable 2)</t>
+          <t>Count of recommended foods in right branch (variable 2)</t>
         </is>
       </c>
       <c r="Q54" s="93" t="inlineStr">
         <is>
-          <t>Block 2 – Not-rec count (right)
-Count of not-recommended foods in right branch (variable 2)</t>
+          <t>Count of not-recommended foods in right branch (variable 2)</t>
         </is>
       </c>
       <c r="R54" s="93" t="inlineStr">
         <is>
-          <t>Block 2 – Misclassification count
-Total misclassified foods for variable 2 threshold</t>
+          <t>Total misclassified foods for variable 2 threshold</t>
         </is>
       </c>
       <c r="S54" s="93" t="inlineStr">
         <is>
-          <t>Block 3 – Variable name
-Name of third chosen variable</t>
+          <t>Name of third chosen variable</t>
         </is>
       </c>
       <c r="T54" s="93" t="inlineStr">
         <is>
-          <t>Block 3 – Threshold ≤
-Left threshold value (≤ side) for variable 3</t>
+          <t>Left threshold value (≤ side) for variable 3</t>
         </is>
       </c>
       <c r="U54" s="93" t="inlineStr">
         <is>
-          <t>Block 3 – Threshold &gt;
-Right threshold value (&gt; side) for variable 3</t>
+          <t>Right threshold value (&gt; side) for variable 3</t>
         </is>
       </c>
       <c r="V54" s="93" t="inlineStr">
         <is>
-          <t>Block 3 – Rec count (left)
-Count of recommended foods in left branch (variable 3)</t>
+          <t>Count of recommended foods in left branch (variable 3)</t>
         </is>
       </c>
       <c r="W54" s="93" t="inlineStr">
         <is>
-          <t>Block 3 – Not-rec count (left)
-Count of not-recommended foods in left branch (variable 3)</t>
+          <t>Count of not-recommended foods in left branch (variable 3)</t>
         </is>
       </c>
       <c r="X54" s="93" t="inlineStr">
         <is>
-          <t>Block 3 – Rec count (right)
-Count of recommended foods in right branch (variable 3)</t>
+          <t>Count of recommended foods in right branch (variable 3)</t>
         </is>
       </c>
       <c r="Y54" s="93" t="inlineStr">
         <is>
-          <t>Block 3 – Not-rec count (right)
-Count of not-recommended foods in right branch (variable 3)</t>
+          <t>Count of not-recommended foods in right branch (variable 3)</t>
         </is>
       </c>
       <c r="Z54" s="93" t="inlineStr">
         <is>
-          <t>Block 3 – Rec total
-Total recommended count across all branches (variable 3)</t>
+          <t>Total recommended count across all branches (variable 3)</t>
         </is>
       </c>
       <c r="AA54" s="93" t="inlineStr">
         <is>
-          <t>Block 3 – Not-rec total
-Total not-recommended count across all branches (variable 3)</t>
+          <t>Total not-recommended count across all branches (variable 3)</t>
         </is>
       </c>
       <c r="AB54" s="93" t="inlineStr">
         <is>
-          <t>Block 3 – Misclassification count
-Total misclassified foods for variable 3 threshold</t>
+          <t>Total misclassified foods for variable 3 threshold</t>
         </is>
       </c>
       <c r="AC54" s="93" t="inlineStr">
         <is>
-          <t>Chosen variable
-Variable name selected as best for final threshold</t>
+          <t>Variable name selected as best for final threshold</t>
         </is>
       </c>
       <c r="AD54" s="93" t="inlineStr">
         <is>
-          <t>Selected threshold value
-'Which threshold do you choose for ___ variable?' — final numerical answer</t>
+          <t>'Which threshold do you choose for ___ variable?' — final numerical answer</t>
         </is>
       </c>
     </row>
@@ -10712,20 +10613,16 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="B5" s="84" t="inlineStr">
-        <is>
-          <t>Ozzy</t>
-        </is>
-      </c>
-      <c r="C5" s="84" t="n"/>
-      <c r="D5" s="84" t="n"/>
-      <c r="E5" s="84" t="n"/>
-      <c r="F5" s="84" t="n"/>
-      <c r="G5" s="84" t="n"/>
-      <c r="H5" s="84" t="n"/>
-      <c r="I5" s="84" t="n"/>
-      <c r="J5" s="84" t="n"/>
-      <c r="K5" s="84" t="n"/>
+      <c r="B5" s="86" t="n"/>
+      <c r="C5" s="86" t="n"/>
+      <c r="D5" s="86" t="n"/>
+      <c r="E5" s="86" t="n"/>
+      <c r="F5" s="86" t="n"/>
+      <c r="G5" s="86" t="n"/>
+      <c r="H5" s="86" t="n"/>
+      <c r="I5" s="86" t="n"/>
+      <c r="J5" s="86" t="n"/>
+      <c r="K5" s="87" t="n"/>
       <c r="L5" s="84" t="n"/>
       <c r="M5" s="84" t="n"/>
       <c r="N5" s="84" t="n"/>
@@ -11769,20 +11666,16 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="B36" s="84" t="inlineStr">
-        <is>
-          <t>Sheila</t>
-        </is>
-      </c>
-      <c r="C36" s="84" t="n"/>
-      <c r="D36" s="84" t="n"/>
-      <c r="E36" s="84" t="n"/>
-      <c r="F36" s="84" t="n"/>
-      <c r="G36" s="84" t="n"/>
-      <c r="H36" s="84" t="n"/>
-      <c r="I36" s="84" t="n"/>
-      <c r="J36" s="84" t="n"/>
-      <c r="K36" s="84" t="n"/>
+      <c r="B36" s="86" t="n"/>
+      <c r="C36" s="86" t="n"/>
+      <c r="D36" s="86" t="n"/>
+      <c r="E36" s="86" t="n"/>
+      <c r="F36" s="86" t="n"/>
+      <c r="G36" s="86" t="n"/>
+      <c r="H36" s="86" t="n"/>
+      <c r="I36" s="86" t="n"/>
+      <c r="J36" s="86" t="n"/>
+      <c r="K36" s="87" t="n"/>
       <c r="L36" s="84" t="n"/>
       <c r="M36" s="84" t="n"/>
       <c r="N36" s="84" t="n"/>
@@ -12333,128 +12226,107 @@
     <row r="54" ht="60" customHeight="1" s="51">
       <c r="C54" s="93" t="inlineStr">
         <is>
-          <t>Root variable
-Name of variable used at the root (first) split node</t>
+          <t>Name of variable used at the root (first) split node</t>
         </is>
       </c>
       <c r="D54" s="93" t="inlineStr">
         <is>
-          <t>Root threshold ≤
-Threshold value on the left (≤) branch of the root</t>
+          <t>Threshold value on the left (≤) branch of the root</t>
         </is>
       </c>
       <c r="E54" s="93" t="inlineStr">
         <is>
-          <t>Root threshold &gt;
-Threshold value on the right (&gt;) branch of the root</t>
+          <t>Threshold value on the right (&gt;) branch of the root</t>
         </is>
       </c>
       <c r="F54" s="93" t="inlineStr">
         <is>
-          <t>Left branch – next node
-Either a leaf classification or name of second-level variable (left side)</t>
+          <t>Either a leaf classification or name of second-level variable (left side)</t>
         </is>
       </c>
       <c r="G54" s="93" t="inlineStr">
         <is>
-          <t>Left leaf – rec count
-Count of recommended foods in left leaf [ rec ]</t>
+          <t>Count of recommended foods in left leaf [ rec ]</t>
         </is>
       </c>
       <c r="H54" s="93" t="inlineStr">
         <is>
-          <t>Left leaf – not-rec count
-Count of not-recommended foods in left leaf [ not-rec ]</t>
+          <t>Count of not-recommended foods in left leaf [ not-rec ]</t>
         </is>
       </c>
       <c r="I54" s="93" t="inlineStr">
         <is>
-          <t>Right branch – next node
-Either a leaf classification or name of second-level variable (right side)</t>
+          <t>Either a leaf classification or name of second-level variable (right side)</t>
         </is>
       </c>
       <c r="J54" s="93" t="inlineStr">
         <is>
-          <t>Right leaf – rec count
-Count of recommended foods in right leaf [ rec ]</t>
+          <t>Count of recommended foods in right leaf [ rec ]</t>
         </is>
       </c>
       <c r="K54" s="93" t="inlineStr">
         <is>
-          <t>Right leaf – not-rec count
-Count of not-recommended foods in right leaf [ not-rec ]</t>
+          <t>Count of not-recommended foods in right leaf [ not-rec ]</t>
         </is>
       </c>
       <c r="L54" s="93" t="inlineStr">
         <is>
-          <t>Sub-left-left threshold/label
-Threshold or class label for sub-branch: left → left</t>
+          <t>Threshold or class label for sub-branch: left → left</t>
         </is>
       </c>
       <c r="M54" s="93" t="inlineStr">
         <is>
-          <t>Sub-left-right threshold/label
-Threshold or class label for sub-branch: left → right</t>
+          <t>Threshold or class label for sub-branch: left → right</t>
         </is>
       </c>
       <c r="N54" s="93" t="inlineStr">
         <is>
-          <t>Sub-right-left threshold/label
-Threshold or class label for sub-branch: right → left</t>
+          <t>Threshold or class label for sub-branch: right → left</t>
         </is>
       </c>
       <c r="O54" s="93" t="inlineStr">
         <is>
-          <t>Sub-right-right threshold/label
-Threshold or class label for sub-branch: right → right</t>
+          <t>Threshold or class label for sub-branch: right → right</t>
         </is>
       </c>
       <c r="P54" s="93" t="inlineStr">
         <is>
-          <t>Leaf LL – rec count
-Recommended count at leaf: left-left</t>
+          <t>Recommended count at leaf: left-left</t>
         </is>
       </c>
       <c r="Q54" s="93" t="inlineStr">
         <is>
-          <t>Leaf LL – not-rec count
-Not-recommended count at leaf: left-left</t>
+          <t>Not-recommended count at leaf: left-left</t>
         </is>
       </c>
       <c r="R54" s="93" t="inlineStr">
         <is>
-          <t>Leaf LR – rec count
-Recommended count at leaf: left-right</t>
+          <t>Recommended count at leaf: left-right</t>
         </is>
       </c>
       <c r="S54" s="93" t="inlineStr">
         <is>
-          <t>Leaf LR – not-rec count
-Not-recommended count at leaf: left-right</t>
+          <t>Not-recommended count at leaf: left-right</t>
         </is>
       </c>
       <c r="T54" s="93" t="inlineStr">
         <is>
-          <t>Leaf RL – rec count
-Recommended count at leaf: right-left</t>
+          <t>Recommended count at leaf: right-left</t>
         </is>
       </c>
       <c r="U54" s="93" t="inlineStr">
         <is>
-          <t>Leaf RL – not-rec count
-Not-recommended count at leaf: right-left</t>
+          <t>Not-recommended count at leaf: right-left</t>
         </is>
       </c>
       <c r="V54" s="93" t="inlineStr">
         <is>
-          <t>Leaf RR – rec count
-Recommended count at leaf: right-right</t>
+          <t>Recommended count at leaf: right-right</t>
         </is>
       </c>
       <c r="W54" s="93" t="inlineStr">
         <is>
-          <t>Leaf RR – not-rec count
-Not-recommended count at leaf: right-right</t>
+          <t>Not-recommended count at leaf: right-right</t>
         </is>
       </c>
     </row>
@@ -12681,20 +12553,16 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="B5" s="84" t="inlineStr">
-        <is>
-          <t>Ozzy</t>
-        </is>
-      </c>
-      <c r="C5" s="84" t="n"/>
-      <c r="D5" s="84" t="n"/>
-      <c r="E5" s="84" t="n"/>
-      <c r="F5" s="84" t="n"/>
-      <c r="G5" s="84" t="n"/>
-      <c r="H5" s="84" t="n"/>
-      <c r="I5" s="84" t="n"/>
-      <c r="J5" s="84" t="n"/>
-      <c r="K5" s="84" t="n"/>
+      <c r="B5" s="86" t="n"/>
+      <c r="C5" s="86" t="n"/>
+      <c r="D5" s="86" t="n"/>
+      <c r="E5" s="86" t="n"/>
+      <c r="F5" s="86" t="n"/>
+      <c r="G5" s="86" t="n"/>
+      <c r="H5" s="86" t="n"/>
+      <c r="I5" s="86" t="n"/>
+      <c r="J5" s="86" t="n"/>
+      <c r="K5" s="87" t="n"/>
       <c r="L5" s="84" t="n"/>
       <c r="M5" s="84" t="n"/>
       <c r="N5" s="84" t="n"/>
@@ -13408,20 +13276,16 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="B36" s="84" t="inlineStr">
-        <is>
-          <t>Sheila</t>
-        </is>
-      </c>
-      <c r="C36" s="84" t="n"/>
-      <c r="D36" s="84" t="n"/>
-      <c r="E36" s="84" t="n"/>
-      <c r="F36" s="84" t="n"/>
-      <c r="G36" s="84" t="n"/>
-      <c r="H36" s="84" t="n"/>
-      <c r="I36" s="84" t="n"/>
-      <c r="J36" s="84" t="n"/>
-      <c r="K36" s="84" t="n"/>
+      <c r="B36" s="86" t="n"/>
+      <c r="C36" s="86" t="n"/>
+      <c r="D36" s="86" t="n"/>
+      <c r="E36" s="86" t="n"/>
+      <c r="F36" s="86" t="n"/>
+      <c r="G36" s="86" t="n"/>
+      <c r="H36" s="86" t="n"/>
+      <c r="I36" s="86" t="n"/>
+      <c r="J36" s="86" t="n"/>
+      <c r="K36" s="87" t="n"/>
       <c r="L36" s="84" t="n"/>
       <c r="M36" s="84" t="n"/>
       <c r="N36" s="84" t="n"/>
@@ -13796,62 +13660,52 @@
     <row r="54" ht="60" customHeight="1" s="51">
       <c r="C54" s="93" t="inlineStr">
         <is>
-          <t>Path A match
-Match Rule A to correct path (letter: A, B, or C)</t>
+          <t>Match Rule A to correct path (letter: A, B, or C)</t>
         </is>
       </c>
       <c r="D54" s="93" t="inlineStr">
         <is>
-          <t>Path B match
-Match Rule B to correct path (letter: A, B, or C)</t>
+          <t>Match Rule B to correct path (letter: A, B, or C)</t>
         </is>
       </c>
       <c r="E54" s="93" t="inlineStr">
         <is>
-          <t>Path C match
-Match Rule C to correct path (letter: A, B, or C)</t>
+          <t>Match Rule C to correct path (letter: A, B, or C)</t>
         </is>
       </c>
       <c r="F54" s="93" t="inlineStr">
         <is>
-          <t>Number of paths
-'My tree contains ___ paths' — total number of decision paths</t>
+          <t>'My tree contains ___ paths' — total number of decision paths</t>
         </is>
       </c>
       <c r="G54" s="93" t="inlineStr">
         <is>
-          <t>Rule 1
-Written if-then decision rule for path 1 of own tree</t>
+          <t>Written if-then decision rule for path 1 of own tree</t>
         </is>
       </c>
       <c r="H54" s="93" t="inlineStr">
         <is>
-          <t>Rule 2
-Written if-then decision rule for path 2 of own tree</t>
+          <t>Written if-then decision rule for path 2 of own tree</t>
         </is>
       </c>
       <c r="I54" s="93" t="inlineStr">
         <is>
-          <t>Rule 3
-Written if-then decision rule for path 3 of own tree</t>
+          <t>Written if-then decision rule for path 3 of own tree</t>
         </is>
       </c>
       <c r="J54" s="93" t="inlineStr">
         <is>
-          <t>Rule 4
-Written if-then decision rule for path 4 of own tree (if applicable)</t>
+          <t>Written if-then decision rule for path 4 of own tree (if applicable)</t>
         </is>
       </c>
       <c r="K54" s="93" t="inlineStr">
         <is>
-          <t>Rule 5
-Written if-then decision rule for path 5 of own tree (if applicable)</t>
+          <t>Written if-then decision rule for path 5 of own tree (if applicable)</t>
         </is>
       </c>
       <c r="L54" s="93" t="inlineStr">
         <is>
-          <t>Rule 6
-Written if-then decision rule for path 6 of own tree (if applicable)</t>
+          <t>Written if-then decision rule for path 6 of own tree (if applicable)</t>
         </is>
       </c>
     </row>
@@ -14054,16 +13908,12 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="B5" s="84" t="inlineStr">
-        <is>
-          <t>Ozzy</t>
-        </is>
-      </c>
-      <c r="C5" s="84" t="n"/>
-      <c r="D5" s="84" t="n"/>
-      <c r="E5" s="84" t="n"/>
-      <c r="F5" s="84" t="n"/>
-      <c r="G5" s="84" t="n"/>
+      <c r="B5" s="86" t="n"/>
+      <c r="C5" s="86" t="n"/>
+      <c r="D5" s="86" t="n"/>
+      <c r="E5" s="86" t="n"/>
+      <c r="F5" s="86" t="n"/>
+      <c r="G5" s="87" t="n"/>
       <c r="H5" s="84" t="n"/>
       <c r="I5" s="84" t="n"/>
       <c r="J5" s="84" t="n"/>
@@ -14721,16 +14571,12 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="B36" s="84" t="inlineStr">
-        <is>
-          <t>Sheila</t>
-        </is>
-      </c>
-      <c r="C36" s="84" t="n"/>
-      <c r="D36" s="84" t="n"/>
-      <c r="E36" s="84" t="n"/>
-      <c r="F36" s="84" t="n"/>
-      <c r="G36" s="84" t="n"/>
+      <c r="B36" s="86" t="n"/>
+      <c r="C36" s="86" t="n"/>
+      <c r="D36" s="86" t="n"/>
+      <c r="E36" s="86" t="n"/>
+      <c r="F36" s="86" t="n"/>
+      <c r="G36" s="87" t="n"/>
       <c r="H36" s="84" t="n"/>
       <c r="I36" s="84" t="n"/>
       <c r="J36" s="84" t="n"/>
@@ -15077,50 +14923,42 @@
     <row r="54" ht="60" customHeight="1" s="51">
       <c r="C54" s="93" t="inlineStr">
         <is>
-          <t>Misclassification @ 28
-Number of misclassified foods if threshold = 28 kcal</t>
+          <t>Number of misclassified foods if threshold = 28 kcal</t>
         </is>
       </c>
       <c r="D54" s="93" t="inlineStr">
         <is>
-          <t>Misclassification @ 69
-Number of misclassified foods if threshold = 69 kcal</t>
+          <t>Number of misclassified foods if threshold = 69 kcal</t>
         </is>
       </c>
       <c r="E54" s="93" t="inlineStr">
         <is>
-          <t>Misclassification @ 219
-Number of misclassified foods if threshold = 219 kcal</t>
+          <t>Number of misclassified foods if threshold = 219 kcal</t>
         </is>
       </c>
       <c r="F54" s="93" t="inlineStr">
         <is>
-          <t>Misclassification @ 346
-Number of misclassified foods if threshold = 346 kcal</t>
+          <t>Number of misclassified foods if threshold = 346 kcal</t>
         </is>
       </c>
       <c r="G54" s="93" t="inlineStr">
         <is>
-          <t>Misclassification @ 359
-Number of misclassified foods if threshold = 359 kcal</t>
+          <t>Number of misclassified foods if threshold = 359 kcal</t>
         </is>
       </c>
       <c r="H54" s="93" t="inlineStr">
         <is>
-          <t>Misclassification @ 408
-Number of misclassified foods if threshold = 408 kcal</t>
+          <t>Number of misclassified foods if threshold = 408 kcal</t>
         </is>
       </c>
       <c r="I54" s="93" t="inlineStr">
         <is>
-          <t>Misclassification @ 489
-Number of misclassified foods if threshold = 489 kcal</t>
+          <t>Number of misclassified foods if threshold = 489 kcal</t>
         </is>
       </c>
       <c r="J54" s="93" t="inlineStr">
         <is>
-          <t>Optimal threshold value
-'The optimal threshold value is: ___' — threshold with fewest misclassifications</t>
+          <t>'The optimal threshold value is: ___' — threshold with fewest misclassifications</t>
         </is>
       </c>
     </row>
@@ -15479,20 +15317,16 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="B5" s="84" t="inlineStr">
-        <is>
-          <t>Ozzy</t>
-        </is>
-      </c>
-      <c r="C5" s="84" t="n"/>
-      <c r="D5" s="84" t="n"/>
-      <c r="E5" s="84" t="n"/>
-      <c r="F5" s="84" t="n"/>
-      <c r="G5" s="84" t="n"/>
-      <c r="H5" s="84" t="n"/>
-      <c r="I5" s="84" t="n"/>
-      <c r="J5" s="84" t="n"/>
-      <c r="K5" s="84" t="n"/>
+      <c r="B5" s="86" t="n"/>
+      <c r="C5" s="86" t="n"/>
+      <c r="D5" s="86" t="n"/>
+      <c r="E5" s="86" t="n"/>
+      <c r="F5" s="86" t="n"/>
+      <c r="G5" s="86" t="n"/>
+      <c r="H5" s="86" t="n"/>
+      <c r="I5" s="86" t="n"/>
+      <c r="J5" s="86" t="n"/>
+      <c r="K5" s="87" t="n"/>
       <c r="L5" s="84" t="n"/>
       <c r="M5" s="84" t="n"/>
       <c r="N5" s="84" t="n"/>
@@ -16536,20 +16370,16 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="B36" s="84" t="inlineStr">
-        <is>
-          <t>Sheila</t>
-        </is>
-      </c>
-      <c r="C36" s="84" t="n"/>
-      <c r="D36" s="84" t="n"/>
-      <c r="E36" s="84" t="n"/>
-      <c r="F36" s="84" t="n"/>
-      <c r="G36" s="84" t="n"/>
-      <c r="H36" s="84" t="n"/>
-      <c r="I36" s="84" t="n"/>
-      <c r="J36" s="84" t="n"/>
-      <c r="K36" s="84" t="n"/>
+      <c r="B36" s="86" t="n"/>
+      <c r="C36" s="86" t="n"/>
+      <c r="D36" s="86" t="n"/>
+      <c r="E36" s="86" t="n"/>
+      <c r="F36" s="86" t="n"/>
+      <c r="G36" s="86" t="n"/>
+      <c r="H36" s="86" t="n"/>
+      <c r="I36" s="86" t="n"/>
+      <c r="J36" s="86" t="n"/>
+      <c r="K36" s="87" t="n"/>
       <c r="L36" s="84" t="n"/>
       <c r="M36" s="84" t="n"/>
       <c r="N36" s="84" t="n"/>
@@ -17100,128 +16930,107 @@
     <row r="54" ht="60" customHeight="1" s="51">
       <c r="C54" s="93" t="inlineStr">
         <is>
-          <t>Q4 – Can explain DT
-Yes/No: Can student explain how a decision tree works?</t>
+          <t>Yes/No: Can student explain how a decision tree works?</t>
         </is>
       </c>
       <c r="D54" s="93" t="inlineStr">
         <is>
-          <t>Q8a – Classify strawberry
-Apply the given decision tree to classify the strawberry card: 'recommended' or 'not recommended'</t>
+          <t>Apply the given decision tree to classify the strawberry card: 'recommended' or 'not recommended'</t>
         </is>
       </c>
       <c r="E54" s="93" t="inlineStr">
         <is>
-          <t>Q8b – Decision rule sentence
-Complete: 'Strawberry is classified as ___ because ___' — formulate the decision rule</t>
+          <t>Complete: 'Strawberry is classified as ___ because ___' — formulate the decision rule</t>
         </is>
       </c>
       <c r="F54" s="93" t="inlineStr">
         <is>
-          <t>Q9 – What is data?
-Open-ended (6 lines): explain what data is and why we need it</t>
+          <t>Open-ended (6 lines): explain what data is and why we need it</t>
         </is>
       </c>
       <c r="G54" s="93" t="inlineStr">
         <is>
-          <t>Q10a – DT statement 1
-True/False: DT statement a — what can a decision tree do?</t>
+          <t>True/False: DT statement a — what can a decision tree do?</t>
         </is>
       </c>
       <c r="H54" s="93" t="inlineStr">
         <is>
-          <t>Q10b – DT statement 2
-True/False: DT statement b</t>
+          <t>True/False: DT statement b</t>
         </is>
       </c>
       <c r="I54" s="93" t="inlineStr">
         <is>
-          <t>Q10c – DT statement 3
-True/False: DT statement c</t>
+          <t>True/False: DT statement c</t>
         </is>
       </c>
       <c r="J54" s="93" t="inlineStr">
         <is>
-          <t>Q10d – DT statement 4
-True/False: DT statement d</t>
+          <t>True/False: DT statement d</t>
         </is>
       </c>
       <c r="K54" s="93" t="inlineStr">
         <is>
-          <t>Q10e – DT statement 5
-True/False: DT statement e</t>
+          <t>True/False: DT statement e</t>
         </is>
       </c>
       <c r="L54" s="93" t="inlineStr">
         <is>
-          <t>Q10f – DT statement 6
-True/False: DT statement f</t>
+          <t>True/False: DT statement f</t>
         </is>
       </c>
       <c r="M54" s="93" t="inlineStr">
         <is>
-          <t>Q10g – DT statement 7
-True/False: DT statement g</t>
+          <t>True/False: DT statement g</t>
         </is>
       </c>
       <c r="N54" s="93" t="inlineStr">
         <is>
-          <t>Q10h – DT statement 8
-True/False: DT statement h</t>
+          <t>True/False: DT statement h</t>
         </is>
       </c>
       <c r="O54" s="93" t="inlineStr">
         <is>
-          <t>Q11a – Step order 1
-Rank step 1 in correct order for building a decision rule (1–4)</t>
+          <t>Rank step 1 in correct order for building a decision rule (1–4)</t>
         </is>
       </c>
       <c r="P54" s="93" t="inlineStr">
         <is>
-          <t>Q11b – Step order 2
-Rank step 2 in correct order (1–4)</t>
+          <t>Rank step 2 in correct order (1–4)</t>
         </is>
       </c>
       <c r="Q54" s="93" t="inlineStr">
         <is>
-          <t>Q11c – Step order 3
-Rank step 3 in correct order (1–4)</t>
+          <t>Rank step 3 in correct order (1–4)</t>
         </is>
       </c>
       <c r="R54" s="93" t="inlineStr">
         <is>
-          <t>Q11d – Step order 4
-Rank step 4 in correct order (1–4)</t>
+          <t>Rank step 4 in correct order (1–4)</t>
         </is>
       </c>
       <c r="S54" s="93" t="inlineStr">
         <is>
-          <t>Q12a – AI statement 1
-True/False: Why is a DT considered AI? — statement a</t>
+          <t>True/False: Why is a DT considered AI? — statement a</t>
         </is>
       </c>
       <c r="T54" s="93" t="inlineStr">
         <is>
-          <t>Q12b – AI statement 2
-True/False: AI statement b</t>
+          <t>True/False: AI statement b</t>
         </is>
       </c>
       <c r="U54" s="93" t="inlineStr">
         <is>
-          <t>Q12c – AI statement 3
-True/False: AI statement c</t>
+          <t>True/False: AI statement c</t>
         </is>
       </c>
       <c r="V54" s="93" t="inlineStr">
         <is>
-          <t>Q12d – AI statement 4
-True/False: AI statement d</t>
+          <t>True/False: AI statement d</t>
         </is>
       </c>
       <c r="W54" s="93" t="inlineStr">
         <is>
-          <t>Q12e – AI statement 5
-True/False: AI statement e</t>
+          <t>True/False: AI statement e</t>
         </is>
       </c>
     </row>
